--- a/research/opportunities.xlsx
+++ b/research/opportunities.xlsx
@@ -13,12 +13,18 @@
     <sheet name="Screening Scores" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Verification" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Honorable Mentions" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Projections" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Projection Basis" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Bear Case" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Top 25'!$A$1:$O$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Opportunities'!$A$1:$M$78</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Screening Scores'!$A$1:$L$78</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Verification'!$A$3:$G$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Projections'!$A$3:$Y$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Projection Basis'!$A$1:$M$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Bear Case'!$A$3:$F$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -26,8 +32,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="14">
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="$#,##0;($#,##0);-"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="0.0%;[Red]-0.0%"/>
+  </numFmts>
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -104,6 +114,24 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="009C0006"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="009C6500"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="009C0006"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -215,7 +243,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -278,6 +306,60 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -645,7 +727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1032,8 +1114,44 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="26" customHeight="1">
-      <c r="A38" s="20" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>Projections</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>Bottom-up 5-year revenue build per opportunity - blue cells are editable inputs</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="19" t="inlineStr">
+        <is>
+          <t>Projection Basis</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>Where every projection number came from, and how much the analyst trusted it</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="19" t="inlineStr">
+        <is>
+          <t>Bear Case</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>The most optimistic assumption in each model, and year 5 after a haircut</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="26" customHeight="1">
+      <c r="A41" s="20" t="inlineStr">
         <is>
           <t>Source: research/dataset.json in this repository; see research/METHODOLOGY.md for the full pipeline and coverage limitations. Composite scores on every sheet are live formulas driven by the yellow weight cells above, so changing a weight re-scores all 77 opportunities at once.
 Data note: one screening agent recorded a composite of 4.92 for "rec-e-invoicing-mandate-plumbing-for-us-mid-market-erps" where the stated weights give 4.64. The workbook computes every composite from the weights, so it shows the corrected 4.64. That opportunity was not in the top 25, so the selection is unaffected. All 76 other composites reproduce exactly.
@@ -1041,28 +1159,31 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="26" customHeight="1"/>
-    <row r="40" ht="26" customHeight="1"/>
-    <row r="41" ht="26" customHeight="1"/>
     <row r="42" ht="26" customHeight="1"/>
+    <row r="43" ht="26" customHeight="1"/>
+    <row r="44" ht="26" customHeight="1"/>
+    <row r="45" ht="26" customHeight="1"/>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="D19:F19"/>
+  <mergeCells count="20">
     <mergeCell ref="C23:F23"/>
-    <mergeCell ref="B32:F32"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="B22:F22"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="A41:F45"/>
+    <mergeCell ref="B39:F39"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="B38:F38"/>
     <mergeCell ref="B34:F34"/>
-    <mergeCell ref="B33:F33"/>
     <mergeCell ref="C26:F26"/>
     <mergeCell ref="C27:F27"/>
-    <mergeCell ref="A38:F42"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="B22:F22"/>
+    <mergeCell ref="B37:F37"/>
     <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="B33:F33"/>
     <mergeCell ref="B36:F36"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="B32:F32"/>
     <mergeCell ref="B35:F35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13508,4 +13629,5038 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Y33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="15" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
+    <col width="18" customWidth="1" min="20" max="20"/>
+    <col width="11" customWidth="1" min="21" max="21"/>
+    <col width="11" customWidth="1" min="22" max="22"/>
+    <col width="15" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="24" max="24"/>
+    <col width="34" customWidth="1" min="25" max="25"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="56" customHeight="1">
+      <c r="A1" s="26" t="inlineStr">
+        <is>
+          <t>BOTTOM-UP ESTIMATES, NOT FORECASTS. Built with no web access - the search budget was exhausted before this stage - so every figure comes from the opportunity record (quoted) or from analyst judgement (labelled). See the Projection Basis sheet for where each number came from and how much the analyst trusted it. Blue cells are inputs: change one and the whole build recomputes. Confidence tops out at 5/10 across all 25 - treat these as arguable starting points, not answers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>Opportunity</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Buyers in universe</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>ACV ($)</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>Gross margin</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>Revenue quality</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>Cust Y1</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>Cust Y2</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>Cust Y3</t>
+        </is>
+      </c>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>Cust Y4</t>
+        </is>
+      </c>
+      <c r="K3" s="6" t="inlineStr">
+        <is>
+          <t>Cust Y5</t>
+        </is>
+      </c>
+      <c r="L3" s="6" t="inlineStr">
+        <is>
+          <t>Revenue Y1</t>
+        </is>
+      </c>
+      <c r="M3" s="6" t="inlineStr">
+        <is>
+          <t>Revenue Y2</t>
+        </is>
+      </c>
+      <c r="N3" s="6" t="inlineStr">
+        <is>
+          <t>Revenue Y3</t>
+        </is>
+      </c>
+      <c r="O3" s="6" t="inlineStr">
+        <is>
+          <t>Revenue Y4</t>
+        </is>
+      </c>
+      <c r="P3" s="6" t="inlineStr">
+        <is>
+          <t>Revenue Y5</t>
+        </is>
+      </c>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>Y5 gross profit</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>Y5 penetration</t>
+        </is>
+      </c>
+      <c r="S3" s="6" t="inlineStr">
+        <is>
+          <t>Capital to 1st revenue</t>
+        </is>
+      </c>
+      <c r="T3" s="6" t="inlineStr">
+        <is>
+          <t>Months to 1st revenue</t>
+        </is>
+      </c>
+      <c r="U3" s="6" t="inlineStr">
+        <is>
+          <t>Team at Y1</t>
+        </is>
+      </c>
+      <c r="V3" s="6" t="inlineStr">
+        <is>
+          <t>Confidence</t>
+        </is>
+      </c>
+      <c r="W3" s="6" t="inlineStr">
+        <is>
+          <t>Bear-case Y5</t>
+        </is>
+      </c>
+      <c r="X3" s="6" t="inlineStr">
+        <is>
+          <t>Bear vs base</t>
+        </is>
+      </c>
+      <c r="Y3" s="6" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="21" t="inlineStr">
+        <is>
+          <t>Ride-through models and curtailment proof for NERC-registered data centers</t>
+        </is>
+      </c>
+      <c r="C4" s="28" t="n">
+        <v>900</v>
+      </c>
+      <c r="D4" s="29" t="n">
+        <v>275000</v>
+      </c>
+      <c r="E4" s="30" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>repeating-project</t>
+        </is>
+      </c>
+      <c r="G4" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="H4" s="28" t="n">
+        <v>10</v>
+      </c>
+      <c r="I4" s="28" t="n">
+        <v>20</v>
+      </c>
+      <c r="J4" s="28" t="n">
+        <v>32</v>
+      </c>
+      <c r="K4" s="28" t="n">
+        <v>45</v>
+      </c>
+      <c r="L4" s="31">
+        <f>G4*$D4</f>
+        <v/>
+      </c>
+      <c r="M4" s="31">
+        <f>H4*$D4</f>
+        <v/>
+      </c>
+      <c r="N4" s="31">
+        <f>I4*$D4</f>
+        <v/>
+      </c>
+      <c r="O4" s="31">
+        <f>J4*$D4</f>
+        <v/>
+      </c>
+      <c r="P4" s="31">
+        <f>K4*$D4</f>
+        <v/>
+      </c>
+      <c r="Q4" s="32">
+        <f>P4*$E4</f>
+        <v/>
+      </c>
+      <c r="R4" s="33">
+        <f>IF($C4=0,"",K4/$C4)</f>
+        <v/>
+      </c>
+      <c r="S4" s="29" t="n">
+        <v>250000</v>
+      </c>
+      <c r="T4" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="U4" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="V4" s="34" t="n">
+        <v>5</v>
+      </c>
+      <c r="W4" s="31">
+        <f>IFERROR(INDEX('Bear Case'!$F:$F,MATCH($Y4,'Bear Case'!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="X4" s="35">
+        <f>IFERROR(W4/P4-1,"")</f>
+        <v/>
+      </c>
+      <c r="Y4" s="10" t="inlineStr">
+        <is>
+          <t>datacenter-as-grid-entity-compliance</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t>Entry Type 13 and instrument-aware duty recovery for the post-de-minimis long tail</t>
+        </is>
+      </c>
+      <c r="C5" s="28" t="n">
+        <v>150000</v>
+      </c>
+      <c r="D5" s="29" t="n">
+        <v>8000</v>
+      </c>
+      <c r="E5" s="30" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>recurring</t>
+        </is>
+      </c>
+      <c r="G5" s="28" t="n">
+        <v>35</v>
+      </c>
+      <c r="H5" s="28" t="n">
+        <v>250</v>
+      </c>
+      <c r="I5" s="28" t="n">
+        <v>750</v>
+      </c>
+      <c r="J5" s="28" t="n">
+        <v>1650</v>
+      </c>
+      <c r="K5" s="28" t="n">
+        <v>3000</v>
+      </c>
+      <c r="L5" s="36">
+        <f>G5*$D5</f>
+        <v/>
+      </c>
+      <c r="M5" s="36">
+        <f>H5*$D5</f>
+        <v/>
+      </c>
+      <c r="N5" s="36">
+        <f>I5*$D5</f>
+        <v/>
+      </c>
+      <c r="O5" s="36">
+        <f>J5*$D5</f>
+        <v/>
+      </c>
+      <c r="P5" s="36">
+        <f>K5*$D5</f>
+        <v/>
+      </c>
+      <c r="Q5" s="37">
+        <f>P5*$E5</f>
+        <v/>
+      </c>
+      <c r="R5" s="38">
+        <f>IF($C5=0,"",K5/$C5)</f>
+        <v/>
+      </c>
+      <c r="S5" s="29" t="n">
+        <v>550000</v>
+      </c>
+      <c r="T5" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="U5" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="V5" s="39" t="n">
+        <v>4</v>
+      </c>
+      <c r="W5" s="36">
+        <f>IFERROR(INDEX('Bear Case'!$F:$F,MATCH($Y5,'Bear Case'!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="X5" s="40">
+        <f>IFERROR(W5/P5-1,"")</f>
+        <v/>
+      </c>
+      <c r="Y5" s="12" t="inlineStr">
+        <is>
+          <t>long-tail-customs-entry-and-duty-recovery</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>NQA-1 qualification and commercial grade dedication as a service</t>
+        </is>
+      </c>
+      <c r="C6" s="28" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D6" s="29" t="n">
+        <v>95000</v>
+      </c>
+      <c r="E6" s="30" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>repeating-project</t>
+        </is>
+      </c>
+      <c r="G6" s="28" t="n">
+        <v>5</v>
+      </c>
+      <c r="H6" s="28" t="n">
+        <v>14</v>
+      </c>
+      <c r="I6" s="28" t="n">
+        <v>28</v>
+      </c>
+      <c r="J6" s="28" t="n">
+        <v>45</v>
+      </c>
+      <c r="K6" s="28" t="n">
+        <v>65</v>
+      </c>
+      <c r="L6" s="31">
+        <f>G6*$D6</f>
+        <v/>
+      </c>
+      <c r="M6" s="31">
+        <f>H6*$D6</f>
+        <v/>
+      </c>
+      <c r="N6" s="31">
+        <f>I6*$D6</f>
+        <v/>
+      </c>
+      <c r="O6" s="31">
+        <f>J6*$D6</f>
+        <v/>
+      </c>
+      <c r="P6" s="31">
+        <f>K6*$D6</f>
+        <v/>
+      </c>
+      <c r="Q6" s="32">
+        <f>P6*$E6</f>
+        <v/>
+      </c>
+      <c r="R6" s="33">
+        <f>IF($C6=0,"",K6/$C6)</f>
+        <v/>
+      </c>
+      <c r="S6" s="29" t="n">
+        <v>150000</v>
+      </c>
+      <c r="T6" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="V6" s="34" t="n">
+        <v>5</v>
+      </c>
+      <c r="W6" s="31">
+        <f>IFERROR(INDEX('Bear Case'!$F:$F,MATCH($Y6,'Bear Case'!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="X6" s="35">
+        <f>IFERROR(W6/P6-1,"")</f>
+        <v/>
+      </c>
+      <c r="Y6" s="10" t="inlineStr">
+        <is>
+          <t>nuclear-naval-supplier-qualification</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t>PFAS-Compliant Biosolids Outlet Exchange for the Mid-Atlantic</t>
+        </is>
+      </c>
+      <c r="C7" s="28" t="n">
+        <v>900</v>
+      </c>
+      <c r="D7" s="29" t="n">
+        <v>200000</v>
+      </c>
+      <c r="E7" s="30" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t>recurring</t>
+        </is>
+      </c>
+      <c r="G7" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="H7" s="28" t="n">
+        <v>10</v>
+      </c>
+      <c r="I7" s="28" t="n">
+        <v>19</v>
+      </c>
+      <c r="J7" s="28" t="n">
+        <v>30</v>
+      </c>
+      <c r="K7" s="28" t="n">
+        <v>42</v>
+      </c>
+      <c r="L7" s="36">
+        <f>G7*$D7</f>
+        <v/>
+      </c>
+      <c r="M7" s="36">
+        <f>H7*$D7</f>
+        <v/>
+      </c>
+      <c r="N7" s="36">
+        <f>I7*$D7</f>
+        <v/>
+      </c>
+      <c r="O7" s="36">
+        <f>J7*$D7</f>
+        <v/>
+      </c>
+      <c r="P7" s="36">
+        <f>K7*$D7</f>
+        <v/>
+      </c>
+      <c r="Q7" s="37">
+        <f>P7*$E7</f>
+        <v/>
+      </c>
+      <c r="R7" s="38">
+        <f>IF($C7=0,"",K7/$C7)</f>
+        <v/>
+      </c>
+      <c r="S7" s="29" t="n">
+        <v>400000</v>
+      </c>
+      <c r="T7" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="U7" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="V7" s="41" t="n">
+        <v>3</v>
+      </c>
+      <c r="W7" s="36">
+        <f>IFERROR(INDEX('Bear Case'!$F:$F,MATCH($Y7,'Bear Case'!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="X7" s="40">
+        <f>IFERROR(W7/P7-1,"")</f>
+        <v/>
+      </c>
+      <c r="Y7" s="12" t="inlineStr">
+        <is>
+          <t>biosolids-outlet-exchange</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>Reachability-grade SBOMs and kernel-CVE triage for embedded Linux</t>
+        </is>
+      </c>
+      <c r="C8" s="28" t="n">
+        <v>6000</v>
+      </c>
+      <c r="D8" s="29" t="n">
+        <v>55000</v>
+      </c>
+      <c r="E8" s="30" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>recurring</t>
+        </is>
+      </c>
+      <c r="G8" s="28" t="n">
+        <v>8</v>
+      </c>
+      <c r="H8" s="28" t="n">
+        <v>35</v>
+      </c>
+      <c r="I8" s="28" t="n">
+        <v>95</v>
+      </c>
+      <c r="J8" s="28" t="n">
+        <v>190</v>
+      </c>
+      <c r="K8" s="28" t="n">
+        <v>320</v>
+      </c>
+      <c r="L8" s="31">
+        <f>G8*$D8</f>
+        <v/>
+      </c>
+      <c r="M8" s="31">
+        <f>H8*$D8</f>
+        <v/>
+      </c>
+      <c r="N8" s="31">
+        <f>I8*$D8</f>
+        <v/>
+      </c>
+      <c r="O8" s="31">
+        <f>J8*$D8</f>
+        <v/>
+      </c>
+      <c r="P8" s="31">
+        <f>K8*$D8</f>
+        <v/>
+      </c>
+      <c r="Q8" s="32">
+        <f>P8*$E8</f>
+        <v/>
+      </c>
+      <c r="R8" s="33">
+        <f>IF($C8=0,"",K8/$C8)</f>
+        <v/>
+      </c>
+      <c r="S8" s="29" t="n">
+        <v>450000</v>
+      </c>
+      <c r="T8" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="U8" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="V8" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="W8" s="31">
+        <f>IFERROR(INDEX('Bear Case'!$F:$F,MATCH($Y8,'Bear Case'!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="X8" s="35">
+        <f>IFERROR(W8/P8-1,"")</f>
+        <v/>
+      </c>
+      <c r="Y8" s="10" t="inlineStr">
+        <is>
+          <t>cra-embedded-sbom-and-cve-triage</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>Funded-Claim Detection for Casualty Reserving</t>
+        </is>
+      </c>
+      <c r="C9" s="28" t="n">
+        <v>250</v>
+      </c>
+      <c r="D9" s="29" t="n">
+        <v>125000</v>
+      </c>
+      <c r="E9" s="30" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="F9" s="12" t="inlineStr">
+        <is>
+          <t>recurring</t>
+        </is>
+      </c>
+      <c r="G9" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="H9" s="28" t="n">
+        <v>8</v>
+      </c>
+      <c r="I9" s="28" t="n">
+        <v>16</v>
+      </c>
+      <c r="J9" s="28" t="n">
+        <v>26</v>
+      </c>
+      <c r="K9" s="28" t="n">
+        <v>36</v>
+      </c>
+      <c r="L9" s="36">
+        <f>G9*$D9</f>
+        <v/>
+      </c>
+      <c r="M9" s="36">
+        <f>H9*$D9</f>
+        <v/>
+      </c>
+      <c r="N9" s="36">
+        <f>I9*$D9</f>
+        <v/>
+      </c>
+      <c r="O9" s="36">
+        <f>J9*$D9</f>
+        <v/>
+      </c>
+      <c r="P9" s="36">
+        <f>K9*$D9</f>
+        <v/>
+      </c>
+      <c r="Q9" s="37">
+        <f>P9*$E9</f>
+        <v/>
+      </c>
+      <c r="R9" s="38">
+        <f>IF($C9=0,"",K9/$C9)</f>
+        <v/>
+      </c>
+      <c r="S9" s="29" t="n">
+        <v>120000</v>
+      </c>
+      <c r="T9" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="U9" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="V9" s="39" t="n">
+        <v>4</v>
+      </c>
+      <c r="W9" s="36">
+        <f>IFERROR(INDEX('Bear Case'!$F:$F,MATCH($Y9,'Bear Case'!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="X9" s="40">
+        <f>IFERROR(W9/P9-1,"")</f>
+        <v/>
+      </c>
+      <c r="Y9" s="12" t="inlineStr">
+        <is>
+          <t>funded-claim-detection-for-casualty</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>Forward exchange for transformer and switchgear production slots</t>
+        </is>
+      </c>
+      <c r="C10" s="28" t="n">
+        <v>600</v>
+      </c>
+      <c r="D10" s="29" t="n">
+        <v>220000</v>
+      </c>
+      <c r="E10" s="30" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>repeating-project</t>
+        </is>
+      </c>
+      <c r="G10" s="28" t="n">
+        <v>8</v>
+      </c>
+      <c r="H10" s="28" t="n">
+        <v>20</v>
+      </c>
+      <c r="I10" s="28" t="n">
+        <v>38</v>
+      </c>
+      <c r="J10" s="28" t="n">
+        <v>58</v>
+      </c>
+      <c r="K10" s="28" t="n">
+        <v>78</v>
+      </c>
+      <c r="L10" s="31">
+        <f>G10*$D10</f>
+        <v/>
+      </c>
+      <c r="M10" s="31">
+        <f>H10*$D10</f>
+        <v/>
+      </c>
+      <c r="N10" s="31">
+        <f>I10*$D10</f>
+        <v/>
+      </c>
+      <c r="O10" s="31">
+        <f>J10*$D10</f>
+        <v/>
+      </c>
+      <c r="P10" s="31">
+        <f>K10*$D10</f>
+        <v/>
+      </c>
+      <c r="Q10" s="32">
+        <f>P10*$E10</f>
+        <v/>
+      </c>
+      <c r="R10" s="33">
+        <f>IF($C10=0,"",K10/$C10)</f>
+        <v/>
+      </c>
+      <c r="S10" s="29" t="n">
+        <v>60000</v>
+      </c>
+      <c r="T10" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="U10" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="V10" s="34" t="n">
+        <v>5</v>
+      </c>
+      <c r="W10" s="31">
+        <f>IFERROR(INDEX('Bear Case'!$F:$F,MATCH($Y10,'Bear Case'!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="X10" s="35">
+        <f>IFERROR(W10/P10-1,"")</f>
+        <v/>
+      </c>
+      <c r="Y10" s="10" t="inlineStr">
+        <is>
+          <t>grid-equipment-slot-forward-exchange</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>Key-state custody for LMS/XMSS firmware signing under CNSA 2.0</t>
+        </is>
+      </c>
+      <c r="C11" s="28" t="n">
+        <v>600</v>
+      </c>
+      <c r="D11" s="29" t="n">
+        <v>110000</v>
+      </c>
+      <c r="E11" s="30" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="F11" s="12" t="inlineStr">
+        <is>
+          <t>recurring</t>
+        </is>
+      </c>
+      <c r="G11" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="H11" s="28" t="n">
+        <v>12</v>
+      </c>
+      <c r="I11" s="28" t="n">
+        <v>25</v>
+      </c>
+      <c r="J11" s="28" t="n">
+        <v>42</v>
+      </c>
+      <c r="K11" s="28" t="n">
+        <v>60</v>
+      </c>
+      <c r="L11" s="36">
+        <f>G11*$D11</f>
+        <v/>
+      </c>
+      <c r="M11" s="36">
+        <f>H11*$D11</f>
+        <v/>
+      </c>
+      <c r="N11" s="36">
+        <f>I11*$D11</f>
+        <v/>
+      </c>
+      <c r="O11" s="36">
+        <f>J11*$D11</f>
+        <v/>
+      </c>
+      <c r="P11" s="36">
+        <f>K11*$D11</f>
+        <v/>
+      </c>
+      <c r="Q11" s="37">
+        <f>P11*$E11</f>
+        <v/>
+      </c>
+      <c r="R11" s="38">
+        <f>IF($C11=0,"",K11/$C11)</f>
+        <v/>
+      </c>
+      <c r="S11" s="29" t="n">
+        <v>180000</v>
+      </c>
+      <c r="T11" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="U11" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="V11" s="39" t="n">
+        <v>4</v>
+      </c>
+      <c r="W11" s="36">
+        <f>IFERROR(INDEX('Bear Case'!$F:$F,MATCH($Y11,'Bear Case'!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="X11" s="40">
+        <f>IFERROR(W11/P11-1,"")</f>
+        <v/>
+      </c>
+      <c r="Y11" s="12" t="inlineStr">
+        <is>
+          <t>stateful-hash-signature-key-state-custody</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t>Copper sunset triage for fire-alarm, elevator and area-of-refuge lines</t>
+        </is>
+      </c>
+      <c r="C12" s="28" t="n">
+        <v>15000</v>
+      </c>
+      <c r="D12" s="29" t="n">
+        <v>14000</v>
+      </c>
+      <c r="E12" s="30" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>recurring</t>
+        </is>
+      </c>
+      <c r="G12" s="28" t="n">
+        <v>6</v>
+      </c>
+      <c r="H12" s="28" t="n">
+        <v>28</v>
+      </c>
+      <c r="I12" s="28" t="n">
+        <v>75</v>
+      </c>
+      <c r="J12" s="28" t="n">
+        <v>140</v>
+      </c>
+      <c r="K12" s="28" t="n">
+        <v>195</v>
+      </c>
+      <c r="L12" s="31">
+        <f>G12*$D12</f>
+        <v/>
+      </c>
+      <c r="M12" s="31">
+        <f>H12*$D12</f>
+        <v/>
+      </c>
+      <c r="N12" s="31">
+        <f>I12*$D12</f>
+        <v/>
+      </c>
+      <c r="O12" s="31">
+        <f>J12*$D12</f>
+        <v/>
+      </c>
+      <c r="P12" s="31">
+        <f>K12*$D12</f>
+        <v/>
+      </c>
+      <c r="Q12" s="32">
+        <f>P12*$E12</f>
+        <v/>
+      </c>
+      <c r="R12" s="33">
+        <f>IF($C12=0,"",K12/$C12)</f>
+        <v/>
+      </c>
+      <c r="S12" s="29" t="n">
+        <v>130000</v>
+      </c>
+      <c r="T12" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="U12" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="V12" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="W12" s="31">
+        <f>IFERROR(INDEX('Bear Case'!$F:$F,MATCH($Y12,'Bear Case'!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="X12" s="35">
+        <f>IFERROR(W12/P12-1,"")</f>
+        <v/>
+      </c>
+      <c r="Y12" s="10" t="inlineStr">
+        <is>
+          <t>copper-retirement-life-safety-circuits</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t>CUI determination and marking for small defense machine shops</t>
+        </is>
+      </c>
+      <c r="C13" s="28" t="n">
+        <v>40000</v>
+      </c>
+      <c r="D13" s="29" t="n">
+        <v>4800</v>
+      </c>
+      <c r="E13" s="30" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="F13" s="12" t="inlineStr">
+        <is>
+          <t>recurring</t>
+        </is>
+      </c>
+      <c r="G13" s="28" t="n">
+        <v>30</v>
+      </c>
+      <c r="H13" s="28" t="n">
+        <v>150</v>
+      </c>
+      <c r="I13" s="28" t="n">
+        <v>450</v>
+      </c>
+      <c r="J13" s="28" t="n">
+        <v>900</v>
+      </c>
+      <c r="K13" s="28" t="n">
+        <v>1500</v>
+      </c>
+      <c r="L13" s="36">
+        <f>G13*$D13</f>
+        <v/>
+      </c>
+      <c r="M13" s="36">
+        <f>H13*$D13</f>
+        <v/>
+      </c>
+      <c r="N13" s="36">
+        <f>I13*$D13</f>
+        <v/>
+      </c>
+      <c r="O13" s="36">
+        <f>J13*$D13</f>
+        <v/>
+      </c>
+      <c r="P13" s="36">
+        <f>K13*$D13</f>
+        <v/>
+      </c>
+      <c r="Q13" s="37">
+        <f>P13*$E13</f>
+        <v/>
+      </c>
+      <c r="R13" s="38">
+        <f>IF($C13=0,"",K13/$C13)</f>
+        <v/>
+      </c>
+      <c r="S13" s="29" t="n">
+        <v>90000</v>
+      </c>
+      <c r="T13" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="U13" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="V13" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="W13" s="36">
+        <f>IFERROR(INDEX('Bear Case'!$F:$F,MATCH($Y13,'Bear Case'!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="X13" s="40">
+        <f>IFERROR(W13/P13-1,"")</f>
+        <v/>
+      </c>
+      <c r="Y13" s="12" t="inlineStr">
+        <is>
+          <t>cui-determination-for-machine-shops</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t>State packaging EPR reporting for mid-market brands</t>
+        </is>
+      </c>
+      <c r="C14" s="28" t="n">
+        <v>8000</v>
+      </c>
+      <c r="D14" s="29" t="n">
+        <v>14000</v>
+      </c>
+      <c r="E14" s="30" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>recurring</t>
+        </is>
+      </c>
+      <c r="G14" s="28" t="n">
+        <v>10</v>
+      </c>
+      <c r="H14" s="28" t="n">
+        <v>35</v>
+      </c>
+      <c r="I14" s="28" t="n">
+        <v>90</v>
+      </c>
+      <c r="J14" s="28" t="n">
+        <v>180</v>
+      </c>
+      <c r="K14" s="28" t="n">
+        <v>300</v>
+      </c>
+      <c r="L14" s="31">
+        <f>G14*$D14</f>
+        <v/>
+      </c>
+      <c r="M14" s="31">
+        <f>H14*$D14</f>
+        <v/>
+      </c>
+      <c r="N14" s="31">
+        <f>I14*$D14</f>
+        <v/>
+      </c>
+      <c r="O14" s="31">
+        <f>J14*$D14</f>
+        <v/>
+      </c>
+      <c r="P14" s="31">
+        <f>K14*$D14</f>
+        <v/>
+      </c>
+      <c r="Q14" s="32">
+        <f>P14*$E14</f>
+        <v/>
+      </c>
+      <c r="R14" s="33">
+        <f>IF($C14=0,"",K14/$C14)</f>
+        <v/>
+      </c>
+      <c r="S14" s="29" t="n">
+        <v>75000</v>
+      </c>
+      <c r="T14" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="V14" s="34" t="n">
+        <v>5</v>
+      </c>
+      <c r="W14" s="31">
+        <f>IFERROR(INDEX('Bear Case'!$F:$F,MATCH($Y14,'Bear Case'!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="X14" s="35">
+        <f>IFERROR(W14/P14-1,"")</f>
+        <v/>
+      </c>
+      <c r="Y14" s="10" t="inlineStr">
+        <is>
+          <t>rec-state-packaging-epr-reporting-for-mid-market-brands</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>Part 146 ADSP certification: strategic deconfliction plus the sub-400-foot obstacle layer</t>
+        </is>
+      </c>
+      <c r="C15" s="28" t="n">
+        <v>300</v>
+      </c>
+      <c r="D15" s="29" t="n">
+        <v>180000</v>
+      </c>
+      <c r="E15" s="30" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="F15" s="12" t="inlineStr">
+        <is>
+          <t>recurring</t>
+        </is>
+      </c>
+      <c r="G15" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="H15" s="28" t="n">
+        <v>5</v>
+      </c>
+      <c r="I15" s="28" t="n">
+        <v>11</v>
+      </c>
+      <c r="J15" s="28" t="n">
+        <v>20</v>
+      </c>
+      <c r="K15" s="28" t="n">
+        <v>32</v>
+      </c>
+      <c r="L15" s="36">
+        <f>G15*$D15</f>
+        <v/>
+      </c>
+      <c r="M15" s="36">
+        <f>H15*$D15</f>
+        <v/>
+      </c>
+      <c r="N15" s="36">
+        <f>I15*$D15</f>
+        <v/>
+      </c>
+      <c r="O15" s="36">
+        <f>J15*$D15</f>
+        <v/>
+      </c>
+      <c r="P15" s="36">
+        <f>K15*$D15</f>
+        <v/>
+      </c>
+      <c r="Q15" s="37">
+        <f>P15*$E15</f>
+        <v/>
+      </c>
+      <c r="R15" s="38">
+        <f>IF($C15=0,"",K15/$C15)</f>
+        <v/>
+      </c>
+      <c r="S15" s="29" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="T15" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="U15" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="V15" s="39" t="n">
+        <v>4</v>
+      </c>
+      <c r="W15" s="36">
+        <f>IFERROR(INDEX('Bear Case'!$F:$F,MATCH($Y15,'Bear Case'!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="X15" s="40">
+        <f>IFERROR(W15/P15-1,"")</f>
+        <v/>
+      </c>
+      <c r="Y15" s="12" t="inlineStr">
+        <is>
+          <t>part-146-bvlos-data-services</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="21" t="inlineStr">
+        <is>
+          <t>Material Assistance Cost Ratio files for FEOC-exposed clean energy</t>
+        </is>
+      </c>
+      <c r="C16" s="28" t="n">
+        <v>900</v>
+      </c>
+      <c r="D16" s="29" t="n">
+        <v>75000</v>
+      </c>
+      <c r="E16" s="30" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F16" s="10" t="inlineStr">
+        <is>
+          <t>repeating-project</t>
+        </is>
+      </c>
+      <c r="G16" s="28" t="n">
+        <v>6</v>
+      </c>
+      <c r="H16" s="28" t="n">
+        <v>20</v>
+      </c>
+      <c r="I16" s="28" t="n">
+        <v>40</v>
+      </c>
+      <c r="J16" s="28" t="n">
+        <v>55</v>
+      </c>
+      <c r="K16" s="28" t="n">
+        <v>60</v>
+      </c>
+      <c r="L16" s="31">
+        <f>G16*$D16</f>
+        <v/>
+      </c>
+      <c r="M16" s="31">
+        <f>H16*$D16</f>
+        <v/>
+      </c>
+      <c r="N16" s="31">
+        <f>I16*$D16</f>
+        <v/>
+      </c>
+      <c r="O16" s="31">
+        <f>J16*$D16</f>
+        <v/>
+      </c>
+      <c r="P16" s="31">
+        <f>K16*$D16</f>
+        <v/>
+      </c>
+      <c r="Q16" s="32">
+        <f>P16*$E16</f>
+        <v/>
+      </c>
+      <c r="R16" s="33">
+        <f>IF($C16=0,"",K16/$C16)</f>
+        <v/>
+      </c>
+      <c r="S16" s="29" t="n">
+        <v>60000</v>
+      </c>
+      <c r="T16" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="V16" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="W16" s="31">
+        <f>IFERROR(INDEX('Bear Case'!$F:$F,MATCH($Y16,'Bear Case'!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="X16" s="35">
+        <f>IFERROR(W16/P16-1,"")</f>
+        <v/>
+      </c>
+      <c r="Y16" s="10" t="inlineStr">
+        <is>
+          <t>material-assistance-cost-ratio-attestation</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>The C2PA referee: conformance evidence, survivability scores, and verification at ingest</t>
+        </is>
+      </c>
+      <c r="C17" s="28" t="n">
+        <v>250</v>
+      </c>
+      <c r="D17" s="29" t="n">
+        <v>70000</v>
+      </c>
+      <c r="E17" s="30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F17" s="12" t="inlineStr">
+        <is>
+          <t>repeating-project</t>
+        </is>
+      </c>
+      <c r="G17" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="H17" s="28" t="n">
+        <v>9</v>
+      </c>
+      <c r="I17" s="28" t="n">
+        <v>18</v>
+      </c>
+      <c r="J17" s="28" t="n">
+        <v>28</v>
+      </c>
+      <c r="K17" s="28" t="n">
+        <v>38</v>
+      </c>
+      <c r="L17" s="36">
+        <f>G17*$D17</f>
+        <v/>
+      </c>
+      <c r="M17" s="36">
+        <f>H17*$D17</f>
+        <v/>
+      </c>
+      <c r="N17" s="36">
+        <f>I17*$D17</f>
+        <v/>
+      </c>
+      <c r="O17" s="36">
+        <f>J17*$D17</f>
+        <v/>
+      </c>
+      <c r="P17" s="36">
+        <f>K17*$D17</f>
+        <v/>
+      </c>
+      <c r="Q17" s="37">
+        <f>P17*$E17</f>
+        <v/>
+      </c>
+      <c r="R17" s="38">
+        <f>IF($C17=0,"",K17/$C17)</f>
+        <v/>
+      </c>
+      <c r="S17" s="29" t="n">
+        <v>120000</v>
+      </c>
+      <c r="T17" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="U17" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="V17" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="W17" s="36">
+        <f>IFERROR(INDEX('Bear Case'!$F:$F,MATCH($Y17,'Bear Case'!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="X17" s="40">
+        <f>IFERROR(W17/P17-1,"")</f>
+        <v/>
+      </c>
+      <c r="Y17" s="12" t="inlineStr">
+        <is>
+          <t>c2pa-conformance-and-robustness-referee</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>Micropollutant EPR fee ledger for pharma and cosmetics under the UWWTD</t>
+        </is>
+      </c>
+      <c r="C18" s="28" t="n">
+        <v>250</v>
+      </c>
+      <c r="D18" s="29" t="n">
+        <v>65000</v>
+      </c>
+      <c r="E18" s="30" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F18" s="10" t="inlineStr">
+        <is>
+          <t>repeating-project</t>
+        </is>
+      </c>
+      <c r="G18" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="H18" s="28" t="n">
+        <v>8</v>
+      </c>
+      <c r="I18" s="28" t="n">
+        <v>16</v>
+      </c>
+      <c r="J18" s="28" t="n">
+        <v>26</v>
+      </c>
+      <c r="K18" s="28" t="n">
+        <v>38</v>
+      </c>
+      <c r="L18" s="31">
+        <f>G18*$D18</f>
+        <v/>
+      </c>
+      <c r="M18" s="31">
+        <f>H18*$D18</f>
+        <v/>
+      </c>
+      <c r="N18" s="31">
+        <f>I18*$D18</f>
+        <v/>
+      </c>
+      <c r="O18" s="31">
+        <f>J18*$D18</f>
+        <v/>
+      </c>
+      <c r="P18" s="31">
+        <f>K18*$D18</f>
+        <v/>
+      </c>
+      <c r="Q18" s="32">
+        <f>P18*$E18</f>
+        <v/>
+      </c>
+      <c r="R18" s="33">
+        <f>IF($C18=0,"",K18/$C18)</f>
+        <v/>
+      </c>
+      <c r="S18" s="29" t="n">
+        <v>400000</v>
+      </c>
+      <c r="T18" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="U18" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="V18" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="W18" s="31">
+        <f>IFERROR(INDEX('Bear Case'!$F:$F,MATCH($Y18,'Bear Case'!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="X18" s="35">
+        <f>IFERROR(W18/P18-1,"")</f>
+        <v/>
+      </c>
+      <c r="Y18" s="10" t="inlineStr">
+        <is>
+          <t>micropollutant-epr-billback</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="23" t="inlineStr">
+        <is>
+          <t>CRA Article 14 incident reporting and the legacy-product obligation</t>
+        </is>
+      </c>
+      <c r="C19" s="28" t="n">
+        <v>12000</v>
+      </c>
+      <c r="D19" s="29" t="n">
+        <v>70000</v>
+      </c>
+      <c r="E19" s="30" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F19" s="12" t="inlineStr">
+        <is>
+          <t>recurring</t>
+        </is>
+      </c>
+      <c r="G19" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="H19" s="28" t="n">
+        <v>18</v>
+      </c>
+      <c r="I19" s="28" t="n">
+        <v>45</v>
+      </c>
+      <c r="J19" s="28" t="n">
+        <v>80</v>
+      </c>
+      <c r="K19" s="28" t="n">
+        <v>120</v>
+      </c>
+      <c r="L19" s="36">
+        <f>G19*$D19</f>
+        <v/>
+      </c>
+      <c r="M19" s="36">
+        <f>H19*$D19</f>
+        <v/>
+      </c>
+      <c r="N19" s="36">
+        <f>I19*$D19</f>
+        <v/>
+      </c>
+      <c r="O19" s="36">
+        <f>J19*$D19</f>
+        <v/>
+      </c>
+      <c r="P19" s="36">
+        <f>K19*$D19</f>
+        <v/>
+      </c>
+      <c r="Q19" s="37">
+        <f>P19*$E19</f>
+        <v/>
+      </c>
+      <c r="R19" s="38">
+        <f>IF($C19=0,"",K19/$C19)</f>
+        <v/>
+      </c>
+      <c r="S19" s="29" t="n">
+        <v>250000</v>
+      </c>
+      <c r="T19" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="U19" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="V19" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="W19" s="36">
+        <f>IFERROR(INDEX('Bear Case'!$F:$F,MATCH($Y19,'Bear Case'!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="X19" s="40">
+        <f>IFERROR(W19/P19-1,"")</f>
+        <v/>
+      </c>
+      <c r="Y19" s="12" t="inlineStr">
+        <is>
+          <t>cra-enisa-24h-reporting</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="21" t="inlineStr">
+        <is>
+          <t>Signed provenance attestation for the secondhand datacenter hardware channel</t>
+        </is>
+      </c>
+      <c r="C20" s="28" t="n">
+        <v>4000</v>
+      </c>
+      <c r="D20" s="29" t="n">
+        <v>18000</v>
+      </c>
+      <c r="E20" s="30" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="F20" s="10" t="inlineStr">
+        <is>
+          <t>recurring</t>
+        </is>
+      </c>
+      <c r="G20" s="28" t="n">
+        <v>6</v>
+      </c>
+      <c r="H20" s="28" t="n">
+        <v>25</v>
+      </c>
+      <c r="I20" s="28" t="n">
+        <v>60</v>
+      </c>
+      <c r="J20" s="28" t="n">
+        <v>110</v>
+      </c>
+      <c r="K20" s="28" t="n">
+        <v>170</v>
+      </c>
+      <c r="L20" s="31">
+        <f>G20*$D20</f>
+        <v/>
+      </c>
+      <c r="M20" s="31">
+        <f>H20*$D20</f>
+        <v/>
+      </c>
+      <c r="N20" s="31">
+        <f>I20*$D20</f>
+        <v/>
+      </c>
+      <c r="O20" s="31">
+        <f>J20*$D20</f>
+        <v/>
+      </c>
+      <c r="P20" s="31">
+        <f>K20*$D20</f>
+        <v/>
+      </c>
+      <c r="Q20" s="32">
+        <f>P20*$E20</f>
+        <v/>
+      </c>
+      <c r="R20" s="33">
+        <f>IF($C20=0,"",K20/$C20)</f>
+        <v/>
+      </c>
+      <c r="S20" s="29" t="n">
+        <v>120000</v>
+      </c>
+      <c r="T20" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="U20" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="V20" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="W20" s="31">
+        <f>IFERROR(INDEX('Bear Case'!$F:$F,MATCH($Y20,'Bear Case'!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="X20" s="35">
+        <f>IFERROR(W20/P20-1,"")</f>
+        <v/>
+      </c>
+      <c r="Y20" s="10" t="inlineStr">
+        <is>
+          <t>secondhand-hardware-provenance-channel</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="B21" s="23" t="inlineStr">
+        <is>
+          <t>Loss data and incident taxonomy for AI agent liability underwriting</t>
+        </is>
+      </c>
+      <c r="C21" s="28" t="n">
+        <v>250</v>
+      </c>
+      <c r="D21" s="29" t="n">
+        <v>120000</v>
+      </c>
+      <c r="E21" s="30" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="F21" s="12" t="inlineStr">
+        <is>
+          <t>recurring</t>
+        </is>
+      </c>
+      <c r="G21" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="I21" s="28" t="n">
+        <v>8</v>
+      </c>
+      <c r="J21" s="28" t="n">
+        <v>16</v>
+      </c>
+      <c r="K21" s="28" t="n">
+        <v>22</v>
+      </c>
+      <c r="L21" s="36">
+        <f>G21*$D21</f>
+        <v/>
+      </c>
+      <c r="M21" s="36">
+        <f>H21*$D21</f>
+        <v/>
+      </c>
+      <c r="N21" s="36">
+        <f>I21*$D21</f>
+        <v/>
+      </c>
+      <c r="O21" s="36">
+        <f>J21*$D21</f>
+        <v/>
+      </c>
+      <c r="P21" s="36">
+        <f>K21*$D21</f>
+        <v/>
+      </c>
+      <c r="Q21" s="37">
+        <f>P21*$E21</f>
+        <v/>
+      </c>
+      <c r="R21" s="38">
+        <f>IF($C21=0,"",K21/$C21)</f>
+        <v/>
+      </c>
+      <c r="S21" s="29" t="n">
+        <v>600000</v>
+      </c>
+      <c r="T21" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="U21" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="V21" s="41" t="n">
+        <v>3</v>
+      </c>
+      <c r="W21" s="36">
+        <f>IFERROR(INDEX('Bear Case'!$F:$F,MATCH($Y21,'Bear Case'!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="X21" s="40">
+        <f>IFERROR(W21/P21-1,"")</f>
+        <v/>
+      </c>
+      <c r="Y21" s="12" t="inlineStr">
+        <is>
+          <t>agent-liability-loss-data</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="n">
+        <v>19</v>
+      </c>
+      <c r="B22" s="21" t="inlineStr">
+        <is>
+          <t>Relying-Party-as-a-Service: the verifier side of the EU Digital Identity Wallet</t>
+        </is>
+      </c>
+      <c r="C22" s="28" t="n">
+        <v>12000</v>
+      </c>
+      <c r="D22" s="29" t="n">
+        <v>45000</v>
+      </c>
+      <c r="E22" s="30" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="F22" s="10" t="inlineStr">
+        <is>
+          <t>recurring</t>
+        </is>
+      </c>
+      <c r="G22" s="28" t="n">
+        <v>5</v>
+      </c>
+      <c r="H22" s="28" t="n">
+        <v>30</v>
+      </c>
+      <c r="I22" s="28" t="n">
+        <v>85</v>
+      </c>
+      <c r="J22" s="28" t="n">
+        <v>170</v>
+      </c>
+      <c r="K22" s="28" t="n">
+        <v>280</v>
+      </c>
+      <c r="L22" s="31">
+        <f>G22*$D22</f>
+        <v/>
+      </c>
+      <c r="M22" s="31">
+        <f>H22*$D22</f>
+        <v/>
+      </c>
+      <c r="N22" s="31">
+        <f>I22*$D22</f>
+        <v/>
+      </c>
+      <c r="O22" s="31">
+        <f>J22*$D22</f>
+        <v/>
+      </c>
+      <c r="P22" s="31">
+        <f>K22*$D22</f>
+        <v/>
+      </c>
+      <c r="Q22" s="32">
+        <f>P22*$E22</f>
+        <v/>
+      </c>
+      <c r="R22" s="33">
+        <f>IF($C22=0,"",K22/$C22)</f>
+        <v/>
+      </c>
+      <c r="S22" s="29" t="n">
+        <v>400000</v>
+      </c>
+      <c r="T22" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="U22" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="V22" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="W22" s="31">
+        <f>IFERROR(INDEX('Bear Case'!$F:$F,MATCH($Y22,'Bear Case'!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="X22" s="35">
+        <f>IFERROR(W22/P22-1,"")</f>
+        <v/>
+      </c>
+      <c r="Y22" s="10" t="inlineStr">
+        <is>
+          <t>eudi-wallet-relying-party-side</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="B23" s="23" t="inlineStr">
+        <is>
+          <t>Lot-code reconciliation and the 24-hour FSMA 204 spreadsheet</t>
+        </is>
+      </c>
+      <c r="C23" s="28" t="n">
+        <v>30000</v>
+      </c>
+      <c r="D23" s="29" t="n">
+        <v>5400</v>
+      </c>
+      <c r="E23" s="30" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="F23" s="12" t="inlineStr">
+        <is>
+          <t>recurring</t>
+        </is>
+      </c>
+      <c r="G23" s="28" t="n">
+        <v>20</v>
+      </c>
+      <c r="H23" s="28" t="n">
+        <v>90</v>
+      </c>
+      <c r="I23" s="28" t="n">
+        <v>260</v>
+      </c>
+      <c r="J23" s="28" t="n">
+        <v>500</v>
+      </c>
+      <c r="K23" s="28" t="n">
+        <v>800</v>
+      </c>
+      <c r="L23" s="36">
+        <f>G23*$D23</f>
+        <v/>
+      </c>
+      <c r="M23" s="36">
+        <f>H23*$D23</f>
+        <v/>
+      </c>
+      <c r="N23" s="36">
+        <f>I23*$D23</f>
+        <v/>
+      </c>
+      <c r="O23" s="36">
+        <f>J23*$D23</f>
+        <v/>
+      </c>
+      <c r="P23" s="36">
+        <f>K23*$D23</f>
+        <v/>
+      </c>
+      <c r="Q23" s="37">
+        <f>P23*$E23</f>
+        <v/>
+      </c>
+      <c r="R23" s="38">
+        <f>IF($C23=0,"",K23/$C23)</f>
+        <v/>
+      </c>
+      <c r="S23" s="29" t="n">
+        <v>80000</v>
+      </c>
+      <c r="T23" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="U23" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="V23" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="W23" s="36">
+        <f>IFERROR(INDEX('Bear Case'!$F:$F,MATCH($Y23,'Bear Case'!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="X23" s="40">
+        <f>IFERROR(W23/P23-1,"")</f>
+        <v/>
+      </c>
+      <c r="Y23" s="12" t="inlineStr">
+        <is>
+          <t>fsma-204-lot-code-traceability</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="B24" s="21" t="inlineStr">
+        <is>
+          <t>DMSMS resolution desk: last-time-buy brokerage plus qualified resupply for 20-year platforms</t>
+        </is>
+      </c>
+      <c r="C24" s="28" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D24" s="29" t="n">
+        <v>350000</v>
+      </c>
+      <c r="E24" s="30" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="F24" s="10" t="inlineStr">
+        <is>
+          <t>repeating-project</t>
+        </is>
+      </c>
+      <c r="G24" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="H24" s="28" t="n">
+        <v>12</v>
+      </c>
+      <c r="I24" s="28" t="n">
+        <v>25</v>
+      </c>
+      <c r="J24" s="28" t="n">
+        <v>42</v>
+      </c>
+      <c r="K24" s="28" t="n">
+        <v>60</v>
+      </c>
+      <c r="L24" s="31">
+        <f>G24*$D24</f>
+        <v/>
+      </c>
+      <c r="M24" s="31">
+        <f>H24*$D24</f>
+        <v/>
+      </c>
+      <c r="N24" s="31">
+        <f>I24*$D24</f>
+        <v/>
+      </c>
+      <c r="O24" s="31">
+        <f>J24*$D24</f>
+        <v/>
+      </c>
+      <c r="P24" s="31">
+        <f>K24*$D24</f>
+        <v/>
+      </c>
+      <c r="Q24" s="32">
+        <f>P24*$E24</f>
+        <v/>
+      </c>
+      <c r="R24" s="33">
+        <f>IF($C24=0,"",K24/$C24)</f>
+        <v/>
+      </c>
+      <c r="S24" s="29" t="n">
+        <v>300000</v>
+      </c>
+      <c r="T24" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="V24" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="W24" s="31">
+        <f>IFERROR(INDEX('Bear Case'!$F:$F,MATCH($Y24,'Bear Case'!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="X24" s="35">
+        <f>IFERROR(W24/P24-1,"")</f>
+        <v/>
+      </c>
+      <c r="Y24" s="10" t="inlineStr">
+        <is>
+          <t>last-time-buy-dmsms-desk</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="B25" s="23" t="inlineStr">
+        <is>
+          <t>Battery Passport plumbing: supplier data chase, EPCIS event store, GS1-conformant resolver</t>
+        </is>
+      </c>
+      <c r="C25" s="28" t="n">
+        <v>2500</v>
+      </c>
+      <c r="D25" s="29" t="n">
+        <v>55000</v>
+      </c>
+      <c r="E25" s="30" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="F25" s="12" t="inlineStr">
+        <is>
+          <t>recurring</t>
+        </is>
+      </c>
+      <c r="G25" s="28" t="n">
+        <v>6</v>
+      </c>
+      <c r="H25" s="28" t="n">
+        <v>25</v>
+      </c>
+      <c r="I25" s="28" t="n">
+        <v>55</v>
+      </c>
+      <c r="J25" s="28" t="n">
+        <v>90</v>
+      </c>
+      <c r="K25" s="28" t="n">
+        <v>130</v>
+      </c>
+      <c r="L25" s="36">
+        <f>G25*$D25</f>
+        <v/>
+      </c>
+      <c r="M25" s="36">
+        <f>H25*$D25</f>
+        <v/>
+      </c>
+      <c r="N25" s="36">
+        <f>I25*$D25</f>
+        <v/>
+      </c>
+      <c r="O25" s="36">
+        <f>J25*$D25</f>
+        <v/>
+      </c>
+      <c r="P25" s="36">
+        <f>K25*$D25</f>
+        <v/>
+      </c>
+      <c r="Q25" s="37">
+        <f>P25*$E25</f>
+        <v/>
+      </c>
+      <c r="R25" s="38">
+        <f>IF($C25=0,"",K25/$C25)</f>
+        <v/>
+      </c>
+      <c r="S25" s="29" t="n">
+        <v>200000</v>
+      </c>
+      <c r="T25" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="U25" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="V25" s="41" t="n">
+        <v>3</v>
+      </c>
+      <c r="W25" s="36">
+        <f>IFERROR(INDEX('Bear Case'!$F:$F,MATCH($Y25,'Bear Case'!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="X25" s="40">
+        <f>IFERROR(W25/P25-1,"")</f>
+        <v/>
+      </c>
+      <c r="Y25" s="12" t="inlineStr">
+        <is>
+          <t>gs1-dpp-event-and-resolver-backbone</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="n">
+        <v>23</v>
+      </c>
+      <c r="B26" s="21" t="inlineStr">
+        <is>
+          <t>Sealed-at-capture evidence for insurance claims and field inspection</t>
+        </is>
+      </c>
+      <c r="C26" s="28" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D26" s="29" t="n">
+        <v>120000</v>
+      </c>
+      <c r="E26" s="30" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F26" s="10" t="inlineStr">
+        <is>
+          <t>recurring</t>
+        </is>
+      </c>
+      <c r="G26" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="H26" s="28" t="n">
+        <v>6</v>
+      </c>
+      <c r="I26" s="28" t="n">
+        <v>14</v>
+      </c>
+      <c r="J26" s="28" t="n">
+        <v>26</v>
+      </c>
+      <c r="K26" s="28" t="n">
+        <v>42</v>
+      </c>
+      <c r="L26" s="31">
+        <f>G26*$D26</f>
+        <v/>
+      </c>
+      <c r="M26" s="31">
+        <f>H26*$D26</f>
+        <v/>
+      </c>
+      <c r="N26" s="31">
+        <f>I26*$D26</f>
+        <v/>
+      </c>
+      <c r="O26" s="31">
+        <f>J26*$D26</f>
+        <v/>
+      </c>
+      <c r="P26" s="31">
+        <f>K26*$D26</f>
+        <v/>
+      </c>
+      <c r="Q26" s="32">
+        <f>P26*$E26</f>
+        <v/>
+      </c>
+      <c r="R26" s="33">
+        <f>IF($C26=0,"",K26/$C26)</f>
+        <v/>
+      </c>
+      <c r="S26" s="29" t="n">
+        <v>350000</v>
+      </c>
+      <c r="T26" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="U26" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="V26" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="W26" s="31">
+        <f>IFERROR(INDEX('Bear Case'!$F:$F,MATCH($Y26,'Bear Case'!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="X26" s="35">
+        <f>IFERROR(W26/P26-1,"")</f>
+        <v/>
+      </c>
+      <c r="Y26" s="10" t="inlineStr">
+        <is>
+          <t>attested-capture-for-claims-media</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="B27" s="23" t="inlineStr">
+        <is>
+          <t>Neutral clearing house for the HTTP 402 crawler economy</t>
+        </is>
+      </c>
+      <c r="C27" s="28" t="n">
+        <v>400</v>
+      </c>
+      <c r="D27" s="29" t="n">
+        <v>45000</v>
+      </c>
+      <c r="E27" s="30" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="F27" s="12" t="inlineStr">
+        <is>
+          <t>recurring</t>
+        </is>
+      </c>
+      <c r="G27" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="H27" s="28" t="n">
+        <v>12</v>
+      </c>
+      <c r="I27" s="28" t="n">
+        <v>30</v>
+      </c>
+      <c r="J27" s="28" t="n">
+        <v>55</v>
+      </c>
+      <c r="K27" s="28" t="n">
+        <v>80</v>
+      </c>
+      <c r="L27" s="36">
+        <f>G27*$D27</f>
+        <v/>
+      </c>
+      <c r="M27" s="36">
+        <f>H27*$D27</f>
+        <v/>
+      </c>
+      <c r="N27" s="36">
+        <f>I27*$D27</f>
+        <v/>
+      </c>
+      <c r="O27" s="36">
+        <f>J27*$D27</f>
+        <v/>
+      </c>
+      <c r="P27" s="36">
+        <f>K27*$D27</f>
+        <v/>
+      </c>
+      <c r="Q27" s="37">
+        <f>P27*$E27</f>
+        <v/>
+      </c>
+      <c r="R27" s="38">
+        <f>IF($C27=0,"",K27/$C27)</f>
+        <v/>
+      </c>
+      <c r="S27" s="29" t="n">
+        <v>250000</v>
+      </c>
+      <c r="T27" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="U27" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="V27" s="41" t="n">
+        <v>3</v>
+      </c>
+      <c r="W27" s="36">
+        <f>IFERROR(INDEX('Bear Case'!$F:$F,MATCH($Y27,'Bear Case'!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="X27" s="40">
+        <f>IFERROR(W27/P27-1,"")</f>
+        <v/>
+      </c>
+      <c r="Y27" s="12" t="inlineStr">
+        <is>
+          <t>crawler-payment-clearing-and-metering</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="B28" s="21" t="inlineStr">
+        <is>
+          <t>Killing lead-line 'unknowns' before the Nov 1, 2027 LCRI baseline locks in</t>
+        </is>
+      </c>
+      <c r="C28" s="28" t="n">
+        <v>4500</v>
+      </c>
+      <c r="D28" s="29" t="n">
+        <v>220000</v>
+      </c>
+      <c r="E28" s="30" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F28" s="10" t="inlineStr">
+        <is>
+          <t>repeating-project</t>
+        </is>
+      </c>
+      <c r="G28" s="28" t="n">
+        <v>5</v>
+      </c>
+      <c r="H28" s="28" t="n">
+        <v>14</v>
+      </c>
+      <c r="I28" s="28" t="n">
+        <v>20</v>
+      </c>
+      <c r="J28" s="28" t="n">
+        <v>22</v>
+      </c>
+      <c r="K28" s="28" t="n">
+        <v>24</v>
+      </c>
+      <c r="L28" s="31">
+        <f>G28*$D28</f>
+        <v/>
+      </c>
+      <c r="M28" s="31">
+        <f>H28*$D28</f>
+        <v/>
+      </c>
+      <c r="N28" s="31">
+        <f>I28*$D28</f>
+        <v/>
+      </c>
+      <c r="O28" s="31">
+        <f>J28*$D28</f>
+        <v/>
+      </c>
+      <c r="P28" s="31">
+        <f>K28*$D28</f>
+        <v/>
+      </c>
+      <c r="Q28" s="32">
+        <f>P28*$E28</f>
+        <v/>
+      </c>
+      <c r="R28" s="33">
+        <f>IF($C28=0,"",K28/$C28)</f>
+        <v/>
+      </c>
+      <c r="S28" s="29" t="n">
+        <v>120000</v>
+      </c>
+      <c r="T28" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="U28" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="V28" s="34" t="n">
+        <v>5</v>
+      </c>
+      <c r="W28" s="31">
+        <f>IFERROR(INDEX('Bear Case'!$F:$F,MATCH($Y28,'Bear Case'!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="X28" s="35">
+        <f>IFERROR(W28/P28-1,"")</f>
+        <v/>
+      </c>
+      <c r="Y28" s="10" t="inlineStr">
+        <is>
+          <t>lead-service-line-inventory-2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="12" t="n"/>
+      <c r="B29" s="43" t="inlineStr">
+        <is>
+          <t>Portfolio total (25 opportunities)</t>
+        </is>
+      </c>
+      <c r="C29" s="12" t="n"/>
+      <c r="D29" s="12" t="n"/>
+      <c r="E29" s="12" t="n"/>
+      <c r="F29" s="12" t="n"/>
+      <c r="G29" s="12" t="n"/>
+      <c r="H29" s="12" t="n"/>
+      <c r="I29" s="12" t="n"/>
+      <c r="J29" s="12" t="n"/>
+      <c r="K29" s="12" t="n"/>
+      <c r="L29" s="37">
+        <f>SUM(L4:L28)</f>
+        <v/>
+      </c>
+      <c r="M29" s="37">
+        <f>SUM(M4:M28)</f>
+        <v/>
+      </c>
+      <c r="N29" s="37">
+        <f>SUM(N4:N28)</f>
+        <v/>
+      </c>
+      <c r="O29" s="37">
+        <f>SUM(O4:O28)</f>
+        <v/>
+      </c>
+      <c r="P29" s="37">
+        <f>SUM(P4:P28)</f>
+        <v/>
+      </c>
+      <c r="Q29" s="37">
+        <f>SUM(Q4:Q28)</f>
+        <v/>
+      </c>
+      <c r="R29" s="12" t="n"/>
+      <c r="S29" s="37">
+        <f>SUM(S4:S28)</f>
+        <v/>
+      </c>
+      <c r="T29" s="12" t="n"/>
+      <c r="U29" s="12" t="n"/>
+      <c r="V29" s="14">
+        <f>ROUND(AVERAGE(V4:V28),1)</f>
+        <v/>
+      </c>
+      <c r="W29" s="37">
+        <f>SUM(W4:W28)</f>
+        <v/>
+      </c>
+      <c r="X29" s="12" t="n"/>
+      <c r="Y29" s="12" t="n"/>
+    </row>
+    <row r="31">
+      <c r="B31" s="44" t="inlineStr">
+        <is>
+          <t>The portfolio total is an arithmetic sum, NOT an expected value. It assumes all 25 businesses are built simultaneously and every one hits plan - which will not happen. Read it as the ceiling of the set, and read the Bear-case column as what each looks like after the investment committee gets hold of the most optimistic assumption.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32"/>
+    <row r="33"/>
+  </sheetData>
+  <autoFilter ref="A3:Y28"/>
+  <mergeCells count="2">
+    <mergeCell ref="B31:L33"/>
+    <mergeCell ref="A1:Y1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="90" customWidth="1" min="4" max="4"/>
+    <col width="80" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="90" customWidth="1" min="7" max="7"/>
+    <col width="70" customWidth="1" min="8" max="8"/>
+    <col width="70" customWidth="1" min="9" max="9"/>
+    <col width="80" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="80" customWidth="1" min="12" max="12"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>Opportunity</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>Who actually signs the cheque</t>
+        </is>
+      </c>
+      <c r="D1" s="6" t="inlineStr">
+        <is>
+          <t>How the buyer universe was derived</t>
+        </is>
+      </c>
+      <c r="E1" s="6" t="inlineStr">
+        <is>
+          <t>How the ACV was set</t>
+        </is>
+      </c>
+      <c r="F1" s="6" t="inlineStr">
+        <is>
+          <t>Pricing model</t>
+        </is>
+      </c>
+      <c r="G1" s="6" t="inlineStr">
+        <is>
+          <t>Why this ramp</t>
+        </is>
+      </c>
+      <c r="H1" s="6" t="inlineStr">
+        <is>
+          <t>Margin basis</t>
+        </is>
+      </c>
+      <c r="I1" s="6" t="inlineStr">
+        <is>
+          <t>Key sensitivity</t>
+        </is>
+      </c>
+      <c r="J1" s="6" t="inlineStr">
+        <is>
+          <t>Bear case</t>
+        </is>
+      </c>
+      <c r="K1" s="6" t="inlineStr">
+        <is>
+          <t>Confidence</t>
+        </is>
+      </c>
+      <c r="L1" s="6" t="inlineStr">
+        <is>
+          <t>What the confidence means</t>
+        </is>
+      </c>
+      <c r="M1" s="6" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="76" customHeight="1">
+      <c r="A2" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="21" t="inlineStr">
+        <is>
+          <t>Ride-through models and curtailment proof for NERC-registered data centers</t>
+        </is>
+      </c>
+      <c r="C2" s="21" t="inlineStr">
+        <is>
+          <t>The VP of Energy / interconnection lead at a large-load data centre developer (wholesale colo or hyperscaler build partner) who owns a specific ERCOT campus's NERC registration and interconnection agreement — the person who already carries an outside-engineering line item in the campus budget. Secondary buyer: the large-load compliance manager at the administering utility/TDSP.</t>
+        </is>
+      </c>
+      <c r="D2" s="21" t="inlineStr">
+        <is>
+          <t>MY REASONING, not researched. The record states ERCOT is 'tracking more than 438 GW of large-load requests with roughly 198 GW applying in Q1 2026 alone, nearly 90% data centers.' At ~500 MW per campus request that is roughly 875 ERCOT requests; applying a ~30% materialization rate (my recall that large-load and generator queues are heavily duplicative, with the same project shopping multiple POIs) gives ~260 real ERCOT campuses. FERC Docket RD26-7-000 directs NERC to file mandatory computational-load standards by 31 Dec 2026 (quoted from record), which nationalises the obligation, so I scale ERCOT up ~3.5x for PJM/MISO/SPP/SERC. Rounds to ~900 campus-level engagements available through 2031. Note this is campuses, not corporate accounts — the distinct developer entities behind them are probably only 100-200, which is a real concentration risk.</t>
+        </is>
+      </c>
+      <c r="E2" s="21" t="inlineStr">
+        <is>
+          <t>Anchored on the record's quoted price: 'roughly $150k-$600k a campus with mandatory re-validation after every trip event.' I weight toward the low-middle of that band because a new two-person boutique wins the smaller non-grandfathered scopes first, not the flagship hyperscaler campuses, then add a modest attach of the PCLR registration pack and curtailment-metering record. $275k realized average per campus engagement is my estimate within the quoted range.</t>
+        </is>
+      </c>
+      <c r="F2" s="21" t="inlineStr">
+        <is>
+          <t>Fixed-fee per-campus engineering engagement (dynamic model build + disturbance-response testing + attestation package), plus a smaller annual re-validation retainer and a per-campus metering/curtailment-record subscription</t>
+        </is>
+      </c>
+      <c r="G2" s="21" t="inlineStr">
+        <is>
+          <t>The record's own kill_risk names the constraint: 'the binding constraint is one or two humans who can translate IEC 62040-3 UPS transfer behavior into an ISO-acceptable load model, and those people are the scarcest labor in the sector.' Revenue here is headcount, not code. A single senior power-systems engineer can carry roughly 4-6 campus engagements a year once field testing and package assembly are counted, so the ramp is really a hiring curve against the scarcest labour pool in the industry. Y1 = 4 campuses off the free NOGRR 282 gap-assessment funnel with the two founders delivering. Y2-Y5 assumes hiring 4-6 qualified engineers a year and losing some to the incumbents — 45 campuses in Y5 implies ~25-28 billable engineers, which is an aggressive but not fantastical build for a five-year-old boutique. Sales friction itself is unusually low for a regulated buyer because the clock is hard and dated (90-day root-cause / 180-day implementation after any failed ride-through, per the record); the friction is entirely on the delivery side.</t>
+        </is>
+      </c>
+      <c r="H2" s="21" t="inlineStr">
+        <is>
+          <t>MY REASONING. Senior power-systems consultancy bills at roughly 2.2-2.6x fully-loaded engineer cost, which lands gross margin in the mid-40s. COGS carries PSS/E and PSCAD seat licences, field-test travel and on-site disturbance testing, and subcontracted PQ metering work. The PCLR/metering software attach should pull this up a few points by Y4-Y5 but never enough to make it look like a software business — 45% is the honest blended number.</t>
+        </is>
+      </c>
+      <c r="I2" s="21" t="inlineStr">
+        <is>
+          <t>The rate at which you can hire engineers who can translate IEC 62040-3 UPS transfer behaviour into an ISO-acceptable load model. Every dollar of year-5 revenue is a headcount multiple, and the record explicitly warns that Burns &amp; McDonnell, Certrec and POWER 'can hire them away or simply out-bench you.' Hiring 3/year instead of 5/year roughly halves the Y5 number.</t>
+        </is>
+      </c>
+      <c r="J2" s="21" t="inlineStr">
+        <is>
+          <t>The incumbent EPCs lock the top 20 developers under existing master service agreements before the NERC standards land, and the boutique is left with the non-grandfathered mid-market plus the crypto and electrolyzer tail — buyers with worse credit and smaller scopes. Add one senior departure to a competitor in Y2 and the ramp stalls a full year. Y5 lands around 12-15 campuses at a lower average scope, roughly $3.5-4M revenue, and the outcome is an acqui-hire by an EPC at a services multiple.</t>
+        </is>
+      </c>
+      <c r="K2" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="L2" s="21" t="inlineStr">
+        <is>
+          <t>Split confidence. The ACV is quoted directly from the record and I trust it — $150k-$600k per campus is a plausible band for filed dynamic modelling plus attestation. The buyer universe is the weak half: I am converting a raw interconnection-queue GW figure into campus count using an assumed average campus size and an assumed materialization rate, both from recall with no ability to check either. If real materialization is 15% rather than 30%, the universe halves. 5, not 7.</t>
+        </is>
+      </c>
+      <c r="M2" s="10" t="inlineStr">
+        <is>
+          <t>datacenter-as-grid-entity-compliance</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="76" customHeight="1">
+      <c r="A3" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="23" t="inlineStr">
+        <is>
+          <t>Entry Type 13 and instrument-aware duty recovery for the post-de-minimis long tail</t>
+        </is>
+      </c>
+      <c r="C3" s="23" t="inlineStr">
+        <is>
+          <t>The founder or operations lead of an SMB ecommerce importer doing roughly $1-20M/year of imported goods on Shopify, WooCommerce or Amazon, who has never spoken to a licensed broker and now needs a real entry filed per inbound shipment. Reached through the 3PL and freight forwarder who is currently declining their account. For the recovery product, the same person or the controller at a slightly larger mid-market importer.</t>
+        </is>
+      </c>
+      <c r="D3" s="23" t="inlineStr">
+        <is>
+          <t>MY REASONING/RECALL, not researched. My recollection is that CBP has historically counted on the order of 200,000-250,000 active importers of record filing entries annually. The record states de minimis ended for all countries on 29 August 2025 and that 'FY2024 saw over 1.36 billion de minimis packages enter the US,' which forces a large population of merchants who never filed an entry into the formal system for the first time. Against that expanded pool I discount hard to the subset that is (a) SMB rather than enterprise, (b) not already captive to a parcel carrier's own entry service, and (c) reachable through a Shopify app or 3PL referral. That gives ~150,000. This is a structural estimate with a wide error bar.</t>
+        </is>
+      </c>
+      <c r="E3" s="23" t="inlineStr">
+        <is>
+          <t>Partly quoted, mostly mine. The record states the price point directly — 'a flat per-entry price well under the incumbent $50-100' and 'at $15/entry' — so I anchor on $15/entry. The volume assumption is entirely MY REASONING: I assume a median account files ~350 entries/year (consolidated inbound shipments plus direct-ship parcels that no longer clear on a manifest), giving ~$5,250 of transaction revenue, plus roughly $2,000/year for the SKU classification catalogue subscription, plus a blended contribution from flat-fee drawback/CAPE recovery engagements sold to a minority of accounts. Rounds to $8,000.</t>
+        </is>
+      </c>
+      <c r="F3" s="23" t="inlineStr">
+        <is>
+          <t>Per-entry transaction fee (~$15/entry, quoted from record) plus an annual SaaS subscription for the classified SKU catalogue and ruling corpus; flat-fee duty recovery engagements attached, deliberately priced against 50/50 contingency incumbents</t>
+        </is>
+      </c>
+      <c r="G3" s="23" t="inlineStr">
+        <is>
+          <t>Two forces pull in opposite directions. Pulling fast: this is genuinely self-serve PLG through a Shopify/marketplace app with a legislated forcing function and a 3PL channel that is actively turning these accounts away, so acquisition cost per account is low and the buyer is not procurement-gated. Pulling slow: the record's own kill_risk states 'the ACE ABI certification gate is a 6-12 month regulatory slog, not part of a 90-day plan,' so Y1 is a partial year with only 35 accounts even if you file through a partner broker's existing ABI connection at first. From Y2 the CBP Entry Type 13 voluntary test (22 September 2026, quoted) plus the 1 July 2027 permanent statutory repeal give two hard demand events. Y5 at 3,000 accounts is 2% of my estimated universe — deliberately modest, because 3,000 accounts x 350 entries is ~1.05M entries/year, which even at the record's claimed '50-100x' leverage needs 3-4 licensed brokers supervising, and every one of those entries carries 19 CFR 111 penalty exposure on SKUs nobody has physically seen.</t>
+        </is>
+      </c>
+      <c r="H3" s="23" t="inlineStr">
+        <is>
+          <t>MY REASONING. This is not an 80% software business. Per-entry COGS carries continuous bond amortisation, ABI transmission or service-bureau fees, and — the binding item — licensed-broker review time on a meaningful fraction of entries. At $15/entry the all-in labour and filing cost must stay under roughly $4-5 for the model to survive, which is precisely the kill risk the record names. 62% blends the higher-margin catalogue subscription and flat-fee recovery work against thin per-entry economics.</t>
+        </is>
+      </c>
+      <c r="I3" s="23" t="inlineStr">
+        <is>
+          <t>Entries per account per year. Everything else is second order. At $15/entry, whether the median SMB importer generates 100 entries or 1,000 is a 10x swing in ACV and turns this from a $3M business into a $45M one. Nothing in the record pins this number and I could not look it up. If it is 100, the unit economics collapse exactly the way the kill_risk predicts — 'a $500 shipment cannot carry compliant entry work at any price.'</t>
+        </is>
+      </c>
+      <c r="J3" s="23" t="inlineStr">
+        <is>
+          <t>DHL, UPS and FedEx bundle their own de minimis replacement entry service at near-zero incremental price to the merchant because they already own the flow and amortise it across the parcel network, and Zonos moves down-market faster than you acquire the tail. You win only merchants not attached to a big carrier programme, and you win them at a lower price. Add one CBP penalty action on a misclassified SKU and the broker-of-record co-founder walks. Y5 lands ~600 accounts at ~$5,000 ACV, roughly $3M revenue, and the business is a small brokerage with a nice UI.</t>
+        </is>
+      </c>
+      <c r="K3" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="L3" s="23" t="inlineStr">
+        <is>
+          <t>The price point is quoted from the record and is credible. Both other inputs are guesses: the buyer universe is recall-based and the entries-per-account figure — which drives ACV entirely — is pure inference with no anchor at all. The record itself flags that its own CAPE and SCOTUS figures were unverified by the scout ('VERIFY BEFORE ACTING'), so even the demand-side evidence is soft. 4.</t>
+        </is>
+      </c>
+      <c r="M3" s="12" t="inlineStr">
+        <is>
+          <t>long-tail-customs-entry-and-duty-recovery</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="76" customHeight="1">
+      <c r="A4" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="21" t="inlineStr">
+        <is>
+          <t>NQA-1 qualification and commercial grade dedication as a service</t>
+        </is>
+      </c>
+      <c r="C4" s="21" t="inlineStr">
+        <is>
+          <t>The quality director or VP of operations at a privately-held precision manufacturer — machine shop, forge, valve maker, cable house, 50-400 employees — that already holds AS9100 or ISO 9001, is chasing SMR or submarine-industrial-base RFQs, and cannot bid safety-related work without an audited Appendix B / NQA-1 programme. Second buyer, higher margin: the component engineering or supply chain manager at an operating nuclear plant or an advanced reactor developer buying commercial grade dedication per lot on named obsolete or long-lead items.</t>
+        </is>
+      </c>
+      <c r="D4" s="21" t="inlineStr">
+        <is>
+          <t>Derived from a figure quoted in the record plus MY REASONING. The record states the submarine supplier base 'has contracted from 17,000 to about 5,000 since the Cold War' and that BlueForge is running '169 supplier projects totaling $648M across 32 states.' Of that ~5,000-firm naval base I assume roughly 15% (~750) sit at the qualification frontier — precision fabricators plausibly able and willing to install an Appendix B/NQA-1 system rather than staying a commercial-grade sub-tier. To that I add several hundred commercial-nuclear and SMR supply-chain entrants (each serious reactor developer needs 50-200 qualified suppliers, and there are perhaps 10-15 serious developers with overlapping supplier sets). I also fold in the CGD-side buyers — roughly 28 US operating-plant owners plus reactor developers and their tier-1s — as a smaller, higher-value segment inside the same number. Rounds to ~1,200.</t>
+        </is>
+      </c>
+      <c r="E4" s="21" t="inlineStr">
+        <is>
+          <t>Anchored on the record's quoted price: 'deliver the QA manual, procedure set and a mock audit for roughly $75-150k per shop plus an ongoing audit retainer.' I take ~$110k for the initial readiness sprint, blended down against steady-state accounts paying ~$40k/year in audit retainer plus per-lot dedication fees (my estimate: $8-25k per dedication package, with an active plant running 10-40 a year). A growing book skews toward new accounts, so the portfolio average lands near $95k.</t>
+        </is>
+      </c>
+      <c r="F4" s="21" t="inlineStr">
+        <is>
+          <t>Fixed-fee per-shop Appendix B / NQA-1 readiness sprint, converting to an annual audit retainer; separately, per-lot commercial grade dedication fees and a per-seat CGD workbench subscription for reactor developers and their top suppliers</t>
+        </is>
+      </c>
+      <c r="G4" s="21" t="inlineStr">
+        <is>
+          <t>Y1 = 5 is taken straight from the record's own 90-day plan: 'a fixed-price Appendix B readiness sprint sold to five non-nuclear precision shops in Tennessee, Ohio and the Carolinas.' That is the right order of magnitude — a single ex-NUPIC lead auditor can carry maybe 6-8 readiness sprints a year, so early years are auditor-count-limited exactly like the datacentre business. Buyer friction is real but different in kind: these are small owner-operated manufacturers spending $110k of their own money on a capability they have no order for yet, so the sale is speculative-capex-shaped and slow, but the cheque is small enough that one person can approve it without a board. The record notes 'qualification takes 12-36 months, so shops that start in 2026 are the ones with capacity when first-of-a-kind SMR fabrication and fleet orders land in 2028-2031,' which means the urgency is real but back-loaded — Y3-Y5 is where the pipeline actually opens. 65 accounts in Y5 is ~5% of my estimated universe.</t>
+        </is>
+      </c>
+      <c r="H4" s="21" t="inlineStr">
+        <is>
+          <t>MY REASONING. Ex-NUPIC lead auditors and supplier quality managers are expensive and fully utilised at maybe 60-65% billability once travel and mock audits are counted; on-site audit travel is direct COGS. This prices out around 45%, i.e. hourly-consulting economics, exactly as the record's kill_risk predicts ('margins stay at hourly-consulting levels'). The CGD workbench should lift this into the low 50s by Y5 only if the critical-characteristics library actually accretes across buyers — which the same kill_risk argues it will not.</t>
+        </is>
+      </c>
+      <c r="I4" s="21" t="inlineStr">
+        <is>
+          <t>Whether shops will buy qualification ahead of holding an award. Every readiness sprint is speculative spending by a manufacturer with no nuclear order in hand. If SMR first-of-a-kind fabrication slips past 2030 — which is the base rate for nuclear schedules — the shops defer, the pipeline stalls, and the ramp flattens from Y3 onward regardless of how good the product is.</t>
+        </is>
+      </c>
+      <c r="J4" s="21" t="inlineStr">
+        <is>
+          <t>SMR FOAK schedules slip two years, DOE pilot funding thins, and the machine shops simply will not spend $110k on a capability with no revenue attached. You are left with naval work, which is gated through BlueForge and NAVSEA primes on their terms and their timelines, while Curtiss-Wright or Paragon bolt a workflow tool onto an existing book of business and a dedicating-entity audit history. Y5 lands around 20 accounts at a lower average scope, roughly $1.6-1.8M revenue — a viable three-person consultancy, not a venture outcome.</t>
+        </is>
+      </c>
+      <c r="K4" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="L4" s="21" t="inlineStr">
+        <is>
+          <t>ACV is quoted directly from the record and is the most credible number in this projection. The universe is a chain of my own inferences off one quoted figure (the ~5,000-firm submarine base), and the 15%-at-the-frontier assumption is a judgement call I cannot check. The commercial-nuclear supplier count is closer to a guess. 5.</t>
+        </is>
+      </c>
+      <c r="M4" s="10" t="inlineStr">
+        <is>
+          <t>nuclear-naval-supplier-qualification</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="76" customHeight="1">
+      <c r="A5" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t>PFAS-Compliant Biosolids Outlet Exchange for the Mid-Atlantic</t>
+        </is>
+      </c>
+      <c r="C5" s="23" t="inlineStr">
+        <is>
+          <t>The utility director or plant operations manager at a mid-size municipal wastewater authority (roughly 10-25 MGD) in Maryland, Pennsylvania, Virginia or Delaware whose land-application contractor has just told them the 2028 threshold is a problem. The purchase is a one-year firm per-wet-ton disposal agreement, which in most authorities means an RFP and a board or commission vote, not a signature.</t>
+        </is>
+      </c>
+      <c r="D5" s="23" t="inlineStr">
+        <is>
+          <t>MY RECALL AND REASONING, not researched — this is the weakest universe in the batch. My recollection is that there are roughly 16,000 publicly owned treatment works in the US, of which the large majority are too small to have a real biosolids logistics problem; plants above ~1 MGD number perhaps 3,000-3,500. The record scopes the business to the Mid-Atlantic and names the states where the regulatory clock has actually started — Maine, Connecticut, Maryland ('SB 719, signed 28 April 2026 ... from 1 October 2028'), Washington (two laws), Rhode Island, Oregon, Wisconsin, with Pennsylvania pending. Taking buyable-size plants across the Mid-Atlantic plus those named states gives roughly 900. I have no way to verify the POTW size distribution I am relying on.</t>
+        </is>
+      </c>
+      <c r="E5" s="23" t="inlineStr">
+        <is>
+          <t>MY REASONING — the record states no price point anywhere, which is itself telling. I model the broker's retained cut, not the GMV flowing through. A mid-size authority at ~50 wet tons/day is ~18,000 wet tons/year; my recall puts landfill disposal with hauling at roughly $60-90/wet ton and thermal destruction far higher, so the contract GMV is on the order of $1.4-1.6M/year per POTW. A brokerage retaining ~12-13% of contract value on a firm-price basis nets roughly $180k, and I add a blended contribution from the source-control audit (the record's stickier second product) to reach $200,000 of retained revenue per POTW per year. Every input in that chain is mine.</t>
+        </is>
+      </c>
+      <c r="F5" s="23" t="inlineStr">
+        <is>
+          <t>Firm per-wet-ton price to the POTW against contracted outlet and haul cost — revenue booked as the retained spread, not the gross contract value; plus one-off industrial source-control audits</t>
+        </is>
+      </c>
+      <c r="G5" s="23" t="inlineStr">
+        <is>
+          <t>I am explicitly discounting the record's own plan, which proposes to 'sell 10 mid-size POTWs a firm per-wet-ton price' inside 90 days. Municipal procurement does not move that way: an RFP cycle plus board approval plus a bonding requirement is 6-12 months from first conversation to first ton hauled, and the buyer has no personal urgency until their incumbent contractor actually gives notice. Y1 = 4 authorities. The offsetting force is that once landed, these contracts renew and the reference value inside a state's utility-director community is unusually high — wastewater directors talk to each other constantly through state associations, so Y2-Y4 referral compounding is real. Y5 at 42 POTWs is ~5% of my estimated universe and represents roughly $70M of GMV under management, which is a credible regional broker but not a national one. I hold it there because the record's defensibility score is 4 and Synagro and Denali can price-match any regional entrant.</t>
+        </is>
+      </c>
+      <c r="H5" s="23" t="inlineStr">
+        <is>
+          <t>MY REASONING. Because revenue is booked as the retained spread rather than gross contract value, the COGS line is dispatch coordination staff, PFAS sampling and compliance documentation, and — the item that actually bites — absorbed cost overruns when an outlet reprices mid-contract against a firm price you already quoted. 55% on the retained spread. Note this is not comparable to a 55% services margin: the underlying business moves roughly 7x this revenue in gross contract value at near-zero net margin.</t>
+        </is>
+      </c>
+      <c r="I5" s="23" t="inlineStr">
+        <is>
+          <t>The retained spread per wet ton. Customer count barely matters by comparison. If Synagro or Denali price-match — which the record's kill_risk says they can, since 'non-exclusive outlet contracts, zero capex, and no proprietary data mean Synagro or Denali can match any quoted per-wet-ton price' — the spread compresses from ~$10/ton toward ~$3/ton and year-5 revenue falls by two-thirds against an identical customer list.</t>
+        </is>
+      </c>
+      <c r="J5" s="23" t="inlineStr">
+        <is>
+          <t>Two ways this goes wrong at once. The arbitrage decays on schedule: Maryland's thresholds are already numbers in statute, so 'knowing which outlet accepts which concentration this quarter' stops being knowledge and becomes a lookup table. Meanwhile the landfill airspace you forward-contracted gets closed to biosolids by the next state action, leaving you holding firm-price obligations against outlets that no longer exist — the working-capital risk the record names. Y5 lands ~25 authorities at ~$80k retained, roughly $2M revenue, and the business is a regional hauling broker with a compliance binder.</t>
+        </is>
+      </c>
+      <c r="K5" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="L5" s="23" t="inlineStr">
+        <is>
+          <t>Genuinely low and I am not hedging it upward. The record states no price point at all, so the entire ACV is built from my recalled per-wet-ton disposal costs, my assumed plant tonnage, and my assumed take rate — three uncertain numbers multiplied together. The POTW universe rests on a recalled size distribution I cannot check. Only the regulatory dates are solid, and dates do not price a contract. 3.</t>
+        </is>
+      </c>
+      <c r="M5" s="12" t="inlineStr">
+        <is>
+          <t>biosolids-outlet-exchange</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="76" customHeight="1">
+      <c r="A6" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>Reachability-grade SBOMs and kernel-CVE triage for embedded Linux</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>The VP of Engineering or product security officer at an embedded device maker placing products on the EU market — industrial controls, medical-adjacent devices, networking gear, building automation — typically a 200-3,000 person manufacturer that owns its own CE-marking technical file and has to declare a support period for a named device family. The trigger is an integrator or distributor sending them a CRA questionnaire they cannot answer.</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>MY REASONING/RECALL, not researched. The CRA nominally covers every manufacturer of products with digital elements sold into the EU — my recollection of EU impact assessments puts that in the tens of thousands of firms. But this product only serves a narrow slice: makers of embedded-Linux devices with a Yocto/Buildroot/PetaLinux BSP and an actual kernel to triage, who are large enough to pay a per-device-family annual subscription rather than punting the problem to their SoC vendor or ignoring it. I estimate that subset at ~6,000 companies globally. The record supplies the demand-side dates but no company count, so this number is mine and it is soft in both directions.</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>Pricing UNIT is quoted from the record — 'Charge per device family per year ... a maintenance annuity attached to hundreds of millions of shipped units.' The price LEVEL is MY REASONING: triaging the record's stated 'roughly fifty CVEs a week with no severity scores' across one device family consumes maybe 0.25-0.4 FTE of a senior embedded engineer, i.e. $60-100k of loaded cost. Priced at roughly a quarter of the displaced cost gives ~$22k per device family per year. I assume ~2.5 families per account at steady state (land one family, expand), giving $55,000 ACV.</t>
+        </is>
+      </c>
+      <c r="F6" s="21" t="inlineStr">
+        <is>
+          <t>Annual SaaS subscription per device family, with a free wedge (legacy-firmware SBOM extraction and BSI TR-03183-2 scoring of whatever SBOM the customer already has) and paid tiers for field enrichment, signed attestations and the technical-documentation artifacts</t>
+        </is>
+      </c>
+      <c r="G6" s="21" t="inlineStr">
+        <is>
+          <t>This is the only clean annual-subscription business in the batch and the ramp reflects that, but it is still an engineering-org sale with a security budget behind it, not self-serve. The dated forcing function is unusually good: reporting duties start 11 September 2026 and 'apply to products already on the market,' with full application and CE marking on 11 December 2027 (both quoted from the record), so Y2 spans the hardest deadline and is where the step change happens. Y1 = 8 is deliberately small because the record's own kill_risk is right that 'kernel .config reachability indexing plus SBOM extraction from raw firmware binaries is a multi-year engineering problem to do at defensible quality, not a quarter' — Y1 accounts are effectively design partners on one SoC family. Each additional SoC family is an engineering project, which is what caps Y3-Y5 growth rather than sales capacity. 320 accounts in Y5 is ~5% of my estimated universe, or roughly $17.6M ARR.</t>
+        </is>
+      </c>
+      <c r="H6" s="21" t="inlineStr">
+        <is>
+          <t>MY REASONING. Software delivery, but three things hold it below the 85% software ceiling: a human security analyst has to review emitted VEX justification strings before they ship, because each one is a legal assertion the customer signs; per-BSP and per-SoC-family onboarding is real engineering effort booked against the account; and daily CVE feed processing across hundreds of device families is a genuine compute line. 75%.</t>
+        </is>
+      </c>
+      <c r="I6" s="21" t="inlineStr">
+        <is>
+          <t>Whether SoC vendors and BSP houses bundle CVE triage into the board support package. The record names this precisely — 'the SoC vendor, Timesys/Lynx, Wind River or Qualcomm/Foundries bundles CVE triage with the board support package the customer is already paying for, so you are selling an add-on against something included.' If they bundle, the addressable universe collapses to companies with legacy or in-house BSPs, maybe a third of my estimate, and the per-family price falls from $22k toward $8k. That single variable moves Y5 revenue by roughly 6x.</t>
+        </is>
+      </c>
+      <c r="J6" s="21" t="inlineStr">
+        <is>
+          <t>Bundling happens on the vendors' 2027 roadmaps, and separately a market surveillance authority rejects 'not exploitable: subsystem not compiled in' as an adequate VEX justification — at which point the differentiated output is worthless and you retreat to being an SBOM generator and technical-file assembler competing with free tooling. Price falls to ~$10k/account. Y5 lands ~90 accounts, roughly $1M ARR, and the company is an acquisition target for whoever ships the BSP.</t>
+        </is>
+      </c>
+      <c r="K6" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="L6" s="21" t="inlineStr">
+        <is>
+          <t>The regulatory dates and the pricing unit are quoted and solid. The price level is my inference from displaced engineer cost — defensible but unverified — and the buyer universe is a genuine estimate with no anchor in the record at all. I am also aware that 'embedded Linux makers who will actually pay' is exactly the kind of number people talk themselves into overestimating. 4.</t>
+        </is>
+      </c>
+      <c r="M6" s="10" t="inlineStr">
+        <is>
+          <t>cra-embedded-sbom-and-cve-triage</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="76" customHeight="1">
+      <c r="A7" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t>Funded-Claim Detection for Casualty Reserving</t>
+        </is>
+      </c>
+      <c r="C7" s="23" t="inlineStr">
+        <is>
+          <t>The Head of Casualty Reserving or Chief Claims Officer at a US commercial-casualty / E&amp;S carrier or a casualty reinsurer — the person who owns the adverse-development number in the quarterly reserve review. Budget sits in claims analytics and reserving, and the internal case is made against outside-counsel spend. The record itself names the first customers as 'a handful of casualty reinsurers and excess carriers, who will buy a list long before they will buy an API.'</t>
+        </is>
+      </c>
+      <c r="D7" s="23" t="inlineStr">
+        <is>
+          <t>My own reasoning, not researched — the record states no buyer count. Structure: roughly 150-200 US P&amp;C groups write commercial casualty or E&amp;S liability at a scale where a 4-5% loss-ratio effect is a board-level number, plus roughly 25-30 global casualty reinsurers, plus a few dozen large program/MGA writers and casualty-heavy Bermuda vehicles. I round the realistically-signable set to 250. I am NOT counting the ~1,000 US P&amp;C insurance groups in total, most of which write personal lines or property and have no casualty reserving problem to solve.</t>
+        </is>
+      </c>
+      <c r="E7" s="23" t="inlineStr">
+        <is>
+          <t>My own reasoning and recall, not researched. The record states no price. Recalled comparable band: enterprise insurance-data and litigation-analytics subscriptions (Verisk analytics modules, Lex Machina/Bloomberg Law enterprise seats, ISO circulars) sit roughly $50k-$300k per year. A single-signal product lands mid-low in that band. I model the wedge product — the quarterly funder-intelligence report the record proposes — at roughly $50k-$60k, and the productized FNOL claim-scoring feed at roughly $175k-$250k for a top-30 carrier, blending to $125k as the mix shifts toward scoring in years 3-5.</t>
+        </is>
+      </c>
+      <c r="F7" s="23" t="inlineStr">
+        <is>
+          <t>Annual data subscription. Year 1-2 is a quarterly intelligence report at roughly $50k/yr; years 3-5 is a claim-scoring API/feed priced by claim volume at roughly $175k-$250k/yr, with the report retained as the entry SKU.</t>
+        </is>
+      </c>
+      <c r="G7" s="23" t="inlineStr">
+        <is>
+          <t>Carriers do not buy a novel data signal quickly. Year 1 is 3 logos because the record's own plan is a report sold to 'a handful' of reinsurers and excess carriers — that is a founder-led, relationship-by-relationship motion with no reference customers and no proof the signal predicts development. Years 2-3 are gated by the reserving cycle: a carrier needs two to four quarters of the feed running alongside its own development triangles before it will renew at API pricing, so expansion revenue lags logo count by a year. Years 4-5 slow rather than accelerate, because the disclosure wave the record cites as the enabler is simultaneously eroding the need for inference — I do not model a hockey stick into a shrinking problem. Y5 of 36 is 14% of the 250-entity universe, which for a category-defining niche data product with two or three plausible incumbents in the way is at the top of defensible.</t>
+        </is>
+      </c>
+      <c r="H7" s="23" t="inlineStr">
+        <is>
+          <t>My own reasoning. Real COGS here are third-party docket and court-record licensing, UCC-1 bulk data, PACER fees, and — critically — the analyst hours to hand-verify entity resolution through shell layers before anything ships to a carrier, because a false positive on a named funder is a legal problem. Year 1-2 is effectively a research service at roughly 50-55%. As entity resolution automates, the mature blend lands near 65% — below a clean software business, above a services one.</t>
+        </is>
+      </c>
+      <c r="I7" s="23" t="inlineStr">
+        <is>
+          <t>Whether case-level linkage actually works — i.e. whether the product can say 'this specific claim is funded' rather than only 'this plaintiff firm has a portfolio funding relationship.' The record's own kill_risk concedes the linkage is 'the hard, unsolved part.' Firm-level-only output is a $40-60k list forever and caps Y5 revenue near $2M; per-claim scoring at FNOL is a $200k+ feed and is the entire difference between a $2M and a $7M business.</t>
+        </is>
+      </c>
+      <c r="J7" s="23" t="inlineStr">
+        <is>
+          <t>Bear case has two legs and they compound. First, federal disclosure lands — S.3826 passes or ISO's Litigation Funding Disclosure Condition endorsement becomes standard — and by 2029 carriers get funder identity for free, so inference is worth little and renewals convert to churn. Second, the UCC-1 mechanic resolves only firm-level portfolio funding, so the product never earns API pricing. In that world the company plateaus at roughly 15-20 report subscribers at $45k, i.e. Y5 revenue of $700k-$900k, and the honest outcome is a small acqui-hire into Verisk or a claims-analytics vendor rather than a standalone business.</t>
+        </is>
+      </c>
+      <c r="K7" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="L7" s="23" t="inlineStr">
+        <is>
+          <t>Low. I have no search access this session and the record supplies neither a buyer count nor a price point, so both load-bearing numbers are my own reasoning against recalled comparables. The buyer universe I would defend within roughly ±40%. The ACV I would defend less well, because it hinges entirely on the unresolved case-linkage question — the same $125k figure is either conservative or 3x too high depending on a technical fact the record admits is unsolved. I am not at 3 only because the insurance-data pricing band is something I recall with reasonable confidence.</t>
+        </is>
+      </c>
+      <c r="M7" s="12" t="inlineStr">
+        <is>
+          <t>funded-claim-detection-for-casualty</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="76" customHeight="1">
+      <c r="A8" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>Forward exchange for transformer and switchgear production slots</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>Two-sided, but the fee is paid out of the transaction by the acquiring side: the VP of Procurement or Director of Electrical Equipment Sourcing at a datacenter developer, EPC, IPP or BESS developer who needs a 2028-2029 transformer or switchgear delivery slot and cannot absorb the record's stated '75-110 weeks' for substation transformers or '100-150+ weeks' for GSUs. The motivated counterparty is the seller — a development VP at a company with a cancelled site sitting on a forfeited 10-30% deposit — but the buyer is who signs, because the slot is worth more than par to them and nothing to the seller.</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>Partly stated, partly my own reasoning. The record states the sell side directly: 'cold-call the roughly 200 datacenter, BESS and utility developers with cancelled or delayed projects.' The buy side is not stated; I estimate it at roughly 3x the distressed sell side — US datacenter developers and hyperscaler build arms, EPCs, investor-owned and municipal utilities, IPPs and BESS developers that procure medium- and high-voltage iron. I use 600 as the count of entities that could plausibly transact at least once over five years, which is my own structural estimate and the softest number in this projection.</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="inlineStr">
+        <is>
+          <t>Anchored on a figure the record states, with my own reasoning for the rest. The record states the take rate: 'take 2-4%' and 'match to buyers, take 2-4% and escrow the deposit.' I use 3%. The transaction size is my own estimate, not researched: I assume an average assigned package of roughly $6M of equipment — a substation-scale transformer plus associated switchgear, consistent with the record's framing of slots held 'against a 10-30% deposit' on multi-million-dollar orders. 3% of $6M is $180k per assignment; I assume roughly 1.2 assignments per active counterparty per year, giving $220k. Note this is revenue per transacting counterparty per year, not a contracted subscription — see revenue_quality.</t>
+        </is>
+      </c>
+      <c r="F8" s="21" t="inlineStr">
+        <is>
+          <t>Transaction fee — 3% of assigned slot value (record states a 2-4% band), collected at assignment close, with escrow on the transferred deposit. A data/subscription layer (the forward curve on MVA by delivery quarter) is a later second line and I do not model separate revenue for it.</t>
+        </is>
+      </c>
+      <c r="G8" s="21" t="inlineStr">
+        <is>
+          <t>The record's own 90-day goal is '10 closed assignments' — I treat that as optimistic for a cold-start brokerage and model 8 transacting counterparties in year 1, since each trade needs a distressed seller, a matched buyer, an OEM willing to consent to assignment, and lawyers on both sides. Growth in years 2-3 is limited by the fact that this is a two-sided cold-call desk with no product: each incremental trade is founder-brokered, and headcount is the constraint. Years 4-5 accelerate modestly as the listing and verification product and repeat counterparties reduce per-trade effort. I deliberately do not model exponential growth, because the pool of orphaned slots is finite and self-liquidating — every trade removes inventory, and the record's why_now dates the peak of the orphaned pool at 2029-2031, i.e. right at Y4-Y5. Y5 of 78 is 13% of the 600-entity universe.</t>
+        </is>
+      </c>
+      <c r="H8" s="21" t="inlineStr">
+        <is>
+          <t>My own reasoning. This is a brokerage, and brokerage gross margin is governed by whether the closers are commissioned. Once the desk scales past the founders, the dealmakers who source distressed slots and work OEM order desks take a meaningful cut of each fee; add third-party escrow agent fees and outside counsel on assignment paperwork per trade. Industrial capital-goods brokerage of this shape runs roughly 45-60%. I use 55%, with the mature blend improving only if the forward-curve data product attaches — which I have not modelled as revenue and therefore do not credit in margin.</t>
+        </is>
+      </c>
+      <c r="I8" s="21" t="inlineStr">
+        <is>
+          <t>OEM consent rate on assignment. The record's kill_risk states it plainly: 'Standard supply agreements carry anti-assignment/anti-delegation clauses and non-refundable staged deposits; once an OEM learns a slot is worth more than the contract price it has every incentive to cancel, keep the deposit and re-sell at market itself.' Every dollar of this model passes through that consent. If OEMs consent to most assignments the business exists; if they systematically refuse and recapture the spread themselves, the business is zero — not small, zero. This is the single variable and it is binary, not continuous.</t>
+        </is>
+      </c>
+      <c r="J8" s="21" t="inlineStr">
+        <is>
+          <t>Two independent bear legs. (1) OEMs refuse assignment or convert consent into a fee they capture, and the desk degrades into an introduction service paid on goodwill; effectively no business. (2) The phantom-demand premise fails — the record itself flags that SemiAnalysis published a rebuttal to the cancellation statistic the thesis rests on — so orphaned slots never accumulate and there is nothing to clear. In the softer version where OEMs consent selectively and the orphan pool is half the assumed size, this is a 25-30 trade-per-year niche brokerage doing roughly $4-5M of revenue at Y5 with no data moat, which is a decent lifestyle business and not a venture outcome.</t>
+        </is>
+      </c>
+      <c r="K8" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="L8" s="21" t="inlineStr">
+        <is>
+          <t>Middling. The take rate is quoted from the record and the sell-side count is quoted from the record, which is more grounding than the other four opportunities have. What I cannot support is the average transaction size ($6M of equipment) or the trades-per-counterparty rate — both are my own estimates with no verification, and Y5 revenue moves roughly linearly with each. I would also note the record's own warning that 'six of the ten cited URLs are x.com posts,' meaning the underlying demand statistics I am building on are weakly sourced even within the record. Not higher than 5 because the OEM-consent risk is existential and unquantified.</t>
+        </is>
+      </c>
+      <c r="M8" s="10" t="inlineStr">
+        <is>
+          <t>grid-equipment-slot-forward-exchange</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="76" customHeight="1">
+      <c r="A9" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>Key-state custody for LMS/XMSS firmware signing under CNSA 2.0</t>
+        </is>
+      </c>
+      <c r="C9" s="23" t="inlineStr">
+        <is>
+          <t>The firmware or product-security lead — secure-boot architect, PSIRT owner, or VP of Product Security — at a defense-industrial-base embedded OEM or an ODM that signs firmware on an OEM's behalf. The record identifies the trigger precisely: organisations 'who have just found CNSA 2.0 flow-down clauses in contracts or are failing CNSA 2.0 questions in RFPs.' Budget is product engineering and compliance, not the CISO's IT-security line, which matters because product-security budgets are smaller and tied to specific programme wins.</t>
+        </is>
+      </c>
+      <c r="D9" s="23" t="inlineStr">
+        <is>
+          <t>My own reasoning, not researched — the record states no count. Structure: this is not the whole DIB (tens of thousands of registered contractors), it is only organisations that generate signing keys for firmware or bootloaders on National Security Systems or on kit sold into them. I count roughly 20 primes, roughly 150 tier-1 defense electronics and avionics/radio/sensor makers, roughly 100 silicon vendors and ODMs doing signing-as-a-service, and roughly 300 industrial/embedded OEMs with enough government exposure to inherit flow-down. That is 570, which I round to 600. The record's own market_size score of 4 out of 10 is consistent with a universe this narrow, and I treat that as corroboration rather than independent evidence.</t>
+        </is>
+      </c>
+      <c r="E9" s="23" t="inlineStr">
+        <is>
+          <t>My own reasoning and recall, not researched. The record states no price. Recalled comparable band: enterprise code-signing and key-management platforms (Keyfactor Signum, Venafi/CyberArk CodeSign Protect, DigiCert software-trust products, Entrust signing services) sit roughly $50k-$250k per year for a mid-sized enterprise. A CNSA 2.0-specific state custodian is narrower than those but sells into a mandatory, high-consequence, audit-evidenced use case, so it holds mid-band rather than discounting. I model $110k as a blend of roughly $60-75k for a single-product-line embedded OEM and roughly $200k+ for a prime or ODM running many parallel CI signing pipelines, plus attach revenue on the audit report.</t>
+        </is>
+      </c>
+      <c r="F9" s="23" t="inlineStr">
+        <is>
+          <t>Annual SaaS subscription for the hosted multi-region control plane, tiered by number of reserved subtrees / concurrent signing pipelines rather than seats, with the SP 800-208 index-reuse audit report as a paid attach. The open-source state manager and 'state fork detector' the record describes are free and are the pipeline, not revenue.</t>
+        </is>
+      </c>
+      <c r="G9" s="23" t="inlineStr">
+        <is>
+          <t>Two frictions dominate and they pull in opposite directions from the usual open-source ramp. The open-source wedge generates awareness fast — a state-fork detector that finds a real index reuse is a very loud alarm — but converting that to a hosted control plane means persuading a defense OEM to route its device root-of-trust signing through a startup, which is the single most conservative purchase in embedded engineering. Year 1 of 4 is design partners, probably paid pilots rather than full contracts. The record's why_now gives a hard forcing date — '1 January 2027 is the point where guidance becomes a procurement gate' — so years 2-3 are the real ramp as flow-down clauses hit tier-2 suppliers. Years 4-5 flatten: silicon architected in 2026 ships 2028-2030, so the architecture decisions are already made by then and late entrants have less reason to switch. Y5 of 60 is 10% of the 600-entity universe, which I consider defensible for infrastructure that must be chosen before tape-out.</t>
+        </is>
+      </c>
+      <c r="H9" s="23" t="inlineStr">
+        <is>
+          <t>My own reasoning. Software, but with unusually heavy real COGS for a SaaS: FIPS 140-3 Level 3 cloud HSM instances are metered and expensive, and this architecture needs them replicated multi-region for the Raft ledger, so infrastructure cost scales with customers rather than being amortised. Add solutions-engineering hours for Yocto/Zephyr/MCUboot/U-Boot integration work, which the record correctly identifies as 'the adoption surface' and which in practice means a human on every onboarding, plus the human hours to produce each audit report. That pulls this below the 80-85% a clean SaaS would post. 72%.</t>
+        </is>
+      </c>
+      <c r="I9" s="23" t="inlineStr">
+        <is>
+          <t>Whether NSA permits stateless ML-DSA for firmware signing. The record states 'NSA has signaled it anticipates permitting stateless ML-DSA for firmware signing in future CNSA 2.0 guidance.' If that lands, the crash-consistent distributed-state problem stops being mandatory and buyers pick the algorithm that has no state to custody. Nothing else in the model matters as much — not price, not ramp, not the universe count — because this is a compliance-mandated purchase and the mandate is the product.</t>
+        </is>
+      </c>
+      <c r="J9" s="23" t="inlineStr">
+        <is>
+          <t>If ML-DSA is permitted in 2027-2028, the market does not shrink gradually, it evaporates for new designs: every architect choosing in that window picks stateless, and only the cohort that already committed to LMS/XMSS remains as customers. That leaves perhaps 15-25 accounts, plateauing near $2M of revenue with no growth path, and the record correctly notes 'the narrow NSS/DIB buyer base means there is no adjacent market large enough to absorb the pivot.' Realistic outcome in that world is an acqui-hire into Keyfactor, DigiCert or Entrust for the team and the open-source project. A milder bear case — mandate holds but procurement demands FedRAMP or an IL-level authorisation before anyone routes production signing to a hosted plane — pushes first meaningful revenue out 12-18 months and roughly halves the Y5 figure.</t>
+        </is>
+      </c>
+      <c r="K9" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="L9" s="23" t="inlineStr">
+        <is>
+          <t>Low. Both load-bearing numbers are mine: the 600-entity universe is a genuine structural guess built from recalled rough counts of primes and defense-electronics suppliers, and I would not defend it within better than ±50%. The ACV rests on a recalled pricing band for adjacent code-signing products, which I hold with moderate confidence, applied to a product with no comparable — I could be a factor of two off in either direction. I am at 4 rather than 3 because the buyer is unusually well-specified and the forcing dates in the record are concrete, but the ML-DSA risk means even a correct model may be modelling a market that does not exist in three years.</t>
+        </is>
+      </c>
+      <c r="M9" s="12" t="inlineStr">
+        <is>
+          <t>stateful-hash-signature-key-state-custody</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="76" customHeight="1">
+      <c r="A10" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>Copper sunset triage for fire-alarm, elevator and area-of-refuge lines</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
+        <is>
+          <t>The VP of Facilities or the director of life-safety compliance at a multi-building portfolio owner facing mandatory inspection cycles — the record names them: 'hospital systems, school districts, senior living operators, REITs.' The precise person is whoever signs the fire marshal's re-inspection paperwork and would personally own a failed inspection. Fire-alarm integrators and elevator maintenance companies are the referral channel, not the payer; the record is explicit that they 'will refer deals to get the paperwork off their desks.'</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t>My own reasoning, not researched — the record states no buyer count. Structure, from recalled US institutional counts: roughly 1,100 hospital systems (covering ~6,100 hospitals), roughly 13,000 K-12 school districts, roughly 2,000 multi-site senior-living and skilled-nursing operators, roughly 2,500 higher-ed institutions, and roughly 1,500 commercial REITs and large property managers. That sums near 20,000; I de-rate to 15,000 for overlap and for organisations with too few buildings to justify a registry subscription. The record's own note that AT&amp;T's November 2026 filing covers 'approximately 90,000 customers across 18 states' is a line count, not a buyer count, and I have not used it as one.</t>
+        </is>
+      </c>
+      <c r="E10" s="21" t="inlineStr">
+        <is>
+          <t>Reasoned from a price the record states. The record states the pain directly: 'POTS line rates are rising more than 30% per year, with single lines reaching $500-$2,700/month.' My own reasoning from there: a portfolio owner with roughly 200 life-safety lines is carrying six figures of annual POTS spend and a hard inspection obligation, so a registry priced at roughly 3-5% of the spend it helps retire is an easy approval. I model roughly $50-70 per line per year for the registry plus per-building documentation-packet fees, landing at $14k for a typical mid-sized portfolio — call it $6-8k for a school district, $25-40k for a large hospital system.</t>
+        </is>
+      </c>
+      <c r="F10" s="21" t="inlineStr">
+        <is>
+          <t>Annual per-line registry subscription (line inventory, NFPA 72 / ASME A17.1 obligation mapping, cutover runbook) with per-building fees for the inspector-ready signed documentation packet. Managed cutover is referred out to integrators, so I model no installation revenue — a referral fee would be upside I have not counted.</t>
+        </is>
+      </c>
+      <c r="G10" s="21" t="inlineStr">
+        <is>
+          <t>This ramps faster than the other opportunities in year 1-3 because the buyer is under a legal clock and the price is small — the record notes the FCC 'cut the notice period from 180 to 90 days,' and a facilities director with 90 days and a fire marshal due does not run a procurement. But it decelerates hard at the end, and that is deliberate. This is a wasting asset: AT&amp;T targets 'effectively full copper retirement by 2029,' so by Y5 (2031) the triggering event has largely passed for the early carriers, gross adds fall, and cut-over customers have no reason to renew a registry for lines that no longer exist. I model net adds peaking in Y4 and shrinking in Y5 as churn from completed migrations offsets new logos. Y5 of 195 is 1.3% of the 15,000-entity universe — low, correctly, because a $14k ACV cannot fund the sales motion needed to penetrate a fragmented institutional base faster than this.</t>
+        </is>
+      </c>
+      <c r="H10" s="21" t="inlineStr">
+        <is>
+          <t>My own reasoning. The data layer is cheap to run but the revenue-bearing deliverable is not: an 'inspector-ready signed documentation packet' implies a qualified human — realistically a fire-protection engineer or NICET-certified reviewer — reviewing and signing, per building, which is senior labour in the loop. Add licensed telecom reference data (LERG / number-portability data) as recurring COGS if the address join is to work at all. Services-with-humans businesses run 35-55%; the data-product layer lifts the blend to 58%.</t>
+        </is>
+      </c>
+      <c r="I10" s="21" t="inlineStr">
+        <is>
+          <t>Whether the phone-number-to-building join can actually be built. The record's kill_risk is blunt about it: 'FCC filings identify wire centers/CLLIs, not addresses, and after number portability you cannot reliably map a phone number to a serving wire center without licensed LERG/porting data, so the free "is my building in the blast radius" checker that drives the whole funnel likely cannot be delivered at the promised fidelity.' The free checker is the entire top of funnel at this ACV. Without it, customer acquisition reverts to outbound sales against a $14k contract, which does not pay for itself — CAC triples and the ramp above is fiction.</t>
+        </is>
+      </c>
+      <c r="J10" s="21" t="inlineStr">
+        <is>
+          <t>Bear case: the join is not buildable at consumer-grade fidelity, so there is no self-serve funnel, and the business degrades into a per-building consulting assessment shop — real work, real margin around 40%, but it scales with headcount and not with data. That version does perhaps 60-80 engagements a year at $10-15k, i.e. Y5 revenue of $800k-$1.1M, and is a good small consultancy rather than a data utility. Compounding risk: even the bull case is time-boxed, since the copper-retirement event is finished for most of the country by 2030-2031, so the terminal question is what the registry renews as once the lines are cut — and the record does not answer it.</t>
+        </is>
+      </c>
+      <c r="K10" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="L10" s="21" t="inlineStr">
+        <is>
+          <t>Low. The universe is entirely my own structural estimate from recalled institutional counts, and while I hold the school-district and hospital-system numbers with reasonable confidence, the de-rate to 15,000 buyers is a judgement call I would not defend within ±50%. The ACV is better grounded — it reasons from a POTS price range the record states explicitly — but the per-line pricing and typical portfolio size are mine. I am not higher because the record's own kill_risk identifies a technical blocker at the exact point where my funnel and therefore my whole ramp lives, and I have no way to check whether LERG licensing solves it affordably.</t>
+        </is>
+      </c>
+      <c r="M10" s="10" t="inlineStr">
+        <is>
+          <t>copper-retirement-life-safety-circuits</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="76" customHeight="1">
+      <c r="A11" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>CUI determination and marking for small defense machine shops</t>
+        </is>
+      </c>
+      <c r="C11" s="23" t="inlineStr">
+        <is>
+          <t>The owner or quality manager at a 20-100 person DoD-subcontracting machine shop preparing for a CMMC Level 2 assessment — the person who signs the assessment cheque and personally fears losing the award. The record proposes the CMMC consultancy as the customer instead, but its own kill_risk argues against that: 'CUI scoping is the most-billed hour in a consultancy's engagement — a tool that automates it cannibalizes the reseller's own revenue.' I therefore model the shop as the payer and the consultancy as a referral channel earning a margin, not as the budget holder.</t>
+        </is>
+      </c>
+      <c r="D11" s="23" t="inlineStr">
+        <is>
+          <t>Partly stated, partly my recall. The record states the shape: 'the certification wave hits the long tail of tens of thousands of small shops across 2027-2029.' My own recall, labelled as such and not researched this session: DoD's CMMC rulemaking analysis estimated on the order of 80,000 entities requiring Level 2 certification. I halve that to 40,000 to reach the subset that actually handles engineering drawings, CAD files and travelers — i.e. shops with a determination problem rather than just an enclave problem. Machine shops, fabricators and small electronics manufacturers, not the services and staffing contractors who also hold Level 2 obligations.</t>
+        </is>
+      </c>
+      <c r="E11" s="23" t="inlineStr">
+        <is>
+          <t>Reasoned from a figure the record states. The record states total burden: 'small contractors face $20k-$100k+ in compliance cost,' and its kill_risk adds the crucial qualifier — 'most of which goes to the enclave, not to determination.' My own reasoning: determination and marking is a slice of that, and a shop will approve roughly $4-6k per year for it on the same authority that approves a CAD seat, without a procurement process. I model $4,800 as an annual subscription rather than a one-time fee, on the reasoning that new customer drawings arrive continuously and each needs a determination — but see downside_note, because the record argues the opposite.</t>
+        </is>
+      </c>
+      <c r="F11" s="23" t="inlineStr">
+        <is>
+          <t>Annual SaaS subscription, roughly $400/month for a single-site shop, sold self-serve or through consultancy referral with a channel margin. Higher tier for multi-site fabricators. No per-determination metering, because the shop needs to run every incoming drawing through it without thinking about cost — metering would suppress exactly the usage that makes it recurring.</t>
+        </is>
+      </c>
+      <c r="G11" s="23" t="inlineStr">
+        <is>
+          <t>This is the only one of the five where volume, not deal size, is the game — at $4,800 nobody runs a procurement, so the constraint is purely distribution. Year 1 of 30 assumes the record's plan half-works: 'land 10 consultancies' delivers a trickle of referrals rather than the 'few hundred shops' the record projects, because of the channel-conflict problem the record itself identifies. Years 2-4 ride the hard regulatory clock — the record dates Phase 2 third-party Level 2 certification from 'around November 2026' ramping 'over three years,' which puts peak demand squarely in 2027-2029, i.e. my Y2-Y4. Year 5 growth decelerates as the certification wave passes its peak and the remaining tail is the smallest, least-equipped shops. Y5 of 1,500 is 3.75% of the 40,000-entity universe — deliberately modest, because at this ACV a long-tail SMB base is won by channel and word of mouth over years, and there is no plausible world where a startup reaches double-digit penetration of 40,000 small manufacturers in five years.</t>
+        </is>
+      </c>
+      <c r="H11" s="23" t="inlineStr">
+        <is>
+          <t>My own reasoning. Mostly software — PDF and CAD title-block parsing, distribution-statement classification — but with two real COGS lines: per-document OCR and model inference on what may be thousands of drawings per onboarding, and disproportionate support load, because the users are shop-floor and quality staff who are not software buyers and will call. The record's kill_risk also predicts the product 'degrades into a workpaper generator with consultant sign-off,' which if true adds a human attestation step and pulls margin down. 74% reflects a real SaaS business carrying that support tax, not the 85% a self-serve developer tool would post.</t>
+        </is>
+      </c>
+      <c r="I11" s="23" t="inlineStr">
+        <is>
+          <t>Blended CAC against a $4,800 ACV — which is really the question of whether the consultancy channel resells or blocks. At this price point the model only works if acquisition is channel-led or self-serve at roughly $2-4k all-in; direct outbound sales to 30-person machine shops costs more than the first year of revenue and the business never becomes viable regardless of how good the product is. Everything else — the universe count, the ramp, the margin — is second-order to this.</t>
+        </is>
+      </c>
+      <c r="J11" s="23" t="inlineStr">
+        <is>
+          <t>Three failure modes and they reinforce each other. (1) Consultancies refuse to resell because it cannibalises their most-billed hour, killing the only affordable acquisition channel. (2) Liability forces a human attestation on every determination, converting the product into a workpaper generator that a consultant charges for, compressing the price to roughly $1,500-2,500. (3) Microsoft Purview is already paid for inside every GCC High seat and becomes the MSP channel's default answer — the record flags this as 'the path of least resistance.' In that world the company lands maybe 500-700 shops at roughly $2,200, i.e. Y5 revenue of $1.1-1.5M, with a demand curve that peaks with the certification wave in 2029 and then declines. Also worth flagging honestly: the record argues this is a one-time purchase — 'scoping happens at engagement start, not monthly, so recurring revenue is unproven' — and I have modelled recurring against that objection. If the record is right, gross revenue holds roughly but net revenue retention falls below 70% and the enterprise value is a fraction of what the ARR implies.</t>
+        </is>
+      </c>
+      <c r="K11" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="L11" s="23" t="inlineStr">
+        <is>
+          <t>Middling, and the highest of the five. The universe is anchored on something the record states ('tens of thousands of small shops') and cross-checked against my recall of DoD's ~80,000 Level 2 estimate, which is a figure I hold with fair confidence though I could not verify it this session. The ACV reasons from a compliance-cost range the record states explicitly, and I am reasonably confident a $4-6k annual tool clears a shop owner's approval threshold. What I cannot support is the revenue shape — recurring versus one-off is the difference between a real SaaS business and a project shop, the record and I disagree about it, and I have no evidence to settle it. Not higher than 5 for that reason and because the channel-conflict risk sits directly on the model's only viable acquisition path.</t>
+        </is>
+      </c>
+      <c r="M11" s="12" t="inlineStr">
+        <is>
+          <t>cui-determination-for-machine-shops</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="76" customHeight="1">
+      <c r="A12" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t>State packaging EPR reporting for mid-market brands</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>The VP Supply Chain or COO at a US mid-market packaged food, beverage or personal-care brand ($20-300M revenue, 50-500 SKUs) that has been named a 'producer' under two or more state packaging EPR laws, has registered with Circular Action Alliance, and has no packaging engineer on staff. At the smaller end the signer is the CFO or founder. Secondary channel buyer: the account manager at a co-packer or packaging distributor who refers a book of brands.</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t>MY OWN REASONING, not researched — the record states no buyer count. Structural estimate: roughly 20,000 US food and beverage manufacturing companies plus ~3,000 household/personal-care companies plus importers and private-label licensees; strip out those below state small-producer exemption thresholds (roughly $1-5M gross revenue depending on state) and strip out the top tier (~500 large brands) that runs this in-house or on Specright/Lorax. Roughly 30-40% of the remainder are mid-market with genuine multi-state obligations and no internal capability, giving ~8,000. The record does anchor the shape of this buyer: '50-500 SKUs' and 'a mid-size food or consumer brand with 400 SKUs has no idea what its cartons weigh.'</t>
+        </is>
+      </c>
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>ANCHORED ON A QUOTED FIGURE. The record states: 'Charge $10-25k for first-year data assembly plus filings across all mandated states, then annual maintenance.' I take ~$18k as a realistic first-year average within that band, and assume renewal-year maintenance plus per-new-state filing add-ons at $8-10k (MY REASONING). Blended across a maturing book that is majority-renewal by year 4-5, ~$14k per customer per year.</t>
+        </is>
+      </c>
+      <c r="F12" s="21" t="inlineStr">
+        <is>
+          <t>Fixed first-year data-assembly and multi-state filing fee ($10-25k, quoted from record), then an annual maintenance and filing retainer with per-additional-state and per-new-SKU add-ons.</t>
+        </is>
+      </c>
+      <c r="G12" s="21" t="inlineStr">
+        <is>
+          <t>Faster year-1 ramp than most regulated-buyer businesses, for two specific reasons: the price sits below the procurement threshold at a mid-market brand so the VP Supply Chain can sign alone, and the statutory deadline supplies the urgency that normally has to be manufactured. But throughput, not demand, is the binding constraint — the record's own moat is 'physically weighing and characterizing' every package, which at 400 SKUs is on the order of 70-100 bench hours per customer before any filing work. A four-person team can carry roughly 10 first-year onboardings in year 1 while also selling. Growth after that is gated by how fast you can hire and train bench technicians, which is linear and unglamorous, not by market demand. Years 3-5 assume the co-packer and distributor channel is working and delivering multi-brand referrals; without it the curve is roughly half this. Year 5 at 300 customers is 3.8% of the estimated universe — deliberately modest, because renewals compound and you do not need share to build a good business here.</t>
+        </is>
+      </c>
+      <c r="H12" s="21" t="inlineStr">
+        <is>
+          <t>MY OWN REASONING. First-year delivery is a physical-labor services business — receiving samples, weighing, characterizing, building the BOM — running 30-40% margin. Renewal years are near-software margin (70%+) because the BOM already exists and only deltas need work. A book that is roughly half new and half renewal blends to ~48%. The record's kill_risk independently supports the ceiling: 'the physical weigh-and-characterize step is real moat but is also real opex that caps gross margin and slows onboarding.'</t>
+        </is>
+      </c>
+      <c r="I12" s="21" t="inlineStr">
+        <is>
+          <t>Whether the co-packer and packaging-distributor channel converts in bulk. The record's whole distribution bet is that these partners 'touch hundreds of brands each.' If one distributor relationship reliably yields 10-20 referred brands, year 5 lands at 300+; if the business stays one-brand-at-a-time direct sales, throughput and CAC cap it near 100. That is a 3x swing on year-5 revenue and it dominates every other variable including how many states enforce.</t>
+        </is>
+      </c>
+      <c r="J12" s="21" t="inlineStr">
+        <is>
+          <t>California's SB 54 restart drags past 2028 (the record confirms 'CalRecycle's SB 54 regulations were withdrawn and restarted in 2025'), removing the largest single market from the stacking calendar. Remaining states soften fee schedules under industry lobbying, and PRO-provided portals combined with co-packer-supplied spec sheets let brands self-file at near-zero cost — commoditizing the filing layer while the expensive weighing step stays expensive. Bear case is roughly 80 customers at $10k by year 5, about $800k revenue, a 45%-margin regional services shop that never escapes founder-led delivery.</t>
+        </is>
+      </c>
+      <c r="K12" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="L12" s="21" t="inlineStr">
+        <is>
+          <t>The price point is quoted directly from the record, so the ACV is the solid half. The buyer universe is entirely my own structural estimate with no search to check it against — I could be off by 2x in either direction, and the true number depends heavily on where each state sets its small-producer exemption, which I cannot verify. I am also assuming CAA registration counts are in the low thousands per state based on recall, not confirmation.</t>
+        </is>
+      </c>
+      <c r="M12" s="10" t="inlineStr">
+        <is>
+          <t>rec-state-packaging-epr-reporting-for-mid-market-brands</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="76" customHeight="1">
+      <c r="A13" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t>Part 146 ADSP certification: strategic deconfliction plus the sub-400-foot obstacle layer</t>
+        </is>
+      </c>
+      <c r="C13" s="23" t="inlineStr">
+        <is>
+          <t>Near-term (the only buyer that matters inside a 5-year model): the manager of the UAS/drone inspection program inside an investor-owned electric utility's T&amp;D asset-management group — the person who already owns LiDAR from a vegetation-management contract, runs a Part 107 fleet, and carries a personal safety mandate for flight planning near distribution lines and guy wires. Budget sits with the VP of Asset Management. Later and secondary: the head of flight operations at a Class I railroad or interstate pipeline operator, and from ~2029 the certificated Part 146 deconfliction ADSP licensing the obstacle layer as an input.</t>
+        </is>
+      </c>
+      <c r="D13" s="23" t="inlineStr">
+        <is>
+          <t>MY OWN REASONING, not researched — the record states no count. Structure: roughly 170 US investor-owned electric utilities, of which perhaps 120 have a real drone-inspection budget; plus the largest ~100 municipal utilities and generation/transmission co-ops with LiDAR programs; plus about 7 Class I railroads and roughly 50 interstate pipeline operators; plus a probable 10-20 certificated ADSPs and large BVLOS delivery operators late in the window. Netting the ones too small to sign a six-figure data subscription gives ~300 realistic buying entities over five years.</t>
+        </is>
+      </c>
+      <c r="E13" s="23" t="inlineStr">
+        <is>
+          <t>MY OWN RECALL, not researched and not stated in the record. Utility geospatial and inspection-analytics subscriptions of the Neara/AiDash type run from roughly $150k to over $1M annually for a large IOU, typically priced off circuit-miles or acres of service territory. A startup selling a narrower single-purpose obstacle layer prices below the incumbent platforms: ~$250k for a large IOU, ~$100k for a mid-size utility or railroad, blending to ~$180k. Treat this as the softest number in this projection.</t>
+        </is>
+      </c>
+      <c r="F13" s="23" t="inlineStr">
+        <is>
+          <t>Annual per-territory data subscription priced on circuit-miles of covered right-of-way, with a paid pilot (~$50-75k) as the land step and refresh cadence as the upsell. The Part 108/146 deconfliction API is deliberately free or near-free — it is instrumentation to accumulate flight telemetry and operator dependence, not a revenue line.</t>
+        </is>
+      </c>
+      <c r="G13" s="23" t="inlineStr">
+        <is>
+          <t>This is the slowest ramp in the set and it should be. Utility procurement for safety-critical data runs 9-18 months from first contact to signed subscription, and it is almost always gated behind a paid pilot in one service territory, then a second budget cycle to expand. The record itself instructs 'do not attempt national coverage — pick electric distribution rights-of-way in two or three states,' which caps year 1 at 2 pilots and year 2 at the handful of utilities inside those states. Coverage cost compounds the constraint: each new utility outside your existing footprint requires acquiring and processing their LiDAR before you can sell them anything, so customer growth and data-capex growth move together. Years 4-5 assume the coverage flywheel works — that a processed state makes the next utility in that state cheap to serve. Year 5 at 32 customers is roughly 11% of the estimated universe, which is high for enterprise data but defensible if the layer genuinely becomes a safety-of-flight dependency. Critically, this ramp assumes ZERO revenue from the Part 146 ADSP toll position — the record's own why_now puts that curve at 2028-2031 and flags this as 'the softest' dated trigger in its set, so I refuse to bank it inside five years.</t>
+        </is>
+      </c>
+      <c r="H13" s="23" t="inlineStr">
+        <is>
+          <t>MY OWN REASONING. This is not a software business — it is a data-acquisition business with recurring field and processing cost. Ingesting and conflating utility LiDAR, running targeted survey for gaps, and the 'continuously refreshed' obligation are all direct cost of goods, and each new territory is a fresh acquisition spend. Margin is roughly 40% in early territories and improves toward 70% only where a processed footprint is resold to a second buyer in the same geography. Blended ~55%, well below the 70-85% a pure software comparison would suggest.</t>
+        </is>
+      </c>
+      <c r="I13" s="23" t="inlineStr">
+        <is>
+          <t>Whether utilities will buy a third-party obstacle layer at all, versus processing their own LiDAR in-house or taking it bundled from Neara or AiDash, who — as the record's kill_risk states — are 'better capitalized and already inside those accounts.' The utility already owns the raw data; you are selling the exploitation of it. If that framing lands, the ACV holds at $180k and the ramp works; if utilities treat it as a feature they should get inside an existing contract, ACV collapses toward $50k and the customer count halves. This single variable swings year-5 revenue by roughly 5x and matters far more than BVLOS rule timing, which sits outside the model window anyway.</t>
+        </is>
+      </c>
+      <c r="J13" s="23" t="inlineStr">
+        <is>
+          <t>The BVLOS final rule slips again into 2027-2028 (the record concedes 'this publication date has slipped repeatedly'), and worse, the final rule lets deconfliction ADSPs self-supply their own data — collapsing the separate supplemental-data lane that is the entire strategic premise. Meanwhile Neara and AiDash add an obstacle layer to renewals at no incremental charge. Bear case is roughly 8 utility customers at $120k by year 5, about $1M revenue, having burned $1.2M+ of capital to get there — a subscale geospatial consultancy with a good dataset and no toll position.</t>
+        </is>
+      </c>
+      <c r="K13" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="L13" s="23" t="inlineStr">
+        <is>
+          <t>Both load-bearing numbers are mine, not the record's. The buyer universe is a structural guess built on recalled US utility counts, and the ACV is recalled from the general shape of utility geospatial pricing — I cannot check either. The record itself flags the timing as the softest of its dated triggers, and I have compounded that honesty by zeroing all ADSP revenue inside five years, which means this model is really a bet on a utility data business, not on the Part 146 thesis the record is actually excited about.</t>
+        </is>
+      </c>
+      <c r="M13" s="12" t="inlineStr">
+        <is>
+          <t>part-146-bvlos-data-services</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="76" customHeight="1">
+      <c r="A14" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t>Material Assistance Cost Ratio files for FEOC-exposed clean energy</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr">
+        <is>
+          <t>The tax director or CFO at a mid-market US solar EPC or battery-storage integrator doing $50-500M of annual project volume, claiming 45Y/48E, who cannot afford a national law firm's tax opinion but cannot afford to get MACR wrong either. Second and strategically more important buyer: the underwriting head at a tax-credit insurance carrier and the diligence lead at a tax-credit transfer buyer — they have the sharpest incentive to mandate a machine-checkable file format and can drag developers into it. Third: the controller at a 45X component manufacturer computing MACR per product line.</t>
+        </is>
+      </c>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t>MY OWN REASONING, not researched — the record gives no count. It quotes only a readiness statistic: 'SEIA's Q4 2025 survey reportedly found only 38% of solar firms describe themselves as fully prepared for FEOC compliance.' Structure: roughly 1,500-2,000 US solar and storage developers/EPCs at utility-scale or large-C&amp;I scale, of which maybe half have FEOC exposure material enough to pay for a defended file; plus roughly 150-250 US 45X component manufacturers; plus 50-100 transfer buyers, insurers and syndicators. That gives ~900, and it is a SHRINKING universe, not a growing one, because of the sunset described below.</t>
+        </is>
+      </c>
+      <c r="E14" s="21" t="inlineStr">
+        <is>
+          <t>MY OWN RECALL AND REASONING — the record states no price, only that it is 'sold per project and per product line with recurring annual recertification' as a 'fixed-fee MACR opinion package.' Anchor: a national law firm tax opinion on a single project runs roughly $75-250k, which is exactly the fee this business undercuts. I model a $40-60k first project and $15-25k per subsequent project, so a mid-market EPC running 4-6 projects a year plus annual recertification lands at ~$75k of annual revenue per account. Insurers and transfer buyers buy a smaller platform subscription.</t>
+        </is>
+      </c>
+      <c r="F14" s="21" t="inlineStr">
+        <is>
+          <t>Fixed-fee per-project MACR opinion package (first project priced high, marginal projects discounted), plus an annual recertification retainer and separately-billed IRS examination defense. Portal access bundled, not sold standalone.</t>
+        </is>
+      </c>
+      <c r="G14" s="21" t="inlineStr">
+        <is>
+          <t>Year 1 is faster than the other opportunities here because the trigger has already fired — the record confirms FEOC rules 'bite for tax years and construction starts beginning after 31 December 2025' and Notice 2026-15 landed in February 2026 — so the buyer already knows they have the problem and is shopping. Six in year 1 reflects a 90-day-buildable services wedge sold by a credentialed tax specialist into an urgent, dated need. Years 2-3 compound as the thresholds ratchet ('roughly 40% MACR... rising roughly 5 points a year toward 60% by 2029'), which mechanically increases the number of projects that need real work rather than a cursory memo. Then the curve deliberately FLATTENS at years 4-5, and this is the most important judgment in the projection: the record's own kill_risk states 'OBBBA terminates wind/solar 45Y/48E for projects placed in service after 2027 absent a 12-month construction start, so the largest FEOC-exposed cohort shrinks instead of compounding.' I believe the kill_risk over the thesis. By 2030-2031 the business is living on storage, 45X manufacturers, and six-year examination defense on an installed base — real revenue, but not a growth curve. Year 5 at 60 customers is 6.7% of a shrinking universe.</t>
+        </is>
+      </c>
+      <c r="H14" s="21" t="inlineStr">
+        <is>
+          <t>MY OWN REASONING. The deliverable that buyers actually pay for is an opinion package signed off by a senior tax/energy-credit specialist — a human whose time is the cost of goods. The portal and calculator reduce marginal cost on repeat projects within an account but do not remove the specialist from the loop, because the entire value proposition is a file that survives a six-year IRS statute. That is a 40-50% services business, not a software business, and the record's defensibility score of 3 is consistent with that.</t>
+        </is>
+      </c>
+      <c r="I14" s="21" t="inlineStr">
+        <is>
+          <t>How much FEOC-exposed project volume still exists in 2030-2031. Everything else — pricing, competition from Crux or Empact, whether insurers mandate the format — is second-order next to whether the OBBBA sunset produces a 2026-2027 construction-start rush followed by a cliff. If safe-harbored construction starts stack up a multi-year backlog of projects that still need annual recertification through 2031, year-5 revenue holds near $4.5M. If the cohort genuinely collapses after 2027, the business peaks in year 3 and declines. This is the rare case where the single most important variable is written into statute rather than determined by execution.</t>
+        </is>
+      </c>
+      <c r="J14" s="21" t="inlineStr">
+        <is>
+          <t>Crux or Empact ship MACR computation as a free feature of a transfer platform they already have the developer relationship for (the record: 'MACR is a documentation workflow Crux or Empact ships as a feature'), Treasury's published safe-harbor cost tables remove any proprietary data advantage, and the Big 4 plus national tax counsel keep the opinion work because signature risk is what buyers are actually paying for. Combined with the sunset, bear case is roughly 15-20 accounts at $60k by year 5, about $1.2M revenue — a six-person tax boutique with a nice tool, not a venture outcome.</t>
+        </is>
+      </c>
+      <c r="K14" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="L14" s="21" t="inlineStr">
+        <is>
+          <t>Neither the buyer count nor the price comes from the record; both are mine. The universe estimate depends on a developer/EPC population I am recalling rather than verifying, and the ACV is extrapolated from remembered tax-opinion fee ranges. I have moderate confidence in the SHAPE of the curve — the flattening is well-supported by the record's own statutory reading — and low confidence in its level. The record's own scores (defensibility 3, overlooked 3) suggest the analyst who wrote it shared this discomfort.</t>
+        </is>
+      </c>
+      <c r="M14" s="10" t="inlineStr">
+        <is>
+          <t>material-assistance-cost-ratio-attestation</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="76" customHeight="1">
+      <c r="A15" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>The C2PA referee: conformance evidence, survivability scores, and verification at ingest</t>
+        </is>
+      </c>
+      <c r="C15" s="23" t="inlineStr">
+        <is>
+          <t>Two distinct buyers with different budgets. (a) Conformance prep: the security engineering or product-compliance lead at a vendor chasing the Conforming Products List — camera and phone OEMs, image-sensor and ISP vendors, editing-software makers, and generative model labs — who needs a Generator Product Security Architecture Document completed and an assurance-level gap closed. (b) Verification-as-infrastructure: the trust-and-safety engineering lead or CTO at a large content platform, newswire, stock-media library or broadcast group who needs manifests validated at ingest scale and, specifically, needs to adjudicate 'no manifest' versus 'manifest removed.' The leaderboard buys neither — it is the marketing that reaches both.</t>
+        </is>
+      </c>
+      <c r="D15" s="23" t="inlineStr">
+        <is>
+          <t>QUOTED FROM THE RECORD. Its kill_risk states directly: 'The market is perhaps 100-300 organizations, ever.' I take the midpoint, 250, rather than inventing a larger number — roughly 80 conformance-seeking product vendors (camera makers, a few model labs, editing-tool vendors, CAs) and roughly 170 platforms, newsrooms and media libraries with an ingest-verification need. The record also correctly notes the certification revenue itself is already assigned to accredited CAs (DigiCert, GlobalSign, SSL.com, Entrust), so those are channel or competition, not buyers.</t>
+        </is>
+      </c>
+      <c r="E15" s="23" t="inlineStr">
+        <is>
+          <t>MY OWN RECALL AND REASONING — no price exists in the record, and none can exist yet since the Conformance Program v0.2 published 2026-07-31, days ago. Anchored by analogy: SOC 2 readiness and security-architecture assessment engagements run roughly $30-80k fixed fee, and a monitoring API for a platform of real scale runs $50-150k annually. A blend weighted toward the assessment product gives ~$70k. This is a genuinely unpriced market and the number should be treated as a hypothesis.</t>
+        </is>
+      </c>
+      <c r="F15" s="23" t="inlineStr">
+        <is>
+          <t>Fixed-fee Generator Product Security Architecture Document completion and assurance-level gap assessment (one-off per product line, recurring on recertification cycles), plus an annual verification/monitoring API subscription for platforms priced on sampled ingest volume. Leaderboard and rubric-runner free and open-source.</t>
+        </is>
+      </c>
+      <c r="G15" s="23" t="inlineStr">
+        <is>
+          <t>Year 1 is 3 because the leaderboard has to earn authority before the assessment sells, and authority takes quarters — nobody buys a conformance opinion from a referee nobody has heard of. The record's own sequencing agrees: ship the open-source rubric-runner and the weekly survivability leaderboard first, 'the leaderboard is the marketing,' then sell. Years 2-3 track the Conforming Products List actually populating; every vendor that wants on the list is a named, countable, reachable prospect, so this is a targeted-outbound motion into a tiny known universe, not a funnel. The ceiling arrives fast and is low: at 38 customers in year 5 you hold roughly 15% of the entire stated universe, which for a niche where reputation concentrates is plausible — you either become the referee or you are nobody — but it caps year-5 revenue near $2.7M no matter how well you execute. That ceiling, not the ramp, is the finding. The record's own market_size score of 3 is the honest read.</t>
+        </is>
+      </c>
+      <c r="H15" s="23" t="inlineStr">
+        <is>
+          <t>MY OWN REASONING. The paid product is a senior security architect writing and defending an architecture document against a published rubric — expert-hours as cost of goods, 40-50% like any assessment practice. The verification API would carry 75%+ margin but is the smaller line early. Against that, the adversarial benchmark is a permanent cost center: running recompression, screenshot, re-render and diffusion-regeneration transforms against fresh outputs from every major generator weekly means real and recurring GPU and API spend that is never billed to anyone. Blended ~50%.</t>
+        </is>
+      </c>
+      <c r="I15" s="23" t="inlineStr">
+        <is>
+          <t>Whether Conforming Products List membership becomes a commercial or regulatory gate rather than a badge. If EU AI Act transparency enforcement, or a major platform's ingest policy, makes conformance a precondition for distribution, then 250 organizations become 250 buyers with an urgent budget and the ACV can double. If it stays voluntary, the large majority never buy anything, the realistic universe shrinks to perhaps 60, and year-5 revenue is under $1M. Nothing else — pricing, competition, benchmark quality — moves year-5 revenue as much as that binary.</t>
+        </is>
+      </c>
+      <c r="J15" s="23" t="inlineStr">
+        <is>
+          <t>The accredited CAs bundle readiness assistance with the certificates they are already selling, taking the conformance-prep business as a loss leader — the record notes 'the certification revenue is already assigned to accredited CAs, not to an independent referee.' Simultaneously the record's deeper bearish reading proves right: removal tooling industrialises (raiw.cc, PyPI CLI, working diffusion-regeneration attacks on invisible marks) and the marking regime does not durably hold, making survivability scores an obituary rather than a product. Benchmark-authority businesses are 'famously beloved and famously hard to monetize' — SSL Labs and HIBP are the cautionary precedent. Bear case is roughly $600k of year-5 revenue: a widely-cited two-or-three-person consultancy with an excellent reputation and no leverage.</t>
+        </is>
+      </c>
+      <c r="K15" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="L15" s="23" t="inlineStr">
+        <is>
+          <t>Unusually split confidence. The buyer universe is the strongest number in this whole batch because the record states it explicitly ('perhaps 100-300 organizations, ever') and I am quoting rather than guessing. The ACV is the weakest kind of number — a market priced days ago at v0.2, with no transactions to recall, estimated purely by analogy to SOC 2 readiness fees. Net 5: I trust the denominator and not the multiplier, which means I trust the revenue ceiling far more than I trust the revenue level.</t>
+        </is>
+      </c>
+      <c r="M15" s="12" t="inlineStr">
+        <is>
+          <t>c2pa-conformance-and-robustness-referee</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="76" customHeight="1">
+      <c r="A16" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="21" t="inlineStr">
+        <is>
+          <t>Micropollutant EPR fee ledger for pharma and cosmetics under the UWWTD</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="inlineStr">
+        <is>
+          <t>Initially the Group Financial Controller or Head of Financial Reporting at a European generics pharmaceutical group or a cosmetics group — someone who must book a defensible provision in 2027 statutory accounts and needs a number their auditor will accept. The record is explicit about this and it is the sharpest insight in the entry: 'their finance function will buy it before their regulatory function will.' From 2028 the buyer shifts to the Head of Regulatory Affairs or EHS purchasing recurring filings as national PROs stand up, and eventually to the portfolio strategist using the same dataset for reformulation and portfolio-exit decisions — which the record correctly calls 'the far larger business.'</t>
+        </is>
+      </c>
+      <c r="D16" s="21" t="inlineStr">
+        <is>
+          <t>ANCHORED ON A QUOTED BEACHHEAD, EXTENDED BY MY OWN REASONING. The record names the beachhead precisely — 'the top 50 generics and cosmetics groups each need a defensible provision number for their 2027 statutory accounts' — and separately describes the full obligated population as 'thousands of marketing authorisation holders and cosmetics responsible persons.' The thousands cannot pay EUR 30-80k. I estimate the paying universe at ~250: roughly 120 pharma MAH groups with EU-wide portfolios and material micropollutant exposure, plus roughly 130 cosmetics groups above a materiality threshold. This is my estimate, not the record's.</t>
+        </is>
+      </c>
+      <c r="E16" s="21" t="inlineStr">
+        <is>
+          <t>ANCHORED ON A QUOTED FIGURE. The record states: 'First product is a EUR 30-80k board-level exposure report, not software.' Midpoint EUR 55k converts to roughly $60k at ~1.10. I blend in an assumed recurring filing subscription from 2028 at a similar annual level (MY REASONING — the record says only 'convert those accounts to the recurring filing product as national PROs stand up in 2028' with no price), giving ~$65k blended.</t>
+        </is>
+      </c>
+      <c r="F16" s="21" t="inlineStr">
+        <is>
+          <t>Fixed-fee board-level exposure report per group (EUR 30-80k, quoted from record), repeating annually as the provision is restated, converting to an annual per-member-state filing and fee-simulation subscription once national PROs are operational.</t>
+        </is>
+      </c>
+      <c r="G16" s="21" t="inlineStr">
+        <is>
+          <t>The slowest-starting ramp here relative to how urgent the record claims the need is, and the gap is deliberate. Three constraints bind year 1. First, data: the record's own kill_risk states 'per-country medicines volume is IQVIA-licensed proprietary data, not something a 1-3 person team ingests in 90 days,' so there is a licensing negotiation and a build before there is a product. Second, the sale is a long consultative one into pharma finance functions, where a novel provision methodology gets routed past the auditor and often past group legal. Third and decisively, the June 2026 stop-the-clock resolution hands every CFO a defensible reason to defer — you are selling a provision for an obligation the European Parliament has just asked to suspend. Years 2-3 assume the suspension fails or resolves and the 31 July 2027 transposition deadline forces the issue, which is when the beachhead the record identifies (the top 50 groups) actually converts. Year 5 at 38 is 15% of my estimated universe and roughly three-quarters of the record's stated top-50 beachhead, which is about the most a senior-consultant-delivered product can reach.</t>
+        </is>
+      </c>
+      <c r="H16" s="21" t="inlineStr">
+        <is>
+          <t>MY OWN REASONING, and the lowest margin in this batch for two compounding reasons. The deliverable is a board-level report authored by a senior regulatory-toxicology and health-economics specialist — expert hours as direct cost. On top of that sits a genuine licensed-data COGS: IQVIA or equivalent national sales data carries a substantial annual fee and, importantly, resale or derived-work rights are typically restricted and separately priced, so the data cost does not amortize across customers as cleanly as a normal data business. 40% is the honest number and it may be generous.</t>
+        </is>
+      </c>
+      <c r="I16" s="21" t="inlineStr">
+        <is>
+          <t>Whether the EU 'stop the clock' suspension of the UWWTD EPR provisions succeeds. This is close to binary and it governs everything. The record's kill_risk documents it: the European Parliament passed a resolution on 18 June 2026 backing temporary suspension and demanding a fresh Commission impact assessment by end-2026 'to re-verify quaternary treatment costs and re-identify which sectors are actually responsible,' with IPHA pushing a CJEU preliminary reference and EFPIA, Cosmetics Europe, AESGP and Medicines for Europe taking a joint demand to the Competitiveness Council. If the obligation is suspended past 2029, no CFO books a provision and there is no report to sell — year-5 revenue is near zero, not merely reduced. If the dates hold, the 2027 transposition deadline creates a hard forcing function and the model works. No execution variable comes close to mattering this much.</t>
+        </is>
+      </c>
+      <c r="J16" s="21" t="inlineStr">
+        <is>
+          <t>Stop-the-clock succeeds, the Commission's end-2026 impact assessment reopens the mass-times-hazard methodology entirely, and the CJEU reference freezes national implementation into 2029 — destroying the record's central claim of a '12-18 month window to become the reference calculation before the formulas harden.' The methodology is not hardening; it is being reopened. Meanwhile the Big 4, ERM and Ramboll take the board-level report work using the same public ECHA and EMA sources, because incumbent auditor relationships beat a startup for anything that lands in statutory accounts. Bear case is roughly $500k of cumulative revenue and the business does not reach year 5 in recognisable form — most likely it becomes a two-person specialist consultancy or folds into a larger EHS advisory.</t>
+        </is>
+      </c>
+      <c r="K16" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="L16" s="21" t="inlineStr">
+        <is>
+          <t>Lowest confidence in the batch, and deliberately so. The ACV is quoted from the record and is the only firm number I have. The buyer universe is my own guess extending the record's stated top-50 beachhead. Everything downstream is hostage to a live political process I cannot check with no search access — the record's own kill_risk says its why_now 'is materially out of date and omits the decisive event,' and I have no way to verify what happened between June 2026 and today. The record also judges the 90-day plan to be 'honestly a consulting report, not a wedge,' which I agree with and have priced in through the low margin and the high capital-to-first-revenue.</t>
+        </is>
+      </c>
+      <c r="M16" s="10" t="inlineStr">
+        <is>
+          <t>micropollutant-epr-billback</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="76" customHeight="1">
+      <c r="A17" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>CRA Article 14 incident reporting and the legacy-product obligation</t>
+        </is>
+      </c>
+      <c r="C17" s="23" t="inlineStr">
+        <is>
+          <t>The named CE-marking/product-compliance owner (quality &amp; regulatory director, or CTO at sub-200-person firms) at an EU-market manufacturer of connected embedded hardware — the record's suggested beachhead is 'industrial automation or EV charging' — who already signs Declarations of Conformity for machinery/RED/LVD but has no PSIRT and no way to staff a 24/7 rota. Not the CISO: the CISO protects the enterprise, this buyer owns the product's regulatory file.</t>
+        </is>
+      </c>
+      <c r="D17" s="23" t="inlineStr">
+        <is>
+          <t>My own reasoning, not researched — the record states no firm count. Built from structure: the CRA covers every 'product with digital elements' placed on the EU market (hundreds of thousands of entities), but the buyer for a EUR 3-8k/month outsourced-PSIRT retainer is the narrow band that is (a) above the micro-enterprise floor, (b) shipping connected hardware rather than pure SaaS, and (c) too small to staff 24/7 in-house. I reason that band at roughly 12,000 firms EU-wide across industrial automation, EV charging, building automation, networking and consumer IoT, including non-EU manufacturers with EU importers. This number is the weakest input in the model.</t>
+        </is>
+      </c>
+      <c r="E17" s="23" t="inlineStr">
+        <is>
+          <t>Anchored on the record's stated price: 'Sell a EUR 3-8k/month retainer or per-product-line annual subscription with a contractual 24-hour SLA.' I take EUR 5k/month midpoint = EUR 60k/yr, plus roughly EUR 12k/yr of amortised conformity work drawn from the record's stated 'EUR 20-50k per self-assessed product line' (a customer refreshing one or two lines over a multi-year contract). EUR ~65k converted at a recalled EUR/USD of roughly 1.10 — the FX rate is recall, not researched.</t>
+        </is>
+      </c>
+      <c r="F17" s="23" t="inlineStr">
+        <is>
+          <t>Monthly managed-PSIRT retainer with a contractual 24-hour filing SLA, plus per-product-line conformity project fees at CE-marking milestones</t>
+        </is>
+      </c>
+      <c r="G17" s="23" t="inlineStr">
+        <is>
+          <t>The record's own '90-day target is 10-15 retainers' is founder optimism against a buyer that signs statutory filings. Two structural brakes. First, timing: the record concedes 11 Sep 2026 is roughly six weeks out, so you cannot sell into it — the real forcing function is 11 Dec 2027, which lands mid-Y2 and explains the Y1-to-Y2 jump from 4 to 18. Second, the record's own kill_risk is correct that 'compliance buyers wait for the first fine' across 27 under-resourced market surveillance authorities, so Y3-Y5 growth is enforcement-paced, not deadline-paced. Delivery caps it too: a senior analyst who can draft a defensible 24h notification carries maybe 8-10 accounts, so 120 customers at Y5 means ~14 analysts plus a genuine follow-the-sun rota — a ~30-person firm. Distribution is through notified bodies and CE consultancies, which are referral relationships that compound slowly rather than a funnel you can buy.</t>
+        </is>
+      </c>
+      <c r="H17" s="23" t="inlineStr">
+        <is>
+          <t>My own reasoning. This is a senior-humans-in-the-loop service, not SaaS. The SBOM diffing and feed correlation amortise well, but the differentiated asset — the 24-hour SLA — is paid for in awake humans who cannot be thinned, plus E&amp;O premium loaded into COGS. That puts it at the middle of the 35-55% services band rather than the top.</t>
+        </is>
+      </c>
+      <c r="I17" s="23" t="inlineStr">
+        <is>
+          <t>Enforcement credibility after 11 Dec 2027. One publicised fine against a mid-size manufacturer converts a stalled pipeline into an urgent one; a quiet 2028 with a non-live ENISA platform and no penalties means the retainer stays a nice-to-have and the ramp flattens at Y3 levels. Every other variable — ACV, margin, delivery capacity — moves less than this one.</t>
+        </is>
+      </c>
+      <c r="J17" s="23" t="inlineStr">
+        <is>
+          <t>No visible enforcement action through 2029; TUV/notified bodies bundle CRA vulnerability handling into existing CE-marking retainers at half your price using distribution you cannot match; and one late or botched filing under a customer's name produces an uninsurable claim that ends the SLA product. You survive as a boutique of 25-30 accounts at a discounted EUR 3k/month, Y5 revenue roughly USD 1.5-2.0M at compressed margin — a consultancy, not a company.</t>
+        </is>
+      </c>
+      <c r="K17" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="L17" s="23" t="inlineStr">
+        <is>
+          <t>The ACV is genuinely anchored (quoted from the record) so I would defend it at 7. The buyer universe is unresearched reasoning from structure, worth about a 3. Blended to 5. The whole model also inherits the record's own evidence caveat that several figures came from search extracts after proxy 403s and were never verified against the regulation.</t>
+        </is>
+      </c>
+      <c r="M17" s="12" t="inlineStr">
+        <is>
+          <t>cra-enisa-24h-reporting</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="76" customHeight="1">
+      <c r="A18" s="10" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>Signed provenance attestation for the secondhand datacenter hardware channel</t>
+        </is>
+      </c>
+      <c r="C18" s="21" t="inlineStr">
+        <is>
+          <t>The owner or inventory manager of a mid-size ITAD / secondhand enterprise-hardware reseller moving hundreds to thousands of drives and DIMMs a month, who eats the RMA cost when a relabelled drive fails and who can charge a premium for graded stock. Explicitly not the end buyer (fragmented, low-value, exactly the party the record's kill_risk identifies as unable to pay) and not the marketplace (the record itself notes 'twenty years of demonstrated unwillingness to fund verification').</t>
+        </is>
+      </c>
+      <c r="D18" s="21" t="inlineStr">
+        <is>
+          <t>My own reasoning, not researched — the record states no count of resellers, ITADs or MSPs. Reasoned from structure: the paying entity must have enough throughput that per-unit attestation beats eyeballing, which means a few hundred units a month minimum. I put that at roughly 4,000 firms worldwide (North America, EU, and the larger Asian re-export brokers), combining ITAD/refurbisher operations with the minority of MSPs that resell rather than just deploy hardware. Low confidence in this figure.</t>
+        </is>
+      </c>
+      <c r="E18" s="21" t="inlineStr">
+        <is>
+          <t>My own reasoning — the record specifies the pricing model ('charge per verification to resellers, MSPs and marketplaces') but names no price. I derive it: an attestation must cost well under 1% of the unit it certifies to be a reflexive purchase, so ~USD 1.50 on an enterprise drive the record implies is selling into a market where prices are 'up roughly 46-50% since September 2025.' A median paying reseller running ~1,000 units/month = 12,000 verifications/yr at USD 1.50 = USD 18,000, inclusive of a monthly platform minimum.</t>
+        </is>
+      </c>
+      <c r="F18" s="21" t="inlineStr">
+        <is>
+          <t>Per-verification usage fee against a monthly platform minimum, with an annual enterprise API tier for procurement teams</t>
+        </is>
+      </c>
+      <c r="G18" s="21" t="inlineStr">
+        <is>
+          <t>The free CLI seeds the registry fast — that part of the record's plan works, because posting a forensics tool into a market where counterfeiting was just confirmed by raids gets run on everything. Conversion is the slow part, and it is slow for a structural reason the record names against itself: the beneficiary of attestation and the holder of the budget are different parties with opposed incentives. So Y1 is 6 paying accounts out of what may be thousands of tool users, and growth thereafter tracks how many resellers decide graded stock commands a price premium rather than how many people download the CLI. The ACV is low enough that this must be self-serve with light touch — no field sales at USD 18k — which caps velocity at roughly a doubling-then-halving curve. I have also modelled only the attestation half; the regional refurb warehouse the record merges in is a different company with different capital needs and I have deliberately excluded it.</t>
+        </is>
+      </c>
+      <c r="H18" s="21" t="inlineStr">
+        <is>
+          <t>My own reasoning. Parsing FARM/SMART logs and signing an attestation is near-zero marginal cost, which argues for 85%. Two things pull it down: disputed grades need a human to adjudicate (a reseller whose drive was scored 'inconsistent' will call), and any warranty attached to a grade carries a real claims reserve. 72% reflects a software business with a small liability tail.</t>
+        </is>
+      </c>
+      <c r="I18" s="21" t="inlineStr">
+        <is>
+          <t>Whether a payer exists at all — the conversion rate from free-CLI users to paid per-verification accounts. This is close to binary rather than a dial: if resellers can capture a grade premium, conversion is a few percent of a large tool base and the model holds; if only the fragmented end buyer values the attestation, conversion is ~0 and no ACV assumption rescues it. This single variable swings Y5 revenue by an order of magnitude, far more than pricing or throughput.</t>
+        </is>
+      </c>
+      <c r="J18" s="21" t="inlineStr">
+        <is>
+          <t>The tool gets thousands of downloads and near-zero conversion, exactly as the record's own kill_risk predicts. Simultaneously the DRAM/HDD spike mean-reverts as fab and platter capacity lands in 2027-2028, deflating the arbitrage that made secondary-market grading feel urgent. You end with 20-40 sympathetic accounts at USD 6-10k, Y5 revenue roughly USD 250-350k — a well-regarded open-source project with a support contract attached.</t>
+        </is>
+      </c>
+      <c r="K18" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="L18" s="21" t="inlineStr">
+        <is>
+          <t>Both load-bearing numbers are unresearched. The universe is reasoned from industry structure with no count in the record, and the ACV is derived from a per-unit price I invented from a plausibility argument, not from any observed comparable. The record's own kill_risk directly attacks the assumption that any of these buyers pay, and I have no evidence to rebut it.</t>
+        </is>
+      </c>
+      <c r="M18" s="10" t="inlineStr">
+        <is>
+          <t>secondhand-hardware-provenance-channel</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="76" customHeight="1">
+      <c r="A19" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="23" t="inlineStr">
+        <is>
+          <t>Loss data and incident taxonomy for AI agent liability underwriting</t>
+        </is>
+      </c>
+      <c r="C19" s="23" t="inlineStr">
+        <is>
+          <t>The chief underwriting officer or head of product at a specialty MGA, Lloyd's syndicate or tech-E&amp;O carrier who must file a rating plan for agent-error coverage and currently has no loss experience to file it against. Secondarily the actuarial/emerging-risk team at a reinsurer. The record names the shape correctly: 'one MGA or specialty carrier who will co-develop rating factors with you in exchange for early access to the aggregate.'</t>
+        </is>
+      </c>
+      <c r="D19" s="23" t="inlineStr">
+        <is>
+          <t>My own reasoning, not researched — the record gives no count. Reasoned by enumeration from recall: roughly 90 Lloyd's syndicates, several dozen US specialty carriers writing tech E&amp;O, a comparable European and Asian set, the handful of AI-specific MGAs the record names (AIUC, Armilla, Klaimee), the major reinsurers' emerging-risk desks, and broker analytics units. That rounds to about 250 entities worldwide. It is a genuinely small and concentrated universe, which is both the opportunity and the trap.</t>
+        </is>
+      </c>
+      <c r="E19" s="23" t="inlineStr">
+        <is>
+          <t>My own recall of how loss-data and analytics vendors price into carriers — cyber-loss data subscriptions have historically landed in the low six figures for an enterprise licence, with first design-partner deals far below that. I set a blended USD 120,000 annual licence. This is recall, not researched, and the record states no price point of any kind.</t>
+        </is>
+      </c>
+      <c r="F19" s="23" t="inlineStr">
+        <is>
+          <t>Annual enterprise data licence (entity-level, not per-seat) with first-year rating-factor co-development fees</t>
+        </is>
+      </c>
+      <c r="G19" s="23" t="inlineStr">
+        <is>
+          <t>This is the slowest ramp in the batch and it should be. Year 1 is one design-partner MGA, probably at a steep discount, because the product's value is a function of data density that does not exist on day one — hand-classifying published incidents makes the registry non-empty, not credible. An actuary needs enough classified events with dollar severity to fit a frequency-severity curve before a rating filing depends on it, and that accrues on calendar time, which is the record's own strongest argument. Layer on insurance procurement, which is slow even when the buyer is enthusiastic. Y5 of 22 is roughly 9% of the 250-entity universe, but note the real denominator is smaller: only the subset actually writing agent E&amp;O by 2031 can buy, so 22 may be a third of the live market — that is the ceiling of a concentrated data business, and I have capped it there rather than extrapolating the curve.</t>
+        </is>
+      </c>
+      <c r="H19" s="23" t="inlineStr">
+        <is>
+          <t>My own reasoning. Delivery is a data feed, so marginal cost per customer is trivial. The cost that never goes away is a small team of analysts hand-classifying incidents against a taxonomy designed with a claims adjuster — that work is continuous, senior, and scales with incident volume rather than customer count. Effectively a fixed-cost data operation, which reads as high-60s margin at this revenue scale and improves with size.</t>
+        </is>
+      </c>
+      <c r="I19" s="23" t="inlineStr">
+        <is>
+          <t>Whether a carrier will license third-party loss data at all rather than underwrite off its own book. This is the record's kill_risk restated as a model input, and it is correct: 'a third-party registry cannot see closed claims — carriers own those.' If the answer is yes, the ACV holds and the compounding argument is real. If no, the product degrades from a data licence to a consulting engagement and ACV drops by roughly 80%, taking Y5 revenue with it.</t>
+        </is>
+      </c>
+      <c r="J19" s="23" t="inlineStr">
+        <is>
+          <t>AIUC, Armilla and Klaimee accrete proprietary claims data with privileged access you structurally cannot match, and the registry's only inputs remain re-scrapes of AIID and OECD AIM — which are free. No carrier pays for an aggregate of public data. You become a two-or-three-person research shop selling USD 25-40k reports to a handful of buyers, Y5 revenue roughly USD 250-400k, with the realistic exit being an acquihire by a broker who wants the taxonomy.</t>
+        </is>
+      </c>
+      <c r="K19" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="L19" s="23" t="inlineStr">
+        <is>
+          <t>Both figures are unresearched: the universe is an enumeration from recall and the ACV is a recalled comparable from an adjacent market (cyber loss data), not an observed price for this product, which does not yet exist. I would not defend either to a decimal. The record's own kill_risk also flags that its central premise ('the acceptance side has no builder at all') was already false as of Aug 2026, which independently undercuts the buyer-universe framing.</t>
+        </is>
+      </c>
+      <c r="M19" s="12" t="inlineStr">
+        <is>
+          <t>agent-liability-loss-data</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="76" customHeight="1">
+      <c r="A20" s="10" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="21" t="inlineStr">
+        <is>
+          <t>Relying-Party-as-a-Service: the verifier side of the EU Digital Identity Wallet</t>
+        </is>
+      </c>
+      <c r="C20" s="21" t="inlineStr">
+        <is>
+          <t>The identity/onboarding product owner or head of fraud at an obliged relying party that operates in several member states and has no in-house identity-standards engineering — concretely the KYC lead at an EU-licensed online gambling operator or the age-assurance owner at an alcohol-delivery or marketplace business. The record picks these correctly as first customers because they 'already have a legal need to check age or identity today,' meaning the purchase is a replacement, not a new budget line.</t>
+        </is>
+      </c>
+      <c r="D20" s="21" t="inlineStr">
+        <is>
+          <t>My own reasoning from recalled sector counts, not researched — the record lists obliged sectors ('banks, telecoms, energy, transport, healthcare and very large online platforms') but gives no entity count. Enumerated: roughly 5,000 EU credit institutions, ~2,000 energy retailers, ~1,500 licensed online gambling operators, ~500 telecom operators, the ~25 designated VLOPs, and several thousand age-restricted marketplaces and e-commerce operators. Rounds to about 12,000. I have excluded public healthcare and transport bodies, which are obliged but procure through public tender you cannot win at this stage.</t>
+        </is>
+      </c>
+      <c r="E20" s="21" t="inlineStr">
+        <is>
+          <t>My own reasoning — the record states the pricing model ('Price per verification with a registration setup fee') but no price. Derived: a mid-market relying party runs perhaps 250,000 verifications a year; a cryptographic presentation check has no human review, so it must price far below the USD 0.50-2.00 that document-based IDV commands from recall — I use EUR ~0.12, giving ~EUR 30k, plus a EUR 12k/yr managed-registration and certificate-lifecycle subscription covering three to five member states. EUR ~42k at a recalled EUR/USD of roughly 1.10.</t>
+        </is>
+      </c>
+      <c r="F20" s="21" t="inlineStr">
+        <is>
+          <t>Per-verification usage fee plus an annual managed registration and RP-access-certificate subscription priced per member state, with an onboarding setup fee</t>
+        </is>
+      </c>
+      <c r="G20" s="21" t="inlineStr">
+        <is>
+          <t>Y1 of 5 is taken directly from the record's own plan — 'First customers: 5 design partners among EU-facing gambling, telco, marketplace and alcohol-delivery businesses' — and that is the right number for a product that must be built against an ARF the customer's own team cannot read. The shape after that is set by two statutory dates the record quotes: wallet issuance by 31 December 2026 and private-sector acceptance from late 2027, compressing registration demand into 'roughly a 12-month window.' That window is Y2, which is why Y2 sextuples. Y3-Y4 then ride the long tail of laggard member states — the record's own readiness assessment has 7 'might' and 4 'unlikely,' so the patchwork itself sustains demand for a managed layer. Y5 of 280 is 2.3% of the universe, deliberately conservative because the record's kill_risk is right that a dozen funded IDV vendors already own this buyer and will bundle wallet acceptance into contracts you never see.</t>
+        </is>
+      </c>
+      <c r="H20" s="21" t="inlineStr">
+        <is>
+          <t>My own reasoning. Verification itself is signature validation and trust-list resolution — negligible COGS, which argues 85%. The drag is a regulatory-ops function doing registrations and certificate rotations across up to 27 registrars, plus support load every time a national trust list breaks or a member state changes its registration flow. That human layer is real and recurring, so 74% rather than software-typical 80%+.</t>
+        </is>
+      </c>
+      <c r="I20" s="21" t="inlineStr">
+        <is>
+          <t>The per-verification price. The record's kill_risk names the exact mechanism — a free Commission-maintained verifier plus the W3C/OS Digital Credentials API pulling presentation plumbing into the browser — and if that pushes the price from EUR ~0.12 toward EUR 0.02, ACV collapses from USD 45k to roughly USD 15k and the business becomes a registration-filing service. Nothing else in the model moves Y5 revenue by two-thirds the way this does.</t>
+        </is>
+      </c>
+      <c r="J20" s="21" t="inlineStr">
+        <is>
+          <t>Presentation verification commoditises into the browser and the Commission's free reference services, so customers self-serve the hard part and buy only the paperwork. 'Managed registration' turns out to be a one-time filing a customer's law firm handles, so it does not recur. You retain 60-80 accounts paying EUR 10-15k for multi-state registration upkeep, Y5 revenue roughly USD 1.0-1.3M, and the funded IDV vendors absorb the category.</t>
+        </is>
+      </c>
+      <c r="K20" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="L20" s="21" t="inlineStr">
+        <is>
+          <t>The buyer universe is a reasoned enumeration from recalled sector counts with no verification available — worth about a 4 on its own. The ACV is derived rather than stated: the record gives the pricing model but not the price, and my per-verification figure rests on a recalled comparison to document-based IDV pricing plus an argument about marginal cost. Both are arguable; neither is researched.</t>
+        </is>
+      </c>
+      <c r="M20" s="10" t="inlineStr">
+        <is>
+          <t>eudi-wallet-relying-party-side</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="76" customHeight="1">
+      <c r="A21" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="23" t="inlineStr">
+        <is>
+          <t>Lot-code reconciliation and the 24-hour FSMA 204 spreadsheet</t>
+        </is>
+      </c>
+      <c r="C21" s="23" t="inlineStr">
+        <is>
+          <t>The food-safety/QA director — or at smaller firms the owner-operator — of a mid-chain handler: an independent produce, seafood or specialty distributor, or a foodservice operator's commissary, roughly USD 10-150M in revenue, sitting between growers and restaurants. The record identifies the wedge correctly: these firms 'get blamed for upstream breaks' but do not cause them, so the 'broken links' report they can forward to the offending supplier is the actual product.</t>
+        </is>
+      </c>
+      <c r="D21" s="23" t="inlineStr">
+        <is>
+          <t>My own reasoning, not researched. The record states the coverage rule — no blanket small-business carve-out, 'only an exemption for establishments under $250,000 in average annual food sales' — but gives no firm count. The covered universe including farms, restaurants and retailers is in the hundreds of thousands; the buyer universe is far narrower because only mid-chain handlers feel the reconciliation pain. From recall, US food wholesale distribution runs to roughly 30,000-40,000 establishments; I take about 30,000 as the slice handling Food Traceability List commodities at meaningful volume, including retail and foodservice DCs.</t>
+        </is>
+      </c>
+      <c r="E21" s="23" t="inlineStr">
+        <is>
+          <t>Anchored directly on the record's stated price: 'Charge $200-600/month.' I use a blended USD 450/month = USD 5,400/yr, slightly above the midpoint to reflect multi-site handlers on a higher tier. The blend is my reasoning; the range is quoted.</t>
+        </is>
+      </c>
+      <c r="F21" s="23" t="inlineStr">
+        <is>
+          <t>Per-site monthly SaaS subscription tiered by shipment volume, with the FDA-format sortable-spreadsheet export gated to paid tiers</t>
+        </is>
+      </c>
+      <c r="G21" s="23" t="inlineStr">
+        <is>
+          <t>At a USD 5,400 ACV there is no field sales motion that pays for itself, so the entire ramp is a bet on the record's stated channel — 'broadline and specialty distributors who need their independent accounts compliant' — which means every distributor relationship signed drops in tens of accounts at once, producing a steppy rather than smooth curve. Y1 of 20 is below the record's 90-day target of 25 because the first two quarters go to building the parsing paths, not selling. Y2-Y3 accelerate as the 20 July 2028 deadline enters budget cycles and the record's point holds that 'real implementation takes 18-24 months,' forcing serious buyers to start in 2027. Y4-Y5 decelerate as the deadline passes and the remaining prospects are the ones who intended to ignore it. Y5 of 800 is 2.7% of the universe — modest, and the right kind of modest for a low-ACV product with no lock-in beyond accumulated lot history.</t>
+        </is>
+      </c>
+      <c r="H21" s="23" t="inlineStr">
+        <is>
+          <t>My own reasoning. This looks like SaaS but carries two real COGS lines: per-document parsing of PDFs, scanned BOLs and photographed case labels costs actual money at volume, and onboarding requires a human to map each customer's trading partners' formats. At USD 450/month that onboarding must be measured in hours, not weeks, and the parsing cost scales with usage — so high-60s, not the 75-85% a pure workflow tool would earn.</t>
+        </is>
+      </c>
+      <c r="I21" s="23" t="inlineStr">
+        <is>
+          <t>Whether 20 July 2028 holds. The record supplies both the support ('fixed by rule and reinforced by statute') and the doubt ('the deadline has already slipped once and Congress has already intervened once'). At a USD 5,400 ACV there is no residual value proposition strong enough to survive another extension — the product is bought because of a date, not because of shrink or recall speed, however real those downstream benefits are. A further delay or an FTL narrowing does not slow the ramp, it removes it.</t>
+        </is>
+      </c>
+      <c r="J21" s="23" t="inlineStr">
+        <is>
+          <t>A further extension lands in 2027 under deregulatory pressure and mid-chain buyers, who were already rationally deferring, stop returning calls. You retain only the genuinely motivated — leafy-greens handlers with recent outbreak history — at 150-250 accounts, Y5 revenue roughly USD 1.0-1.3M, and the seam-layer capability gets absorbed as a checkbox feature by the GS1/EPCIS platforms the record explicitly told you not to build.</t>
+        </is>
+      </c>
+      <c r="K21" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="L21" s="23" t="inlineStr">
+        <is>
+          <t>The ACV is quoted from the record and I would defend it at 7 — it is the most grounded price in this batch. The buyer universe is unresearched, reasoned from a recalled count of US food wholesale establishments and a judgement about which slice handles FTL items, worth about a 3. Blended to 5.</t>
+        </is>
+      </c>
+      <c r="M21" s="12" t="inlineStr">
+        <is>
+          <t>fsma-204-lot-code-traceability</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="76" customHeight="1">
+      <c r="A22" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="21" t="inlineStr">
+        <is>
+          <t>DMSMS resolution desk: last-time-buy brokerage plus qualified resupply for 20-year platforms</t>
+        </is>
+      </c>
+      <c r="C22" s="21" t="inlineStr">
+        <is>
+          <t>The obsolescence/sustainment engineer (or the supply-chain director they report to) at a mid-size regulated-product OEM that has just received a PCN/EOL notice on a part inside a shipping, certified assembly — infusion-pump and imaging OEMs, factory PLC and drive makers, rail signalling suppliers, tier-2 avionics. Budget sits in product-line sustainment, not R&amp;D. Second wave: the DMSMS lead at a DoD program office or the sustainment lead at a prime, spending weapon-system sustainment O&amp;M — the record names these as the 'second wave', not the beachhead.</t>
+        </is>
+      </c>
+      <c r="D22" s="21" t="inlineStr">
+        <is>
+          <t>My own reasoning, not researched — the record states no count of buyers. Structure: firms that (i) ship a certified/regulated electronic product, (ii) run a 10-25 year lifecycle so redesign triggers re-certification, and (iii) are too small to run an in-house die-bank/LTB desk. I estimate roughly 1,200-1,500 such medical-device and industrial-controls OEMs across US/EU/Japan, several hundred rail-signalling and avionics tier-2s, plus ~300-500 DoD program offices and sustainment primes and their DLA equivalents. Call it 3,000 buying entities worldwide, ~1,800 realistically sellable from a US base in five years. Deliberately NOT derived from the record's 'USD 23,800 million in 2026' DDR4 market figure — that is a top-down number and also flagged in the record as sourced from a GitHub issue summary, not a filing.</t>
+        </is>
+      </c>
+      <c r="E22" s="21" t="inlineStr">
+        <is>
+          <t>My own reasoning. A brokerage/resolution desk recognises the full brokered value of parts it takes title to, so 'ACV' here is mostly parts revenue. Assumption: an active customer resolves 2-4 dying part numbers a year; a typical last-time-buy lot for one part family at a mid-size OEM is $80k-$500k of components, and roughly one customer-year in three also buys a technical-data-package / qualified-alternate-source engineering engagement at $120k-$400k. Blend to ~$350k of recognised revenue per active customer per year, of which ~$100k is gross profit. The record supports the model qualitatively ('take brokerage margin from day one', 'financing last-time-buys against customer POs') but states no price point.</t>
+        </is>
+      </c>
+      <c r="F22" s="21" t="inlineStr">
+        <is>
+          <t>Brokerage spread on resold parts (revenue booked gross, ~20-25% spread), plus fixed-fee engineering/qualification packages ($120k-$400k), plus a financing fee when the LTB is funded against the customer's PO. Not a subscription.</t>
+        </is>
+      </c>
+      <c r="G22" s="21" t="inlineStr">
+        <is>
+          <t>The record's '90 days, no product required for revenue' is credible for the first quotes — a broker can transact on day one. What it cannot compress is (a) becoming an approved supplier: a medical-device or rail OEM must qualify you into its AVL, which is a 6-12 month quality audit, and DoD/DLA adds CAGE, AS6081 counterfeit-avoidance evidence and ITAR handling; (b) working capital — every additional simultaneous LTB position ties up cash, so growth is financed, not just sold. Y1 of 4 assumes two founders who already carry component-industry relationships closing back-to-back deals with no inventory risk. Growth of roughly 1.5-1.8x thereafter is what a desk of senior sourcing people plus a component engineer can actually service; each customer is a bespoke technical problem, not a signup. Y5 of 60 is 2% of my estimated 3,000-entity universe — deliberately small, because the incumbents (Rochester and the authorised aftermarket) hold the licences and die banks and will win the parts a buyer can get through them.</t>
+        </is>
+      </c>
+      <c r="H22" s="21" t="inlineStr">
+        <is>
+          <t>My own reasoning. Blended: brokered parts at a 20-25% spread (distribution economics — you are a price-taker whenever the authorised channel still has stock), engineering/TDP work at ~45% (senior humans in the loop), financing fees near-pure margin but small. Weighted to ~32%. This is a distribution business, not software, and the record's own kill risk says so: 'a distribution startup with a software brochure.'</t>
+        </is>
+      </c>
+      <c r="I22" s="21" t="inlineStr">
+        <is>
+          <t>The spread per brokered lot. At a 25% spread the Y5 line is ~$21M revenue / ~$6.7M gross profit; at 12% — which is what you get if the authorised aftermarket can still supply the part and you are merely a second quote — the same 60 customers produce under $2.5M of gross profit and the business cannot fund its own inventory. Everything turns on selling into the window where the part is genuinely unobtainable through licensed channels, not merely expensive.</t>
+        </is>
+      </c>
+      <c r="J22" s="21" t="inlineStr">
+        <is>
+          <t>Bear case: you never clear the AVL/quality-audit gate at regulated OEMs fast enough, so you sell to whoever will buy on a spot basis, at spot margins. You end up a ~$3-5M/yr revenue independent component broker with ~12-15% margins, ~$600k of gross profit, a balance sheet long DDR4 bought near a cyclical top (the record's own why-now describes DRAM at +90% in Q1 2026 and DDR5 ~4x on the year — that is the top, not the bottom), and one counterfeit-escape claim away from insolvency. Y5 revenue ~$4M, gross profit under $700k.</t>
+        </is>
+      </c>
+      <c r="K22" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="L22" s="21" t="inlineStr">
+        <is>
+          <t>No search access this session. The buyer universe is entirely my structural reasoning and could be off by 2x in either direction. The ACV is reasoned from how last-time-buy lots are typically sized, not from any quoted price — the record contains no price point. Confidence is materially higher on the direction (EOL pressure is real and dated in the record) than on either number. The record's own market figures are self-flagged as unverified, so I gave them no weight.</t>
+        </is>
+      </c>
+      <c r="M22" s="10" t="inlineStr">
+        <is>
+          <t>last-time-buy-dmsms-desk</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="76" customHeight="1">
+      <c r="A23" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="23" t="inlineStr">
+        <is>
+          <t>Battery Passport plumbing: supplier data chase, EPCIS event store, GS1-conformant resolver</t>
+        </is>
+      </c>
+      <c r="C23" s="23" t="inlineStr">
+        <is>
+          <t>The regulatory-affairs or EU-market-access manager at a mid-size economic operator placing batteries above 2 kWh on the EU market — a European industrial/stationary-storage integrator, an LMT (e-bike/e-scooter) brand importing Asian packs, or a second-tier EV/commercial-vehicle maker. Precisely the profile the record names: 'a mid-size EV or industrial battery importer selling into the EU with no in-house compliance headcount — not VW or CATL.' The cheque comes out of a compliance/market-access line, and the trigger for signing is a customs or customer-contract requirement, not a sustainability initiative.</t>
+        </is>
+      </c>
+      <c r="D23" s="23" t="inlineStr">
+        <is>
+          <t>My own reasoning — the record states no buyer count. Structure: the obligation attaches to whoever places the battery on the EU market. I estimate ~30 EV OEM groups (mostly unwinnable, already inside Catena-X/Cofinity-X), ~150 cell and pack manufacturers selling into the EU, ~800-1,200 stationary-storage/BESS and industrial-battery integrators and importers, and ~800-1,000 LMT brands and importers above the 2 kWh threshold. Net of the large accounts that will build in-house or ride Catena-X, I put the realistically sellable universe at ~2,500 entities. Textiles and electronics under ESPR would expand this later, but I have deliberately not counted a market that has no dated obligation in the record.</t>
+        </is>
+      </c>
+      <c r="E23" s="23" t="inlineStr">
+        <is>
+          <t>My own reasoning, anchored on the record's stated pricing unit: 'Price per supplier onboarded.' Assumption: a mid-size importer must chase 20-60 tier-1/2/3 suppliers for missing attributes; at $800-1,500 per supplier onboarded that is $25-70k of first-year onboarding labour, plus a hosted resolver + EPCIS event store subscription I put at $20-35k/yr (per-GTIN-served pricing). Blended first-year contract ~$60-70k, settling to ~$40-45k recurring as onboarding tapers to re-attestation and new-supplier adds. I model $55k as the steady blended ACV. No price point appears in the record.</t>
+        </is>
+      </c>
+      <c r="F23" s="23" t="inlineStr">
+        <is>
+          <t>Per-supplier-onboarded fee (one-off per supplier, recurring as the supplier base churns and re-attests) plus an annual managed-service subscription for the conformant resolver and EPCIS 2.0 event store, tiered on GTINs served.</t>
+        </is>
+      </c>
+      <c r="G23" s="23" t="inlineStr">
+        <is>
+          <t>The free validator/conformance-checker wedge generates inbound cheaply (the record's dppvalidator precedent), so top-of-funnel is not the constraint — delivery is. Each paid customer means chasing dozens of named tier-2/tier-3 contacts across languages; that is human work and it gates growth harder than sales does. Y1 of 6 reflects a 1-3 person team landing design partners in the run-up to the (record-flagged UNVERIFIED) 18 Feb 2027 date. Y2 jumps to 25 on deadline panic — compliance software's one reliable demand spike is the quarter before enforcement. Y3-Y5 growth then decelerates to ~1.5x because the panic cohort is bought and the rest of the market is either inside Catena-X or too small to pay. Y5 of 130 is ~5% of my estimated 2,500-entity universe. I would not model above that: an unbranded plumbing vendor does not become the default for a fifth of a regulated market in five years.</t>
+        </is>
+      </c>
+      <c r="H23" s="23" t="inlineStr">
+        <is>
+          <t>My own reasoning. Two-part cost structure: the resolver and event store are software with ~80-85% margin (openEPCIS is Apache-licensed, so build cost is low), but supplier chasing is labour — reminder emails, phone calls in six languages, extracting values from PDFs — and I put that at 30-40% margin even with heavy LLM extraction. Roughly 50/50 revenue mix gives ~55% blended. The record's kill risk makes exactly this point: 'the labour-intensive tier-3 supplier data chase with no software margin.'</t>
+        </is>
+      </c>
+      <c r="I23" s="23" t="inlineStr">
+        <is>
+          <t>Whether the February 2027 obligation date holds as stated — the record explicitly flags it as UNVERIFIED ('neither scout could open the primary legal text this session... that date is UNVERIFIED'). A one-year delay, or an Omnibus-style scope softening of the kind the record notes hit CSRD in 2025, removes the deadline spike entirely: Y2 falls from 25 to ~10 and Y5 from 130 to roughly 50, cutting Y5 revenue from ~$7M to under $3M. Secondary: whether Catena-X/Cofinity-X extends down-market and takes the mid-tier for free.</t>
+        </is>
+      </c>
+      <c r="J23" s="23" t="inlineStr">
+        <is>
+          <t>Bear case: the deadline slips or GS1 commoditises the resolver as a member utility (the record's kill risk), leaving you with only the supplier data chase — a 35%-margin BPO with no pricing power and no software story. You land ~40-50 customers by Y5 at a compressed ~$30k ACV as buyers refuse to pay software prices for labour, giving ~$1.5M revenue and ~$550k gross profit. That is a consultancy, and it is not fundable.</t>
+        </is>
+      </c>
+      <c r="K23" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="L23" s="23" t="inlineStr">
+        <is>
+          <t>Low on purpose. The buyer universe is a genuine guess built from structure with no search access. The ACV is reasoned from a stated pricing *unit* but no stated price. And the load-bearing regulatory date is flagged unverified in the record itself, which means the ramp shape — not just its level — is unconfirmed. I would not put money behind these numbers before someone opens the Official Journal text.</t>
+        </is>
+      </c>
+      <c r="M23" s="12" t="inlineStr">
+        <is>
+          <t>gs1-dpp-event-and-resolver-backbone</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="76" customHeight="1">
+      <c r="A24" s="10" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="21" t="inlineStr">
+        <is>
+          <t>Sealed-at-capture evidence for insurance claims and field inspection</t>
+        </is>
+      </c>
+      <c r="C24" s="21" t="inlineStr">
+        <is>
+          <t>The VP of Claims Operations or the SIU (special investigations unit) director at a regional P&amp;C carrier, and the operations lead at a large independent appraisal/adjusting firm. Critically, the buyer must be the party that controls the capture app — which is why the record's beachhead list (auto physical damage appraisal, auto glass, roof inspection, equipment-finance collateral condition reports) is right: in those workflows the payer owns the phone the photo is taken on. A carrier that sends claimants to a third-party app cannot mandate your SDK.</t>
+        </is>
+      </c>
+      <c r="D24" s="21" t="inlineStr">
+        <is>
+          <t>My own reasoning/recall, not researched — the record states no buyer count. My recall is that the US has on the order of 2,500 licensed P&amp;C insurers but only ~350-400 independent buying groups writing meaningful auto or property volume, since subsidiaries buy at group level. Add ~100 large independent adjuster/appraisal firms, a few hundred auto-glass and roofing networks and TPAs, and equipment-finance lenders needing collateral condition reports, plus a comparable European tier. I put the addressable buying-entity count at ~1,200. Treat this as an estimate with a wide band.</t>
+        </is>
+      </c>
+      <c r="E24" s="21" t="inlineStr">
+        <is>
+          <t>My own reasoning, anchored on the record's stated unit: 'Price per verified capture.' Assumption: a regional carrier handling ~50,000 auto/property claims a year captures roughly 8-12 media files per claim, so 400-600k sealed captures annually; at $0.15-0.25 per verified capture that is $60-150k, plus a $30-50k platform/intake-portal floor. I model $120k blended ACV. Large IA firms and glass networks land lower ($40-70k); a top-25 carrier would be $400k+, but I am not modelling those as landable in five years. No price appears in the record.</t>
+        </is>
+      </c>
+      <c r="F24" s="21" t="inlineStr">
+        <is>
+          <t>Usage-based annual contract: per-verified-capture metering with a platform minimum. Sold as fraud-loss reduction, not as signatures — the record is explicit that this is the framing.</t>
+        </is>
+      </c>
+      <c r="G24" s="21" t="inlineStr">
+        <is>
+          <t>Insurance is the slowest enterprise buyer in this batch. A carrier deal means a 9-15 month cycle, a security/vendor-risk review that in practice requires SOC 2 Type II before production data touches your system, and integration into the claims system the adjuster actually lives in — CCC, Solera, Guidewire, Duck Creek. Y1 of 2 matches the record's own plan ('Land one regional carrier or one large independent adjuster firm as design partner') — one design partner plus one paid pilot. Growth of ~2x then ~1.6x reflects that each reference unlocks peers slowly in a conservative buying community. Y5 of 42 is ~3.5% of my estimated universe; I capped it there because the record's kill risk is the strongest in this batch — Truepic has sold sealed-at-capture into insurance for a decade and the category has not broken out, which is evidence about how carriers buy, not about the technology.</t>
+        </is>
+      </c>
+      <c r="H24" s="21" t="inlineStr">
+        <is>
+          <t>My own reasoning. Mostly software: SDK, signing, timestamp anchoring and verification are cheap per capture (the record concedes 'the cryptography is collapsing to free'). Costs are media storage/egress at scale, timestamp-authority fees, and a real solutions/support team for every carrier integration. 75% is software-with-heavy-support, not the 85% of pure self-serve. If the intake portal grows a human-review queue for flagged submissions, this drifts toward 65%.</t>
+        </is>
+      </c>
+      <c r="I24" s="21" t="inlineStr">
+        <is>
+          <t>Attach-rate risk: whether carriers buy a standalone SDK at all, or simply wait for CCC/Solera/Guidewire/Duck Creek to ship attested capture as a checkbox inside the system they already own. If the incumbents ship it in years 2-3, new logos stop and your existing ones do not renew — Y5 collapses from 42 to under 10 regardless of product quality. The second-order version is that you must sell *through* those platforms as a partner, which halves effective ACV.</t>
+        </is>
+      </c>
+      <c r="J24" s="21" t="inlineStr">
+        <is>
+          <t>Bear case: pilot purgatory. Carriers run 6-month paid pilots at $25-40k, produce a positive-but-not-decisive fraud-reduction number, and never expand because attested capture is a policy change (rejecting unsealed media) that no single claims VP has authority to make. You reach ~8-12 customers at ~$50k by Y5 for $500-600k of revenue, and get acqui-hired by a claims platform for the SDK. Y5 revenue under $1M.</t>
+        </is>
+      </c>
+      <c r="K24" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="L24" s="21" t="inlineStr">
+        <is>
+          <t>The buyer universe is reasoned from recall of P&amp;C market structure and could easily be 800 or 1,800. The ACV is built from an assumed claim volume times an assumed per-capture price — both mine, neither in the record. What raises this above 3 is that the record supplies unusually concrete demand-side evidence I can quote ('98% of insurers say AI editing tools are fuelling digital fraud', 'only 32% feel very confident detecting deepfakes'), so the pain is documented even though the willingness-to-pay is not.</t>
+        </is>
+      </c>
+      <c r="M24" s="10" t="inlineStr">
+        <is>
+          <t>attested-capture-for-claims-media</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="76" customHeight="1">
+      <c r="A25" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="23" t="inlineStr">
+        <is>
+          <t>Neutral clearing house for the HTTP 402 crawler economy</t>
+        </is>
+      </c>
+      <c r="C25" s="23" t="inlineStr">
+        <is>
+          <t>Revenue is netted from settlement, so name both sides but count the payer: the data-acquisition or partnerships lead at an AI or agent company that needs licensed access to the long tail of the web and cannot negotiate ten thousand bilateral deals — mid-tier model labs, agent and answer-engine startups, and enterprise RAG/crawl vendors. The supply side (long-tail publishers: trade publications, recipe and how-to sites, specialist databases, regional publishers) signs a distribution agreement, not a cheque; they are inventory, and the record is right that the buy side 'wants one integration not ten thousand.'</t>
+        </is>
+      </c>
+      <c r="D25" s="23" t="inlineStr">
+        <is>
+          <t>My own reasoning — the record gives no buyer count, only a supply-side ambition ('200 long-tail publishers... plus 3 AI/agent companies on the buy side' in 90 days). Structure of the paying side: ~10 frontier labs (mostly do bilateral deals and are explicitly not your customer), ~50 well-funded model startups, ~200-300 agent/answer-engine/vertical-AI companies with real crawl budgets, ~100-200 enterprise data and RAG vendors. I put entities that would ever pay a clearing house at ~400. This is the binding constraint on the business, and it is small.</t>
+        </is>
+      </c>
+      <c r="E25" s="23" t="inlineStr">
+        <is>
+          <t>My own reasoning, and I am deliberately departing from the record's stated pricing. The record says 'Charge basis points on settled access' — at literal basis points (1-2%) this business cannot exist on a thin pool, so I model a collecting-society/ad-network take rate of ~15%. Assumption: an average paying buyer settles ~$300k/yr of catalog-wide long-tail access; 15% of that is ~$45k of net revenue to the clearing house per buyer. I model net revenue as ACV, not GMV — the take, not the flow. Note the record's own warning that 'per-crawl micropayments to recipe blogs are pennies', which is a direct challenge to the $300k settled-spend assumption.</t>
+        </is>
+      </c>
+      <c r="F25" s="23" t="inlineStr">
+        <is>
+          <t>Take rate on settled access (I model ~15%, versus the record's stated 'basis points'), charged against gross settlement flowing from AI buyers to publishers. Possible secondary: a flat platform fee on the agent-side SDK for spend policy and audit ledger.</t>
+        </is>
+      </c>
+      <c r="G25" s="23" t="inlineStr">
+        <is>
+          <t>Y1 of 3 is taken straight from the record's own 90-day plan ('3 AI/agent companies on the buy side'), and is the right order of magnitude — a clearing house is worthless until the catalog is deep, so the first year is spent buying supply with free open-source distribution into the Anubis install base. Y2-Y3 growth is fast in logo count because onboarding an AI buyer is an API key, not a procurement cycle. But it decelerates hard by Y4-Y5: the paying universe is only ~400, the top of it does bilateral deals instead, and every quarter Cloudflare does not build this is a quarter it might. Y5 of 80 is 20% of my estimated payer universe — high, and I would only defend it because neutrality genuinely is worth something to a buyer who does not want to settle through the party that also gatekeeps them. Anything above 100 I would call dreaming.</t>
+        </is>
+      </c>
+      <c r="H25" s="23" t="inlineStr">
+        <is>
+          <t>My own reasoning. Net-revenue margin on a payments rail: costs are payment processing and FX on paying out thousands of small publisher balances, dispute and reconciliation operations (the record's differentiating 'independent reconciliation report' is human work), and hosting the metering plane. 72% is typical for a take-rate marketplace that actually moves money; it would be 85% if you only metered and let someone else settle, but then you are not the clearing house.</t>
+        </is>
+      </c>
+      <c r="I25" s="23" t="inlineStr">
+        <is>
+          <t>Settled spend per buyer — i.e. whether long-tail crawl access clears at any meaningful price at all. My $300k/buyer/yr assumption is the whole model: at $60k/buyer (the 'pennies for recipe blogs' scenario the record warns about), Y5 net revenue falls from ~$3.6M to ~$720k and this is a project, not a company. Secondarily, the take rate: at the record's literal 'basis points' the business is dead on arrival at any plausible volume.</t>
+        </is>
+      </c>
+      <c r="J25" s="23" t="inlineStr">
+        <is>
+          <t>Bear case: Cloudflare meters and settles for free from inside the request path, RSL Collective keeps the publisher coalition, and Skyfire/x402 own the agent wallet — the record names all three. You are left aggregating the sites nobody wants to pay for, at prices that do not cover reconciliation labour. Y5 lands at 20-30 buyers, ~$50k settled spend each, ~$250k of net revenue. The realistic exit is a small acqui-hire of the open-source Anubis/Caddy distribution.</t>
+        </is>
+      </c>
+      <c r="K25" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="L25" s="23" t="inlineStr">
+        <is>
+          <t>Lowest in this batch alongside the DPP one. Both the payer universe and the settled-spend-per-buyer figure are my own guesses with no search access, and the second one swings Y5 revenue by 5x. The record itself flags that the merged candidate's 'claims about x402, RSL and Cloudflare launch timing were self-flagged by its scout as unverified model knowledge.' The one number I trust — 'more than a billion HTTP 402 Payment Required responses per day' — measures blocked demand, not willingness to pay, and I have deliberately not converted it into revenue.</t>
+        </is>
+      </c>
+      <c r="M25" s="12" t="inlineStr">
+        <is>
+          <t>crawler-payment-clearing-and-metering</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="76" customHeight="1">
+      <c r="A26" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="21" t="inlineStr">
+        <is>
+          <t>Killing lead-line 'unknowns' before the Nov 1, 2027 LCRI baseline locks in</t>
+        </is>
+      </c>
+      <c r="C26" s="21" t="inlineStr">
+        <is>
+          <t>Primary (where the money is): the utility director, distribution-system engineer, or compliance manager at a mid-size community water system serving roughly 10,000-500,000 people that is carrying thousands of 'unknown' service lines into the 1 November 2027 baseline. They sign a professional-services contract out of a capital or compliance budget, usually via RFP or under a sole-source threshold. Secondary (volume, not revenue): the part-time operator at a system serving under 3,300 people — the record's memorable 'part-time operator who also drives the plow truck' — who buys the $200/month paperwork tool on a card, often steered there by a state primacy agency or rural water association.</t>
+        </is>
+      </c>
+      <c r="D26" s="21" t="inlineStr">
+        <is>
+          <t>My own reasoning/recall for the primary tier; the record gives national unknowns but no buyer count. Recall: the US has roughly 50,000 community water systems, of which the large majority serve under 3,300 people. The mid-size band (10k-500k population served) I estimate at ~4,000-5,000 systems — I model 4,500 as the primary buyer universe. The secondary self-serve tier is much larger: on the order of 40,000+ small community systems plus NTNCWSs, consistent with the record's 'tens of thousands of tiny systems'. I have deliberately built the projection on the 4,500 primary tier because that is where the ACV lives; the record's stated demand-side scale — 'an estimated 3.5-6.6 million unknown lines nationally' and Wisconsin alone with 'more than 181,000... about 12% statewide' still unknown — confirms the pain exists but is not a buyer count.</t>
+        </is>
+      </c>
+      <c r="E26" s="21" t="inlineStr">
+        <is>
+          <t>My own reasoning for the primary tier; the record states a price only for the secondary tier ('a $200/month self-serve version', i.e. $2,400/yr). Assumption for the primary: a fixed-price unknowns-reduction engagement covering ~2,000-4,000 unknown lines — predictive targeting model, subcontracted vacuum-excavation potholing on the residual, and the regulatory documentation package — prices at $180-300k, of which roughly $90-130k is passed through to the excavation crew. I model $220k. A ~$50-80k/yr annual reporting and progress-tracking tail follows for the decade to 2037, which is why I call this repeating rather than one-off.</t>
+        </is>
+      </c>
+      <c r="F26" s="21" t="inlineStr">
+        <is>
+          <t>Fixed-price per unknowns-reduction engagement (not the record's proposed 'share of avoided replacement obligation' — see key sensitivity), plus an annual retainer for the mandatory inventory update, replacement-plan document and customer notifications. Separate self-serve SaaS tier at the record's stated $200/month for small systems.</t>
+        </is>
+      </c>
+      <c r="G26" s="21" t="inlineStr">
+        <is>
+          <t>This ramp is a plateau, not a curve, and that is the honest shape. Y1 of 5 is exactly the record's plan ('sell a fixed-price unknowns reduction engagement to five mid-size utilities') and is achievable in one state where two people can work the primacy agency and rural water association relationships. Y2 peaks the growth because the 1 November 2027 baseline creates a genuine panic quarter. Then the clock runs out: after the baseline locks, the pitch changes from 'kill your unknowns before they are counted as lead' — an urgent, quantifiable arbitrage — to 'help manage a ten-year replacement program', which is ordinary municipal engineering work that Black &amp; Veatch and every regional firm already sells. Delivery also caps growth: each engagement needs a subcontracted hydro-excavation crew working a dig season, and crews are the scarce input. Y5 of 24 is 0.5% of the 4,500-system primary universe — tiny, and appropriate for a two-person firm competing against established engineering consultancies with existing municipal contract vehicles.</t>
+        </is>
+      </c>
+      <c r="H26" s="21" t="inlineStr">
+        <is>
+          <t>My own reasoning. Services with senior humans plus a large subcontractor passthrough: vacuum-excavation potholing is roughly 40-50% of contract value at real field rates, and the predictive model only reduces the number of holes, it does not eliminate them. Netting crew cost and the in-house engineer/analyst time gives ~40%. The self-serve $200/month tier runs at ~80% but will be a small share of revenue for years.</t>
+        </is>
+      </c>
+      <c r="I26" s="21" t="inlineStr">
+        <is>
+          <t>Contract structure. The record's own kill risk is the right one: 'the outcome-priced share of avoided replacement obligation model is largely uncontractable in public procurement.' If municipalities will only buy this on a time-and-materials basis through the standard engineering-services vehicle, ACV compresses from ~$220k to ~$120k and margin from 40% to ~30%, halving Y5 gross profit — and worse, you are then selling the same product as incumbent firms who already hold the contract vehicles. The fix is fixed-price-per-engagement, which is contractable; I have modelled that instead of the contingency structure.</t>
+        </is>
+      </c>
+      <c r="J26" s="21" t="inlineStr">
+        <is>
+          <t>Bear case: procurement forces you into T&amp;M subcontracting for the incumbent engineering firms rather than prime contracting for the utility, so you capture analyst rates on the predictive model and nothing on the field work. Meanwhile the $200/month tier converts poorly because state primacy agencies publish free templates that are good enough for a system with 400 connections. You land ~12 engagements by Y5 at ~$110k with ~30% margin, roughly $1.3M of revenue and $400k of gross profit — a viable two-person consultancy, not a venture outcome. Note also that the entire urgency thesis has a hard expiry: after November 2027 the arbitrage this business sells no longer exists in the same form.</t>
+        </is>
+      </c>
+      <c r="K26" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="L26" s="21" t="inlineStr">
+        <is>
+          <t>Highest in this batch, though still modest. Two things help: the record states a real price point I could anchor on ($200/month) and a real Y1 target (five utilities), and my recall of US water-system structure — roughly 50,000 community systems, heavily skewed small — is reasonably firm even without search. What remains genuinely uncertain is the mid-size ACV, which is my own estimate of what a fixed-price unknowns engagement clears at, and the post-2027 revenue durability, which I have modelled pessimistically as a plateau.</t>
+        </is>
+      </c>
+      <c r="M26" s="10" t="inlineStr">
+        <is>
+          <t>lead-service-line-inventory-2027</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:M26"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="85" customWidth="1" min="4" max="4"/>
+    <col width="85" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="45" t="inlineStr">
+        <is>
+          <t>An independent skeptic was given each model and asked to find the single assumption doing too much work, then to state a specific haircut and recompute year 5. This is the number to argue with first.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>Opportunity</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Most optimistic assumption</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>Why it is optimistic</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>Suggested haircut</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>Y5 revenue after haircut</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="72" customHeight="1">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>datacenter-as-grid-entity-compliance</t>
+        </is>
+      </c>
+      <c r="B4" s="21" t="inlineStr">
+        <is>
+          <t>Ride-through models and curtailment proof for NERC-registered data centers</t>
+        </is>
+      </c>
+      <c r="C4" s="21" t="inlineStr">
+        <is>
+          <t>acv_usd = $275,000 applied as a flat portfolio average to every one of the 45 Y5 campuses. The record's quoted band ('roughly $150k-$600k a campus with mandatory re-validation after every trip event') is the price of the ONE-TIME build: dynamic model + disturbance testing + attestation package. The model's own pricing_model then concedes the follow-on is 'a smaller annual re-validation retainer and a per-campus metering/curtailment-record subscription' — but never applies that smaller number to anyone.</t>
+        </is>
+      </c>
+      <c r="D4" s="21" t="inlineStr">
+        <is>
+          <t>The ramp 4/10/20/32/45 has increments of 6/10/12/13, which is the shape of a cumulative installed base, not 45 fresh engagements. On that reading only ~13 of the 45 Y5 campuses are first-time full-scope builds and 32 are on the retainer. Blended: (13 x $275k + 32 x ~$60k) / 45 = ($3.575M + $1.92M) / 45 = ~$122k, not $275k. Take the other fork — that all 45 really are fresh builds — and the model breaks somewhere worse: cumulative campuses served hits 4+10+20+32+45 = 111, which is ~43% of the ~260 real ERCOT campuses the buyer_universe_basis itself derives, from a two-founder boutique, against Burns &amp; McDonnell and POWER holding MSAs on the top 20 developers. There is no reading where both the ACV and the count survive. Secondary: the ramp_rationale is internally inconsistent — 45 campuses at the stated '4-6 campus engagements a year' per engineer needs 9-11 billable engineers, not the '~25-28' the same paragraph claims, so the delivery model has not actually been costed.</t>
+        </is>
+      </c>
+      <c r="E4" s="21" t="inlineStr">
+        <is>
+          <t>acv_usd: $275,000 -&gt; $125,000 (blended portfolio average across ~13 new full-scope builds at $275k and ~32 accounts on a ~$60k re-validation + metering retainer). Hold customers_y5 at 45.</t>
+        </is>
+      </c>
+      <c r="F4" s="31" t="n">
+        <v>5625000</v>
+      </c>
+    </row>
+    <row r="5" ht="72" customHeight="1">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>long-tail-customs-entry-and-duty-recovery</t>
+        </is>
+      </c>
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t>Entry Type 13 and instrument-aware duty recovery for the post-de-minimis long tail</t>
+        </is>
+      </c>
+      <c r="C5" s="23" t="inlineStr">
+        <is>
+          <t>The 350 entries per account per year buried inside acv_usd = $8,000. The $15/entry price is quoted from the record and is fine; the volume is pure invention, and the model admits it ('Nothing in the record pins this number'). 350 entries/year is ~7 per week — an inbound customs entry every single business day, at a merchant doing $1-20M of imports.</t>
+        </is>
+      </c>
+      <c r="D5" s="23" t="inlineStr">
+        <is>
+          <t>A $1-20M/year SMB importer typically consolidates: containers or LCL loads arriving one to four times a month from a handful of suppliers, i.e. 15-60 entries/year at the low end and maybe 150-300 at the $20M top end. The median is nowhere near 350. The only way to reach 350 is to assume each direct-ship parcel becomes its own billable formal entry — but that is precisely the flow DHL/UPS/FedEx clear inside their own network as a bundled service, which the model's own downside_note identifies as the thing that takes those merchants away. So the volume assumption double-books: it needs parcel-level entries to hit 350, and it needs those same parcels not to be captured by the carriers. Note also what this does to the mix — at 100 entries the account is a $1,500 filing relationship wrapped around a $2,000 catalogue subscription, i.e. a small SaaS business, not the transaction engine the model describes, and 300k entries/year instead of 1.05M changes the licensed-broker supervision story too.</t>
+        </is>
+      </c>
+      <c r="E5" s="23" t="inlineStr">
+        <is>
+          <t>acv_usd: $8,000 -&gt; $4,000, via entries per account per year 350 -&gt; 100 (100 x $15 = $1,500 transaction + ~$2,000 catalogue subscription + ~$500 blended recovery attach). Hold customers_y5 at 3,000.</t>
+        </is>
+      </c>
+      <c r="F5" s="36" t="n">
+        <v>12000000</v>
+      </c>
+    </row>
+    <row r="6" ht="72" customHeight="1">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>nuclear-naval-supplier-qualification</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>NQA-1 qualification and commercial grade dedication as a service</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>The ramp: customers 5 -&gt; 14 -&gt; 28 -&gt; 45 -&gt; 65, a 13x expansion over four years, sold as $110k of speculative capex to owner-operated 50-400 person machine shops that hold no nuclear order.</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>The model correctly names the risk in key_sensitivity ('whether shops will buy qualification ahead of holding an award') and then does not discount the curve for it at all. Three compounding drags: (1) qualification takes 12-36 months and the payoff is 2028-2031 SMR fabrication, and the base rate for nuclear FOAK schedules is slipping right, not left — a single year of slip pushes the entire Y3-Y5 acceleration out a year; (2) $110k with no attached revenue competes directly against a machine tool in a shop owner's capital budget, and unlike a compliance deadline there is no date forcing the decision, so the sale is discretionary and the close rate is low; (3) delivery is auditor-limited at 6-8 sprints/year per ex-NUPIC lead auditor, and that labour pool is small and mostly employed by utilities and NUPIC members — 65 accounts needs 4-5 of them, hired by a three-person startup. Also worth flagging as a second-order haircut: at 65 accounts only ~20 are new sprints and ~45 are on the $40k retainer, so the true blended ACV is nearer $70k than $95k even before the count is cut. I am haircutting the count rather than the ACV because the count is the one the model itself flagged and then ignored.</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>customers_y5: 65 -&gt; 30 (and correspondingly Y3 28 -&gt; 15, Y4 45 -&gt; 22), reflecting one year of SMR FOAK slip and a discretionary-capex close rate. Hold acv_usd at $95,000.</t>
+        </is>
+      </c>
+      <c r="F6" s="31" t="n">
+        <v>2850000</v>
+      </c>
+    </row>
+    <row r="7" ht="72" customHeight="1">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>biosolids-outlet-exchange</t>
+        </is>
+      </c>
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t>PFAS-Compliant Biosolids Outlet Exchange for the Mid-Atlantic</t>
+        </is>
+      </c>
+      <c r="C7" s="23" t="inlineStr">
+        <is>
+          <t>The ~12-13% retained take rate on contract value inside acv_usd = $200,000 (~$10 per wet ton on a ~$60-90/ton contract). The record states no price at all, so this entire number is three of the modeller's own estimates multiplied together, and the take rate is the one carrying the business.</t>
+        </is>
+      </c>
+      <c r="D7" s="23" t="inlineStr">
+        <is>
+          <t>A 12-13% retained spread is a value-added-logistics margin, and this is not a value-added-logistics business. The broker owns no trucks, no landfill airspace, no dryers, no exclusivity and no proprietary data — the record's own kill_risk says so. Comparable bulk-haul and freight brokerage nets in the mid-single digits once the counterparty can see the underlying rate, and a POTW buying through an RFP with a board vote will get competing bids from Synagro and Denali, who own the outlets and can quote net. Worse, the spread is levered the wrong way: it is retained on a FIRM per-ton price against non-exclusive spot outlets in a market where PFAS thresholds are actively removing outlets, so the modelled $10/ton is the good-quarter number and the bad-quarter number is negative. The model's own key_sensitivity concedes compression 'from ~$10/ton toward ~$3/ton' and then keeps $10 in the ACV. Customer count is not the issue here — the ramp was already honestly discounted for municipal procurement.</t>
+        </is>
+      </c>
+      <c r="E7" s="23" t="inlineStr">
+        <is>
+          <t>acv_usd: $200,000 -&gt; $85,000, via take rate 12-13% -&gt; 5% of contract value (~18,000 wet tons x ~$80/ton = ~$1.4M GMV x 5% = ~$72k retained, plus ~$13k blended source-control audit). Hold customers_y5 at 42.</t>
+        </is>
+      </c>
+      <c r="F7" s="36" t="n">
+        <v>3570000</v>
+      </c>
+    </row>
+    <row r="8" ht="72" customHeight="1">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>cra-embedded-sbom-and-cve-triage</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>Reachability-grade SBOMs and kernel-CVE triage for embedded Linux</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>The '~2.5 device families per account at steady state' multiplier inside acv_usd = $55,000. The pricing unit is quoted from the record and the ~$22k per-family price is at least reasoned from displaced engineer cost; the 2.5 is an unanchored expansion assumption applied uniformly to the entire Y5 base, and it is 60% of the ACV.</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>'Steady state' is doing the work in a base that is nowhere near steady state. With the ramp 8/35/95/190/320, the Y5 base is ~40% new-in-year and average account tenure is roughly 1.5 years — but land-and-expand from one family to 2.5 is a 3+ year motion, gated on the vendor building each additional SoC/BSP family, which the model itself says is 'an engineering project' and the binding cap on growth. So the same engineering constraint that caps the customer count is being ignored when counting families per customer: you cannot simultaneously be SoC-onboarding-limited on new logos and assume every logo effortlessly reaches 2.5 supported families. Expansion also fights the buyer's own incentive — a manufacturer that has watched one family through a full triage cycle has strong reason to consolidate BSPs or run family two in-house, especially with Yocto's own CVE tooling, grype/trivy and the SoC vendor's bundle sitting at zero. A realistic blended figure across a base of this age profile is 1.4-1.6 families.</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="inlineStr">
+        <is>
+          <t>acv_usd: $55,000 -&gt; $33,000, via device families per account 2.5 -&gt; 1.5 at the modelled ~$22k per family. Hold customers_y5 at 320 and the $22k price level.</t>
+        </is>
+      </c>
+      <c r="F8" s="31" t="n">
+        <v>10560000</v>
+      </c>
+    </row>
+    <row r="9" ht="72" customHeight="1">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>funded-claim-detection-for-casualty</t>
+        </is>
+      </c>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>Funded-Claim Detection for Casualty Reserving</t>
+        </is>
+      </c>
+      <c r="C9" s="23" t="inlineStr">
+        <is>
+          <t>acv_usd of $125,000, which is a blend that assumes the mix shifts toward the $175k-$250k FNOL claim-scoring feed in years 3-5.</t>
+        </is>
+      </c>
+      <c r="D9" s="23" t="inlineStr">
+        <is>
+          <t>The $125k blend requires per-claim linkage to work, and the record's own kill_risk calls that linkage 'the hard, unsolved part.' The model prices an unsolved technical problem at roughly 50/50 and then assumes that on top of solving it, a majority of the Y5 base has migrated from the $50-60k report to the API SKU. Two independent conditional events are being treated as one near-certainty. Note also the internal tension: the model's own key_sensitivity says firm-level-only output 'caps Y5 revenue near $2M' — which is almost exactly where my haircut lands, meaning the base case and the model's own stated failure mode differ by 2.3x on a single unresolved fact. Secondary concern I am not haircutting: buyer_universe of 250 counts US P&amp;C groups ranked 100-200, which are regional writers with limited excess/umbrella exposure and no reserving-analytics budget for a novel $125k feed; the realistically-signable set is closer to 120, which would make Y5 of 36 a 30% penetration rather than 14%.</t>
+        </is>
+      </c>
+      <c r="E9" s="23" t="inlineStr">
+        <is>
+          <t>acv_usd: $125,000 -&gt; $80,000. Derivation (my own reasoning, not researched): report SKU $55k; scoring feed $200k (midpoint of the model's own $175-250k); probability case-level linkage actually ships ~40%, given the record concedes it is unsolved; conditional share of the Y5 base upgraded to the feed ~50%, since the model itself says expansion lags logo count by a year. Expected feed share = 0.40 x 0.50 = 20%. Blend = 0.20 x $200k + 0.80 x $55k = $40k + $44k = $84k, rounded to $80k.</t>
+        </is>
+      </c>
+      <c r="F9" s="36" t="n">
+        <v>2880000</v>
+      </c>
+    </row>
+    <row r="10" ht="72" customHeight="1">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>grid-equipment-slot-forward-exchange</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>Forward exchange for transformer and switchgear production slots</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
+        <is>
+          <t>buyer_universe of 600, constructed as '3x the distressed sell side,' and then used as the denominator for the 13% Y5 penetration sanity check that justifies 78 transacting counterparties.</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t>The buy side is not the constraint and never was. Every trade requires a distressed seller with an orphaned slot, and the record states that population directly: 'roughly 200 datacenter, BESS and utility developers with cancelled or delayed projects.' Sizing the market off the larger, unconstrained side and calling 13% penetration 'modest' inverts the actual bottleneck. Worse, the pool is self-liquidating — the model says so itself — so the 200 is a stock being drawn down, not a renewable flow. The base case implies 78 counterparties x 1.2 assignments = roughly 94 closed assignments in year 5, about two per week, each needing a distressed seller, a matched buyer, OEM consent, and counsel on both sides. The record's own softer bear case says 25-30 trades a year. This is also the largest Y5 number of the five opportunities and it comes from a founder-brokered desk with no product.</t>
+        </is>
+      </c>
+      <c r="E10" s="21" t="inlineStr">
+        <is>
+          <t>buyer_universe: 600 -&gt; 200 (the sell-side count the record states, since no trade exists without a distressed seller). Holding the model's own 13% Y5 penetration logic, customers_y5 falls from 78 to 26 — roughly 31 assignments a year, consistent with the record's own bear-case trade count. Y5 revenue = 26 x $220,000 = $5.72M. I am deliberately not also haircutting the unverified $6M average package, though I believe $2.5-3M is nearer the truth for a distressed seller offloading one or two units rather than a full substation package; applying both cuts together would take this to roughly $2.3M.</t>
+        </is>
+      </c>
+      <c r="F10" s="31" t="n">
+        <v>5720000</v>
+      </c>
+    </row>
+    <row r="11" ht="72" customHeight="1">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>stateful-hash-signature-key-state-custody</t>
+        </is>
+      </c>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>Key-state custody for LMS/XMSS firmware signing under CNSA 2.0</t>
+        </is>
+      </c>
+      <c r="C11" s="23" t="inlineStr">
+        <is>
+          <t>acv_usd of $110,000, anchored on the enterprise code-signing platform band (Keyfactor Signum, Venafi CodeSign Protect, DigiCert, Entrust) at $50k-$250k.</t>
+        </is>
+      </c>
+      <c r="D11" s="23" t="inlineStr">
+        <is>
+          <t>The model contradicts itself in the space of two fields. Its buyer description states budget 'is product engineering and compliance, not the CISO's IT-security line, which matters because product-security budgets are smaller and tied to specific programme wins' — and then prices off comparables that are bought precisely on the CISO line and replace an entire enterprise signing workflow. This product is one subsystem, not a platform. It is also competing against its own free tier: the record's open-source state manager and state-fork detector do the core job, so the paid hosted plane must justify itself on multi-region availability and audit evidence alone, which is a much narrower value claim than 'we run your code signing.' The hosted-only revenue model compounds this — many NSS-adjacent OEMs cannot route production root-of-trust signing to an unauthorized third-party plane at all, so the OSS build is not a funnel for them, it is the destination.</t>
+        </is>
+      </c>
+      <c r="E11" s="23" t="inlineStr">
+        <is>
+          <t>acv_usd: $110,000 -&gt; $55,000. Derivation (my own reasoning, not researched): roughly 8 primes / ODMs running many parallel signing pipelines at $120k, and roughly 52 tier-1 and embedded OEMs with one to three pipelines at $45k. Blend = (8 x $120,000 + 52 x $45,000) / 60 = ($960,000 + $2,340,000) / 60 = $55,000. Y5 revenue = 60 x $55,000 = $3.30M. Separately worth flagging that buyer_universe 600 includes 'roughly 300 industrial/embedded OEMs with enough government exposure to inherit flow-down' — most of those never sign firmware for a National Security System and will never see a CNSA 2.0 clause, so the true universe is likely nearer 300.</t>
+        </is>
+      </c>
+      <c r="F11" s="36" t="n">
+        <v>3300000</v>
+      </c>
+    </row>
+    <row r="12" ht="72" customHeight="1">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>copper-retirement-life-safety-circuits</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t>Copper sunset triage for fire-alarm, elevator and area-of-refuge lines</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>acv_usd of $14,000, derived from 'a portfolio owner with roughly 200 life-safety lines' at $50-70 per line per year plus per-building documentation fees.</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t>A 200-line portfolio is the top decile of this buyer set, not the typical one. The model's own universe is dominated by K-12 districts (13,000 of the 20,000 pre-de-rate), and the median US school district runs a handful of buildings. My own reasoning on line counts, not researched: life-safety copper is roughly two fire-alarm DACT lines per building plus about one elevator phone line per elevator, so a ten-building district or senior-living operator carries 25-35 lines, not 200. At $60 per line that is roughly $1,800 a year, plus a per-building inspector packet at say $250 x 10 = $2,500, for a total near $4,300. The $25-40k hospital systems are real but there are only about 1,100 of them and they are not who fills a 195-customer Y5 base. The model priced the whale and applied it to the tail. This is the same error as sizing off the 200-line portfolio while de-rating the universe only 25% for 'organisations with too few buildings' — if those organisations are too small to buy, they should not be in the universe; if they are in the universe, they should not carry the whale's ACV.</t>
+        </is>
+      </c>
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>acv_usd: $14,000 -&gt; $6,000, reflecting a base that is mostly 8-15 building institutions at $4-5k with a minority of hospital systems and REITs at $25-40k. Y5 revenue = 195 x $6,000 = $1.17M. Sanity check: this lands just above the model's own bear case of $800k-$1.1M, which tells you the base case was never more than one ACV assumption away from its own downside — the ramp was doing very little of the work here.</t>
+        </is>
+      </c>
+      <c r="F12" s="31" t="n">
+        <v>1170000</v>
+      </c>
+    </row>
+    <row r="13" ht="72" customHeight="1">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>cui-determination-for-machine-shops</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t>CUI determination and marking for small defense machine shops</t>
+        </is>
+      </c>
+      <c r="C13" s="23" t="inlineStr">
+        <is>
+          <t>customers_y5 of 1,500, reached via a 30 -&gt; 150 -&gt; 450 -&gt; 900 -&gt; 1,500 curve that implicitly assumes near-zero churn.</t>
+        </is>
+      </c>
+      <c r="D13" s="23" t="inlineStr">
+        <is>
+          <t>That is a healthy self-serve SaaS growth shape applied to a motion the model itself says may not exist. Its key_sensitivity concedes everything depends on channel-led or self-serve acquisition at $2-4k all-in, and its kill_risk says the channel has a direct financial reason to block: 'CUI scoping is the most-billed hour in a consultancy's engagement.' You cannot model 5x then 3x then 2x growth off a channel you have just argued is conflicted. Second and compounding: the ramp treats every logo as permanent, but the record argues determination is a one-time scoping exercise, and the model's own downside_note admits net revenue retention would fall below 70% in that world. A 1,500 active-subscriber base at Y5 requires both a working channel and near-full retention on a product the record says is bought once per certification cycle.</t>
+        </is>
+      </c>
+      <c r="E13" s="23" t="inlineStr">
+        <is>
+          <t>customers_y5: 1,500 -&gt; 500. Derivation (my own reasoning, not researched): assume the conflicted channel half-works, giving gross adds of roughly 25 / 90 / 200 / 280 / 320 across Y1-Y5, and apply 60% annual retention for a purchase tied to the assessment cycle. Cohort roll-forward: Y1 25; Y2 15 + 90 = 105; Y3 63 + 200 = 263; Y4 158 + 280 = 438; Y5 263 + 320 = 583, which I round down to 500 to account for the certification wave cresting in 2029 and the Purview default the record flags. Y5 revenue = 500 x $4,800 = $2.40M. I have held acv_usd at $4,800 rather than compounding the record's predicted compression to $1,500-2,500 — applying both would take this to roughly $1.1M, which is precisely the model's stated bear case.</t>
+        </is>
+      </c>
+      <c r="F13" s="36" t="n">
+        <v>2400000</v>
+      </c>
+    </row>
+    <row r="14" ht="72" customHeight="1">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>rec-state-packaging-epr-reporting-for-mid-market-brands</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t>State packaging EPR reporting for mid-market brands</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr">
+        <is>
+          <t>The Y3-Y5 customer ramp (90 -&gt; 180 -&gt; 300), which triples on the assumption that the co-packer / packaging-distributor referral channel converts in bulk — combined with an implicit zero-churn assumption across all five years.</t>
+        </is>
+      </c>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t>The model's own key_sensitivity concedes that without the channel, 'throughput and CAC cap it near 100' — and then books the channel-works branch as base case at full weight. Two independent reasons the channel underperforms. (a) Incentive misalignment: a co-packer or distributor account manager gets no revenue share and no compensation event for handing over a book, and referring the brand invites a vendor who will then audit the co-packer's own spec sheets and packaging weights. The referrer's interest is negatively correlated with the referral. Indirect channels with no economics attached typically deliver well under a third of forecast. (b) The model's own throughput constraint compounds it: Y5 at 300 implies 120 new onboardings in year 5 alone, at the stated 70-100 bench hours each — roughly 10,000 bench hours, about 6 FTE technicians on weighing alone, inside a team that must scale from 4 to roughly 25-30 people by Y5, hired and trained out of 48%-margin services cash on $75k of starting capital. Separately, the ramp is gross adds with no churn: at a plausible 20% annual churn on a renewal product the customer can self-file once you have handed them the BOM, gross adds of 10/25/55/90/120 net to ~244, not 300, before any channel haircut. Note also the ACV arithmetic is internally loose — the Y5 mix of 120 new at ~$18k and 180 renewals at ~$9k blends to $12.6k, not the $14k modelled.</t>
+        </is>
+      </c>
+      <c r="E14" s="21" t="inlineStr">
+        <is>
+          <t>customers_y5: 300 -&gt; 140 (and correspondingly customers_y3 90 -&gt; 55, customers_y4 180 -&gt; 95). This is the direct-sales outcome the model itself puts 'near 100,' plus modest partner contribution, less ~20% annual churn. Hold acv_usd at $14,000 so the haircut is isolated to the ramp.</t>
+        </is>
+      </c>
+      <c r="F14" s="31" t="n">
+        <v>1960000</v>
+      </c>
+    </row>
+    <row r="15" ht="72" customHeight="1">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>part-146-bvlos-data-services</t>
+        </is>
+      </c>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>Part 146 ADSP certification: strategic deconfliction plus the sub-400-foot obstacle layer</t>
+        </is>
+      </c>
+      <c r="C15" s="23" t="inlineStr">
+        <is>
+          <t>acv_usd of $180,000 — a fully recalled number, blending $250k for a large IOU and $100k for a mid-size utility or railroad, for a single derived obstacle layer.</t>
+        </is>
+      </c>
+      <c r="D15" s="23" t="inlineStr">
+        <is>
+          <t>The model itself labels this 'the softest number in this projection' and its key_sensitivity says ACV 'collapses toward $50k' in the bad branch — then it models the good branch at full value. The structural problem is that the utility already owns the raw LiDAR; you are reselling the exploitation of an asset they paid for, which caps willingness-to-pay well below a platform price. $250k for a large IOU is 70-100% of what Neara or AiDash charge for an entire vegetation-management and network-modelling platform, and those two are already inside the account with the ability to add an obstacle layer to a renewal at zero incremental charge — which is precisely what sets the ceiling on a standalone layer. The pricing model also states the land step is a $50-75k paid pilot; a jump from a $60k pilot to a $250k territory subscription is a 3-5x expansion inside one budget cycle for a single-purpose dataset, which utility procurement almost never grants. The realistic shape is a module price: ~$130-150k for a large IOU, ~$60-80k for a mid-size utility or Class I railroad, blending to roughly $95k. Worth flagging as a second-order issue: 32 customers by Y5 requires presence in roughly 10 states, which contradicts the record's own instruction to 'pick electric distribution rights-of-way in two or three states' and ignores that each new state needs LiDAR acquisition and processing capex before a single dollar of revenue.</t>
+        </is>
+      </c>
+      <c r="E15" s="23" t="inlineStr">
+        <is>
+          <t>acv_usd: $180,000 -&gt; $95,000. (If the coverage-footprint contradiction is also taken seriously and customers_y5 is cut 32 -&gt; 20, Y5 revenue falls further to roughly $1.9M.)</t>
+        </is>
+      </c>
+      <c r="F15" s="36" t="n">
+        <v>3040000</v>
+      </c>
+    </row>
+    <row r="16" ht="72" customHeight="1">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>material-assistance-cost-ratio-attestation</t>
+        </is>
+      </c>
+      <c r="B16" s="21" t="inlineStr">
+        <is>
+          <t>Material Assistance Cost Ratio files for FEOC-exposed clean energy</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="inlineStr">
+        <is>
+          <t>acv_usd held flat at $75,000 through year 5, while the customer count is haircut for the OBBBA sunset.</t>
+        </is>
+      </c>
+      <c r="D16" s="21" t="inlineStr">
+        <is>
+          <t>The ACV is explicitly constructed as project throughput: '$40-60k first project and $15-25k per subsequent project, so a mid-market EPC running 4-6 projects a year plus annual recertification lands at ~$75k.' That number is a direct function of new FEOC-exposed construction starts. The model correctly flattens the logo count at Y4-Y5 (55, 60) because it believes the kill_risk that '45Y/48E terminates for projects placed in service after 2027... the largest FEOC-exposed cohort shrinks instead of compounding' — but then leaves the per-account revenue at its peak-year level. That double-counts the growth it has already said will not happen. You cannot hold both beliefs: if the cohort collapses after 2027, the surviving 2031 account is not running 4-6 new opinion-grade projects a year, it is a recertification-and-examination-defense relationship on an installed base of prior opinions plus residual storage and 45X component work. Realistic Y5 per-account: 8-10 installed projects on annual recert at ~$3k each ($25-30k), plus one or two genuinely new engagements at ~$15k — call it $35k. The right way to model a statutory cliff in a repeating-project business is to haircut price and volume together; this model haircut only volume.</t>
+        </is>
+      </c>
+      <c r="E16" s="21" t="inlineStr">
+        <is>
+          <t>acv_usd: $75,000 -&gt; $35,000 in year 5 (recertification on installed base plus residual new-project work only). Hold customers_y5 at 60 so the haircut is isolated to the per-account line.</t>
+        </is>
+      </c>
+      <c r="F16" s="31" t="n">
+        <v>2100000</v>
+      </c>
+    </row>
+    <row r="17" ht="72" customHeight="1">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>c2pa-conformance-and-robustness-referee</t>
+        </is>
+      </c>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>The C2PA referee: conformance evidence, survivability scores, and verification at ingest</t>
+        </is>
+      </c>
+      <c r="C17" s="23" t="inlineStr">
+        <is>
+          <t>Applying a flat $70,000 ACV to a cumulative logo count — i.e. treating a one-off conformance assessment as if it were an annually recurring contract.</t>
+        </is>
+      </c>
+      <c r="D17" s="23" t="inlineStr">
+        <is>
+          <t>The model's own pricing_model describes the paid product as a 'Generator Product Security Architecture Document completion and assurance-level gap assessment (one-off per product line, recurring on recertification cycles).' Once a camera OEM or model lab is on the Conforming Products List, they do not repurchase a $70k readiness assessment twelve months later; they buy a recert every two-to-three years at a fraction of the price plus the occasional incremental product line. So 38 in year 5 is cumulative logos, of which only about 10 are new-assessment revenue. Building it bottom-up: 10 new assessments at ~$60k = ~$600k, plus ~28 prior accounts on recert and verification-API monitoring at $15-20k = ~$500k, giving ~$1.1M — not $2.66M. The anchor is also weak in a specific way the model does not price: SOC 2 readiness fees are what they are because enterprise buyers contractually mandate SOC 2. CPL membership is a badge unless a platform ingest policy or EU AI Act enforcement makes it a gate, which the model's own key_sensitivity flags as an unresolved binary. Charging SOC 2 prices for a voluntary badge is the leap.</t>
+        </is>
+      </c>
+      <c r="E17" s="23" t="inlineStr">
+        <is>
+          <t>acv_usd: $70,000 -&gt; $30,000 blended (roughly 25% of the year-5 base on new assessments at ~$60k, 75% on recert and monitoring at ~$18k). Hold customers_y5 at 38.</t>
+        </is>
+      </c>
+      <c r="F17" s="36" t="n">
+        <v>1140000</v>
+      </c>
+    </row>
+    <row r="18" ht="72" customHeight="1">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>micropollutant-epr-billback</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>Micropollutant EPR fee ledger for pharma and cosmetics under the UWWTD</t>
+        </is>
+      </c>
+      <c r="C18" s="21" t="inlineStr">
+        <is>
+          <t>The customer ramp 3 -&gt; 8 -&gt; 16 -&gt; 26 -&gt; 38, which assigns effectively 100% probability to the June 2026 stop-the-clock resolution failing, and simultaneously assumes ~76% penetration of the record's own stated 50-group beachhead.</t>
+        </is>
+      </c>
+      <c r="D18" s="21" t="inlineStr">
+        <is>
+          <t>Two compounding problems in one field. First, the political binary: the model calls it 'close to binary,' states that if suspension holds past 2029 'year-5 revenue is near zero, not merely reduced,' and then books the timeline-holds branch at full weight with no probability adjustment. The evidence in the record points the other way — Parliament has already passed the suspension resolution, four trade associations (EFPIA, Cosmetics Europe, AESGP, Medicines for Europe) are working the Competitiveness Council, a CJEU preliminary reference is pending, and a Commission impact assessment due end-2026 will 're-identify which sectors are actually responsible.' That last item is not background risk: it means the obligation you are selling a provision against may cease to be your customer's obligation at all. I would put the timeline holding intact at roughly 40%, not 100%. Second, even inside the good branch, 38 signings is about three-quarters of the record's quoted top-50 beachhead. The model notices this ('about the most a senior-consultant-delivered product can reach') and then adopts the theoretical maximum as the expected value. A four-person startup does not win three of every four top European pharma and cosmetics groups on a deliverable that must clear the group's statutory auditor, against Big 4, ERM and Ramboll incumbents who already hold that relationship and can use the same public ECHA and EMA sources. Note the ACV is also structurally soft in the same way as the C2PA entry — a EUR 30-80k board report does not repeat at full price annually, since a provision restatement is a re-run, not a rebuild — but the ramp is doing far more of the work.</t>
+        </is>
+      </c>
+      <c r="E18" s="21" t="inlineStr">
+        <is>
+          <t>customers_y5: 38 -&gt; 12. Arithmetic: 40% probability the transposition timeline survives x 28 accounts (beachhead penetration cut from 38 for Big 4 / ERM incumbency) = 11.2; plus 60% probability of suspension or methodology reopening x 3 accounts of residual voluntary provision work = 1.8; total ~13, rounded down to 12. Hold acv_usd at $65,000.</t>
+        </is>
+      </c>
+      <c r="F18" s="31" t="n">
+        <v>780000</v>
+      </c>
+    </row>
+    <row r="19" ht="72" customHeight="1">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>cra-enisa-24h-reporting</t>
+        </is>
+      </c>
+      <c r="B19" s="23" t="inlineStr">
+        <is>
+          <t>CRA Article 14 incident reporting and the legacy-product obligation</t>
+        </is>
+      </c>
+      <c r="C19" s="23" t="inlineStr">
+        <is>
+          <t>acv_usd of $70,000. It is built as EUR 5k/month — the midpoint of the record's quoted EUR 3-8k/month band — plus a further EUR 12k/yr of amortised conformity work applied to 100% of accounts, and then labelled the most defensible number in the batch ('genuinely anchored... I would defend it at 7'). Baseline Y5 = 120 x $70,000 = $8.4M.</t>
+        </is>
+      </c>
+      <c r="D19" s="23" t="inlineStr">
+        <is>
+          <t>Two separate optimisms are compounded and then presented as 'quoted from the record.' The record quotes a range; nothing in it supports the midpoint except the fact that it is the midpoint. (1) The buyer is defined by the model itself as a firm too small to staff a 24/7 rota — sub-200 headcount, no PSIRT, no standing security budget line. A population defined by 'too small to do this in-house' skews hard toward the bottom of any price band, so the volume-weighted ACV sits near the floor, not the centre. EUR 8k/month is EUR 96k/yr, which is CISO-scale spend at a company that has no CISO. (2) The EUR 12k conformity attach is applied at a 100% rate — it assumes every retainer customer refreshes a self-assessed product line every single year, forever. A mid-size manufacturer with two or three CE-marked lines on a multi-year refresh cycle generates that project work maybe one year in three; a realistic attach is ~35% of accounts in any given year. (3) The model's own downside_note prices the survivable case at EUR 3k/month, and its own named competitive threat is notified bodies and TUV bundling CRA vulnerability handling into existing CE retainers at 'half your price using distribution you cannot match.' Both forces push the realised price toward the floor of the range, not the middle. A grudge purchase driven by a statutory filing obligation, sold against an incumbent channel that can bundle, does not clear at midpoint. Note this is the assumption doing the most work precisely because it was mislabelled as grounded — the buyer_universe of 12,000 is the model's self-declared weak point but it never binds, since 120 customers is 1% of it.</t>
+        </is>
+      </c>
+      <c r="E19" s="23" t="inlineStr">
+        <is>
+          <t>acv_usd: $70,000 -&gt; $50,000. Rebuild it as EUR 3.5k/month retainer (EUR 42k/yr, lower-third of the quoted band) plus conformity attach at 35% of accounts rather than 100% (EUR 12k x 0.35 = ~EUR 4k), = ~EUR 46k, converted at the model's own recalled EUR/USD of 1.10 = ~$50k. Customer ramp (4/18/45/80/120) and 45% margin left unchanged — the ramp is already honestly discounted from the founder's 90-day target and the margin already refuses to pretend a 24/7 rota scales.</t>
+        </is>
+      </c>
+      <c r="F19" s="36" t="n">
+        <v>6000000</v>
+      </c>
+    </row>
+    <row r="20" ht="72" customHeight="1">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>secondhand-hardware-provenance-channel</t>
+        </is>
+      </c>
+      <c r="B20" s="21" t="inlineStr">
+        <is>
+          <t>Signed provenance attestation for the secondhand datacenter hardware channel</t>
+        </is>
+      </c>
+      <c r="C20" s="21" t="inlineStr">
+        <is>
+          <t>acv_usd of $18,000. It embeds an unstated and unargued assumption that the median paying reseller runs 1,000 units/month AND verifies 100% of them at $1.50 — 12,000 paid verifications per account per year, every year. Baseline Y5 = 170 x $18,000 = $3.06M.</t>
+        </is>
+      </c>
+      <c r="D20" s="21" t="inlineStr">
+        <is>
+          <t>The model's stated key_sensitivity is conversion, and it argues that carefully. The volume term inside the ACV is where it stops arguing, and that term is a pure multiplier on Y5 revenue. (1) The model defines its own qualifying universe as firms doing 'a few hundred units a month minimum,' then sets the median payer at 1,000/month — that is the top of its own qualifying band being used as the centre of it. A genuine median for a 4,000-firm population whose floor is ~300/month is more like 600/month. (2) The throughput-to-verification conversion is set at 1.00 and never defended. Per-verification pricing means revenue is metered by scans, not by seats. A reseller buys attestation where it pays: high-value enterprise SSDs and DIMMs headed for premium graded listings, disputed returns, and anything going to a customer who will RMA. Paying $1.50 to grade a $40 commodity drive to protect a $40 RMA exposure is negative-margin behaviour for the buyer — they will eyeball it, which is exactly what they do today. A realistic verified share is 30-50% of units, not all of them. (3) The pricing model is 'per-verification usage against a monthly platform minimum,' which means usage counts against the minimum rather than stacking on top of it, so the ACV cannot be built by adding a floor to full-throughput usage. Rebuilt: 600 units/mo x 40% verified = ~240/mo = ~2,900 verifications/yr x $1.50 = ~$4,300, floored by a small platform minimum, with a minority on an enterprise API tier — call it $6,000 blended.</t>
+        </is>
+      </c>
+      <c r="E20" s="21" t="inlineStr">
+        <is>
+          <t>acv_usd: $18,000 -&gt; $6,000. Median payer throughput 1,000 -&gt; 600 units/month, and verified share 100% -&gt; 40%, with the platform minimum treated as a floor rather than an additive line. Customer ramp (6/25/60/110/170) left unchanged — the free-CLI-to-paid conversion is already the model's declared binary risk and cutting both at once would double-count the same doubt.</t>
+        </is>
+      </c>
+      <c r="F20" s="31" t="n">
+        <v>1020000</v>
+      </c>
+    </row>
+    <row r="21" ht="72" customHeight="1">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>agent-liability-loss-data</t>
+        </is>
+      </c>
+      <c r="B21" s="23" t="inlineStr">
+        <is>
+          <t>Loss data and incident taxonomy for AI agent liability underwriting</t>
+        </is>
+      </c>
+      <c r="C21" s="23" t="inlineStr">
+        <is>
+          <t>acv_usd of $120,000, recalled from enterprise cyber-loss-data licences and transplanted onto a product whose only inputs are free public sources (AIID, OECD AIM). Baseline Y5 = 22 x $120,000 = $2.64M.</t>
+        </is>
+      </c>
+      <c r="D21" s="23" t="inlineStr">
+        <is>
+          <t>The comparable is wrong in the direction that matters most. Cyber-loss data commands low six figures because it carries roughly two decades of closed claims with dollar severity attached, and because the vendors wrap a modelling platform around it. This product, by the model's own kill_risk, 'cannot see closed claims — carriers own those.' What a chief underwriting officer would actually be licensing is a hand-classified aggregate of two free public registries. The buy-versus-build arithmetic bites on day one and it is not close: one emerging-risk analyst at roughly $150k fully loaded can re-run the classification internally against the same free sources, and the carrier keeps the taxonomy and the institutional knowledge. A $120k annual licence has to beat that from the first renewal — before the registry is dense enough for anyone to fit a frequency-severity curve to it, which the model itself concedes accrues on calendar time measured in years. Products in this actual shape — research subscriptions and taxonomy/benchmark feeds without proprietary claims access — price in the $25-60k band. Note that the model's own downside_note lands at '$25-40k reports': the base case and the downside case are describing the same object at a 3-4x price difference, which is the tell. A secondary optimism compounds it: the model reasons its way to the observation that the live market is only 'the subset actually writing agent E&amp;O by 2031' — maybe 60 of the 250 entities — notes that 22 customers would therefore be about a third of the real market, and then keeps 22 anyway. A third of a concentrated market, taken by an entrant selling public data against AIUC, Armilla and Klaimee holding privileged claims access, is not a ceiling that was capped; it is a ceiling that was waved at.</t>
+        </is>
+      </c>
+      <c r="E21" s="23" t="inlineStr">
+        <is>
+          <t>acv_usd: $120,000 -&gt; $40,000. Price it as what it is — a classified public-incident research feed with rating-factor co-development attached, sold against a $150k internal-analyst alternative — rather than as a closed-claims modelling licence. Customer ramp (1/3/8/16/22) left unchanged, though I would separately argue customers_y5 down to 9-10 on the 60-entity live-market denominator; that second cut would take Y5 to roughly $360-400k.</t>
+        </is>
+      </c>
+      <c r="F21" s="36" t="n">
+        <v>880000</v>
+      </c>
+    </row>
+    <row r="22" ht="72" customHeight="1">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>eudi-wallet-relying-party-side</t>
+        </is>
+      </c>
+      <c r="B22" s="21" t="inlineStr">
+        <is>
+          <t>Relying-Party-as-a-Service: the verifier side of the EU Digital Identity Wallet</t>
+        </is>
+      </c>
+      <c r="C22" s="21" t="inlineStr">
+        <is>
+          <t>acv_usd of $45,000 — specifically the ~EUR 30k verification component, which assumes 250,000 wallet presentations per customer per year, i.e. that 100% of a relying party's identity-check volume arrives via EUDI wallet from the moment it integrates. The model has no consumer-adoption term anywhere in it. Baseline Y5 = 280 x $45,000 = $12.6M, the largest number in the batch.</t>
+        </is>
+      </c>
+      <c r="D22" s="21" t="inlineStr">
+        <is>
+          <t>Per-verification revenue is a function of wallet presentations, not of relying-party count — and the model carefully forecasts the second while silently assuming the first away. It builds a defensible RP ramp off two statutory dates, then multiplies it by an RP's entire annual check volume as though the wallet were the only rail. It cannot be. Wallets must first be issued (the Dec 2026 mandate binds member states, not citizens), then downloaded, then populated with a PID, then trusted enough that a user reaches for it at a KYC prompt. The precedent is eIDAS 1 national eIDs: after a decade, uptake ranged from roughly 90% in Estonia and Denmark to single digits in several member states, and the model's own readiness read (7 'might', 4 'unlikely') describes exactly that spread persisting. A gambling operator or alcohol-delivery business will run document IDV, card-based age checks and bank-ID in parallel for years; the wallet is one lane. A blended EU wallet-presented share of 15-30% by 2030-31 is the optimistic-realistic case, not the pessimistic one. Two further problems compound it. 250,000 checks/year is roughly 700/day — that is a large-mid-market operator, not a median one. And the model's own key_sensitivity already concedes downward price pressure from a free Commission verifier and the W3C/OS Digital Credentials API, toward EUR 0.02. The genuinely durable line is the EUR 12k/yr managed registration and RP-access-certificate subscription across member states — that is real, recurring, and nobody wants to do it — but it is only 27% of the stated ACV. The model's revenue is 73% dependent on a variable it never modelled.</t>
+        </is>
+      </c>
+      <c r="E22" s="21" t="inlineStr">
+        <is>
+          <t>acv_usd: $45,000 -&gt; $20,000. Hold the EUR 12k managed-registration and certificate-lifecycle subscription in full; cut wallet-presented volume from 250,000 to 50,000 (20% of a 250k check base) at the model's own EUR 0.12, = EUR 6k. EUR 18k x 1.10 = ~$20k. Customer ramp (5/30/85/170/280) left unchanged — the registration-window compression argument for the Y2 jump is sound and is about RP count, which is the half of the model that was actually reasoned.</t>
+        </is>
+      </c>
+      <c r="F22" s="31" t="n">
+        <v>5600000</v>
+      </c>
+    </row>
+    <row r="23" ht="72" customHeight="1">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>fsma-204-lot-code-traceability</t>
+        </is>
+      </c>
+      <c r="B23" s="23" t="inlineStr">
+        <is>
+          <t>Lot-code reconciliation and the 24-hour FSMA 204 spreadsheet</t>
+        </is>
+      </c>
+      <c r="C23" s="23" t="inlineStr">
+        <is>
+          <t>customers_y5 of 800 (and customers_y4 of 500) — a gross-adds curve that keeps compounding for three straight years after its own forcing deadline has passed, with no churn term anywhere in the model. Baseline Y5 = 800 x $5,400 = $4.32M. Note this is the one model in the batch whose ACV is genuinely quoted from the record, which is precisely why the optimism migrated into the ramp.</t>
+        </is>
+      </c>
+      <c r="D23" s="23" t="inlineStr">
+        <is>
+          <t>Date the years and the rationale contradicts itself. First revenue is 4 months out from Aug 2026, so Y1 is roughly 2027, Y2 is 2028, Y3 2029, Y4 2030, Y5 2031. The 20 July 2028 compliance date therefore lands inside Y2 — not 'Y2-Y3 as the deadline enters budget cycles' as the rationale states. That means 260 / 500 / 800 in Y3-Y5 are entirely post-deadline, and the model's own key_sensitivity concedes the ground out from under them: 'there is no residual value proposition strong enough' at $5,400, 'the product is bought because of a date, not because of shrink or recall speed.' A compliance SaaS whose gross adds peak in the deadline year should decay after it, not accelerate for three more. Second, there is no churn assumption at all — the customer counts are cumulative adds presented as net accounts. At $450/month, with lock-in limited to accumulated lot history a customer can export, sold to a buyer who bought under duress and whose duress has expired, 25-35% annual churn is the normal shape for low-ACV compliance SaaS. Third, the channel claim is doing quiet work the model never audits: broadline and specialty distributors are assumed to push a third-party SaaS to their independent accounts in batches of tens. Distributors satisfy their own FSMA 204 obligation with their own records; they carry no obligation for their customers' compliance and no commercial incentive to inject a procurement conversation into an account relationship they are actively defending against a competitor. Run it net at 30% churn with adds decaying after 2028: Y2 90; Y3 = 90 x 0.7 + ~180 adds = ~245 (the stated 260 is roughly fair); Y4 = 260 x 0.7 + ~130 = ~310; Y5 = 310 x 0.7 + ~90 = ~305.</t>
+        </is>
+      </c>
+      <c r="E23" s="23" t="inlineStr">
+        <is>
+          <t>customers_y5: 800 -&gt; 300 (and customers_y4: 500 -&gt; 310), applying 30% annual gross churn and decaying gross adds after the July 2028 deadline lands in Y2 rather than compounding through it. Y1-Y3 (20/90/260) left as stated — those are the deadline-driven years and the model reasoned them well. acv_usd held at $5,400 since it is quoted from the record, though $450/month is slightly above the $400 midpoint and a channel-led motion into price-sensitive independents would more likely blend to $350-400.</t>
+        </is>
+      </c>
+      <c r="F23" s="36" t="n">
+        <v>1620000</v>
+      </c>
+    </row>
+    <row r="24" ht="72" customHeight="1">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>last-time-buy-dmsms-desk</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="inlineStr">
+        <is>
+          <t>DMSMS resolution desk: last-time-buy brokerage plus qualified resupply for 20-year platforms</t>
+        </is>
+      </c>
+      <c r="C24" s="21" t="inlineStr">
+        <is>
+          <t>acv_usd = $350,000, held flat across all 60 Y5 customers as if every landed logo were a full-rate annuity.</t>
+        </is>
+      </c>
+      <c r="D24" s="21" t="inlineStr">
+        <is>
+          <t>The model's own revenue_quality field says 'repeating-project', but the Y5 line (60 x $350k = $21.0M) treats it as a subscription. Three things stack. (i) A landed logo is not an active logo: a PCN/EOL notice is a discrete event, arriving lumpily per account, so the share of the installed base with a live last-time-buy in any given year is plausibly 50-60%, not 100%. (ii) On most lots you are one of two or three quotes, so you win the lot, not the customer-year — the model's own key_sensitivity concedes you are 'merely a second quote' whenever the authorised aftermarket still has stock. (iii) The engineering attach ('roughly one customer-year in three' at $120-400k) is carrying roughly $60k of the $350k blend and assumes the OEM buys its qualified-alternate-source TDP from its broker rather than from the design consultancy already inside its quality system. The record's stated lot band is '$80k-$500k'; a $350k recognised-revenue blend sits above the middle of that band before any active-rate discount. Note what is NOT the problem: buyer_universe (3,000) and the ramp are not load-bearing here — Y5 of 60 is 2% of the universe and is honestly derived. The per-customer annuity is where all the work is being done. Basis: my own reasoning applied to figures quoted from the record.</t>
+        </is>
+      </c>
+      <c r="E24" s="21" t="inlineStr">
+        <is>
+          <t>acv_usd: $350,000 -&gt; $180,000 (~55% of the base carrying an active LTB in a given year x ~$330k average resolved value including the engineering attach). Hold customers_y5 at 60 and gross_margin_pct at 32%, which drops Y5 gross profit from ~$6.7M to ~$3.5M.</t>
+        </is>
+      </c>
+      <c r="F24" s="31" t="n">
+        <v>10800000</v>
+      </c>
+    </row>
+    <row r="25" ht="72" customHeight="1">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>gs1-dpp-event-and-resolver-backbone</t>
+        </is>
+      </c>
+      <c r="B25" s="23" t="inlineStr">
+        <is>
+          <t>Battery Passport plumbing: supplier data chase, EPCIS event store, GS1-conformant resolver</t>
+        </is>
+      </c>
+      <c r="C25" s="23" t="inlineStr">
+        <is>
+          <t>acv_usd = $55,000 treated as steady blended revenue in every year including Y5, when the stated pricing unit ('price per supplier onboarded') is a one-time event.</t>
+        </is>
+      </c>
+      <c r="D25" s="23" t="inlineStr">
+        <is>
+          <t>The model contradicts itself in its own acv_basis: 'Blended first-year contract ~$60-70k, settling to ~$40-45k recurring as onboarding tapers' — and then models $55k flat. Chasing 20-60 tier-2/3 suppliers happens once per customer; what recurs is the resolver + EPCIS subscription the model itself prices at '$20-35k/yr' plus re-attestation adds. Do the Y5 mix properly: only ~40 of the 130 logos are new-in-year (130 - 90), the other ~90 are on the recurring tail. (40 x ~$65k) + (90 x ~$30k) = $2.6M + $2.7M = $5.3M, a blended $41k — and that is before churn, which the cumulative count sets at zero for a compliance product whose buyer's acute need ends the day the passport is filed. $35k prices in real churn and downgrade. Secondary and entirely un-hedged: ramp_rationale asserts 'delivery gates growth harder than sales' and then models Y1 6 -&gt; Y2 25, i.e. ~19 net adds x 20-60 suppliers each = roughly 750 supplier chases in six languages off a team that was 3 people in Y1. The deadline risk the model does flag is real, but it flagged it; this one it did not. Basis: my own arithmetic on figures quoted from the model record.</t>
+        </is>
+      </c>
+      <c r="E25" s="23" t="inlineStr">
+        <is>
+          <t>acv_usd: $55,000 -&gt; $35,000 (steady-state blend: ~30% of the base in its onboarding year at ~$65k, ~70% on the ~$30k resolver/event-store subscription, net of churn). Hold customers_y5 at 130.</t>
+        </is>
+      </c>
+      <c r="F25" s="36" t="n">
+        <v>4550000</v>
+      </c>
+    </row>
+    <row r="26" ht="72" customHeight="1">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>attested-capture-for-claims-media</t>
+        </is>
+      </c>
+      <c r="B26" s="21" t="inlineStr">
+        <is>
+          <t>Sealed-at-capture evidence for insurance claims and field inspection</t>
+        </is>
+      </c>
+      <c r="C26" s="21" t="inlineStr">
+        <is>
+          <t>acv_usd = $120,000 applied to all 42 Y5 customers, when it is derived from the single richest buyer profile in the model and the named beachhead is priced by the model itself at $40-70k.</t>
+        </is>
+      </c>
+      <c r="D26" s="21" t="inlineStr">
+        <is>
+          <t>The $120k is built from a ~50,000-claim/yr regional carrier x 8-12 captures x $0.15-0.25 plus a $30-50k platform floor. But the model's own buyer definition says the customer must be 'the party that controls the capture app', and the beachhead it names — auto glass networks, roof inspection, equipment-finance collateral condition reports, large IA firms — is exactly the tier the same acv_basis prices at '$40-70k'. Those low-ACV buyers are the majority of the winnable list precisely because they own the phone; the 50k-claim carrier is the exception, and the model explicitly excludes top-25 carriers as unlandable in five years. So the blend anchors on the top of its own quoted range. Second compression: $0.20/capture is ~$2 per claim for provenance metadata, and per-unit metering is the first line item carrier procurement attacks at renewal — volume tiers realistically land nearer $0.08-0.12, which alone takes the metered component from ~$100k to ~$50k. A realistic mix is ~1/3 carriers at ~$110k and ~2/3 networks/IA/lenders at ~$50k. Basis: my own reasoning on ranges quoted from the record.</t>
+        </is>
+      </c>
+      <c r="E26" s="21" t="inlineStr">
+        <is>
+          <t>acv_usd: $120,000 -&gt; $70,000 (mix-weighted, with per-capture pricing at $0.10-0.15 rather than $0.15-0.25). Hold customers_y5 at 42.</t>
+        </is>
+      </c>
+      <c r="F26" s="31" t="n">
+        <v>2940000</v>
+      </c>
+    </row>
+    <row r="27" ht="72" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>crawler-payment-clearing-and-metering</t>
+        </is>
+      </c>
+      <c r="B27" s="23" t="inlineStr">
+        <is>
+          <t>Neutral clearing house for the HTTP 402 crawler economy</t>
+        </is>
+      </c>
+      <c r="C27" s="23" t="inlineStr">
+        <is>
+          <t>The ~15% take rate embedded in acv_usd = $45,000 — a rate the model invented after explicitly discarding the record's stated pricing of 'basis points on settled access'.</t>
+        </is>
+      </c>
+      <c r="D27" s="23" t="inlineStr">
+        <is>
+          <t>The acv_basis says it plainly: 'at literal basis points (1-2%) this business cannot exist on a thin pool, so I model a collecting-society/ad-network take rate of ~15%.' That is repairing the unit economics by assuming a different price than the one in the record, which is the single largest tell in this batch. Collecting societies and ad networks earn 15% because they have something this business does not: ASCAP/BMI have statutory backing and de facto exclusivity over the catalog; ad networks generate the demand. A neutral clearing house has no exclusivity (a long-tail publisher can also sign with RSL, or just use Cloudflare), generates no demand (the AI buyer already knew it wanted the data), and competes with a free substitute sitting inside the request path. Rails that only move money and produce a reconciliation report clear at 2-5%. At 5% on the same $300k of settled spend, net revenue per buyer is $15k, not $45k, and Y5 goes from $3.6M to $1.2M. The compounding matters more than either factor alone: 5% take x the model's own already-flagged '$60k pennies-for-recipe-blogs' spend case = ~$3k per buyer, or roughly $240k of Y5 net revenue on 80 logos. Basis: my own recall of take-rate benchmarks plus figures quoted from the record.</t>
+        </is>
+      </c>
+      <c r="E27" s="23" t="inlineStr">
+        <is>
+          <t>Take rate: ~15% -&gt; 5%, i.e. acv_usd: $45,000 -&gt; $15,000, holding settled spend at $300k/buyer/yr and customers_y5 at 80.</t>
+        </is>
+      </c>
+      <c r="F27" s="36" t="n">
+        <v>1200000</v>
+      </c>
+    </row>
+    <row r="28" ht="72" customHeight="1">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>lead-service-line-inventory-2027</t>
+        </is>
+      </c>
+      <c r="B28" s="21" t="inlineStr">
+        <is>
+          <t>Killing lead-line 'unknowns' before the Nov 1, 2027 LCRI baseline locks in</t>
+        </is>
+      </c>
+      <c r="C28" s="21" t="inlineStr">
+        <is>
+          <t>acv_usd = $220,000 charged against all 24 Y5 customers, when the $220k unknowns-reduction engagement is a once-per-utility event with a hard expiry the model itself names.</t>
+        </is>
+      </c>
+      <c r="D28" s="21" t="inlineStr">
+        <is>
+          <t>You retire a system's unknowns once. The model's own acv_basis says the follow-on is 'a ~$50-80k/yr annual reporting and progress-tracking tail', and its ramp_rationale says the arbitrage has 'a hard expiry' after 1 November 2027. But the customer counts are cumulative and nearly flat by Y5 (22 -&gt; 24), so Y5 contains only ~2 new engagements and ~22 accounts already past their engagement: (2 x $220k) + (22 x $65k) = $440k + $1.43M = $1.87M, a blended $78k. Modelling $220k in Y5 means billing every utility a full first-engagement fee roughly nine years into a program whose urgent phase ended in year 2. This is the same structural error as the DMSMS desk — a one-time remediation event annualised into an ACV — and here it is sharper because the model's own ramp is a deliberate plateau, which is exactly the shape that exposes it: a flat logo count with a one-shot ACV means revenue should be falling by Y5, not holding at $5.3M. I use $85k rather than the strict $78k to credit phased multi-year engagements at larger systems and the $200/month self-serve tier. Basis: my own arithmetic on figures quoted from the record.</t>
+        </is>
+      </c>
+      <c r="E28" s="21" t="inlineStr">
+        <is>
+          <t>acv_usd: $220,000 -&gt; $85,000 (Y5 blend of ~2 new fixed-price engagements at $220k against ~22 accounts on the $50-80k annual reporting retainer). Hold customers_y5 at 24; at the model's 40% margin, Y5 gross profit falls from ~$2.1M to ~$820k.</t>
+        </is>
+      </c>
+      <c r="F28" s="31" t="n">
+        <v>2040000</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:F28"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/research/opportunities.xlsx
+++ b/research/opportunities.xlsx
@@ -16,6 +16,11 @@
     <sheet name="Projections" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Projection Basis" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="Bear Case" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Model Detail" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Model Summary" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Sourcing" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Corrections" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="30-Day Tests" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Top 25'!$A$1:$O$26</definedName>
@@ -25,6 +30,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Projections'!$A$3:$Y$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Projection Basis'!$A$1:$M$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Bear Case'!$A$3:$F$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Model Detail'!$A$3:$V$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Model Summary'!$A$3:$AQ$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Corrections'!$A$3:$D$79</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -37,7 +45,7 @@
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="0.0%;[Red]-0.0%"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -133,6 +141,18 @@
       <b val="1"/>
       <color rgb="001F3864"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="009C0006"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="8">
@@ -243,7 +263,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -360,6 +380,75 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -970,6 +1059,9 @@
           <t>Essentially nobody is building this, verified by search</t>
         </is>
       </c>
+      <c r="D24" s="7" t="n"/>
+      <c r="E24" s="7" t="n"/>
+      <c r="F24" s="8" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
@@ -985,6 +1077,9 @@
           <t>Near-certain to be a large market by 2029-2031</t>
         </is>
       </c>
+      <c r="D25" s="7" t="n"/>
+      <c r="E25" s="7" t="n"/>
+      <c r="F25" s="8" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
@@ -1000,6 +1095,9 @@
           <t>A 1-3 person team ships a real wedge in 90 days</t>
         </is>
       </c>
+      <c r="D26" s="7" t="n"/>
+      <c r="E26" s="7" t="n"/>
+      <c r="F26" s="8" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
@@ -1015,6 +1113,9 @@
           <t>Multi-billion addressable</t>
         </is>
       </c>
+      <c r="D27" s="7" t="n"/>
+      <c r="E27" s="7" t="n"/>
+      <c r="F27" s="8" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="10" t="inlineStr">
@@ -1030,6 +1131,9 @@
           <t>Strong compounding moat</t>
         </is>
       </c>
+      <c r="D28" s="7" t="n"/>
+      <c r="E28" s="7" t="n"/>
+      <c r="F28" s="8" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="14" t="inlineStr">
@@ -1185,6 +1289,7739 @@
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B32:F32"/>
     <mergeCell ref="B35:F35"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:V40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="9" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
+    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="13" customWidth="1" min="22" max="22"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="45" t="inlineStr">
+        <is>
+          <t>Every revenue line modelled separately. Blue cells are inputs. Revenue = units x price; gross profit = revenue x margin. Model Summary rolls these up with SUMIF, so adding a line here flows straight through.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="34" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Opportunity</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>Revenue line</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>One unit is</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>Price ($)</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>Units Y1</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>Units Y2</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>Units Y3</t>
+        </is>
+      </c>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>Units Y4</t>
+        </is>
+      </c>
+      <c r="K3" s="6" t="inlineStr">
+        <is>
+          <t>Units Y5</t>
+        </is>
+      </c>
+      <c r="L3" s="6" t="inlineStr">
+        <is>
+          <t>Rev Y1</t>
+        </is>
+      </c>
+      <c r="M3" s="6" t="inlineStr">
+        <is>
+          <t>Rev Y2</t>
+        </is>
+      </c>
+      <c r="N3" s="6" t="inlineStr">
+        <is>
+          <t>Rev Y3</t>
+        </is>
+      </c>
+      <c r="O3" s="6" t="inlineStr">
+        <is>
+          <t>Rev Y4</t>
+        </is>
+      </c>
+      <c r="P3" s="6" t="inlineStr">
+        <is>
+          <t>Rev Y5</t>
+        </is>
+      </c>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>GM %</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>GP Y1</t>
+        </is>
+      </c>
+      <c r="S3" s="6" t="inlineStr">
+        <is>
+          <t>GP Y2</t>
+        </is>
+      </c>
+      <c r="T3" s="6" t="inlineStr">
+        <is>
+          <t>GP Y3</t>
+        </is>
+      </c>
+      <c r="U3" s="6" t="inlineStr">
+        <is>
+          <t>GP Y4</t>
+        </is>
+      </c>
+      <c r="V3" s="6" t="inlineStr">
+        <is>
+          <t>GP Y5</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="46" t="inlineStr">
+        <is>
+          <t>datacenter-as-grid-entity-compliance</t>
+        </is>
+      </c>
+      <c r="B4" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="47" t="inlineStr">
+        <is>
+          <t>Ride-through models and curtailment proof for NERC-registered data centers</t>
+        </is>
+      </c>
+      <c r="D4" s="47" t="inlineStr">
+        <is>
+          <t>Utility / transmission-planner large-load reliability program</t>
+        </is>
+      </c>
+      <c r="E4" s="47" t="inlineStr">
+        <is>
+          <t>One fixed-fee program engagement with a TO/TP/PC/BA (Level 3 Alert Essential Actions implementation: large-load screening and study methodology, contingency and stability study process, disturbance-monitoring and instrumentation design, protection coordination standards, commissioning requirements). 4-7 month delivery.</t>
+        </is>
+      </c>
+      <c r="F4" s="48" t="n">
+        <v>175000</v>
+      </c>
+      <c r="G4" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" s="49" t="n">
+        <v>6</v>
+      </c>
+      <c r="I4" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="J4" s="49" t="n">
+        <v>13</v>
+      </c>
+      <c r="K4" s="49" t="n">
+        <v>16</v>
+      </c>
+      <c r="L4" s="50">
+        <f>G4*$F4</f>
+        <v/>
+      </c>
+      <c r="M4" s="50">
+        <f>H4*$F4</f>
+        <v/>
+      </c>
+      <c r="N4" s="50">
+        <f>I4*$F4</f>
+        <v/>
+      </c>
+      <c r="O4" s="50">
+        <f>J4*$F4</f>
+        <v/>
+      </c>
+      <c r="P4" s="50">
+        <f>K4*$F4</f>
+        <v/>
+      </c>
+      <c r="Q4" s="51" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R4" s="50">
+        <f>L4*$Q4</f>
+        <v/>
+      </c>
+      <c r="S4" s="50">
+        <f>M4*$Q4</f>
+        <v/>
+      </c>
+      <c r="T4" s="50">
+        <f>N4*$Q4</f>
+        <v/>
+      </c>
+      <c r="U4" s="50">
+        <f>O4*$Q4</f>
+        <v/>
+      </c>
+      <c r="V4" s="50">
+        <f>P4*$Q4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="52" t="inlineStr">
+        <is>
+          <t>datacenter-as-grid-entity-compliance</t>
+        </is>
+      </c>
+      <c r="B5" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="53" t="inlineStr">
+        <is>
+          <t>Ride-through models and curtailment proof for NERC-registered data centers</t>
+        </is>
+      </c>
+      <c r="D5" s="53" t="inlineStr">
+        <is>
+          <t>Large-load campus interconnection model and study package</t>
+        </is>
+      </c>
+      <c r="E5" s="53" t="inlineStr">
+        <is>
+          <t>One data-center (or electrolyzer/crypto) campus: EMT plus positive-sequence dynamic load model, UPS transfer-threshold / rectifier / chiller disturbance-response and ride-through study, POI protection coordination, filed model and attestation package. Fixed fee.</t>
+        </is>
+      </c>
+      <c r="F5" s="48" t="n">
+        <v>200000</v>
+      </c>
+      <c r="G5" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" s="49" t="n">
+        <v>4</v>
+      </c>
+      <c r="I5" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="J5" s="49" t="n">
+        <v>11</v>
+      </c>
+      <c r="K5" s="49" t="n">
+        <v>14</v>
+      </c>
+      <c r="L5" s="54">
+        <f>G5*$F5</f>
+        <v/>
+      </c>
+      <c r="M5" s="54">
+        <f>H5*$F5</f>
+        <v/>
+      </c>
+      <c r="N5" s="54">
+        <f>I5*$F5</f>
+        <v/>
+      </c>
+      <c r="O5" s="54">
+        <f>J5*$F5</f>
+        <v/>
+      </c>
+      <c r="P5" s="54">
+        <f>K5*$F5</f>
+        <v/>
+      </c>
+      <c r="Q5" s="51" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="R5" s="54">
+        <f>L5*$Q5</f>
+        <v/>
+      </c>
+      <c r="S5" s="54">
+        <f>M5*$Q5</f>
+        <v/>
+      </c>
+      <c r="T5" s="54">
+        <f>N5*$Q5</f>
+        <v/>
+      </c>
+      <c r="U5" s="54">
+        <f>O5*$Q5</f>
+        <v/>
+      </c>
+      <c r="V5" s="54">
+        <f>P5*$Q5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="46" t="inlineStr">
+        <is>
+          <t>datacenter-as-grid-entity-compliance</t>
+        </is>
+      </c>
+      <c r="B6" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="47" t="inlineStr">
+        <is>
+          <t>Ride-through models and curtailment proof for NERC-registered data centers</t>
+        </is>
+      </c>
+      <c r="D6" s="47" t="inlineStr">
+        <is>
+          <t>Regulatory, docket and expert support</t>
+        </is>
+      </c>
+      <c r="E6" s="47" t="inlineStr">
+        <is>
+          <t>One billable senior-principal day: RM26-4 compliance-filing analysis and comments in the six RTO/ISO dockets, NERC CLE registry and standards-drafting participation, state PUC and PUCT large-load tariff proceedings, technical affidavits and litigation support.</t>
+        </is>
+      </c>
+      <c r="F6" s="48" t="n">
+        <v>4500</v>
+      </c>
+      <c r="G6" s="49" t="n">
+        <v>80</v>
+      </c>
+      <c r="H6" s="49" t="n">
+        <v>150</v>
+      </c>
+      <c r="I6" s="49" t="n">
+        <v>190</v>
+      </c>
+      <c r="J6" s="49" t="n">
+        <v>215</v>
+      </c>
+      <c r="K6" s="49" t="n">
+        <v>240</v>
+      </c>
+      <c r="L6" s="50">
+        <f>G6*$F6</f>
+        <v/>
+      </c>
+      <c r="M6" s="50">
+        <f>H6*$F6</f>
+        <v/>
+      </c>
+      <c r="N6" s="50">
+        <f>I6*$F6</f>
+        <v/>
+      </c>
+      <c r="O6" s="50">
+        <f>J6*$F6</f>
+        <v/>
+      </c>
+      <c r="P6" s="50">
+        <f>K6*$F6</f>
+        <v/>
+      </c>
+      <c r="Q6" s="51" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="R6" s="50">
+        <f>L6*$Q6</f>
+        <v/>
+      </c>
+      <c r="S6" s="50">
+        <f>M6*$Q6</f>
+        <v/>
+      </c>
+      <c r="T6" s="50">
+        <f>N6*$Q6</f>
+        <v/>
+      </c>
+      <c r="U6" s="50">
+        <f>O6*$Q6</f>
+        <v/>
+      </c>
+      <c r="V6" s="50">
+        <f>P6*$Q6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="52" t="inlineStr">
+        <is>
+          <t>datacenter-as-grid-entity-compliance</t>
+        </is>
+      </c>
+      <c r="B7" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="53" t="inlineStr">
+        <is>
+          <t>Ride-through models and curtailment proof for NERC-registered data centers</t>
+        </is>
+      </c>
+      <c r="D7" s="53" t="inlineStr">
+        <is>
+          <t>Model maintenance and re-validation retainer</t>
+        </is>
+      </c>
+      <c r="E7" s="53" t="inlineStr">
+        <is>
+          <t>One campus under annual retainer: model refresh on configuration change, post-event re-validation inside the NOGRR 282 90-day root-cause / 90-day corrective-plan / 180-day implementation cycle, ISO data-request response. Annual subscription, attaches to a prior campus package.</t>
+        </is>
+      </c>
+      <c r="F7" s="48" t="n">
+        <v>45000</v>
+      </c>
+      <c r="G7" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" s="49" t="n">
+        <v>5</v>
+      </c>
+      <c r="J7" s="49" t="n">
+        <v>11</v>
+      </c>
+      <c r="K7" s="49" t="n">
+        <v>19</v>
+      </c>
+      <c r="L7" s="54">
+        <f>G7*$F7</f>
+        <v/>
+      </c>
+      <c r="M7" s="54">
+        <f>H7*$F7</f>
+        <v/>
+      </c>
+      <c r="N7" s="54">
+        <f>I7*$F7</f>
+        <v/>
+      </c>
+      <c r="O7" s="54">
+        <f>J7*$F7</f>
+        <v/>
+      </c>
+      <c r="P7" s="54">
+        <f>K7*$F7</f>
+        <v/>
+      </c>
+      <c r="Q7" s="51" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="R7" s="54">
+        <f>L7*$Q7</f>
+        <v/>
+      </c>
+      <c r="S7" s="54">
+        <f>M7*$Q7</f>
+        <v/>
+      </c>
+      <c r="T7" s="54">
+        <f>N7*$Q7</f>
+        <v/>
+      </c>
+      <c r="U7" s="54">
+        <f>O7*$Q7</f>
+        <v/>
+      </c>
+      <c r="V7" s="54">
+        <f>P7*$Q7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="46" t="inlineStr">
+        <is>
+          <t>datacenter-as-grid-entity-compliance</t>
+        </is>
+      </c>
+      <c r="B8" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="47" t="inlineStr">
+        <is>
+          <t>Ride-through models and curtailment proof for NERC-registered data centers</t>
+        </is>
+      </c>
+      <c r="D8" s="47" t="inlineStr">
+        <is>
+          <t>Computational Load Entity compliance program management</t>
+        </is>
+      </c>
+      <c r="E8" s="47" t="inlineStr">
+        <is>
+          <t>One registered CLE site under managed annual compliance: RSAW preparation, evidence retention and internal controls, self-certification and audit support, standards-change monitoring. Annual subscription. Only becomes real once NERC's registry criteria (Board target 5 Dec 2026, FERC filing due 31 Dec 2026) are approved and effective — hence zero in Y1.</t>
+        </is>
+      </c>
+      <c r="F8" s="48" t="n">
+        <v>60000</v>
+      </c>
+      <c r="G8" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" s="49" t="n">
+        <v>7</v>
+      </c>
+      <c r="J8" s="49" t="n">
+        <v>14</v>
+      </c>
+      <c r="K8" s="49" t="n">
+        <v>24</v>
+      </c>
+      <c r="L8" s="50">
+        <f>G8*$F8</f>
+        <v/>
+      </c>
+      <c r="M8" s="50">
+        <f>H8*$F8</f>
+        <v/>
+      </c>
+      <c r="N8" s="50">
+        <f>I8*$F8</f>
+        <v/>
+      </c>
+      <c r="O8" s="50">
+        <f>J8*$F8</f>
+        <v/>
+      </c>
+      <c r="P8" s="50">
+        <f>K8*$F8</f>
+        <v/>
+      </c>
+      <c r="Q8" s="51" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="R8" s="50">
+        <f>L8*$Q8</f>
+        <v/>
+      </c>
+      <c r="S8" s="50">
+        <f>M8*$Q8</f>
+        <v/>
+      </c>
+      <c r="T8" s="50">
+        <f>N8*$Q8</f>
+        <v/>
+      </c>
+      <c r="U8" s="50">
+        <f>O8*$Q8</f>
+        <v/>
+      </c>
+      <c r="V8" s="50">
+        <f>P8*$Q8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="52" t="inlineStr">
+        <is>
+          <t>datacenter-as-grid-entity-compliance</t>
+        </is>
+      </c>
+      <c r="B9" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="53" t="inlineStr">
+        <is>
+          <t>Ride-through models and curtailment proof for NERC-registered data centers</t>
+        </is>
+      </c>
+      <c r="D9" s="53" t="inlineStr">
+        <is>
+          <t>Flexible-load registration and curtailment evidence pack</t>
+        </is>
+      </c>
+      <c r="E9" s="53" t="inlineStr">
+        <is>
+          <t>One site registered as a controllable/flexible load (ERCOT PCLR/CLR or RTO equivalent) with self-limiting control description, dispatch-performance telemetry pipeline and signed timestamped curtailment record. Deliberately modelled small: total installed ERCOT Controllable Load Resource capacity today is about 36 MW, so this is an option on a market that does not yet exist, not a plan.</t>
+        </is>
+      </c>
+      <c r="F9" s="48" t="n">
+        <v>40000</v>
+      </c>
+      <c r="G9" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="49" t="n">
+        <v>3</v>
+      </c>
+      <c r="J9" s="49" t="n">
+        <v>6</v>
+      </c>
+      <c r="K9" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="L9" s="54">
+        <f>G9*$F9</f>
+        <v/>
+      </c>
+      <c r="M9" s="54">
+        <f>H9*$F9</f>
+        <v/>
+      </c>
+      <c r="N9" s="54">
+        <f>I9*$F9</f>
+        <v/>
+      </c>
+      <c r="O9" s="54">
+        <f>J9*$F9</f>
+        <v/>
+      </c>
+      <c r="P9" s="54">
+        <f>K9*$F9</f>
+        <v/>
+      </c>
+      <c r="Q9" s="51" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="R9" s="54">
+        <f>L9*$Q9</f>
+        <v/>
+      </c>
+      <c r="S9" s="54">
+        <f>M9*$Q9</f>
+        <v/>
+      </c>
+      <c r="T9" s="54">
+        <f>N9*$Q9</f>
+        <v/>
+      </c>
+      <c r="U9" s="54">
+        <f>O9*$Q9</f>
+        <v/>
+      </c>
+      <c r="V9" s="54">
+        <f>P9*$Q9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="46" t="inlineStr">
+        <is>
+          <t>long-tail-customs-entry-and-duty-recovery</t>
+        </is>
+      </c>
+      <c r="B10" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" s="47" t="inlineStr">
+        <is>
+          <t>Entry Type 13 and instrument-aware duty recovery for the post-de-minimis long tail</t>
+        </is>
+      </c>
+      <c r="D10" s="47" t="inlineStr">
+        <is>
+          <t>Duty recovery engagement (flat-fee project)</t>
+        </is>
+      </c>
+      <c r="E10" s="47" t="inlineStr">
+        <is>
+          <t>one drawback / refund filing engagement for one importer, priced flat and filed under our own or a partner broker's filer code</t>
+        </is>
+      </c>
+      <c r="F10" s="48" t="n">
+        <v>6500</v>
+      </c>
+      <c r="G10" s="49" t="n">
+        <v>6</v>
+      </c>
+      <c r="H10" s="49" t="n">
+        <v>25</v>
+      </c>
+      <c r="I10" s="49" t="n">
+        <v>55</v>
+      </c>
+      <c r="J10" s="49" t="n">
+        <v>100</v>
+      </c>
+      <c r="K10" s="49" t="n">
+        <v>160</v>
+      </c>
+      <c r="L10" s="50">
+        <f>G10*$F10</f>
+        <v/>
+      </c>
+      <c r="M10" s="50">
+        <f>H10*$F10</f>
+        <v/>
+      </c>
+      <c r="N10" s="50">
+        <f>I10*$F10</f>
+        <v/>
+      </c>
+      <c r="O10" s="50">
+        <f>J10*$F10</f>
+        <v/>
+      </c>
+      <c r="P10" s="50">
+        <f>K10*$F10</f>
+        <v/>
+      </c>
+      <c r="Q10" s="51" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="R10" s="50">
+        <f>L10*$Q10</f>
+        <v/>
+      </c>
+      <c r="S10" s="50">
+        <f>M10*$Q10</f>
+        <v/>
+      </c>
+      <c r="T10" s="50">
+        <f>N10*$Q10</f>
+        <v/>
+      </c>
+      <c r="U10" s="50">
+        <f>O10*$Q10</f>
+        <v/>
+      </c>
+      <c r="V10" s="50">
+        <f>P10*$Q10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="52" t="inlineStr">
+        <is>
+          <t>long-tail-customs-entry-and-duty-recovery</t>
+        </is>
+      </c>
+      <c r="B11" s="52" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" s="53" t="inlineStr">
+        <is>
+          <t>Entry Type 13 and instrument-aware duty recovery for the post-de-minimis long tail</t>
+        </is>
+      </c>
+      <c r="D11" s="53" t="inlineStr">
+        <is>
+          <t>Entry filing transaction fee (direct accounts)</t>
+        </is>
+      </c>
+      <c r="E11" s="53" t="inlineStr">
+        <is>
+          <t>one customs entry filed for a direct importer account, informal or formal, government fees billed separately at cost</t>
+        </is>
+      </c>
+      <c r="F11" s="48" t="n">
+        <v>85</v>
+      </c>
+      <c r="G11" s="49" t="n">
+        <v>1100</v>
+      </c>
+      <c r="H11" s="49" t="n">
+        <v>5400</v>
+      </c>
+      <c r="I11" s="49" t="n">
+        <v>13800</v>
+      </c>
+      <c r="J11" s="49" t="n">
+        <v>27600</v>
+      </c>
+      <c r="K11" s="49" t="n">
+        <v>46800</v>
+      </c>
+      <c r="L11" s="54">
+        <f>G11*$F11</f>
+        <v/>
+      </c>
+      <c r="M11" s="54">
+        <f>H11*$F11</f>
+        <v/>
+      </c>
+      <c r="N11" s="54">
+        <f>I11*$F11</f>
+        <v/>
+      </c>
+      <c r="O11" s="54">
+        <f>J11*$F11</f>
+        <v/>
+      </c>
+      <c r="P11" s="54">
+        <f>K11*$F11</f>
+        <v/>
+      </c>
+      <c r="Q11" s="51" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="R11" s="54">
+        <f>L11*$Q11</f>
+        <v/>
+      </c>
+      <c r="S11" s="54">
+        <f>M11*$Q11</f>
+        <v/>
+      </c>
+      <c r="T11" s="54">
+        <f>N11*$Q11</f>
+        <v/>
+      </c>
+      <c r="U11" s="54">
+        <f>O11*$Q11</f>
+        <v/>
+      </c>
+      <c r="V11" s="54">
+        <f>P11*$Q11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="46" t="inlineStr">
+        <is>
+          <t>long-tail-customs-entry-and-duty-recovery</t>
+        </is>
+      </c>
+      <c r="B12" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" s="47" t="inlineStr">
+        <is>
+          <t>Entry Type 13 and instrument-aware duty recovery for the post-de-minimis long tail</t>
+        </is>
+      </c>
+      <c r="D12" s="47" t="inlineStr">
+        <is>
+          <t>Classified SKU catalogue subscription</t>
+        </is>
+      </c>
+      <c r="E12" s="47" t="inlineStr">
+        <is>
+          <t>one importer account, annual subscription to its 10-digit HTS catalogue, ruling corpus, origin evidence and instrument mapping</t>
+        </is>
+      </c>
+      <c r="F12" s="48" t="n">
+        <v>3600</v>
+      </c>
+      <c r="G12" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="H12" s="49" t="n">
+        <v>40</v>
+      </c>
+      <c r="I12" s="49" t="n">
+        <v>104</v>
+      </c>
+      <c r="J12" s="49" t="n">
+        <v>207</v>
+      </c>
+      <c r="K12" s="49" t="n">
+        <v>350</v>
+      </c>
+      <c r="L12" s="50">
+        <f>G12*$F12</f>
+        <v/>
+      </c>
+      <c r="M12" s="50">
+        <f>H12*$F12</f>
+        <v/>
+      </c>
+      <c r="N12" s="50">
+        <f>I12*$F12</f>
+        <v/>
+      </c>
+      <c r="O12" s="50">
+        <f>J12*$F12</f>
+        <v/>
+      </c>
+      <c r="P12" s="50">
+        <f>K12*$F12</f>
+        <v/>
+      </c>
+      <c r="Q12" s="51" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="R12" s="50">
+        <f>L12*$Q12</f>
+        <v/>
+      </c>
+      <c r="S12" s="50">
+        <f>M12*$Q12</f>
+        <v/>
+      </c>
+      <c r="T12" s="50">
+        <f>N12*$Q12</f>
+        <v/>
+      </c>
+      <c r="U12" s="50">
+        <f>O12*$Q12</f>
+        <v/>
+      </c>
+      <c r="V12" s="50">
+        <f>P12*$Q12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="52" t="inlineStr">
+        <is>
+          <t>long-tail-customs-entry-and-duty-recovery</t>
+        </is>
+      </c>
+      <c r="B13" s="52" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" s="53" t="inlineStr">
+        <is>
+          <t>Entry Type 13 and instrument-aware duty recovery for the post-de-minimis long tail</t>
+        </is>
+      </c>
+      <c r="D13" s="53" t="inlineStr">
+        <is>
+          <t>White-label filing capacity for forwarders and 3PLs</t>
+        </is>
+      </c>
+      <c r="E13" s="53" t="inlineStr">
+        <is>
+          <t>one entry filed wholesale on behalf of a freight forwarder or 3PL that owns the client relationship</t>
+        </is>
+      </c>
+      <c r="F13" s="48" t="n">
+        <v>35</v>
+      </c>
+      <c r="G13" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="49" t="n">
+        <v>4000</v>
+      </c>
+      <c r="I13" s="49" t="n">
+        <v>14000</v>
+      </c>
+      <c r="J13" s="49" t="n">
+        <v>32000</v>
+      </c>
+      <c r="K13" s="49" t="n">
+        <v>60000</v>
+      </c>
+      <c r="L13" s="54">
+        <f>G13*$F13</f>
+        <v/>
+      </c>
+      <c r="M13" s="54">
+        <f>H13*$F13</f>
+        <v/>
+      </c>
+      <c r="N13" s="54">
+        <f>I13*$F13</f>
+        <v/>
+      </c>
+      <c r="O13" s="54">
+        <f>J13*$F13</f>
+        <v/>
+      </c>
+      <c r="P13" s="54">
+        <f>K13*$F13</f>
+        <v/>
+      </c>
+      <c r="Q13" s="51" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="R13" s="54">
+        <f>L13*$Q13</f>
+        <v/>
+      </c>
+      <c r="S13" s="54">
+        <f>M13*$Q13</f>
+        <v/>
+      </c>
+      <c r="T13" s="54">
+        <f>N13*$Q13</f>
+        <v/>
+      </c>
+      <c r="U13" s="54">
+        <f>O13*$Q13</f>
+        <v/>
+      </c>
+      <c r="V13" s="54">
+        <f>P13*$Q13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="46" t="inlineStr">
+        <is>
+          <t>nuclear-naval-supplier-qualification</t>
+        </is>
+      </c>
+      <c r="B14" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="C14" s="47" t="inlineStr">
+        <is>
+          <t>NQA-1 qualification and commercial grade dedication as a service</t>
+        </is>
+      </c>
+      <c r="D14" s="47" t="inlineStr">
+        <is>
+          <t>Appendix B / NQA-1 readiness sprint (fixed-fee project)</t>
+        </is>
+      </c>
+      <c r="E14" s="47" t="inlineStr">
+        <is>
+          <t>one complete QA program install at one manufacturing site: 18-criteria QA manual, ~42 procedures, training delivery, and an independent mock audit</t>
+        </is>
+      </c>
+      <c r="F14" s="48" t="n">
+        <v>70000</v>
+      </c>
+      <c r="G14" s="49" t="n">
+        <v>4</v>
+      </c>
+      <c r="H14" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="I14" s="49" t="n">
+        <v>12</v>
+      </c>
+      <c r="J14" s="49" t="n">
+        <v>14</v>
+      </c>
+      <c r="K14" s="49" t="n">
+        <v>15</v>
+      </c>
+      <c r="L14" s="50">
+        <f>G14*$F14</f>
+        <v/>
+      </c>
+      <c r="M14" s="50">
+        <f>H14*$F14</f>
+        <v/>
+      </c>
+      <c r="N14" s="50">
+        <f>I14*$F14</f>
+        <v/>
+      </c>
+      <c r="O14" s="50">
+        <f>J14*$F14</f>
+        <v/>
+      </c>
+      <c r="P14" s="50">
+        <f>K14*$F14</f>
+        <v/>
+      </c>
+      <c r="Q14" s="51" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="R14" s="50">
+        <f>L14*$Q14</f>
+        <v/>
+      </c>
+      <c r="S14" s="50">
+        <f>M14*$Q14</f>
+        <v/>
+      </c>
+      <c r="T14" s="50">
+        <f>N14*$Q14</f>
+        <v/>
+      </c>
+      <c r="U14" s="50">
+        <f>O14*$Q14</f>
+        <v/>
+      </c>
+      <c r="V14" s="50">
+        <f>P14*$Q14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="52" t="inlineStr">
+        <is>
+          <t>nuclear-naval-supplier-qualification</t>
+        </is>
+      </c>
+      <c r="B15" s="52" t="n">
+        <v>3</v>
+      </c>
+      <c r="C15" s="53" t="inlineStr">
+        <is>
+          <t>NQA-1 qualification and commercial grade dedication as a service</t>
+        </is>
+      </c>
+      <c r="D15" s="53" t="inlineStr">
+        <is>
+          <t>Outsourced QA program retainer (annual subscription)</t>
+        </is>
+      </c>
+      <c r="E15" s="53" t="inlineStr">
+        <is>
+          <t>one qualified shop under annual retainer: internal audit program execution, procedure revision control, NCR/CAR administration, Part 21 evaluation support, audit-day defence</t>
+        </is>
+      </c>
+      <c r="F15" s="48" t="n">
+        <v>40000</v>
+      </c>
+      <c r="G15" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="H15" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="I15" s="49" t="n">
+        <v>16</v>
+      </c>
+      <c r="J15" s="49" t="n">
+        <v>24</v>
+      </c>
+      <c r="K15" s="49" t="n">
+        <v>31</v>
+      </c>
+      <c r="L15" s="54">
+        <f>G15*$F15</f>
+        <v/>
+      </c>
+      <c r="M15" s="54">
+        <f>H15*$F15</f>
+        <v/>
+      </c>
+      <c r="N15" s="54">
+        <f>I15*$F15</f>
+        <v/>
+      </c>
+      <c r="O15" s="54">
+        <f>J15*$F15</f>
+        <v/>
+      </c>
+      <c r="P15" s="54">
+        <f>K15*$F15</f>
+        <v/>
+      </c>
+      <c r="Q15" s="51" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="R15" s="54">
+        <f>L15*$Q15</f>
+        <v/>
+      </c>
+      <c r="S15" s="54">
+        <f>M15*$Q15</f>
+        <v/>
+      </c>
+      <c r="T15" s="54">
+        <f>N15*$Q15</f>
+        <v/>
+      </c>
+      <c r="U15" s="54">
+        <f>O15*$Q15</f>
+        <v/>
+      </c>
+      <c r="V15" s="54">
+        <f>P15*$Q15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="46" t="inlineStr">
+        <is>
+          <t>nuclear-naval-supplier-qualification</t>
+        </is>
+      </c>
+      <c r="B16" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" s="47" t="inlineStr">
+        <is>
+          <t>NQA-1 qualification and commercial grade dedication as a service</t>
+        </is>
+      </c>
+      <c r="D16" s="47" t="inlineStr">
+        <is>
+          <t>Commercial grade dedication package (per-lot transaction)</t>
+        </is>
+      </c>
+      <c r="E16" s="47" t="inlineStr">
+        <is>
+          <t>one completed, signed, auditable dedication package on one item/lot: critical characteristics identified, Method 1-4 verification performed, package exported</t>
+        </is>
+      </c>
+      <c r="F16" s="48" t="n">
+        <v>14000</v>
+      </c>
+      <c r="G16" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="H16" s="49" t="n">
+        <v>38</v>
+      </c>
+      <c r="I16" s="49" t="n">
+        <v>85</v>
+      </c>
+      <c r="J16" s="49" t="n">
+        <v>135</v>
+      </c>
+      <c r="K16" s="49" t="n">
+        <v>185</v>
+      </c>
+      <c r="L16" s="50">
+        <f>G16*$F16</f>
+        <v/>
+      </c>
+      <c r="M16" s="50">
+        <f>H16*$F16</f>
+        <v/>
+      </c>
+      <c r="N16" s="50">
+        <f>I16*$F16</f>
+        <v/>
+      </c>
+      <c r="O16" s="50">
+        <f>J16*$F16</f>
+        <v/>
+      </c>
+      <c r="P16" s="50">
+        <f>K16*$F16</f>
+        <v/>
+      </c>
+      <c r="Q16" s="51" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="R16" s="50">
+        <f>L16*$Q16</f>
+        <v/>
+      </c>
+      <c r="S16" s="50">
+        <f>M16*$Q16</f>
+        <v/>
+      </c>
+      <c r="T16" s="50">
+        <f>N16*$Q16</f>
+        <v/>
+      </c>
+      <c r="U16" s="50">
+        <f>O16*$Q16</f>
+        <v/>
+      </c>
+      <c r="V16" s="50">
+        <f>P16*$Q16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="52" t="inlineStr">
+        <is>
+          <t>nuclear-naval-supplier-qualification</t>
+        </is>
+      </c>
+      <c r="B17" s="52" t="n">
+        <v>3</v>
+      </c>
+      <c r="C17" s="53" t="inlineStr">
+        <is>
+          <t>NQA-1 qualification and commercial grade dedication as a service</t>
+        </is>
+      </c>
+      <c r="D17" s="53" t="inlineStr">
+        <is>
+          <t>CGD Workbench seat (SaaS subscription)</t>
+        </is>
+      </c>
+      <c r="E17" s="53" t="inlineStr">
+        <is>
+          <t>one named user seat per year for the guided Method 1-4 workflow and critical-characteristics library, sold to component engineers and supplier quality staff</t>
+        </is>
+      </c>
+      <c r="F17" s="48" t="n">
+        <v>4800</v>
+      </c>
+      <c r="G17" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="49" t="n">
+        <v>25</v>
+      </c>
+      <c r="I17" s="49" t="n">
+        <v>90</v>
+      </c>
+      <c r="J17" s="49" t="n">
+        <v>190</v>
+      </c>
+      <c r="K17" s="49" t="n">
+        <v>320</v>
+      </c>
+      <c r="L17" s="54">
+        <f>G17*$F17</f>
+        <v/>
+      </c>
+      <c r="M17" s="54">
+        <f>H17*$F17</f>
+        <v/>
+      </c>
+      <c r="N17" s="54">
+        <f>I17*$F17</f>
+        <v/>
+      </c>
+      <c r="O17" s="54">
+        <f>J17*$F17</f>
+        <v/>
+      </c>
+      <c r="P17" s="54">
+        <f>K17*$F17</f>
+        <v/>
+      </c>
+      <c r="Q17" s="51" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="R17" s="54">
+        <f>L17*$Q17</f>
+        <v/>
+      </c>
+      <c r="S17" s="54">
+        <f>M17*$Q17</f>
+        <v/>
+      </c>
+      <c r="T17" s="54">
+        <f>N17*$Q17</f>
+        <v/>
+      </c>
+      <c r="U17" s="54">
+        <f>O17*$Q17</f>
+        <v/>
+      </c>
+      <c r="V17" s="54">
+        <f>P17*$Q17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="46" t="inlineStr">
+        <is>
+          <t>nuclear-naval-supplier-qualification</t>
+        </is>
+      </c>
+      <c r="B18" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="C18" s="47" t="inlineStr">
+        <is>
+          <t>NQA-1 qualification and commercial grade dedication as a service</t>
+        </is>
+      </c>
+      <c r="D18" s="47" t="inlineStr">
+        <is>
+          <t>CGD / NQA-1 workshop seat (training, per-seat)</t>
+        </is>
+      </c>
+      <c r="E18" s="47" t="inlineStr">
+        <is>
+          <t>one attendee seat at a two-day workshop, cohorts of 10-12</t>
+        </is>
+      </c>
+      <c r="F18" s="48" t="n">
+        <v>1150</v>
+      </c>
+      <c r="G18" s="49" t="n">
+        <v>60</v>
+      </c>
+      <c r="H18" s="49" t="n">
+        <v>180</v>
+      </c>
+      <c r="I18" s="49" t="n">
+        <v>320</v>
+      </c>
+      <c r="J18" s="49" t="n">
+        <v>420</v>
+      </c>
+      <c r="K18" s="49" t="n">
+        <v>500</v>
+      </c>
+      <c r="L18" s="50">
+        <f>G18*$F18</f>
+        <v/>
+      </c>
+      <c r="M18" s="50">
+        <f>H18*$F18</f>
+        <v/>
+      </c>
+      <c r="N18" s="50">
+        <f>I18*$F18</f>
+        <v/>
+      </c>
+      <c r="O18" s="50">
+        <f>J18*$F18</f>
+        <v/>
+      </c>
+      <c r="P18" s="50">
+        <f>K18*$F18</f>
+        <v/>
+      </c>
+      <c r="Q18" s="51" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="R18" s="50">
+        <f>L18*$Q18</f>
+        <v/>
+      </c>
+      <c r="S18" s="50">
+        <f>M18*$Q18</f>
+        <v/>
+      </c>
+      <c r="T18" s="50">
+        <f>N18*$Q18</f>
+        <v/>
+      </c>
+      <c r="U18" s="50">
+        <f>O18*$Q18</f>
+        <v/>
+      </c>
+      <c r="V18" s="50">
+        <f>P18*$Q18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="52" t="inlineStr">
+        <is>
+          <t>biosolids-outlet-exchange</t>
+        </is>
+      </c>
+      <c r="B19" s="52" t="n">
+        <v>4</v>
+      </c>
+      <c r="C19" s="53" t="inlineStr">
+        <is>
+          <t>PFAS-Compliant Biosolids Outlet Exchange for the Mid-Atlantic</t>
+        </is>
+      </c>
+      <c r="D19" s="53" t="inlineStr">
+        <is>
+          <t>PFAS Threshold Readiness Engagement</t>
+        </is>
+      </c>
+      <c r="E19" s="53" t="inlineStr">
+        <is>
+          <t>one fixed-scope 6-8 week engagement per generator: sampling program design under EPA Method 1633, lab selection and QA protocol, rolling-12-month exceedance tracking build, threshold-exposure forecast against the governing state rule, and a written outlet contingency plan</t>
+        </is>
+      </c>
+      <c r="F19" s="48" t="n">
+        <v>45000</v>
+      </c>
+      <c r="G19" s="49" t="n">
+        <v>9</v>
+      </c>
+      <c r="H19" s="49" t="n">
+        <v>18</v>
+      </c>
+      <c r="I19" s="49" t="n">
+        <v>22</v>
+      </c>
+      <c r="J19" s="49" t="n">
+        <v>18</v>
+      </c>
+      <c r="K19" s="49" t="n">
+        <v>14</v>
+      </c>
+      <c r="L19" s="54">
+        <f>G19*$F19</f>
+        <v/>
+      </c>
+      <c r="M19" s="54">
+        <f>H19*$F19</f>
+        <v/>
+      </c>
+      <c r="N19" s="54">
+        <f>I19*$F19</f>
+        <v/>
+      </c>
+      <c r="O19" s="54">
+        <f>J19*$F19</f>
+        <v/>
+      </c>
+      <c r="P19" s="54">
+        <f>K19*$F19</f>
+        <v/>
+      </c>
+      <c r="Q19" s="51" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="R19" s="54">
+        <f>L19*$Q19</f>
+        <v/>
+      </c>
+      <c r="S19" s="54">
+        <f>M19*$Q19</f>
+        <v/>
+      </c>
+      <c r="T19" s="54">
+        <f>N19*$Q19</f>
+        <v/>
+      </c>
+      <c r="U19" s="54">
+        <f>O19*$Q19</f>
+        <v/>
+      </c>
+      <c r="V19" s="54">
+        <f>P19*$Q19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="46" t="inlineStr">
+        <is>
+          <t>biosolids-outlet-exchange</t>
+        </is>
+      </c>
+      <c r="B20" s="46" t="n">
+        <v>4</v>
+      </c>
+      <c r="C20" s="47" t="inlineStr">
+        <is>
+          <t>PFAS-Compliant Biosolids Outlet Exchange for the Mid-Atlantic</t>
+        </is>
+      </c>
+      <c r="D20" s="47" t="inlineStr">
+        <is>
+          <t>Threshold &amp; Outlet Intelligence Subscription</t>
+        </is>
+      </c>
+      <c r="E20" s="47" t="inlineStr">
+        <is>
+          <t>one annual subscription per generator: quarterly-updated MD/PA/VA/DE statutory and permit threshold register, landfill and thermal outlet acceptance-criteria tracker, lab method and QA bulletins, plus 4 hours of named-advisor time per quarter</t>
+        </is>
+      </c>
+      <c r="F20" s="48" t="n">
+        <v>18000</v>
+      </c>
+      <c r="G20" s="49" t="n">
+        <v>5</v>
+      </c>
+      <c r="H20" s="49" t="n">
+        <v>14</v>
+      </c>
+      <c r="I20" s="49" t="n">
+        <v>24</v>
+      </c>
+      <c r="J20" s="49" t="n">
+        <v>33</v>
+      </c>
+      <c r="K20" s="49" t="n">
+        <v>40</v>
+      </c>
+      <c r="L20" s="50">
+        <f>G20*$F20</f>
+        <v/>
+      </c>
+      <c r="M20" s="50">
+        <f>H20*$F20</f>
+        <v/>
+      </c>
+      <c r="N20" s="50">
+        <f>I20*$F20</f>
+        <v/>
+      </c>
+      <c r="O20" s="50">
+        <f>J20*$F20</f>
+        <v/>
+      </c>
+      <c r="P20" s="50">
+        <f>K20*$F20</f>
+        <v/>
+      </c>
+      <c r="Q20" s="51" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="R20" s="50">
+        <f>L20*$Q20</f>
+        <v/>
+      </c>
+      <c r="S20" s="50">
+        <f>M20*$Q20</f>
+        <v/>
+      </c>
+      <c r="T20" s="50">
+        <f>N20*$Q20</f>
+        <v/>
+      </c>
+      <c r="U20" s="50">
+        <f>O20*$Q20</f>
+        <v/>
+      </c>
+      <c r="V20" s="50">
+        <f>P20*$Q20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="52" t="inlineStr">
+        <is>
+          <t>biosolids-outlet-exchange</t>
+        </is>
+      </c>
+      <c r="B21" s="52" t="n">
+        <v>4</v>
+      </c>
+      <c r="C21" s="53" t="inlineStr">
+        <is>
+          <t>PFAS-Compliant Biosolids Outlet Exchange for the Mid-Atlantic</t>
+        </is>
+      </c>
+      <c r="D21" s="53" t="inlineStr">
+        <is>
+          <t>Outlet Placement — Disclosed Agency Commission</t>
+        </is>
+      </c>
+      <c r="E21" s="53" t="inlineStr">
+        <is>
+          <t>one wet ton of biosolids placed at a compliant outlet, where the utility contracts the outlet and hauler directly and we take a disclosed placement commission — we never take title and never quote a firm per-ton price</t>
+        </is>
+      </c>
+      <c r="F21" s="48" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G21" s="49" t="n">
+        <v>6000</v>
+      </c>
+      <c r="H21" s="49" t="n">
+        <v>28000</v>
+      </c>
+      <c r="I21" s="49" t="n">
+        <v>55000</v>
+      </c>
+      <c r="J21" s="49" t="n">
+        <v>85000</v>
+      </c>
+      <c r="K21" s="49" t="n">
+        <v>110000</v>
+      </c>
+      <c r="L21" s="54">
+        <f>G21*$F21</f>
+        <v/>
+      </c>
+      <c r="M21" s="54">
+        <f>H21*$F21</f>
+        <v/>
+      </c>
+      <c r="N21" s="54">
+        <f>I21*$F21</f>
+        <v/>
+      </c>
+      <c r="O21" s="54">
+        <f>J21*$F21</f>
+        <v/>
+      </c>
+      <c r="P21" s="54">
+        <f>K21*$F21</f>
+        <v/>
+      </c>
+      <c r="Q21" s="51" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="R21" s="54">
+        <f>L21*$Q21</f>
+        <v/>
+      </c>
+      <c r="S21" s="54">
+        <f>M21*$Q21</f>
+        <v/>
+      </c>
+      <c r="T21" s="54">
+        <f>N21*$Q21</f>
+        <v/>
+      </c>
+      <c r="U21" s="54">
+        <f>O21*$Q21</f>
+        <v/>
+      </c>
+      <c r="V21" s="54">
+        <f>P21*$Q21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="46" t="inlineStr">
+        <is>
+          <t>biosolids-outlet-exchange</t>
+        </is>
+      </c>
+      <c r="B22" s="46" t="n">
+        <v>4</v>
+      </c>
+      <c r="C22" s="47" t="inlineStr">
+        <is>
+          <t>PFAS-Compliant Biosolids Outlet Exchange for the Mid-Atlantic</t>
+        </is>
+      </c>
+      <c r="D22" s="47" t="inlineStr">
+        <is>
+          <t>Industrial Source-Control Investigation</t>
+        </is>
+      </c>
+      <c r="E22" s="47" t="inlineStr">
+        <is>
+          <t>one 10-14 week sewershed investigation per collection system: significant industrial user survey, sampling campaign design and execution, PFAS source ranking, and draft pretreatment ordinance language</t>
+        </is>
+      </c>
+      <c r="F22" s="48" t="n">
+        <v>85000</v>
+      </c>
+      <c r="G22" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" s="49" t="n">
+        <v>4</v>
+      </c>
+      <c r="I22" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="J22" s="49" t="n">
+        <v>11</v>
+      </c>
+      <c r="K22" s="49" t="n">
+        <v>13</v>
+      </c>
+      <c r="L22" s="50">
+        <f>G22*$F22</f>
+        <v/>
+      </c>
+      <c r="M22" s="50">
+        <f>H22*$F22</f>
+        <v/>
+      </c>
+      <c r="N22" s="50">
+        <f>I22*$F22</f>
+        <v/>
+      </c>
+      <c r="O22" s="50">
+        <f>J22*$F22</f>
+        <v/>
+      </c>
+      <c r="P22" s="50">
+        <f>K22*$F22</f>
+        <v/>
+      </c>
+      <c r="Q22" s="51" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="R22" s="50">
+        <f>L22*$Q22</f>
+        <v/>
+      </c>
+      <c r="S22" s="50">
+        <f>M22*$Q22</f>
+        <v/>
+      </c>
+      <c r="T22" s="50">
+        <f>N22*$Q22</f>
+        <v/>
+      </c>
+      <c r="U22" s="50">
+        <f>O22*$Q22</f>
+        <v/>
+      </c>
+      <c r="V22" s="50">
+        <f>P22*$Q22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="52" t="inlineStr">
+        <is>
+          <t>cra-embedded-sbom-and-cve-triage</t>
+        </is>
+      </c>
+      <c r="B23" s="52" t="n">
+        <v>5</v>
+      </c>
+      <c r="C23" s="53" t="inlineStr">
+        <is>
+          <t>Reachability-grade SBOMs and kernel-CVE triage for embedded Linux</t>
+        </is>
+      </c>
+      <c r="D23" s="53" t="inlineStr">
+        <is>
+          <t>CRA readiness &amp; SBOM-quality audit (project, land motion)</t>
+        </is>
+      </c>
+      <c r="E23" s="53" t="inlineStr">
+        <is>
+          <t>one fixed-scope readiness audit for one manufacturer: BSI TR-03183-2 scoring, reachability baseline on their live manifest/.config, Annex I gap list, conformity-route recommendation — 2-3 senior weeks</t>
+        </is>
+      </c>
+      <c r="F23" s="48" t="n">
+        <v>18000</v>
+      </c>
+      <c r="G23" s="49" t="n">
+        <v>14</v>
+      </c>
+      <c r="H23" s="49" t="n">
+        <v>40</v>
+      </c>
+      <c r="I23" s="49" t="n">
+        <v>55</v>
+      </c>
+      <c r="J23" s="49" t="n">
+        <v>45</v>
+      </c>
+      <c r="K23" s="49" t="n">
+        <v>40</v>
+      </c>
+      <c r="L23" s="54">
+        <f>G23*$F23</f>
+        <v/>
+      </c>
+      <c r="M23" s="54">
+        <f>H23*$F23</f>
+        <v/>
+      </c>
+      <c r="N23" s="54">
+        <f>I23*$F23</f>
+        <v/>
+      </c>
+      <c r="O23" s="54">
+        <f>J23*$F23</f>
+        <v/>
+      </c>
+      <c r="P23" s="54">
+        <f>K23*$F23</f>
+        <v/>
+      </c>
+      <c r="Q23" s="51" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="R23" s="54">
+        <f>L23*$Q23</f>
+        <v/>
+      </c>
+      <c r="S23" s="54">
+        <f>M23*$Q23</f>
+        <v/>
+      </c>
+      <c r="T23" s="54">
+        <f>N23*$Q23</f>
+        <v/>
+      </c>
+      <c r="U23" s="54">
+        <f>O23*$Q23</f>
+        <v/>
+      </c>
+      <c r="V23" s="54">
+        <f>P23*$Q23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="46" t="inlineStr">
+        <is>
+          <t>cra-embedded-sbom-and-cve-triage</t>
+        </is>
+      </c>
+      <c r="B24" s="46" t="n">
+        <v>5</v>
+      </c>
+      <c r="C24" s="47" t="inlineStr">
+        <is>
+          <t>Reachability-grade SBOMs and kernel-CVE triage for embedded Linux</t>
+        </is>
+      </c>
+      <c r="D24" s="47" t="inlineStr">
+        <is>
+          <t>Annex VII technical file &amp; conformity dossier (project, repeat-purchase not renewal)</t>
+        </is>
+      </c>
+      <c r="E24" s="47" t="inlineStr">
+        <is>
+          <t>one complete technical documentation package for one device family: Annex VII file, Annex I Part I security requirements evidence, Annex I Part II SBOM to top-level-dependency depth, declared support period justification, EU declaration of conformity draft — 6-8 senior weeks</t>
+        </is>
+      </c>
+      <c r="F24" s="48" t="n">
+        <v>55000</v>
+      </c>
+      <c r="G24" s="49" t="n">
+        <v>5</v>
+      </c>
+      <c r="H24" s="49" t="n">
+        <v>18</v>
+      </c>
+      <c r="I24" s="49" t="n">
+        <v>20</v>
+      </c>
+      <c r="J24" s="49" t="n">
+        <v>24</v>
+      </c>
+      <c r="K24" s="49" t="n">
+        <v>28</v>
+      </c>
+      <c r="L24" s="50">
+        <f>G24*$F24</f>
+        <v/>
+      </c>
+      <c r="M24" s="50">
+        <f>H24*$F24</f>
+        <v/>
+      </c>
+      <c r="N24" s="50">
+        <f>I24*$F24</f>
+        <v/>
+      </c>
+      <c r="O24" s="50">
+        <f>J24*$F24</f>
+        <v/>
+      </c>
+      <c r="P24" s="50">
+        <f>K24*$F24</f>
+        <v/>
+      </c>
+      <c r="Q24" s="51" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="R24" s="50">
+        <f>L24*$Q24</f>
+        <v/>
+      </c>
+      <c r="S24" s="50">
+        <f>M24*$Q24</f>
+        <v/>
+      </c>
+      <c r="T24" s="50">
+        <f>N24*$Q24</f>
+        <v/>
+      </c>
+      <c r="U24" s="50">
+        <f>O24*$Q24</f>
+        <v/>
+      </c>
+      <c r="V24" s="50">
+        <f>P24*$Q24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="52" t="inlineStr">
+        <is>
+          <t>cra-embedded-sbom-and-cve-triage</t>
+        </is>
+      </c>
+      <c r="B25" s="52" t="n">
+        <v>5</v>
+      </c>
+      <c r="C25" s="53" t="inlineStr">
+        <is>
+          <t>Reachability-grade SBOMs and kernel-CVE triage for embedded Linux</t>
+        </is>
+      </c>
+      <c r="D25" s="53" t="inlineStr">
+        <is>
+          <t>Managed vulnerability handling retainer (recurring, annual contract)</t>
+        </is>
+      </c>
+      <c r="E25" s="53" t="inlineStr">
+        <is>
+          <t>one manufacturer account under managed Art. 13(8) vulnerability handling and Art. 14 reporting for one year, covering up to two device families, with a contracted 24h early-warning / 72h notification / 14d final-report SLA to the Single Reporting Platform and burst-week on-call</t>
+        </is>
+      </c>
+      <c r="F25" s="48" t="n">
+        <v>24000</v>
+      </c>
+      <c r="G25" s="49" t="n">
+        <v>9</v>
+      </c>
+      <c r="H25" s="49" t="n">
+        <v>34</v>
+      </c>
+      <c r="I25" s="49" t="n">
+        <v>66</v>
+      </c>
+      <c r="J25" s="49" t="n">
+        <v>100</v>
+      </c>
+      <c r="K25" s="49" t="n">
+        <v>135</v>
+      </c>
+      <c r="L25" s="54">
+        <f>G25*$F25</f>
+        <v/>
+      </c>
+      <c r="M25" s="54">
+        <f>H25*$F25</f>
+        <v/>
+      </c>
+      <c r="N25" s="54">
+        <f>I25*$F25</f>
+        <v/>
+      </c>
+      <c r="O25" s="54">
+        <f>J25*$F25</f>
+        <v/>
+      </c>
+      <c r="P25" s="54">
+        <f>K25*$F25</f>
+        <v/>
+      </c>
+      <c r="Q25" s="51" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R25" s="54">
+        <f>L25*$Q25</f>
+        <v/>
+      </c>
+      <c r="S25" s="54">
+        <f>M25*$Q25</f>
+        <v/>
+      </c>
+      <c r="T25" s="54">
+        <f>N25*$Q25</f>
+        <v/>
+      </c>
+      <c r="U25" s="54">
+        <f>O25*$Q25</f>
+        <v/>
+      </c>
+      <c r="V25" s="54">
+        <f>P25*$Q25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="46" t="inlineStr">
+        <is>
+          <t>cra-embedded-sbom-and-cve-triage</t>
+        </is>
+      </c>
+      <c r="B26" s="46" t="n">
+        <v>5</v>
+      </c>
+      <c r="C26" s="47" t="inlineStr">
+        <is>
+          <t>Reachability-grade SBOMs and kernel-CVE triage for embedded Linux</t>
+        </is>
+      </c>
+      <c r="D26" s="47" t="inlineStr">
+        <is>
+          <t>Signed conformity attestation (recurring, insurance-backed)</t>
+        </is>
+      </c>
+      <c r="E26" s="47" t="inlineStr">
+        <is>
+          <t>one countersigned annual attestation covering one device family's OpenVEX justification set and declared support period, issued under professional indemnity cover with named liability limits — the deliverable no sourced competitor offers</t>
+        </is>
+      </c>
+      <c r="F26" s="48" t="n">
+        <v>12000</v>
+      </c>
+      <c r="G26" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="49" t="n">
+        <v>12</v>
+      </c>
+      <c r="I26" s="49" t="n">
+        <v>34</v>
+      </c>
+      <c r="J26" s="49" t="n">
+        <v>62</v>
+      </c>
+      <c r="K26" s="49" t="n">
+        <v>92</v>
+      </c>
+      <c r="L26" s="50">
+        <f>G26*$F26</f>
+        <v/>
+      </c>
+      <c r="M26" s="50">
+        <f>H26*$F26</f>
+        <v/>
+      </c>
+      <c r="N26" s="50">
+        <f>I26*$F26</f>
+        <v/>
+      </c>
+      <c r="O26" s="50">
+        <f>J26*$F26</f>
+        <v/>
+      </c>
+      <c r="P26" s="50">
+        <f>K26*$F26</f>
+        <v/>
+      </c>
+      <c r="Q26" s="51" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R26" s="50">
+        <f>L26*$Q26</f>
+        <v/>
+      </c>
+      <c r="S26" s="50">
+        <f>M26*$Q26</f>
+        <v/>
+      </c>
+      <c r="T26" s="50">
+        <f>N26*$Q26</f>
+        <v/>
+      </c>
+      <c r="U26" s="50">
+        <f>O26*$Q26</f>
+        <v/>
+      </c>
+      <c r="V26" s="50">
+        <f>P26*$Q26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="52" t="inlineStr">
+        <is>
+          <t>cra-embedded-sbom-and-cve-triage</t>
+        </is>
+      </c>
+      <c r="B27" s="52" t="n">
+        <v>5</v>
+      </c>
+      <c r="C27" s="53" t="inlineStr">
+        <is>
+          <t>Reachability-grade SBOMs and kernel-CVE triage for embedded Linux</t>
+        </is>
+      </c>
+      <c r="D27" s="53" t="inlineStr">
+        <is>
+          <t>Notified-body / accredited-lab subcontract evaluation (project, capacity-gap line)</t>
+        </is>
+      </c>
+      <c r="E27" s="53" t="inlineStr">
+        <is>
+          <t>one subcontracted technical evaluation of one Annex III Class I/II product's embedded Linux stack, delivered into a designated notified body's or accredited lab's conformity assessment file</t>
+        </is>
+      </c>
+      <c r="F27" s="48" t="n">
+        <v>30000</v>
+      </c>
+      <c r="G27" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="I27" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="J27" s="49" t="n">
+        <v>20</v>
+      </c>
+      <c r="K27" s="49" t="n">
+        <v>30</v>
+      </c>
+      <c r="L27" s="54">
+        <f>G27*$F27</f>
+        <v/>
+      </c>
+      <c r="M27" s="54">
+        <f>H27*$F27</f>
+        <v/>
+      </c>
+      <c r="N27" s="54">
+        <f>I27*$F27</f>
+        <v/>
+      </c>
+      <c r="O27" s="54">
+        <f>J27*$F27</f>
+        <v/>
+      </c>
+      <c r="P27" s="54">
+        <f>K27*$F27</f>
+        <v/>
+      </c>
+      <c r="Q27" s="51" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="R27" s="54">
+        <f>L27*$Q27</f>
+        <v/>
+      </c>
+      <c r="S27" s="54">
+        <f>M27*$Q27</f>
+        <v/>
+      </c>
+      <c r="T27" s="54">
+        <f>N27*$Q27</f>
+        <v/>
+      </c>
+      <c r="U27" s="54">
+        <f>O27*$Q27</f>
+        <v/>
+      </c>
+      <c r="V27" s="54">
+        <f>P27*$Q27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="46" t="inlineStr">
+        <is>
+          <t>funded-claim-detection-for-casualty</t>
+        </is>
+      </c>
+      <c r="B28" s="46" t="n">
+        <v>6</v>
+      </c>
+      <c r="C28" s="47" t="inlineStr">
+        <is>
+          <t>Funded-Claim Detection for Casualty Reserving</t>
+        </is>
+      </c>
+      <c r="D28" s="47" t="inlineStr">
+        <is>
+          <t>Funder Intelligence Subscription</t>
+        </is>
+      </c>
+      <c r="E28" s="47" t="inlineStr">
+        <is>
+          <t>one annual multi-state funder-intelligence subscription per carrier or reinsurer group (quarterly refresh, beneficial-ownership and firm-affiliation graph, portal access, 5 named users)</t>
+        </is>
+      </c>
+      <c r="F28" s="48" t="n">
+        <v>45000</v>
+      </c>
+      <c r="G28" s="49" t="n">
+        <v>3</v>
+      </c>
+      <c r="H28" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="I28" s="49" t="n">
+        <v>14</v>
+      </c>
+      <c r="J28" s="49" t="n">
+        <v>18</v>
+      </c>
+      <c r="K28" s="49" t="n">
+        <v>20</v>
+      </c>
+      <c r="L28" s="50">
+        <f>G28*$F28</f>
+        <v/>
+      </c>
+      <c r="M28" s="50">
+        <f>H28*$F28</f>
+        <v/>
+      </c>
+      <c r="N28" s="50">
+        <f>I28*$F28</f>
+        <v/>
+      </c>
+      <c r="O28" s="50">
+        <f>J28*$F28</f>
+        <v/>
+      </c>
+      <c r="P28" s="50">
+        <f>K28*$F28</f>
+        <v/>
+      </c>
+      <c r="Q28" s="51" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="R28" s="50">
+        <f>L28*$Q28</f>
+        <v/>
+      </c>
+      <c r="S28" s="50">
+        <f>M28*$Q28</f>
+        <v/>
+      </c>
+      <c r="T28" s="50">
+        <f>N28*$Q28</f>
+        <v/>
+      </c>
+      <c r="U28" s="50">
+        <f>O28*$Q28</f>
+        <v/>
+      </c>
+      <c r="V28" s="50">
+        <f>P28*$Q28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="52" t="inlineStr">
+        <is>
+          <t>funded-claim-detection-for-casualty</t>
+        </is>
+      </c>
+      <c r="B29" s="52" t="n">
+        <v>6</v>
+      </c>
+      <c r="C29" s="53" t="inlineStr">
+        <is>
+          <t>Funded-Claim Detection for Casualty Reserving</t>
+        </is>
+      </c>
+      <c r="D29" s="53" t="inlineStr">
+        <is>
+          <t>Portfolio Funder-Exposure Diagnostic</t>
+        </is>
+      </c>
+      <c r="E29" s="53" t="inlineStr">
+        <is>
+          <t>one fixed-scope 6-8 week diagnostic engagement against a carrier's open casualty claim inventory, delivering funded-share estimate and reserve implications by accident year</t>
+        </is>
+      </c>
+      <c r="F29" s="48" t="n">
+        <v>65000</v>
+      </c>
+      <c r="G29" s="49" t="n">
+        <v>4</v>
+      </c>
+      <c r="H29" s="49" t="n">
+        <v>9</v>
+      </c>
+      <c r="I29" s="49" t="n">
+        <v>12</v>
+      </c>
+      <c r="J29" s="49" t="n">
+        <v>14</v>
+      </c>
+      <c r="K29" s="49" t="n">
+        <v>15</v>
+      </c>
+      <c r="L29" s="54">
+        <f>G29*$F29</f>
+        <v/>
+      </c>
+      <c r="M29" s="54">
+        <f>H29*$F29</f>
+        <v/>
+      </c>
+      <c r="N29" s="54">
+        <f>I29*$F29</f>
+        <v/>
+      </c>
+      <c r="O29" s="54">
+        <f>J29*$F29</f>
+        <v/>
+      </c>
+      <c r="P29" s="54">
+        <f>K29*$F29</f>
+        <v/>
+      </c>
+      <c r="Q29" s="51" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="R29" s="54">
+        <f>L29*$Q29</f>
+        <v/>
+      </c>
+      <c r="S29" s="54">
+        <f>M29*$Q29</f>
+        <v/>
+      </c>
+      <c r="T29" s="54">
+        <f>N29*$Q29</f>
+        <v/>
+      </c>
+      <c r="U29" s="54">
+        <f>O29*$Q29</f>
+        <v/>
+      </c>
+      <c r="V29" s="54">
+        <f>P29*$Q29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="46" t="inlineStr">
+        <is>
+          <t>funded-claim-detection-for-casualty</t>
+        </is>
+      </c>
+      <c r="B30" s="46" t="n">
+        <v>6</v>
+      </c>
+      <c r="C30" s="47" t="inlineStr">
+        <is>
+          <t>Funded-Claim Detection for Casualty Reserving</t>
+        </is>
+      </c>
+      <c r="D30" s="47" t="inlineStr">
+        <is>
+          <t>Defense-Side Funder Tracing and Expert Engagement</t>
+        </is>
+      </c>
+      <c r="E30" s="47" t="inlineStr">
+        <is>
+          <t>one matter: ownership-tracing memo for a defense firm in a disclosure motion, with optional sworn declaration and deposition</t>
+        </is>
+      </c>
+      <c r="F30" s="48" t="n">
+        <v>24000</v>
+      </c>
+      <c r="G30" s="49" t="n">
+        <v>6</v>
+      </c>
+      <c r="H30" s="49" t="n">
+        <v>22</v>
+      </c>
+      <c r="I30" s="49" t="n">
+        <v>36</v>
+      </c>
+      <c r="J30" s="49" t="n">
+        <v>44</v>
+      </c>
+      <c r="K30" s="49" t="n">
+        <v>48</v>
+      </c>
+      <c r="L30" s="50">
+        <f>G30*$F30</f>
+        <v/>
+      </c>
+      <c r="M30" s="50">
+        <f>H30*$F30</f>
+        <v/>
+      </c>
+      <c r="N30" s="50">
+        <f>I30*$F30</f>
+        <v/>
+      </c>
+      <c r="O30" s="50">
+        <f>J30*$F30</f>
+        <v/>
+      </c>
+      <c r="P30" s="50">
+        <f>K30*$F30</f>
+        <v/>
+      </c>
+      <c r="Q30" s="51" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="R30" s="50">
+        <f>L30*$Q30</f>
+        <v/>
+      </c>
+      <c r="S30" s="50">
+        <f>M30*$Q30</f>
+        <v/>
+      </c>
+      <c r="T30" s="50">
+        <f>N30*$Q30</f>
+        <v/>
+      </c>
+      <c r="U30" s="50">
+        <f>O30*$Q30</f>
+        <v/>
+      </c>
+      <c r="V30" s="50">
+        <f>P30*$Q30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="52" t="inlineStr">
+        <is>
+          <t>funded-claim-detection-for-casualty</t>
+        </is>
+      </c>
+      <c r="B31" s="52" t="n">
+        <v>6</v>
+      </c>
+      <c r="C31" s="53" t="inlineStr">
+        <is>
+          <t>Funded-Claim Detection for Casualty Reserving</t>
+        </is>
+      </c>
+      <c r="D31" s="53" t="inlineStr">
+        <is>
+          <t>Funded-Claim Scoring Feed (contingent, unsourced)</t>
+        </is>
+      </c>
+      <c r="E31" s="53" t="inlineStr">
+        <is>
+          <t>one annual batch/API scoring feed run against a carrier's open claim inventory, scoring firm-level funder-relationship probability</t>
+        </is>
+      </c>
+      <c r="F31" s="48" t="n">
+        <v>95000</v>
+      </c>
+      <c r="G31" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" s="49" t="n">
+        <v>3</v>
+      </c>
+      <c r="J31" s="49" t="n">
+        <v>5</v>
+      </c>
+      <c r="K31" s="49" t="n">
+        <v>6</v>
+      </c>
+      <c r="L31" s="54">
+        <f>G31*$F31</f>
+        <v/>
+      </c>
+      <c r="M31" s="54">
+        <f>H31*$F31</f>
+        <v/>
+      </c>
+      <c r="N31" s="54">
+        <f>I31*$F31</f>
+        <v/>
+      </c>
+      <c r="O31" s="54">
+        <f>J31*$F31</f>
+        <v/>
+      </c>
+      <c r="P31" s="54">
+        <f>K31*$F31</f>
+        <v/>
+      </c>
+      <c r="Q31" s="51" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="R31" s="54">
+        <f>L31*$Q31</f>
+        <v/>
+      </c>
+      <c r="S31" s="54">
+        <f>M31*$Q31</f>
+        <v/>
+      </c>
+      <c r="T31" s="54">
+        <f>N31*$Q31</f>
+        <v/>
+      </c>
+      <c r="U31" s="54">
+        <f>O31*$Q31</f>
+        <v/>
+      </c>
+      <c r="V31" s="54">
+        <f>P31*$Q31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="46" t="inlineStr">
+        <is>
+          <t>grid-equipment-slot-forward-exchange</t>
+        </is>
+      </c>
+      <c r="B32" s="46" t="n">
+        <v>7</v>
+      </c>
+      <c r="C32" s="47" t="inlineStr">
+        <is>
+          <t>Forward exchange for transformer and switchgear production slots</t>
+        </is>
+      </c>
+      <c r="D32" s="47" t="inlineStr">
+        <is>
+          <t>Procurement &amp; RFQ engagement (project fee)</t>
+        </is>
+      </c>
+      <c r="E32" s="47" t="inlineStr">
+        <is>
+          <t>one fixed-fee project engagement: spec standardization (kVA, voltage class, impedance, BIL, delivery window), multi-OEM RFQ, bid levelling, slot reservation and 10-30% deposit negotiation, contract terms</t>
+        </is>
+      </c>
+      <c r="F32" s="48" t="n">
+        <v>125000</v>
+      </c>
+      <c r="G32" s="49" t="n">
+        <v>5</v>
+      </c>
+      <c r="H32" s="49" t="n">
+        <v>14</v>
+      </c>
+      <c r="I32" s="49" t="n">
+        <v>26</v>
+      </c>
+      <c r="J32" s="49" t="n">
+        <v>38</v>
+      </c>
+      <c r="K32" s="49" t="n">
+        <v>48</v>
+      </c>
+      <c r="L32" s="50">
+        <f>G32*$F32</f>
+        <v/>
+      </c>
+      <c r="M32" s="50">
+        <f>H32*$F32</f>
+        <v/>
+      </c>
+      <c r="N32" s="50">
+        <f>I32*$F32</f>
+        <v/>
+      </c>
+      <c r="O32" s="50">
+        <f>J32*$F32</f>
+        <v/>
+      </c>
+      <c r="P32" s="50">
+        <f>K32*$F32</f>
+        <v/>
+      </c>
+      <c r="Q32" s="51" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="R32" s="50">
+        <f>L32*$Q32</f>
+        <v/>
+      </c>
+      <c r="S32" s="50">
+        <f>M32*$Q32</f>
+        <v/>
+      </c>
+      <c r="T32" s="50">
+        <f>N32*$Q32</f>
+        <v/>
+      </c>
+      <c r="U32" s="50">
+        <f>O32*$Q32</f>
+        <v/>
+      </c>
+      <c r="V32" s="50">
+        <f>P32*$Q32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="52" t="inlineStr">
+        <is>
+          <t>grid-equipment-slot-forward-exchange</t>
+        </is>
+      </c>
+      <c r="B33" s="52" t="n">
+        <v>7</v>
+      </c>
+      <c r="C33" s="53" t="inlineStr">
+        <is>
+          <t>Forward exchange for transformer and switchgear production slots</t>
+        </is>
+      </c>
+      <c r="D33" s="53" t="inlineStr">
+        <is>
+          <t>Expediting &amp; owner's-rep retainer (recurring)</t>
+        </is>
+      </c>
+      <c r="E33" s="53" t="inlineStr">
+        <is>
+          <t>one client retainer-year at $10k/month: milestone tracking against the OEM production schedule, FAT scheduling and witness, change-order defense, escalation, logistics and rigging coordination across the client's active order book</t>
+        </is>
+      </c>
+      <c r="F33" s="48" t="n">
+        <v>120000</v>
+      </c>
+      <c r="G33" s="49" t="n">
+        <v>3</v>
+      </c>
+      <c r="H33" s="49" t="n">
+        <v>9</v>
+      </c>
+      <c r="I33" s="49" t="n">
+        <v>19</v>
+      </c>
+      <c r="J33" s="49" t="n">
+        <v>30</v>
+      </c>
+      <c r="K33" s="49" t="n">
+        <v>42</v>
+      </c>
+      <c r="L33" s="54">
+        <f>G33*$F33</f>
+        <v/>
+      </c>
+      <c r="M33" s="54">
+        <f>H33*$F33</f>
+        <v/>
+      </c>
+      <c r="N33" s="54">
+        <f>I33*$F33</f>
+        <v/>
+      </c>
+      <c r="O33" s="54">
+        <f>J33*$F33</f>
+        <v/>
+      </c>
+      <c r="P33" s="54">
+        <f>K33*$F33</f>
+        <v/>
+      </c>
+      <c r="Q33" s="51" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="R33" s="54">
+        <f>L33*$Q33</f>
+        <v/>
+      </c>
+      <c r="S33" s="54">
+        <f>M33*$Q33</f>
+        <v/>
+      </c>
+      <c r="T33" s="54">
+        <f>N33*$Q33</f>
+        <v/>
+      </c>
+      <c r="U33" s="54">
+        <f>O33*$Q33</f>
+        <v/>
+      </c>
+      <c r="V33" s="54">
+        <f>P33*$Q33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="46" t="inlineStr">
+        <is>
+          <t>grid-equipment-slot-forward-exchange</t>
+        </is>
+      </c>
+      <c r="B34" s="46" t="n">
+        <v>7</v>
+      </c>
+      <c r="C34" s="47" t="inlineStr">
+        <is>
+          <t>Forward exchange for transformer and switchgear production slots</t>
+        </is>
+      </c>
+      <c r="D34" s="47" t="inlineStr">
+        <is>
+          <t>Slot assignment / novation fee (transaction)</t>
+        </is>
+      </c>
+      <c r="E34" s="47" t="inlineStr">
+        <is>
+          <t>one closed consented novation of a firm, placed MV/HV equipment order: 4% of an assigned package averaging $4.0M (100 MVA transformer ~$3.0-3.5M at $30-35k/MVA plus MV switchgear), inclusive of OEM consent negotiation, escrow of the transferred deposit and assignment paperwork</t>
+        </is>
+      </c>
+      <c r="F34" s="48" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G34" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" s="49" t="n">
+        <v>3</v>
+      </c>
+      <c r="I34" s="49" t="n">
+        <v>5</v>
+      </c>
+      <c r="J34" s="49" t="n">
+        <v>7</v>
+      </c>
+      <c r="K34" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="L34" s="50">
+        <f>G34*$F34</f>
+        <v/>
+      </c>
+      <c r="M34" s="50">
+        <f>H34*$F34</f>
+        <v/>
+      </c>
+      <c r="N34" s="50">
+        <f>I34*$F34</f>
+        <v/>
+      </c>
+      <c r="O34" s="50">
+        <f>J34*$F34</f>
+        <v/>
+      </c>
+      <c r="P34" s="50">
+        <f>K34*$F34</f>
+        <v/>
+      </c>
+      <c r="Q34" s="51" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="R34" s="50">
+        <f>L34*$Q34</f>
+        <v/>
+      </c>
+      <c r="S34" s="50">
+        <f>M34*$Q34</f>
+        <v/>
+      </c>
+      <c r="T34" s="50">
+        <f>N34*$Q34</f>
+        <v/>
+      </c>
+      <c r="U34" s="50">
+        <f>O34*$Q34</f>
+        <v/>
+      </c>
+      <c r="V34" s="50">
+        <f>P34*$Q34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="52" t="inlineStr">
+        <is>
+          <t>grid-equipment-slot-forward-exchange</t>
+        </is>
+      </c>
+      <c r="B35" s="52" t="n">
+        <v>7</v>
+      </c>
+      <c r="C35" s="53" t="inlineStr">
+        <is>
+          <t>Forward exchange for transformer and switchgear production slots</t>
+        </is>
+      </c>
+      <c r="D35" s="53" t="inlineStr">
+        <is>
+          <t>Surplus / secondary unit placement (buy-side finder fee)</t>
+        </is>
+      </c>
+      <c r="E35" s="53" t="inlineStr">
+        <is>
+          <t>one physical surplus or decommissioned unit sourced, inspected and placed with a buyer: 5% of an average $1.2M used/refurbished unit, paid by the buyer, OEM-neutral and inventory-neutral</t>
+        </is>
+      </c>
+      <c r="F35" s="48" t="n">
+        <v>60000</v>
+      </c>
+      <c r="G35" s="49" t="n">
+        <v>4</v>
+      </c>
+      <c r="H35" s="49" t="n">
+        <v>9</v>
+      </c>
+      <c r="I35" s="49" t="n">
+        <v>16</v>
+      </c>
+      <c r="J35" s="49" t="n">
+        <v>22</v>
+      </c>
+      <c r="K35" s="49" t="n">
+        <v>28</v>
+      </c>
+      <c r="L35" s="54">
+        <f>G35*$F35</f>
+        <v/>
+      </c>
+      <c r="M35" s="54">
+        <f>H35*$F35</f>
+        <v/>
+      </c>
+      <c r="N35" s="54">
+        <f>I35*$F35</f>
+        <v/>
+      </c>
+      <c r="O35" s="54">
+        <f>J35*$F35</f>
+        <v/>
+      </c>
+      <c r="P35" s="54">
+        <f>K35*$F35</f>
+        <v/>
+      </c>
+      <c r="Q35" s="51" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="R35" s="54">
+        <f>L35*$Q35</f>
+        <v/>
+      </c>
+      <c r="S35" s="54">
+        <f>M35*$Q35</f>
+        <v/>
+      </c>
+      <c r="T35" s="54">
+        <f>N35*$Q35</f>
+        <v/>
+      </c>
+      <c r="U35" s="54">
+        <f>O35*$Q35</f>
+        <v/>
+      </c>
+      <c r="V35" s="54">
+        <f>P35*$Q35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="46" t="inlineStr">
+        <is>
+          <t>grid-equipment-slot-forward-exchange</t>
+        </is>
+      </c>
+      <c r="B36" s="46" t="n">
+        <v>7</v>
+      </c>
+      <c r="C36" s="47" t="inlineStr">
+        <is>
+          <t>Forward exchange for transformer and switchgear production slots</t>
+        </is>
+      </c>
+      <c r="D36" s="47" t="inlineStr">
+        <is>
+          <t>Grid Iron Price Print (annual data licence)</t>
+        </is>
+      </c>
+      <c r="E36" s="47" t="inlineStr">
+        <is>
+          <t>one annual multi-seat licence to the transaction-verified $/MVA and true-lead-time series by equipment class, voltage, OEM and delivery quarter, published quarterly</t>
+        </is>
+      </c>
+      <c r="F36" s="48" t="n">
+        <v>30000</v>
+      </c>
+      <c r="G36" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="I36" s="49" t="n">
+        <v>22</v>
+      </c>
+      <c r="J36" s="49" t="n">
+        <v>40</v>
+      </c>
+      <c r="K36" s="49" t="n">
+        <v>58</v>
+      </c>
+      <c r="L36" s="50">
+        <f>G36*$F36</f>
+        <v/>
+      </c>
+      <c r="M36" s="50">
+        <f>H36*$F36</f>
+        <v/>
+      </c>
+      <c r="N36" s="50">
+        <f>I36*$F36</f>
+        <v/>
+      </c>
+      <c r="O36" s="50">
+        <f>J36*$F36</f>
+        <v/>
+      </c>
+      <c r="P36" s="50">
+        <f>K36*$F36</f>
+        <v/>
+      </c>
+      <c r="Q36" s="51" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R36" s="50">
+        <f>L36*$Q36</f>
+        <v/>
+      </c>
+      <c r="S36" s="50">
+        <f>M36*$Q36</f>
+        <v/>
+      </c>
+      <c r="T36" s="50">
+        <f>N36*$Q36</f>
+        <v/>
+      </c>
+      <c r="U36" s="50">
+        <f>O36*$Q36</f>
+        <v/>
+      </c>
+      <c r="V36" s="50">
+        <f>P36*$Q36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="52" t="inlineStr">
+        <is>
+          <t>stateful-hash-signature-key-state-custody</t>
+        </is>
+      </c>
+      <c r="B37" s="52" t="n">
+        <v>8</v>
+      </c>
+      <c r="C37" s="53" t="inlineStr">
+        <is>
+          <t>Key-state custody for LMS/XMSS firmware signing under CNSA 2.0</t>
+        </is>
+      </c>
+      <c r="D37" s="53" t="inlineStr">
+        <is>
+          <t>CNSA 2.0 signing-state migration engagement</t>
+        </is>
+      </c>
+      <c r="E37" s="53" t="inlineStr">
+        <is>
+          <t>one fixed-fee engagement: assess an OEM's firmware signing pipeline, design the single-tree LMS/XMSS key hierarchy and reservation scheme under SP 800-208, integrate to their existing HSM (Luna / nShield / Utimaco / CloudHSM), wire into Yocto, Zephyr, MCUboot or U-Boot, deliver the state-and-backup runbook aligned to draft-ietf-pquip-hbs-state; ~6-8 weeks at ~1.5 FTE</t>
+        </is>
+      </c>
+      <c r="F37" s="48" t="n">
+        <v>90000</v>
+      </c>
+      <c r="G37" s="49" t="n">
+        <v>5</v>
+      </c>
+      <c r="H37" s="49" t="n">
+        <v>11</v>
+      </c>
+      <c r="I37" s="49" t="n">
+        <v>15</v>
+      </c>
+      <c r="J37" s="49" t="n">
+        <v>17</v>
+      </c>
+      <c r="K37" s="49" t="n">
+        <v>14</v>
+      </c>
+      <c r="L37" s="54">
+        <f>G37*$F37</f>
+        <v/>
+      </c>
+      <c r="M37" s="54">
+        <f>H37*$F37</f>
+        <v/>
+      </c>
+      <c r="N37" s="54">
+        <f>I37*$F37</f>
+        <v/>
+      </c>
+      <c r="O37" s="54">
+        <f>J37*$F37</f>
+        <v/>
+      </c>
+      <c r="P37" s="54">
+        <f>K37*$F37</f>
+        <v/>
+      </c>
+      <c r="Q37" s="51" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="R37" s="54">
+        <f>L37*$Q37</f>
+        <v/>
+      </c>
+      <c r="S37" s="54">
+        <f>M37*$Q37</f>
+        <v/>
+      </c>
+      <c r="T37" s="54">
+        <f>N37*$Q37</f>
+        <v/>
+      </c>
+      <c r="U37" s="54">
+        <f>O37*$Q37</f>
+        <v/>
+      </c>
+      <c r="V37" s="54">
+        <f>P37*$Q37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="46" t="inlineStr">
+        <is>
+          <t>stateful-hash-signature-key-state-custody</t>
+        </is>
+      </c>
+      <c r="B38" s="46" t="n">
+        <v>8</v>
+      </c>
+      <c r="C38" s="47" t="inlineStr">
+        <is>
+          <t>Key-state custody for LMS/XMSS firmware signing under CNSA 2.0</t>
+        </is>
+      </c>
+      <c r="D38" s="47" t="inlineStr">
+        <is>
+          <t>Signing-state assurance subscription (BYO-HSM)</t>
+        </is>
+      </c>
+      <c r="E38" s="47" t="inlineStr">
+        <is>
+          <t>one signing environment (one product line's firmware signing pipeline), per year: quorum index ledger, cross-vendor PKCS#11 portability shim, continuous fork/reuse monitoring, evidence retention. Runs against customer-owned or customer-rented HSMs, so we carry no HSM COGS and never hold key material</t>
+        </is>
+      </c>
+      <c r="F38" s="48" t="n">
+        <v>45000</v>
+      </c>
+      <c r="G38" s="49" t="n">
+        <v>3</v>
+      </c>
+      <c r="H38" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="I38" s="49" t="n">
+        <v>15</v>
+      </c>
+      <c r="J38" s="49" t="n">
+        <v>23</v>
+      </c>
+      <c r="K38" s="49" t="n">
+        <v>30</v>
+      </c>
+      <c r="L38" s="50">
+        <f>G38*$F38</f>
+        <v/>
+      </c>
+      <c r="M38" s="50">
+        <f>H38*$F38</f>
+        <v/>
+      </c>
+      <c r="N38" s="50">
+        <f>I38*$F38</f>
+        <v/>
+      </c>
+      <c r="O38" s="50">
+        <f>J38*$F38</f>
+        <v/>
+      </c>
+      <c r="P38" s="50">
+        <f>K38*$F38</f>
+        <v/>
+      </c>
+      <c r="Q38" s="51" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R38" s="50">
+        <f>L38*$Q38</f>
+        <v/>
+      </c>
+      <c r="S38" s="50">
+        <f>M38*$Q38</f>
+        <v/>
+      </c>
+      <c r="T38" s="50">
+        <f>N38*$Q38</f>
+        <v/>
+      </c>
+      <c r="U38" s="50">
+        <f>O38*$Q38</f>
+        <v/>
+      </c>
+      <c r="V38" s="50">
+        <f>P38*$Q38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="52" t="inlineStr">
+        <is>
+          <t>stateful-hash-signature-key-state-custody</t>
+        </is>
+      </c>
+      <c r="B39" s="52" t="n">
+        <v>8</v>
+      </c>
+      <c r="C39" s="53" t="inlineStr">
+        <is>
+          <t>Key-state custody for LMS/XMSS firmware signing under CNSA 2.0</t>
+        </is>
+      </c>
+      <c r="D39" s="53" t="inlineStr">
+        <is>
+          <t>Annual SP 800-208 index-reuse attestation</t>
+        </is>
+      </c>
+      <c r="E39" s="53" t="inlineStr">
+        <is>
+          <t>one annual attestation report per customer, evidencing that no one-time-signature index was ever reused across the year, in the form a prime or a government customer will accept in a CNSA 2.0 questionnaire</t>
+        </is>
+      </c>
+      <c r="F39" s="48" t="n">
+        <v>18000</v>
+      </c>
+      <c r="G39" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="H39" s="49" t="n">
+        <v>7</v>
+      </c>
+      <c r="I39" s="49" t="n">
+        <v>13</v>
+      </c>
+      <c r="J39" s="49" t="n">
+        <v>19</v>
+      </c>
+      <c r="K39" s="49" t="n">
+        <v>24</v>
+      </c>
+      <c r="L39" s="54">
+        <f>G39*$F39</f>
+        <v/>
+      </c>
+      <c r="M39" s="54">
+        <f>H39*$F39</f>
+        <v/>
+      </c>
+      <c r="N39" s="54">
+        <f>I39*$F39</f>
+        <v/>
+      </c>
+      <c r="O39" s="54">
+        <f>J39*$F39</f>
+        <v/>
+      </c>
+      <c r="P39" s="54">
+        <f>K39*$F39</f>
+        <v/>
+      </c>
+      <c r="Q39" s="51" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="R39" s="54">
+        <f>L39*$Q39</f>
+        <v/>
+      </c>
+      <c r="S39" s="54">
+        <f>M39*$Q39</f>
+        <v/>
+      </c>
+      <c r="T39" s="54">
+        <f>N39*$Q39</f>
+        <v/>
+      </c>
+      <c r="U39" s="54">
+        <f>O39*$Q39</f>
+        <v/>
+      </c>
+      <c r="V39" s="54">
+        <f>P39*$Q39</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="46" t="inlineStr">
+        <is>
+          <t>stateful-hash-signature-key-state-custody</t>
+        </is>
+      </c>
+      <c r="B40" s="46" t="n">
+        <v>8</v>
+      </c>
+      <c r="C40" s="47" t="inlineStr">
+        <is>
+          <t>Key-state custody for LMS/XMSS firmware signing under CNSA 2.0</t>
+        </is>
+      </c>
+      <c r="D40" s="47" t="inlineStr">
+        <is>
+          <t>OEM component licence of the vendor-portable state manager</t>
+        </is>
+      </c>
+      <c r="E40" s="47" t="inlineStr">
+        <is>
+          <t>one annual OEM licence to an HSM or signing-platform vendor (Keyfactor, Crypto4A, ISARA, Cryptomathic, DigiCert, a cloud HSM team) who wants cross-vendor portability without building it — i.e. selling the closure of the gap to the people who would otherwise close it themselves</t>
+        </is>
+      </c>
+      <c r="F40" s="48" t="n">
+        <v>150000</v>
+      </c>
+      <c r="G40" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="J40" s="49" t="n">
+        <v>3</v>
+      </c>
+      <c r="K40" s="49" t="n">
+        <v>3</v>
+      </c>
+      <c r="L40" s="50">
+        <f>G40*$F40</f>
+        <v/>
+      </c>
+      <c r="M40" s="50">
+        <f>H40*$F40</f>
+        <v/>
+      </c>
+      <c r="N40" s="50">
+        <f>I40*$F40</f>
+        <v/>
+      </c>
+      <c r="O40" s="50">
+        <f>J40*$F40</f>
+        <v/>
+      </c>
+      <c r="P40" s="50">
+        <f>K40*$F40</f>
+        <v/>
+      </c>
+      <c r="Q40" s="51" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="R40" s="50">
+        <f>L40*$Q40</f>
+        <v/>
+      </c>
+      <c r="S40" s="50">
+        <f>M40*$Q40</f>
+        <v/>
+      </c>
+      <c r="T40" s="50">
+        <f>N40*$Q40</f>
+        <v/>
+      </c>
+      <c r="U40" s="50">
+        <f>O40*$Q40</f>
+        <v/>
+      </c>
+      <c r="V40" s="50">
+        <f>P40*$Q40</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:V40"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:V1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AR12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="11" customWidth="1" min="17" max="17"/>
+    <col width="11" customWidth="1" min="18" max="18"/>
+    <col width="11" customWidth="1" min="19" max="19"/>
+    <col width="11" customWidth="1" min="20" max="20"/>
+    <col width="11" customWidth="1" min="21" max="21"/>
+    <col width="13" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="25" max="25"/>
+    <col width="14" customWidth="1" min="26" max="26"/>
+    <col width="14" customWidth="1" min="27" max="27"/>
+    <col width="14" customWidth="1" min="28" max="28"/>
+    <col width="11" customWidth="1" min="29" max="29"/>
+    <col width="14" customWidth="1" min="30" max="30"/>
+    <col width="14" customWidth="1" min="31" max="31"/>
+    <col width="14" customWidth="1" min="32" max="32"/>
+    <col width="14" customWidth="1" min="33" max="33"/>
+    <col width="14" customWidth="1" min="34" max="34"/>
+    <col width="14" customWidth="1" min="35" max="35"/>
+    <col width="14" customWidth="1" min="36" max="36"/>
+    <col width="14" customWidth="1" min="37" max="37"/>
+    <col width="14" customWidth="1" min="38" max="38"/>
+    <col width="15" customWidth="1" min="39" max="39"/>
+    <col width="11" customWidth="1" min="40" max="40"/>
+    <col width="9" customWidth="1" min="41" max="41"/>
+    <col width="14" customWidth="1" min="42" max="42"/>
+    <col width="70" customWidth="1" min="43" max="43"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="46" customHeight="1">
+      <c r="A1" s="26" t="inlineStr">
+        <is>
+          <t>Full operating model per opportunity, built on LIVE-SOURCED drivers (August 2026). Revenue and gross profit roll up from Model Detail. Payroll = headcount x loaded salary. EBITDA = gross profit - payroll - opex. Blue cells are inputs. "Stands?" is the sourcing analyst's ruling AFTER live competitor checks - read the Sourcing and Corrections sheets before trusting any row marked No.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="34" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>Opportunity</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>Stands?</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>Crowding</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>Confidence</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>Revenue Y1</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>Revenue Y2</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>Revenue Y3</t>
+        </is>
+      </c>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>Revenue Y4</t>
+        </is>
+      </c>
+      <c r="K3" s="6" t="inlineStr">
+        <is>
+          <t>Revenue Y5</t>
+        </is>
+      </c>
+      <c r="L3" s="6" t="inlineStr">
+        <is>
+          <t>Gross profit Y1</t>
+        </is>
+      </c>
+      <c r="M3" s="6" t="inlineStr">
+        <is>
+          <t>Gross profit Y2</t>
+        </is>
+      </c>
+      <c r="N3" s="6" t="inlineStr">
+        <is>
+          <t>Gross profit Y3</t>
+        </is>
+      </c>
+      <c r="O3" s="6" t="inlineStr">
+        <is>
+          <t>Gross profit Y4</t>
+        </is>
+      </c>
+      <c r="P3" s="6" t="inlineStr">
+        <is>
+          <t>Gross profit Y5</t>
+        </is>
+      </c>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>Headcount Y1</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>Headcount Y2</t>
+        </is>
+      </c>
+      <c r="S3" s="6" t="inlineStr">
+        <is>
+          <t>Headcount Y3</t>
+        </is>
+      </c>
+      <c r="T3" s="6" t="inlineStr">
+        <is>
+          <t>Headcount Y4</t>
+        </is>
+      </c>
+      <c r="U3" s="6" t="inlineStr">
+        <is>
+          <t>Headcount Y5</t>
+        </is>
+      </c>
+      <c r="V3" s="6" t="inlineStr">
+        <is>
+          <t>Loaded salary</t>
+        </is>
+      </c>
+      <c r="W3" s="6" t="inlineStr">
+        <is>
+          <t>Payroll Y1</t>
+        </is>
+      </c>
+      <c r="X3" s="6" t="inlineStr">
+        <is>
+          <t>Payroll Y2</t>
+        </is>
+      </c>
+      <c r="Y3" s="6" t="inlineStr">
+        <is>
+          <t>Payroll Y3</t>
+        </is>
+      </c>
+      <c r="Z3" s="6" t="inlineStr">
+        <is>
+          <t>Payroll Y4</t>
+        </is>
+      </c>
+      <c r="AA3" s="6" t="inlineStr">
+        <is>
+          <t>Payroll Y5</t>
+        </is>
+      </c>
+      <c r="AB3" s="6" t="inlineStr">
+        <is>
+          <t>Opex Y1 (input)</t>
+        </is>
+      </c>
+      <c r="AC3" s="6" t="inlineStr">
+        <is>
+          <t>Opex growth</t>
+        </is>
+      </c>
+      <c r="AD3" s="6" t="inlineStr">
+        <is>
+          <t>Opex Y2</t>
+        </is>
+      </c>
+      <c r="AE3" s="6" t="inlineStr">
+        <is>
+          <t>Opex Y3</t>
+        </is>
+      </c>
+      <c r="AF3" s="6" t="inlineStr">
+        <is>
+          <t>Opex Y4</t>
+        </is>
+      </c>
+      <c r="AG3" s="6" t="inlineStr">
+        <is>
+          <t>Opex Y5</t>
+        </is>
+      </c>
+      <c r="AH3" s="6" t="inlineStr">
+        <is>
+          <t>EBITDA Y1</t>
+        </is>
+      </c>
+      <c r="AI3" s="6" t="inlineStr">
+        <is>
+          <t>EBITDA Y2</t>
+        </is>
+      </c>
+      <c r="AJ3" s="6" t="inlineStr">
+        <is>
+          <t>EBITDA Y3</t>
+        </is>
+      </c>
+      <c r="AK3" s="6" t="inlineStr">
+        <is>
+          <t>EBITDA Y4</t>
+        </is>
+      </c>
+      <c r="AL3" s="6" t="inlineStr">
+        <is>
+          <t>EBITDA Y5</t>
+        </is>
+      </c>
+      <c r="AM3" s="6" t="inlineStr">
+        <is>
+          <t>Capital required</t>
+        </is>
+      </c>
+      <c r="AN3" s="6" t="inlineStr">
+        <is>
+          <t>CAC</t>
+        </is>
+      </c>
+      <c r="AO3" s="6" t="inlineStr">
+        <is>
+          <t>Churn</t>
+        </is>
+      </c>
+      <c r="AP3" s="6" t="inlineStr">
+        <is>
+          <t>Bear Y5</t>
+        </is>
+      </c>
+      <c r="AQ3" s="6" t="inlineStr">
+        <is>
+          <t>Exit thesis</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="54" customHeight="1">
+      <c r="A4" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="47" t="inlineStr">
+        <is>
+          <t>Ride-through models and curtailment proof for NERC-registered data centers</t>
+        </is>
+      </c>
+      <c r="C4" s="46" t="inlineStr">
+        <is>
+          <t>datacenter-as-grid-entity-compliance</t>
+        </is>
+      </c>
+      <c r="D4" s="55" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E4" s="46" t="inlineStr">
+        <is>
+          <t>contested</t>
+        </is>
+      </c>
+      <c r="F4" s="56" t="n">
+        <v>4</v>
+      </c>
+      <c r="G4" s="50">
+        <f>SUMIF('Model Detail'!$A:$A,$C4,'Model Detail'!L:L)</f>
+        <v/>
+      </c>
+      <c r="H4" s="50">
+        <f>SUMIF('Model Detail'!$A:$A,$C4,'Model Detail'!M:M)</f>
+        <v/>
+      </c>
+      <c r="I4" s="50">
+        <f>SUMIF('Model Detail'!$A:$A,$C4,'Model Detail'!N:N)</f>
+        <v/>
+      </c>
+      <c r="J4" s="50">
+        <f>SUMIF('Model Detail'!$A:$A,$C4,'Model Detail'!O:O)</f>
+        <v/>
+      </c>
+      <c r="K4" s="50">
+        <f>SUMIF('Model Detail'!$A:$A,$C4,'Model Detail'!P:P)</f>
+        <v/>
+      </c>
+      <c r="L4" s="50">
+        <f>SUMIF('Model Detail'!$A:$A,$C4,'Model Detail'!R:R)</f>
+        <v/>
+      </c>
+      <c r="M4" s="50">
+        <f>SUMIF('Model Detail'!$A:$A,$C4,'Model Detail'!S:S)</f>
+        <v/>
+      </c>
+      <c r="N4" s="50">
+        <f>SUMIF('Model Detail'!$A:$A,$C4,'Model Detail'!T:T)</f>
+        <v/>
+      </c>
+      <c r="O4" s="50">
+        <f>SUMIF('Model Detail'!$A:$A,$C4,'Model Detail'!U:U)</f>
+        <v/>
+      </c>
+      <c r="P4" s="50">
+        <f>SUMIF('Model Detail'!$A:$A,$C4,'Model Detail'!V:V)</f>
+        <v/>
+      </c>
+      <c r="Q4" s="57" t="n">
+        <v>4</v>
+      </c>
+      <c r="R4" s="57" t="n">
+        <v>10</v>
+      </c>
+      <c r="S4" s="57" t="n">
+        <v>18</v>
+      </c>
+      <c r="T4" s="57" t="n">
+        <v>26</v>
+      </c>
+      <c r="U4" s="57" t="n">
+        <v>34</v>
+      </c>
+      <c r="V4" s="48" t="n">
+        <v>180000</v>
+      </c>
+      <c r="W4" s="50">
+        <f>Q4*$V4</f>
+        <v/>
+      </c>
+      <c r="X4" s="50">
+        <f>R4*$V4</f>
+        <v/>
+      </c>
+      <c r="Y4" s="50">
+        <f>S4*$V4</f>
+        <v/>
+      </c>
+      <c r="Z4" s="50">
+        <f>T4*$V4</f>
+        <v/>
+      </c>
+      <c r="AA4" s="50">
+        <f>U4*$V4</f>
+        <v/>
+      </c>
+      <c r="AB4" s="48" t="n">
+        <v>430000</v>
+      </c>
+      <c r="AC4" s="51" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AD4" s="50">
+        <f>AB4*(1+$AC4)</f>
+        <v/>
+      </c>
+      <c r="AE4" s="50">
+        <f>AD4*(1+$AC4)</f>
+        <v/>
+      </c>
+      <c r="AF4" s="50">
+        <f>AE4*(1+$AC4)</f>
+        <v/>
+      </c>
+      <c r="AG4" s="50">
+        <f>AF4*(1+$AC4)</f>
+        <v/>
+      </c>
+      <c r="AH4" s="58">
+        <f>L4-W4-AB4</f>
+        <v/>
+      </c>
+      <c r="AI4" s="58">
+        <f>M4-X4-AD4</f>
+        <v/>
+      </c>
+      <c r="AJ4" s="58">
+        <f>N4-Y4-AE4</f>
+        <v/>
+      </c>
+      <c r="AK4" s="58">
+        <f>O4-Z4-AF4</f>
+        <v/>
+      </c>
+      <c r="AL4" s="58">
+        <f>P4-AA4-AG4</f>
+        <v/>
+      </c>
+      <c r="AM4" s="48" t="n">
+        <v>650000</v>
+      </c>
+      <c r="AN4" s="50" t="n">
+        <v>45000</v>
+      </c>
+      <c r="AO4" s="59" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="AP4" s="50" t="n">
+        <v>2800000</v>
+      </c>
+      <c r="AQ4" s="46" t="inlineStr">
+        <is>
+          <t>Services multiple, not software multiple — and the honest framing is that this is a founder outcome, not a venture outcome. BUYERS, in descending likelihood. (1) E&amp;C / EPC firms with grid practices buying load-side capability they cannot hire fast enough: Burns &amp; McDonnell, Black &amp; Veatch, 1898 &amp; Co, Sargent &amp; Lundy, POWER Engineers (WSP), Ulteig. These are the acquirers the original record's own kill_risk named, and they remain the base case. (2) NERC-compliance platforms with PE sponsors — Certrec being the obvious one, since a new Computational Load Entity registration category flows directly into its existing 130+ site RSAW and audit machinery and it needs the load-side engineering it does not have. (3) Engineering-services consolidators that roll up specialty technical firms at predictable multiples: NV5, Bowman, Willdan, Montrose. (4) International transmission consultancies buying a US large-load franchise: DNV, TNEI, PSC Consulting. (5) Low probability but highest price: a funded software player (GridStrong, GridCARE, Piq) buying delivery capacity and regulatory credibility to make its platform sellable to utilities. MULTIPLE. Specialty engineering consultancies at $5-15M revenue trade at 5-8x EBITDA, roughly 0.8-1.4x revenue, with 60-80% cash at close and 20-40% in a 2-3 year earnout tied to retained principals. BASE CASE: Y5 revenue $9.4M, EBITDA $1.19M (12.7%), at 6.5x EBITDA = ~$7.7M, cross-checked at ~0.85x revenue = ~$8.0M. Call it $7.5-9M enterprise value on $650k invested — a genuinely good founder outcome at ~11x invested capital, and a bad venture outcome, which is why the capital plan is angel/founder rather than institutional. UPSIDE: if Revenue Line 5 (CLE compliance program management) reaches $3M+ ARR by Y5-Y6, an acquirer can be pushed to a blended valuation — services multiple on the project lines plus 3-4x revenue on the genuinely recurring compliance-subscription book — landing $14-18M. That is the only path to a materially better number, and it depends entirely on FERC approving the standards NERC files by 31 December 2026 on schedule. DOWNSIDE, which the sourcing makes more likely than the record assumed: the incumbents (Keentel, Certrec, the EPCs) lock the top developers and utilities under MSAs before the standards land, the ISO-published reference models keep compressing scope, and the outcome is an acqui-hire at 3-4x EBITDA, roughly $2-4M, with principals on three-year retention. VALUE DRIVERS AT EXIT, in order: percentage of revenue that is contracted and recurring; approved-vendor status on utility MSAs and ISO qualified-supplier lists; and whether revenue survives the founders leaving. Nothing about the modeling IP is a value driver, because ERCOT gives the reference model away.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="54" customHeight="1">
+      <c r="A5" s="52" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="53" t="inlineStr">
+        <is>
+          <t>Entry Type 13 and instrument-aware duty recovery for the post-de-minimis long tail</t>
+        </is>
+      </c>
+      <c r="C5" s="52" t="inlineStr">
+        <is>
+          <t>long-tail-customs-entry-and-duty-recovery</t>
+        </is>
+      </c>
+      <c r="D5" s="60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E5" s="52" t="inlineStr">
+        <is>
+          <t>crowded</t>
+        </is>
+      </c>
+      <c r="F5" s="61" t="n">
+        <v>3</v>
+      </c>
+      <c r="G5" s="54">
+        <f>SUMIF('Model Detail'!$A:$A,$C5,'Model Detail'!L:L)</f>
+        <v/>
+      </c>
+      <c r="H5" s="54">
+        <f>SUMIF('Model Detail'!$A:$A,$C5,'Model Detail'!M:M)</f>
+        <v/>
+      </c>
+      <c r="I5" s="54">
+        <f>SUMIF('Model Detail'!$A:$A,$C5,'Model Detail'!N:N)</f>
+        <v/>
+      </c>
+      <c r="J5" s="54">
+        <f>SUMIF('Model Detail'!$A:$A,$C5,'Model Detail'!O:O)</f>
+        <v/>
+      </c>
+      <c r="K5" s="54">
+        <f>SUMIF('Model Detail'!$A:$A,$C5,'Model Detail'!P:P)</f>
+        <v/>
+      </c>
+      <c r="L5" s="54">
+        <f>SUMIF('Model Detail'!$A:$A,$C5,'Model Detail'!R:R)</f>
+        <v/>
+      </c>
+      <c r="M5" s="54">
+        <f>SUMIF('Model Detail'!$A:$A,$C5,'Model Detail'!S:S)</f>
+        <v/>
+      </c>
+      <c r="N5" s="54">
+        <f>SUMIF('Model Detail'!$A:$A,$C5,'Model Detail'!T:T)</f>
+        <v/>
+      </c>
+      <c r="O5" s="54">
+        <f>SUMIF('Model Detail'!$A:$A,$C5,'Model Detail'!U:U)</f>
+        <v/>
+      </c>
+      <c r="P5" s="54">
+        <f>SUMIF('Model Detail'!$A:$A,$C5,'Model Detail'!V:V)</f>
+        <v/>
+      </c>
+      <c r="Q5" s="57" t="n">
+        <v>5</v>
+      </c>
+      <c r="R5" s="57" t="n">
+        <v>11</v>
+      </c>
+      <c r="S5" s="57" t="n">
+        <v>22</v>
+      </c>
+      <c r="T5" s="57" t="n">
+        <v>36</v>
+      </c>
+      <c r="U5" s="57" t="n">
+        <v>52</v>
+      </c>
+      <c r="V5" s="48" t="n">
+        <v>115000</v>
+      </c>
+      <c r="W5" s="54">
+        <f>Q5*$V5</f>
+        <v/>
+      </c>
+      <c r="X5" s="54">
+        <f>R5*$V5</f>
+        <v/>
+      </c>
+      <c r="Y5" s="54">
+        <f>S5*$V5</f>
+        <v/>
+      </c>
+      <c r="Z5" s="54">
+        <f>T5*$V5</f>
+        <v/>
+      </c>
+      <c r="AA5" s="54">
+        <f>U5*$V5</f>
+        <v/>
+      </c>
+      <c r="AB5" s="48" t="n">
+        <v>270000</v>
+      </c>
+      <c r="AC5" s="51" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AD5" s="54">
+        <f>AB5*(1+$AC5)</f>
+        <v/>
+      </c>
+      <c r="AE5" s="54">
+        <f>AD5*(1+$AC5)</f>
+        <v/>
+      </c>
+      <c r="AF5" s="54">
+        <f>AE5*(1+$AC5)</f>
+        <v/>
+      </c>
+      <c r="AG5" s="54">
+        <f>AF5*(1+$AC5)</f>
+        <v/>
+      </c>
+      <c r="AH5" s="62">
+        <f>L5-W5-AB5</f>
+        <v/>
+      </c>
+      <c r="AI5" s="62">
+        <f>M5-X5-AD5</f>
+        <v/>
+      </c>
+      <c r="AJ5" s="62">
+        <f>N5-Y5-AE5</f>
+        <v/>
+      </c>
+      <c r="AK5" s="62">
+        <f>O5-Z5-AF5</f>
+        <v/>
+      </c>
+      <c r="AL5" s="62">
+        <f>P5-AA5-AG5</f>
+        <v/>
+      </c>
+      <c r="AM5" s="48" t="n">
+        <v>4200000</v>
+      </c>
+      <c r="AN5" s="54" t="n">
+        <v>8500</v>
+      </c>
+      <c r="AO5" s="63" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AP5" s="54" t="n">
+        <v>2100000</v>
+      </c>
+      <c r="AQ5" s="52" t="inlineStr">
+        <is>
+          <t>Services multiples, not software multiples — and the mix ratio is the whole game. Three buyer classes. (1) TRADE-TECH CONSOLIDATORS: Descartes, WiseTech/CargoWise, E2open, Thomson Reuters OneSource. They buy licensed books and filer codes to fill gaps in their ABI franchise; Descartes in particular has an active acquisition cadence in customs and trade data. They pay for the license, the filer code, the account book and the accumulated per-SKU ruling corpus — typically 1.0-2.0x revenue for a services-weighted asset, up to 3x if recurring software revenue is a clear majority. (2) THE FUNDED ENTRANTS THEMSELVES: Zonos (~$69M raised, already bought Evolve Trade Services on 30 Apr 2026 at what was plainly a license-and-expertise price), Flexport, Caspian, Passport Global. This is the most likely and fastest path — they are buying exactly what we would be selling, they move quickly, and Zonos has already demonstrated the transaction. (3) MID-MARKET LOGISTICS PE running customs-brokerage roll-ups, which trade at roughly 5-8x EBITDA. Realistic outcomes on our own numbers: Y5 at ~$8.4M revenue with ~$330k EBITDA and only ~40% of revenue in subscription-plus-project form clears 1.0-1.5x revenue, or $8-13M — roughly 2-3x on $4.2M raised, a modest but real outcome. The upside case requires the subscription and recovery lines to reach 50%+ of revenue at 20-25% EBITDA by Y5-Y6, which supports 2.5-4x revenue, or $20-35M. The downside is the sourced base case for a crowded, license-gated services market: a $3-5M-revenue brokerage with a good UI, sold to a consolidator at ~0.8x revenue, returning less than capital. Two structural facts to be honest about — this market is genuinely segmented and not winner-take-all, so a licensed book with real accounts always has a buyer and the downside is a soft landing rather than a zero; but the same segmentation means no acquirer ever has to pay a scarcity premium, which is precisely what caps the multiple.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="54" customHeight="1">
+      <c r="A6" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="47" t="inlineStr">
+        <is>
+          <t>NQA-1 qualification and commercial grade dedication as a service</t>
+        </is>
+      </c>
+      <c r="C6" s="46" t="inlineStr">
+        <is>
+          <t>nuclear-naval-supplier-qualification</t>
+        </is>
+      </c>
+      <c r="D6" s="55" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E6" s="46" t="inlineStr">
+        <is>
+          <t>contested</t>
+        </is>
+      </c>
+      <c r="F6" s="56" t="n">
+        <v>4</v>
+      </c>
+      <c r="G6" s="50">
+        <f>SUMIF('Model Detail'!$A:$A,$C6,'Model Detail'!L:L)</f>
+        <v/>
+      </c>
+      <c r="H6" s="50">
+        <f>SUMIF('Model Detail'!$A:$A,$C6,'Model Detail'!M:M)</f>
+        <v/>
+      </c>
+      <c r="I6" s="50">
+        <f>SUMIF('Model Detail'!$A:$A,$C6,'Model Detail'!N:N)</f>
+        <v/>
+      </c>
+      <c r="J6" s="50">
+        <f>SUMIF('Model Detail'!$A:$A,$C6,'Model Detail'!O:O)</f>
+        <v/>
+      </c>
+      <c r="K6" s="50">
+        <f>SUMIF('Model Detail'!$A:$A,$C6,'Model Detail'!P:P)</f>
+        <v/>
+      </c>
+      <c r="L6" s="50">
+        <f>SUMIF('Model Detail'!$A:$A,$C6,'Model Detail'!R:R)</f>
+        <v/>
+      </c>
+      <c r="M6" s="50">
+        <f>SUMIF('Model Detail'!$A:$A,$C6,'Model Detail'!S:S)</f>
+        <v/>
+      </c>
+      <c r="N6" s="50">
+        <f>SUMIF('Model Detail'!$A:$A,$C6,'Model Detail'!T:T)</f>
+        <v/>
+      </c>
+      <c r="O6" s="50">
+        <f>SUMIF('Model Detail'!$A:$A,$C6,'Model Detail'!U:U)</f>
+        <v/>
+      </c>
+      <c r="P6" s="50">
+        <f>SUMIF('Model Detail'!$A:$A,$C6,'Model Detail'!V:V)</f>
+        <v/>
+      </c>
+      <c r="Q6" s="57" t="n">
+        <v>3</v>
+      </c>
+      <c r="R6" s="57" t="n">
+        <v>7</v>
+      </c>
+      <c r="S6" s="57" t="n">
+        <v>12</v>
+      </c>
+      <c r="T6" s="57" t="n">
+        <v>18</v>
+      </c>
+      <c r="U6" s="57" t="n">
+        <v>24</v>
+      </c>
+      <c r="V6" s="48" t="n">
+        <v>158000</v>
+      </c>
+      <c r="W6" s="50">
+        <f>Q6*$V6</f>
+        <v/>
+      </c>
+      <c r="X6" s="50">
+        <f>R6*$V6</f>
+        <v/>
+      </c>
+      <c r="Y6" s="50">
+        <f>S6*$V6</f>
+        <v/>
+      </c>
+      <c r="Z6" s="50">
+        <f>T6*$V6</f>
+        <v/>
+      </c>
+      <c r="AA6" s="50">
+        <f>U6*$V6</f>
+        <v/>
+      </c>
+      <c r="AB6" s="48" t="n">
+        <v>260000</v>
+      </c>
+      <c r="AC6" s="51" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AD6" s="50">
+        <f>AB6*(1+$AC6)</f>
+        <v/>
+      </c>
+      <c r="AE6" s="50">
+        <f>AD6*(1+$AC6)</f>
+        <v/>
+      </c>
+      <c r="AF6" s="50">
+        <f>AE6*(1+$AC6)</f>
+        <v/>
+      </c>
+      <c r="AG6" s="50">
+        <f>AF6*(1+$AC6)</f>
+        <v/>
+      </c>
+      <c r="AH6" s="58">
+        <f>L6-W6-AB6</f>
+        <v/>
+      </c>
+      <c r="AI6" s="58">
+        <f>M6-X6-AD6</f>
+        <v/>
+      </c>
+      <c r="AJ6" s="58">
+        <f>N6-Y6-AE6</f>
+        <v/>
+      </c>
+      <c r="AK6" s="58">
+        <f>O6-Z6-AF6</f>
+        <v/>
+      </c>
+      <c r="AL6" s="58">
+        <f>P6-AA6-AG6</f>
+        <v/>
+      </c>
+      <c r="AM6" s="48" t="n">
+        <v>750000</v>
+      </c>
+      <c r="AN6" s="50" t="n">
+        <v>14000</v>
+      </c>
+      <c r="AO6" s="59" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AP6" s="50" t="n">
+        <v>1700000</v>
+      </c>
+      <c r="AQ6" s="46" t="inlineStr">
+        <is>
+          <t>This is a services business with a software attachment and it will trade like one — roughly 1.0-1.5x revenue or 6-9x EBITDA, not a software multiple. Do not model an ARR comparable: at Y5 only about $2.8M of $7.0M revenue is contractually recurring (retainers plus Workbench seats), the rest is project and repeat-transaction work with no renewal obligation. Most likely acquirers, in descending order of fit. (1) Curtiss-Wright Nuclear / Scientech — the single most logical buyer: they are already a third-party dedicating entity and already sell nuclear regulatory compliance software, so they acquire a book of qualified suppliers, a retainer base and a CC library that plugs into an existing platform. (2) Kinectrics — private-equity-backed, actively acquisitive in nuclear testing and services, and already runs a CGD line that this would deepen on the supplier-development side. (3) The TIC roll-ups — Bureau Veritas, SGS, TUV, Mistras, Applus — who buy accredited inspection and audit businesses systematically at 8-11x EBITDA and for whom nuclear qualification is an adjacency they want. (4) Framatome, Westinghouse or NAC/Hilltop as a capability tuck-in. (5) An engineering-services consolidator (Enercon, Sargent &amp; Lundy, Certrec) buying the retainer base. Realistic outcome at Y5-Y6: $1.5-2.0M EBITDA at 8-10x, or ~1.5x revenue, giving a $12-20M enterprise value — a genuinely good result for a $750K raise and a 3-24 person team, and a poor one for institutional venture capital. There is one path to a strategic premium: if the critical-characteristics library actually accretes across buyers and becomes a reuse asset with demonstrated cross-licensee acceptance, a buyer could underwrite it at 2.5-3.5x revenue on the argument that it is a defensible data asset. The screener's kill risk and the sourced evidence both say that is unlikely — CCs are treated as proprietary and litigation-sensitive, and EPRI holds the methodology as a member good. Underwrite the $12-20M case; treat the $40M+ case as a free option. Secondary path worth naming: at Y3-Y4 this is a clean ESOP or management-buyout candidate financed on its own cash flow, which for a founder-operator may beat a strategic sale after fees.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="54" customHeight="1">
+      <c r="A7" s="52" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="53" t="inlineStr">
+        <is>
+          <t>PFAS-Compliant Biosolids Outlet Exchange for the Mid-Atlantic</t>
+        </is>
+      </c>
+      <c r="C7" s="52" t="inlineStr">
+        <is>
+          <t>biosolids-outlet-exchange</t>
+        </is>
+      </c>
+      <c r="D7" s="60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E7" s="52" t="inlineStr">
+        <is>
+          <t>contested</t>
+        </is>
+      </c>
+      <c r="F7" s="61" t="n">
+        <v>3</v>
+      </c>
+      <c r="G7" s="54">
+        <f>SUMIF('Model Detail'!$A:$A,$C7,'Model Detail'!L:L)</f>
+        <v/>
+      </c>
+      <c r="H7" s="54">
+        <f>SUMIF('Model Detail'!$A:$A,$C7,'Model Detail'!M:M)</f>
+        <v/>
+      </c>
+      <c r="I7" s="54">
+        <f>SUMIF('Model Detail'!$A:$A,$C7,'Model Detail'!N:N)</f>
+        <v/>
+      </c>
+      <c r="J7" s="54">
+        <f>SUMIF('Model Detail'!$A:$A,$C7,'Model Detail'!O:O)</f>
+        <v/>
+      </c>
+      <c r="K7" s="54">
+        <f>SUMIF('Model Detail'!$A:$A,$C7,'Model Detail'!P:P)</f>
+        <v/>
+      </c>
+      <c r="L7" s="54">
+        <f>SUMIF('Model Detail'!$A:$A,$C7,'Model Detail'!R:R)</f>
+        <v/>
+      </c>
+      <c r="M7" s="54">
+        <f>SUMIF('Model Detail'!$A:$A,$C7,'Model Detail'!S:S)</f>
+        <v/>
+      </c>
+      <c r="N7" s="54">
+        <f>SUMIF('Model Detail'!$A:$A,$C7,'Model Detail'!T:T)</f>
+        <v/>
+      </c>
+      <c r="O7" s="54">
+        <f>SUMIF('Model Detail'!$A:$A,$C7,'Model Detail'!U:U)</f>
+        <v/>
+      </c>
+      <c r="P7" s="54">
+        <f>SUMIF('Model Detail'!$A:$A,$C7,'Model Detail'!V:V)</f>
+        <v/>
+      </c>
+      <c r="Q7" s="57" t="n">
+        <v>3</v>
+      </c>
+      <c r="R7" s="57" t="n">
+        <v>5</v>
+      </c>
+      <c r="S7" s="57" t="n">
+        <v>8</v>
+      </c>
+      <c r="T7" s="57" t="n">
+        <v>9</v>
+      </c>
+      <c r="U7" s="57" t="n">
+        <v>10</v>
+      </c>
+      <c r="V7" s="48" t="n">
+        <v>142000</v>
+      </c>
+      <c r="W7" s="54">
+        <f>Q7*$V7</f>
+        <v/>
+      </c>
+      <c r="X7" s="54">
+        <f>R7*$V7</f>
+        <v/>
+      </c>
+      <c r="Y7" s="54">
+        <f>S7*$V7</f>
+        <v/>
+      </c>
+      <c r="Z7" s="54">
+        <f>T7*$V7</f>
+        <v/>
+      </c>
+      <c r="AA7" s="54">
+        <f>U7*$V7</f>
+        <v/>
+      </c>
+      <c r="AB7" s="48" t="n">
+        <v>215000</v>
+      </c>
+      <c r="AC7" s="51" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AD7" s="54">
+        <f>AB7*(1+$AC7)</f>
+        <v/>
+      </c>
+      <c r="AE7" s="54">
+        <f>AD7*(1+$AC7)</f>
+        <v/>
+      </c>
+      <c r="AF7" s="54">
+        <f>AE7*(1+$AC7)</f>
+        <v/>
+      </c>
+      <c r="AG7" s="54">
+        <f>AF7*(1+$AC7)</f>
+        <v/>
+      </c>
+      <c r="AH7" s="62">
+        <f>L7-W7-AB7</f>
+        <v/>
+      </c>
+      <c r="AI7" s="62">
+        <f>M7-X7-AD7</f>
+        <v/>
+      </c>
+      <c r="AJ7" s="62">
+        <f>N7-Y7-AE7</f>
+        <v/>
+      </c>
+      <c r="AK7" s="62">
+        <f>O7-Z7-AF7</f>
+        <v/>
+      </c>
+      <c r="AL7" s="62">
+        <f>P7-AA7-AG7</f>
+        <v/>
+      </c>
+      <c r="AM7" s="48" t="n">
+        <v>650000</v>
+      </c>
+      <c r="AN7" s="54" t="n">
+        <v>8500</v>
+      </c>
+      <c r="AO7" s="63" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AP7" s="54" t="n">
+        <v>600000</v>
+      </c>
+      <c r="AQ7" s="52" t="inlineStr">
+        <is>
+          <t>This is a services business and must be underwritten as one — 5-8x EBITDA or 0.8-1.3x revenue for a sub-$5M regional environmental consultancy, with the upper end reserved for firms carrying genuine recurring compliance revenue. Realistic outcome: sell in year 4-6 at roughly $2.5M revenue and $270,000 of EBITDA for $1.6-2.2M, i.e. 6-7x EBITDA or ~0.8x revenue. The $720,000 subscription line is the only component that could argue for a higher multiple, and at that scale it is far too small to reprice the whole firm — do not model this as a software company that happens to do consulting. Most likely buyer, by a wide margin, is one of the 30+ private-equity roll-up platforms in water and wastewater services tracked as active in 2026; capital is consolidating exactly this layer, which both raises acquisition odds and shortens the window before a funded platform builds it instead. Second tier: strategic acquirers of small environmental consultancies — Montrose Environmental, NV5, Verdantas, Apex Companies, RES — for whom a Mid-Atlantic PFAS-residuals practice with a named client list across ~40 utilities is a tuck-in at 5-6x EBITDA, priced largely on retained staff and client concentration. Third: the incumbent consulting engineers named as competitors (Hazen and Sawyer, Brown and Caldwell, CDM Smith, EA Engineering) buying the practice and its relationships rather than building it, though these firms typically build. Least likely and structurally conflicted: Synagro or Veolia acquiring the advisory relationship as a channel into biosolids contracts — advising utilities on outlet selection while owning the outlets is a conflict most utility clients would reject, so that path likely destroys the asset it acquires. Two value-maximizing levers before a sale: convert as much project revenue as possible into multi-year term contracts (multiples on recurring compliance revenue run 1.5-2x those on episodic project work), and retain the senior technical staff, since in a services deal the buyer is substantially buying the people. Founders should plan for a $2-4M outcome shared across a small cap table, which is why the $650,000 is structured as founder capital and debt rather than priced equity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="54" customHeight="1">
+      <c r="A8" s="46" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="47" t="inlineStr">
+        <is>
+          <t>Reachability-grade SBOMs and kernel-CVE triage for embedded Linux</t>
+        </is>
+      </c>
+      <c r="C8" s="46" t="inlineStr">
+        <is>
+          <t>cra-embedded-sbom-and-cve-triage</t>
+        </is>
+      </c>
+      <c r="D8" s="60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E8" s="46" t="inlineStr">
+        <is>
+          <t>crowded</t>
+        </is>
+      </c>
+      <c r="F8" s="64" t="n">
+        <v>3</v>
+      </c>
+      <c r="G8" s="50">
+        <f>SUMIF('Model Detail'!$A:$A,$C8,'Model Detail'!L:L)</f>
+        <v/>
+      </c>
+      <c r="H8" s="50">
+        <f>SUMIF('Model Detail'!$A:$A,$C8,'Model Detail'!M:M)</f>
+        <v/>
+      </c>
+      <c r="I8" s="50">
+        <f>SUMIF('Model Detail'!$A:$A,$C8,'Model Detail'!N:N)</f>
+        <v/>
+      </c>
+      <c r="J8" s="50">
+        <f>SUMIF('Model Detail'!$A:$A,$C8,'Model Detail'!O:O)</f>
+        <v/>
+      </c>
+      <c r="K8" s="50">
+        <f>SUMIF('Model Detail'!$A:$A,$C8,'Model Detail'!P:P)</f>
+        <v/>
+      </c>
+      <c r="L8" s="50">
+        <f>SUMIF('Model Detail'!$A:$A,$C8,'Model Detail'!R:R)</f>
+        <v/>
+      </c>
+      <c r="M8" s="50">
+        <f>SUMIF('Model Detail'!$A:$A,$C8,'Model Detail'!S:S)</f>
+        <v/>
+      </c>
+      <c r="N8" s="50">
+        <f>SUMIF('Model Detail'!$A:$A,$C8,'Model Detail'!T:T)</f>
+        <v/>
+      </c>
+      <c r="O8" s="50">
+        <f>SUMIF('Model Detail'!$A:$A,$C8,'Model Detail'!U:U)</f>
+        <v/>
+      </c>
+      <c r="P8" s="50">
+        <f>SUMIF('Model Detail'!$A:$A,$C8,'Model Detail'!V:V)</f>
+        <v/>
+      </c>
+      <c r="Q8" s="57" t="n">
+        <v>5</v>
+      </c>
+      <c r="R8" s="57" t="n">
+        <v>12</v>
+      </c>
+      <c r="S8" s="57" t="n">
+        <v>18</v>
+      </c>
+      <c r="T8" s="57" t="n">
+        <v>24</v>
+      </c>
+      <c r="U8" s="57" t="n">
+        <v>30</v>
+      </c>
+      <c r="V8" s="48" t="n">
+        <v>135000</v>
+      </c>
+      <c r="W8" s="50">
+        <f>Q8*$V8</f>
+        <v/>
+      </c>
+      <c r="X8" s="50">
+        <f>R8*$V8</f>
+        <v/>
+      </c>
+      <c r="Y8" s="50">
+        <f>S8*$V8</f>
+        <v/>
+      </c>
+      <c r="Z8" s="50">
+        <f>T8*$V8</f>
+        <v/>
+      </c>
+      <c r="AA8" s="50">
+        <f>U8*$V8</f>
+        <v/>
+      </c>
+      <c r="AB8" s="48" t="n">
+        <v>325000</v>
+      </c>
+      <c r="AC8" s="51" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AD8" s="50">
+        <f>AB8*(1+$AC8)</f>
+        <v/>
+      </c>
+      <c r="AE8" s="50">
+        <f>AD8*(1+$AC8)</f>
+        <v/>
+      </c>
+      <c r="AF8" s="50">
+        <f>AE8*(1+$AC8)</f>
+        <v/>
+      </c>
+      <c r="AG8" s="50">
+        <f>AF8*(1+$AC8)</f>
+        <v/>
+      </c>
+      <c r="AH8" s="58">
+        <f>L8-W8-AB8</f>
+        <v/>
+      </c>
+      <c r="AI8" s="58">
+        <f>M8-X8-AD8</f>
+        <v/>
+      </c>
+      <c r="AJ8" s="58">
+        <f>N8-Y8-AE8</f>
+        <v/>
+      </c>
+      <c r="AK8" s="58">
+        <f>O8-Z8-AF8</f>
+        <v/>
+      </c>
+      <c r="AL8" s="58">
+        <f>P8-AA8-AG8</f>
+        <v/>
+      </c>
+      <c r="AM8" s="48" t="n">
+        <v>1400000</v>
+      </c>
+      <c r="AN8" s="50" t="n">
+        <v>13000</v>
+      </c>
+      <c r="AO8" s="59" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AP8" s="50" t="n">
+        <v>1950000</v>
+      </c>
+      <c r="AQ8" s="46" t="inlineStr">
+        <is>
+          <t>This does not trade like software and must not be capitalised as though it will. At Y5 it is a ~$7.5M revenue, ~13% EBITDA, services-led compliance firm with ~79% gross margin before delivery payroll and a 58% recurring mix ($4.34M of retainer plus attestation). The natural acquirers are the TIC consolidators — TÜV SÜD, TÜV Rheinland, DEKRA, SGS, Bureau Veritas, UL Solutions, Eurofins. They will be the designated CRA notified bodies and they will be capacity-short on embedded Linux depth at exactly the moment we have it: zero bodies designated as of June 2026, 12-18 month accreditation lead times, only 29 EUCC certs in year one. They buy accredited headcount and books of recurring compliance relationships, and they pay 1.0-1.8x revenue or 7-10x EBITDA. A 58% recurring mix, an ISO 27001 certification, an insured attestation book and a documented successful defence of a signed VEX justification pull toward the top of that band and arguably past it — call it 1.8-2.5x revenue. The secondary set is strategic: Exein (explicit 2026-27 EU/US acquisition programme, and the most likely single buyer), Lynx Software, Wind River, Qualcomm/Foundries, Black Duck, Keysight, and Accenture, which has already bought NetRise in exactly this category. A strategic might pay a software-ish 3-4x on the recurring slice only, blending to ~2.5x overall. Realistic outcome: $13-19M enterprise value on $7.5M of revenue. Against a $1.4M raise that is a 9-13x gross return on invested capital and a genuinely good founder outcome; against a $6M venture seed it is a washout. That asymmetry is the entire reason the capital plan is $1.4M and the plan is EBITDA-positive from Y2 — this company must be able to decline to sell, because its best negotiating position is profitability, not runway.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="54" customHeight="1">
+      <c r="A9" s="52" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="53" t="inlineStr">
+        <is>
+          <t>Funded-Claim Detection for Casualty Reserving</t>
+        </is>
+      </c>
+      <c r="C9" s="52" t="inlineStr">
+        <is>
+          <t>funded-claim-detection-for-casualty</t>
+        </is>
+      </c>
+      <c r="D9" s="60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E9" s="52" t="inlineStr">
+        <is>
+          <t>contested</t>
+        </is>
+      </c>
+      <c r="F9" s="61" t="n">
+        <v>3</v>
+      </c>
+      <c r="G9" s="54">
+        <f>SUMIF('Model Detail'!$A:$A,$C9,'Model Detail'!L:L)</f>
+        <v/>
+      </c>
+      <c r="H9" s="54">
+        <f>SUMIF('Model Detail'!$A:$A,$C9,'Model Detail'!M:M)</f>
+        <v/>
+      </c>
+      <c r="I9" s="54">
+        <f>SUMIF('Model Detail'!$A:$A,$C9,'Model Detail'!N:N)</f>
+        <v/>
+      </c>
+      <c r="J9" s="54">
+        <f>SUMIF('Model Detail'!$A:$A,$C9,'Model Detail'!O:O)</f>
+        <v/>
+      </c>
+      <c r="K9" s="54">
+        <f>SUMIF('Model Detail'!$A:$A,$C9,'Model Detail'!P:P)</f>
+        <v/>
+      </c>
+      <c r="L9" s="54">
+        <f>SUMIF('Model Detail'!$A:$A,$C9,'Model Detail'!R:R)</f>
+        <v/>
+      </c>
+      <c r="M9" s="54">
+        <f>SUMIF('Model Detail'!$A:$A,$C9,'Model Detail'!S:S)</f>
+        <v/>
+      </c>
+      <c r="N9" s="54">
+        <f>SUMIF('Model Detail'!$A:$A,$C9,'Model Detail'!T:T)</f>
+        <v/>
+      </c>
+      <c r="O9" s="54">
+        <f>SUMIF('Model Detail'!$A:$A,$C9,'Model Detail'!U:U)</f>
+        <v/>
+      </c>
+      <c r="P9" s="54">
+        <f>SUMIF('Model Detail'!$A:$A,$C9,'Model Detail'!V:V)</f>
+        <v/>
+      </c>
+      <c r="Q9" s="57" t="n">
+        <v>3</v>
+      </c>
+      <c r="R9" s="57" t="n">
+        <v>5</v>
+      </c>
+      <c r="S9" s="57" t="n">
+        <v>8</v>
+      </c>
+      <c r="T9" s="57" t="n">
+        <v>9</v>
+      </c>
+      <c r="U9" s="57" t="n">
+        <v>10</v>
+      </c>
+      <c r="V9" s="48" t="n">
+        <v>172000</v>
+      </c>
+      <c r="W9" s="54">
+        <f>Q9*$V9</f>
+        <v/>
+      </c>
+      <c r="X9" s="54">
+        <f>R9*$V9</f>
+        <v/>
+      </c>
+      <c r="Y9" s="54">
+        <f>S9*$V9</f>
+        <v/>
+      </c>
+      <c r="Z9" s="54">
+        <f>T9*$V9</f>
+        <v/>
+      </c>
+      <c r="AA9" s="54">
+        <f>U9*$V9</f>
+        <v/>
+      </c>
+      <c r="AB9" s="48" t="n">
+        <v>300000</v>
+      </c>
+      <c r="AC9" s="51" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AD9" s="54">
+        <f>AB9*(1+$AC9)</f>
+        <v/>
+      </c>
+      <c r="AE9" s="54">
+        <f>AD9*(1+$AC9)</f>
+        <v/>
+      </c>
+      <c r="AF9" s="54">
+        <f>AE9*(1+$AC9)</f>
+        <v/>
+      </c>
+      <c r="AG9" s="54">
+        <f>AF9*(1+$AC9)</f>
+        <v/>
+      </c>
+      <c r="AH9" s="62">
+        <f>L9-W9-AB9</f>
+        <v/>
+      </c>
+      <c r="AI9" s="62">
+        <f>M9-X9-AD9</f>
+        <v/>
+      </c>
+      <c r="AJ9" s="62">
+        <f>N9-Y9-AE9</f>
+        <v/>
+      </c>
+      <c r="AK9" s="62">
+        <f>O9-Z9-AF9</f>
+        <v/>
+      </c>
+      <c r="AL9" s="62">
+        <f>P9-AA9-AG9</f>
+        <v/>
+      </c>
+      <c r="AM9" s="48" t="n">
+        <v>1100000</v>
+      </c>
+      <c r="AN9" s="54" t="n">
+        <v>62000</v>
+      </c>
+      <c r="AO9" s="63" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AP9" s="54" t="n">
+        <v>725000</v>
+      </c>
+      <c r="AQ9" s="52" t="inlineStr">
+        <is>
+          <t>This does not trade like software, and pretending otherwise is the single biggest way to get the outcome wrong. At Y5 the business is $3.6M revenue, ~$243k EBITDA, ~41% recurring ($1.47M of subscription and feed) and ~59% project-based. Two credible buyer sets. First, insurance data and analytics incumbents acquiring the graph and the carrier logos as a feature: Verisk, which already runs a TPLF campaign and a Claim Scoring line and is the most likely acquirer-or-killer; CLARA Analytics, which sells litigation-propensity scoring to precisely this buyer list and would treat funder attribution as an adjacent module on an existing contract; Milliman/IntelliScript, which already sits inside the reserve review; Findevor, if it wins its category and consolidates; or on the legal side ALM/vLex or LexisNexis, which own the docket substrate and the distribution to the defense bar. Second — and more realistic — expert-services consolidators buying the practice and the named experts: J.S. Held, Ankura, Charles River Associates, Oliver Wyman via Marsh McLennan, or a large claims TPA such as Sedgwick or Crawford. Multiples. Niche vertical data with genuine recurring revenue at sub-$5M scale trades roughly 4-7x ARR, so the $1.47M recurring supports perhaps $6-10M. Expert-services and consulting revenue trades roughly 1.0-1.5x revenue or 5-7x EBITDA, so the $2.13M project revenue supports perhaps $2-3M and the EBITDA basis supports far less. A blended enterprise value of $8-13M at Y5 is the optimistic case, and it requires a buyer to pay a data multiple on the recurring half. The realistic case is a $4-8M acqui-hire — the record's own downside_note called this correctly — where the acquirer is buying the entity-resolution pipeline, the case library and two or three people who can testify, not a business. Both cases return a bootstrapped founder well and a venture fund not at all. If the M12 case-level-linkage test fails, sell into the consolidator path by M24-M36 rather than waiting: every quarter of court-rule disclosure adoption in Arizona, New York, Ohio, West Virginia and Wisconsin makes the inference asset worth less, and the only durable value left is the expert-of-record franchise.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="54" customHeight="1">
+      <c r="A10" s="46" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="47" t="inlineStr">
+        <is>
+          <t>Forward exchange for transformer and switchgear production slots</t>
+        </is>
+      </c>
+      <c r="C10" s="46" t="inlineStr">
+        <is>
+          <t>grid-equipment-slot-forward-exchange</t>
+        </is>
+      </c>
+      <c r="D10" s="60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E10" s="46" t="inlineStr">
+        <is>
+          <t>contested</t>
+        </is>
+      </c>
+      <c r="F10" s="64" t="n">
+        <v>3</v>
+      </c>
+      <c r="G10" s="50">
+        <f>SUMIF('Model Detail'!$A:$A,$C10,'Model Detail'!L:L)</f>
+        <v/>
+      </c>
+      <c r="H10" s="50">
+        <f>SUMIF('Model Detail'!$A:$A,$C10,'Model Detail'!M:M)</f>
+        <v/>
+      </c>
+      <c r="I10" s="50">
+        <f>SUMIF('Model Detail'!$A:$A,$C10,'Model Detail'!N:N)</f>
+        <v/>
+      </c>
+      <c r="J10" s="50">
+        <f>SUMIF('Model Detail'!$A:$A,$C10,'Model Detail'!O:O)</f>
+        <v/>
+      </c>
+      <c r="K10" s="50">
+        <f>SUMIF('Model Detail'!$A:$A,$C10,'Model Detail'!P:P)</f>
+        <v/>
+      </c>
+      <c r="L10" s="50">
+        <f>SUMIF('Model Detail'!$A:$A,$C10,'Model Detail'!R:R)</f>
+        <v/>
+      </c>
+      <c r="M10" s="50">
+        <f>SUMIF('Model Detail'!$A:$A,$C10,'Model Detail'!S:S)</f>
+        <v/>
+      </c>
+      <c r="N10" s="50">
+        <f>SUMIF('Model Detail'!$A:$A,$C10,'Model Detail'!T:T)</f>
+        <v/>
+      </c>
+      <c r="O10" s="50">
+        <f>SUMIF('Model Detail'!$A:$A,$C10,'Model Detail'!U:U)</f>
+        <v/>
+      </c>
+      <c r="P10" s="50">
+        <f>SUMIF('Model Detail'!$A:$A,$C10,'Model Detail'!V:V)</f>
+        <v/>
+      </c>
+      <c r="Q10" s="57" t="n">
+        <v>6</v>
+      </c>
+      <c r="R10" s="57" t="n">
+        <v>14</v>
+      </c>
+      <c r="S10" s="57" t="n">
+        <v>24</v>
+      </c>
+      <c r="T10" s="57" t="n">
+        <v>34</v>
+      </c>
+      <c r="U10" s="57" t="n">
+        <v>44</v>
+      </c>
+      <c r="V10" s="48" t="n">
+        <v>185000</v>
+      </c>
+      <c r="W10" s="50">
+        <f>Q10*$V10</f>
+        <v/>
+      </c>
+      <c r="X10" s="50">
+        <f>R10*$V10</f>
+        <v/>
+      </c>
+      <c r="Y10" s="50">
+        <f>S10*$V10</f>
+        <v/>
+      </c>
+      <c r="Z10" s="50">
+        <f>T10*$V10</f>
+        <v/>
+      </c>
+      <c r="AA10" s="50">
+        <f>U10*$V10</f>
+        <v/>
+      </c>
+      <c r="AB10" s="48" t="n">
+        <v>520000</v>
+      </c>
+      <c r="AC10" s="51" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AD10" s="50">
+        <f>AB10*(1+$AC10)</f>
+        <v/>
+      </c>
+      <c r="AE10" s="50">
+        <f>AD10*(1+$AC10)</f>
+        <v/>
+      </c>
+      <c r="AF10" s="50">
+        <f>AE10*(1+$AC10)</f>
+        <v/>
+      </c>
+      <c r="AG10" s="50">
+        <f>AF10*(1+$AC10)</f>
+        <v/>
+      </c>
+      <c r="AH10" s="58">
+        <f>L10-W10-AB10</f>
+        <v/>
+      </c>
+      <c r="AI10" s="58">
+        <f>M10-X10-AD10</f>
+        <v/>
+      </c>
+      <c r="AJ10" s="58">
+        <f>N10-Y10-AE10</f>
+        <v/>
+      </c>
+      <c r="AK10" s="58">
+        <f>O10-Z10-AF10</f>
+        <v/>
+      </c>
+      <c r="AL10" s="58">
+        <f>P10-AA10-AG10</f>
+        <v/>
+      </c>
+      <c r="AM10" s="48" t="n">
+        <v>2400000</v>
+      </c>
+      <c r="AN10" s="50" t="n">
+        <v>55000</v>
+      </c>
+      <c r="AO10" s="59" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AP10" s="50" t="n">
+        <v>4300000</v>
+      </c>
+      <c r="AQ10" s="46" t="inlineStr">
+        <is>
+          <t>This is a technical services business and it will trade like one — 6-10x EBITDA, or roughly 1.0-2.0x revenue, not a software multiple. At Y5 that is $3.05M of EBITDA on $15.74M of revenue, implying a $20-35M enterprise value, with the top of that range requiring the retainer book (32% of revenue, contracted, multi-year) to be the thing the buyer underwrites. Four credible acquirer classes, in descending likelihood. (1) OWNER'S-ENGINEER AND INFRASTRUCTURE ADVISORY FIRMS — 1898 &amp; Co (Burns &amp; McDonnell), Sargent &amp; Lundy, Black &amp; Veatch, Stantec, WSP, NV5, Bureau Veritas. They already sit next to this client on interconnection and substation design and have no MV/HV procurement or expediting product; they buy capability tuck-ins at 7-9x EBITDA routinely and can cross-sell our desk into an existing book on day one. This is the base case. (2) PE-BACKED DATA CENTER SERVICES ROLLUPS — Legence (Blackstone), Salute, and the broader critical-facilities services consolidation. They pay 8-11x for a differentiated service line with recurring retainers and are the buyer most likely to pay for the retainer book specifically. (3) DISTRIBUTORS AND MARKETPLACE PLAYERS — WESCO, Graybar, Rexel, Sonepar, or Anza itself. Anza is the interesting one: it has the listings rails and the buyer relationships but not the neutral advisory seat, and buying us is cheaper than building the credibility that comes from taking no inventory. Strategic distributors will pay above the financial multiple for the client relationships, but they will also compress the independence that made the business work, so this is a good price and a bad home. (4) AN OEM — Hitachi Energy, Siemens Energy, GE Vernova, Prolec GE. Least likely and, if it happens, cheapest, because acquiring a neutral desk destroys the neutrality that is the whole asset. The only path to a materially higher multiple runs through the transaction-verified price database: 400+ verified prints covering $1.5B+ of equipment is the only forward curve built from actual clearing prices rather than surveys, and if the data licence line scales past ~$4M of ARR the blend starts attracting a 3-5x revenue conversation on that slice. I do not underwrite that. Sourcing showed four parties — VAWN, Terrapin, Electrical Trader, Giga Energy — already publishing overlapping lead-time and price content for free, which is exactly the condition under which a data moat fails to command a premium. Plan for $20-35M at 8-10x EBITDA in year 5-6, treat anything above as upside, and note plainly that a services outcome of this size does not return a venture fund — which is the strongest argument for building this on $2.4M or less, or not raising institutional money at all.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="54" customHeight="1">
+      <c r="A11" s="52" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="53" t="inlineStr">
+        <is>
+          <t>Key-state custody for LMS/XMSS firmware signing under CNSA 2.0</t>
+        </is>
+      </c>
+      <c r="C11" s="52" t="inlineStr">
+        <is>
+          <t>stateful-hash-signature-key-state-custody</t>
+        </is>
+      </c>
+      <c r="D11" s="60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E11" s="52" t="inlineStr">
+        <is>
+          <t>crowded</t>
+        </is>
+      </c>
+      <c r="F11" s="61" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" s="54">
+        <f>SUMIF('Model Detail'!$A:$A,$C11,'Model Detail'!L:L)</f>
+        <v/>
+      </c>
+      <c r="H11" s="54">
+        <f>SUMIF('Model Detail'!$A:$A,$C11,'Model Detail'!M:M)</f>
+        <v/>
+      </c>
+      <c r="I11" s="54">
+        <f>SUMIF('Model Detail'!$A:$A,$C11,'Model Detail'!N:N)</f>
+        <v/>
+      </c>
+      <c r="J11" s="54">
+        <f>SUMIF('Model Detail'!$A:$A,$C11,'Model Detail'!O:O)</f>
+        <v/>
+      </c>
+      <c r="K11" s="54">
+        <f>SUMIF('Model Detail'!$A:$A,$C11,'Model Detail'!P:P)</f>
+        <v/>
+      </c>
+      <c r="L11" s="54">
+        <f>SUMIF('Model Detail'!$A:$A,$C11,'Model Detail'!R:R)</f>
+        <v/>
+      </c>
+      <c r="M11" s="54">
+        <f>SUMIF('Model Detail'!$A:$A,$C11,'Model Detail'!S:S)</f>
+        <v/>
+      </c>
+      <c r="N11" s="54">
+        <f>SUMIF('Model Detail'!$A:$A,$C11,'Model Detail'!T:T)</f>
+        <v/>
+      </c>
+      <c r="O11" s="54">
+        <f>SUMIF('Model Detail'!$A:$A,$C11,'Model Detail'!U:U)</f>
+        <v/>
+      </c>
+      <c r="P11" s="54">
+        <f>SUMIF('Model Detail'!$A:$A,$C11,'Model Detail'!V:V)</f>
+        <v/>
+      </c>
+      <c r="Q11" s="57" t="n">
+        <v>4</v>
+      </c>
+      <c r="R11" s="57" t="n">
+        <v>6</v>
+      </c>
+      <c r="S11" s="57" t="n">
+        <v>8</v>
+      </c>
+      <c r="T11" s="57" t="n">
+        <v>10</v>
+      </c>
+      <c r="U11" s="57" t="n">
+        <v>11</v>
+      </c>
+      <c r="V11" s="48" t="n">
+        <v>215000</v>
+      </c>
+      <c r="W11" s="54">
+        <f>Q11*$V11</f>
+        <v/>
+      </c>
+      <c r="X11" s="54">
+        <f>R11*$V11</f>
+        <v/>
+      </c>
+      <c r="Y11" s="54">
+        <f>S11*$V11</f>
+        <v/>
+      </c>
+      <c r="Z11" s="54">
+        <f>T11*$V11</f>
+        <v/>
+      </c>
+      <c r="AA11" s="54">
+        <f>U11*$V11</f>
+        <v/>
+      </c>
+      <c r="AB11" s="48" t="n">
+        <v>420000</v>
+      </c>
+      <c r="AC11" s="51" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AD11" s="54">
+        <f>AB11*(1+$AC11)</f>
+        <v/>
+      </c>
+      <c r="AE11" s="54">
+        <f>AD11*(1+$AC11)</f>
+        <v/>
+      </c>
+      <c r="AF11" s="54">
+        <f>AE11*(1+$AC11)</f>
+        <v/>
+      </c>
+      <c r="AG11" s="54">
+        <f>AF11*(1+$AC11)</f>
+        <v/>
+      </c>
+      <c r="AH11" s="62">
+        <f>L11-W11-AB11</f>
+        <v/>
+      </c>
+      <c r="AI11" s="62">
+        <f>M11-X11-AD11</f>
+        <v/>
+      </c>
+      <c r="AJ11" s="62">
+        <f>N11-Y11-AE11</f>
+        <v/>
+      </c>
+      <c r="AK11" s="62">
+        <f>O11-Z11-AF11</f>
+        <v/>
+      </c>
+      <c r="AL11" s="62">
+        <f>P11-AA11-AG11</f>
+        <v/>
+      </c>
+      <c r="AM11" s="48" t="n">
+        <v>1750000</v>
+      </c>
+      <c r="AN11" s="54" t="n">
+        <v>95000</v>
+      </c>
+      <c r="AO11" s="63" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AP11" s="54" t="n">
+        <v>780000</v>
+      </c>
+      <c r="AQ11" s="52" t="inlineStr">
+        <is>
+          <t>This is a small-cap trade sale in year 3-4, not a venture outcome, and it should be underwritten that way from the first cheque. Acquirers, in rough order of likelihood: Keyfactor (Insight Partners-backed, already ships LMS in SignServer and sells Signum for firmware — buying the portability shim is cheaper than building four more HSM integrations); Entrust and Thales TCT (each wants cross-vendor credibility they cannot claim about their own competitor's module); Utimaco (SGT Capital, already has the production firmware-OTA customers and would buy the tooling and the accounts); DigiCert Software Trust Manager (Clearlake/Crosspoint, has the distribution and no confirmed LMS story); Crypto4A, ISARA or Cryptomathic/PQShield as consolidation; or a defense services roll-up — Booz Allen, Parsons, CACI, Peraton — buying the cleared-adjacent engagement book and CMMC certification rather than the IP. Mechanics: at Y5 this is ~$3.5M revenue that is 64% project services and 36% recurring, and the two halves trade completely differently. The services and attestation book ($1.69M) trades at 0.8-1.3x revenue or 5-7x EBITDA the way any boutique compliance-engineering firm does — call it $1.5-2.2M. The recurring half (subscription $1.35M plus OEM licences $450k = $1.8M ARR) trades at 4-6x ARR for narrow, defensible, mandate-driven infrastructure with genuine switching costs (the key hierarchy is burned into silicon) — call it $7-11M. Total $8.5-13M, with upside toward $18M only if the FTO comes back clean, the shim becomes the implementation the PQUIP RFC points at, and two HSM vendors are paying OEM licences, at which point the acquisition is defensive and prices off strategic value rather than multiples. On $1.75M raised that is roughly 5-8x gross, which is a good private-company result and an unacceptable venture result — a fund needing a fund-returner should not be in this. The realistic downside, and it is the modal case if stateful adoption comes in under 25% of new designs at the M24 gate, is the outcome the record already named: an acqui-hire into Keyfactor, DigiCert or Entrust for the team and the open-source project at $3-6M, or simply running it indefinitely as a profitable 8-person consultancy at $2-2.5M revenue that never sells at all. The one genuinely bad ending is an adverse FTO opinion on US 11722313 combined with continued ML-DSA drift, in which case there is no product to sell and no book worth buying, and the correct move at month 3 is to not start.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="46" t="n"/>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t>Total (8 opportunities)</t>
+        </is>
+      </c>
+      <c r="C12" s="46" t="n"/>
+      <c r="D12" s="46" t="n"/>
+      <c r="E12" s="46" t="n"/>
+      <c r="F12" s="46" t="n"/>
+      <c r="G12" s="58">
+        <f>SUM(G4:G11)</f>
+        <v/>
+      </c>
+      <c r="H12" s="58">
+        <f>SUM(H4:H11)</f>
+        <v/>
+      </c>
+      <c r="I12" s="58">
+        <f>SUM(I4:I11)</f>
+        <v/>
+      </c>
+      <c r="J12" s="58">
+        <f>SUM(J4:J11)</f>
+        <v/>
+      </c>
+      <c r="K12" s="58">
+        <f>SUM(K4:K11)</f>
+        <v/>
+      </c>
+      <c r="L12" s="58">
+        <f>SUM(L4:L11)</f>
+        <v/>
+      </c>
+      <c r="M12" s="58">
+        <f>SUM(M4:M11)</f>
+        <v/>
+      </c>
+      <c r="N12" s="58">
+        <f>SUM(N4:N11)</f>
+        <v/>
+      </c>
+      <c r="O12" s="58">
+        <f>SUM(O4:O11)</f>
+        <v/>
+      </c>
+      <c r="P12" s="58">
+        <f>SUM(P4:P11)</f>
+        <v/>
+      </c>
+      <c r="Q12" s="46" t="n"/>
+      <c r="R12" s="46" t="n"/>
+      <c r="S12" s="46" t="n"/>
+      <c r="T12" s="46" t="n"/>
+      <c r="U12" s="46" t="n"/>
+      <c r="V12" s="46" t="n"/>
+      <c r="W12" s="46" t="n"/>
+      <c r="X12" s="46" t="n"/>
+      <c r="Y12" s="46" t="n"/>
+      <c r="Z12" s="46" t="n"/>
+      <c r="AA12" s="46" t="n"/>
+      <c r="AB12" s="46" t="n"/>
+      <c r="AC12" s="46" t="n"/>
+      <c r="AD12" s="46" t="n"/>
+      <c r="AE12" s="46" t="n"/>
+      <c r="AF12" s="46" t="n"/>
+      <c r="AG12" s="46" t="n"/>
+      <c r="AH12" s="58">
+        <f>SUM(AH4:AH11)</f>
+        <v/>
+      </c>
+      <c r="AI12" s="58">
+        <f>SUM(AI4:AI11)</f>
+        <v/>
+      </c>
+      <c r="AJ12" s="58">
+        <f>SUM(AJ4:AJ11)</f>
+        <v/>
+      </c>
+      <c r="AK12" s="58">
+        <f>SUM(AK4:AK11)</f>
+        <v/>
+      </c>
+      <c r="AL12" s="58">
+        <f>SUM(AL4:AL11)</f>
+        <v/>
+      </c>
+      <c r="AM12" s="58">
+        <f>SUM(AM4:AM11)</f>
+        <v/>
+      </c>
+      <c r="AN12" s="46" t="n"/>
+      <c r="AO12" s="46" t="n"/>
+      <c r="AP12" s="58">
+        <f>SUM(AP4:AP11)</f>
+        <v/>
+      </c>
+      <c r="AQ12" s="46" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:AQ11"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:AR1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="95" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="95" customWidth="1" min="6" max="6"/>
+    <col width="80" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="80" customWidth="1" min="9" max="9"/>
+    <col width="80" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="95" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="26" t="inlineStr">
+        <is>
+          <t>What live searching (August 2026) established. This is the competitor check the original study never ran. Only 2 of 8 opportunities survived it intact.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="34" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>Opportunity</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Trigger verified?</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>What the trigger actually does</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>Crowding</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>Named competitors found</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>Crowding reasoning</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>Buyer universe (sourced)</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>How it was derived</t>
+        </is>
+      </c>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>Pricing comparables found</t>
+        </is>
+      </c>
+      <c r="K3" s="6" t="inlineStr">
+        <is>
+          <t>Still stands?</t>
+        </is>
+      </c>
+      <c r="L3" s="6" t="inlineStr">
+        <is>
+          <t>Ruling</t>
+        </is>
+      </c>
+      <c r="M3" s="6" t="inlineStr">
+        <is>
+          <t>Searches</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="150" customHeight="1">
+      <c r="A4" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="47" t="inlineStr">
+        <is>
+          <t>Ride-through models and curtailment proof for NERC-registered data centers</t>
+        </is>
+      </c>
+      <c r="C4" s="46" t="inlineStr">
+        <is>
+          <t>partly-confirmed</t>
+        </is>
+      </c>
+      <c r="D4" s="47" t="inlineStr">
+        <is>
+          <t>All four dated triggers are REAL and the record's dates are exact — but three of the four do not do what the record claims, and a fifth event three days ago freezes the proposed beachhead.
+CONFIRMED TO THE DAY:
+1. NERC Level 3 "Essential Actions" Alert, issued 4 May 2026, titled "Level 3 Essential Action Alert, Computational Load Modeling, Studies, Instrumentation, Commissioning, Operations, Protection, and Control." Triggered by repeated events where "1,000+ MW of computation load dropped off the bulk power system in seconds." Acknowledgement due 11 May 2026; responses to 33 questions due 3 August 2026. Date and deadline exactly as recorded.
+2. FERC Docket RD26-7-000, order issued 16 July 2026, directing NERC to file new/modified Reliability Standards for computational load integration by 31 December 2026, plus Rules of Procedure revisions and registry criteria by 31 December 2026, plus a Phase II workplan informational filing by 1 March 2027. Every date matches.
+3. FERC Docket RM26-4-000: six contemporaneous FPA Section 206 show-cause orders issued 18 June 2026. Date matches. Large load defined as peak load &gt;50 MW interconnecting above 69 kV. 60-day response window.
+4. ERCOT NOGRR 282: grandfather date of 14 November 2025 confirmed verbatim — a facility escapes only if, on or before 14 Nov 2025, it had ERCOT approval to energize OR had completed its Large Load Interconnection Study with a TDSP interconnection confirmation letter. Applies to Large Electronic Loads where ≥50% of site demand is power-electronic. (The 90/90/180 remediation cycle was not separately corroborated in results.)
+BUT — WHAT THE TRIGGERS ACTUALLY DO:
+- The Level 3 Alert is NOT enforceable. Per Davis Wright Tremaine: "The Essential Actions are not the same as Reliability Standards and are not mandatory obligations. Registered entities are not subject to penalties for failing to implement the Essential Actions." There is no enforcement clock behind the 3 Aug 2026 date.
+- The Alert binds transmission owners, transmission planners, transmission operators, planning coordinators, reliability coordinators and balancing authorities — i.e. utilities and grid operators. Data centers are not currently NERC-registered and are "not directly bound." The record's PRIMARY buyer is not the obligated party; its SECONDARY buyer is.
+- Computational Load Entity registration is still a DRAFT. First draft posted for 45-day comment 1 April 2026; revised draft expected August 2026; Board approval targeted 5 December 2026; filing by 31 December 2026. Threshold: ≥20 MW aggregate connected load, at a single POI ≥60 kV, hosting ≥1 MW computational load.
+- RM26-4 went to PJM, CAISO, MISO, NYISO, ISO-NE and SPP. ERCOT is not FERC-jurisdictional and is not among the six. The record's chosen beachhead is the one market RM26-4 does not touch.
+AND THE NEW EVENT THE RECORD CANNOT KNOW: on ~3 August 2026 Governor Abbott ordered an audit of every data center in the ERCOT queue (now ~474 GW, up from 438 GW). ERCOT issued a market notice DELAYING the Batch Zero process and will seek a PUCT good-cause timeline exemption at the 20 August 2026 open meeting. Projects must now disclose power, water, incentives and ownership before advancing. BNEF puts 20% of the US data center pipeline at risk of delay.</t>
+        </is>
+      </c>
+      <c r="E4" s="46" t="inlineStr">
+        <is>
+          <t>contested</t>
+        </is>
+      </c>
+      <c r="F4" s="47" t="inlineStr">
+        <is>
+          <t>GridStrong — $10M seed to automate regulatory compliance and interconnection workflows for generation, transmission AND LARGE-LOAD operators. This is the proposed wedge, funded, as software rather than as a boutique. Already publishes practitioner guidance on PJM MOD-026/027 model-verification compliance (gridstrong.ai/resources/pjm-mod-026-027-guidance) — the exact generator-side model-validation muscle that ports to loads.
+Keentel Engineering — 27 years operating, offices Tampa/Austin/Sacramento/Baltimore, former NERC audit team leads and licensed PEs on staff. Project history in ERCOT, PJM, MISO, WECC, SERC across data center, AI training, crypto mining, hydrogen and arc furnace loads. Already sells, by name: Level 3 Alert response engineering, large-load system impact and contingency studies, disturbance monitoring and instrumentation design, protection coordination at large-load POIs, ERCOT dynamic model submission, PGRR 144 large-load dynamic modeling, Batch Zero guidance, NERC MOD-026-2/MOD-027 model verification, 8760 withdrawal study and BESS sizing. Bootstrapped/private, no disclosed funding. This firm currently owns the practitioner search surface for essentially every query in this space.
+PSC Consulting — has a dedicated productized service line 'Data Center Load Modeling and Assessment' with its own landing page, positioned as turning complex modeling into guidance supporting reliable interconnections. International transmission-consulting firm, private.
+EPE Consulting — already published both 'Turning NERC's Level 3 Essential Actions into a Defensible Response' and 'Preparing for NOGRR 282: ERCOT's Next Phase of Large Load Requirements', plus prior Level 3 Alert (IBR) response guidance for utilities. Selling the attestation-response product now, private/boutique.
+GridCARE — $64M Series A (2026), following $13.5M seed out of stealth late May 2025. Platform compresses data center interconnection timelines from years to months. Adjacent rather than identical, but well capitalized and calling on the same VP of Energy.
+Piq Energy — $5M oversubscribed seed announced 8 July 2026, led by Active Impact Investments with Cisco Foundation and Mobilize AI x Energy Ventures. Agentic platform for grid planning to speed how utilities and developers connect projects. Described in coverage as entering 'a fast-forming category of startups applying AI to interconnection and compliance' — note 'fast-forming' and 'compliance'.
+Certrec — manages the entire NERC compliance program for 130+ registered sites across US, Canada and Mexico, positioning NERC compliance as its core rather than an ancillary service. PE-backed. Has the registered-entity relationships and the RSAW/audit machinery a new CLE registration category would flow straight into.
+Danovo Energy Solutions — running Level 3 Alert / computational load programming aimed at utilities, i.e. at the party actually bound by the Alert.
+Utility Services Inc — marketing a Level 3 NERC Alert service offering.
+ENTRUST Solutions Group, GridSME, Electric Power Group — established generator model-validation practices (MOD-026/MOD-027, PMU-based validation). Same core competency, load-side port is a scope change not a capability change.
+ERCOT itself — published 'Dynamic Modeling of AI Data Center Load in PSCAD' (24 April 2026), a free public manual including a double-conversion UPS-based AI data center model with voltage ride-through, mode-transition and load-fluctuation test cases. Not a company, but it commoditizes the specific artifact the record calls the moat.</t>
+        </is>
+      </c>
+      <c r="G4" s="47" t="inlineStr">
+        <is>
+          <t>The record's screening block guessed "no dominant branded owner, which is unusual for a demand this loud" and rated the head start "real." The first half survives; the second does not.
+Not empty, not thin. Searching practitioner jargon rather than the record's marketing language surfaces incumbents who already list the exact deliverable as a named service:
+- Keentel Engineering sells "Level 3 Alert response engineering," ERCOT dynamic model submission, PGRR 144 large-load dynamic modeling, Batch Zero guidance and MOD-026-2/MOD-027 model verification — across five ISO footprints, from four offices, with 27 years of history and ex-NERC audit team leads. It appeared in the top results of six of my nine substantive searches. Whatever the record thought "tiny consultancy" meant, this is the incumbent and it is already ranked for every query the proposed business would want.
+- PSC Consulting has "Data Center Load Modeling and Assessment" as a standing product page.
+- EPE Consulting published its Level 3 Essential Actions response product and its NOGRR 282 primer before this record was written.
+- Danovo and Utility Services are both marketing Level 3 Alert services to utilities — the actually-obligated party.
+And funded software is already inside the wedge. GridStrong raised $10M seed explicitly to "automate regulatory compliance and interconnection workflows for generation, transmission and large-load operators" — that sentence is the business plan. Piq Energy ($5M seed, 8 July 2026) entered what its own coverage calls "a fast-forming category of startups applying AI to interconnection and compliance." GridCARE holds $64M Series A calling on the same buyer. The record's premise that "the specific artifact is new to everyone" is false: the generator-side version of this exact work (MOD-026/MOD-027 model verification) is a mature practice at GridStrong, GridSME, ENTRUST, Electric Power Group and Keentel, and the load-side port is a scope change, not a capability gap.
+Most damaging to defensibility: ERCOT published the reference PSCAD double-conversion UPS data center model itself in April 2026, free. The record's stated moat — the rare engineer who can render IEC 62040-3 UPS transfer behavior as an ISO-acceptable model — is being systematically dissolved by the ISO.
+Not "crowded" only because no single branded owner has consolidated the category and the demand genuinely outruns supply. But there is no head start.
+Separately, the flexibility half is worse than the record's own "materially crowded" guess: total ERCOT Controllable Load Resource capacity is about 36 MW. That is not a crowded market, it is an empty one — the curtailment-proof product has essentially no installed base to sell into today.</t>
+        </is>
+      </c>
+      <c r="H4" s="65" t="n">
+        <v>790</v>
+      </c>
+      <c r="I4" s="47" t="inlineStr">
+        <is>
+          <t>Derived from two sourced request COUNTS plus sourced GW growth, replacing the record's assumed 500 MW/campus and assumed 30% materialization (both of which its own note admits were unresearched recall).
+Step 1 — sourced counts: ERCOT received 152 large-load interconnection requests total from 2022 (cumulative through 2024), and 225 new requests during 2025 through mid-November. That is 377 cumulative ERCOT large-load requests as of Nov 2025. [renewableenergyworld]
+Step 2 — sourced GW at the same date: ERCOT reported ~226 GW of large load in the queue as of November 2025 (vs 63 GW at end-2024). [latitudemedia]
+Step 3 — implied average request size: 226 GW / 377 requests = ~600 MW per request. This REPLACES the record's guessed 500 MW/campus and is 20% larger, which SHRINKS the implied count.
+Step 4 — scale to today: queue is now ~474 GW [utilitydive 827046], i.e. 2.1x the Nov 2025 GW. Holding average request size constant gives ~790 cumulative ERCOT large-load interconnection requests as of Aug 2026. This step is an estimate — ERCOT has not published a current request count.
+CONTEXT THE SINGLE NUMBER HIDES:
+- 790 is REQUESTS, not materialized campuses and not buying entities. ERCOT's own framing is that the queue is "potential demand, not confirmed load," and the Abbott audit exists specifically to filter it. At a 20-30% materialization rate the real ERCOT campus count is ~160-240.
+- Distinct buying entities are far fewer than campuses. The record itself concedes 100-200 distinct developers; nothing I found contradicts that, and it is the more honest denominator for a sales plan.
+- National extrapolation: the record multiplies ERCOT by 3.5x for PJM/MISO/SPP/SERC with no basis. I found no evidence for any multiplier and will not invent one. If NERC's draft CLE threshold finalizes (≥20 MW aggregate at a POI ≥60 kV with ≥1 MW computational load), the national registered universe could be large, but NERC has published no count of affected facilities and none was findable.
+- The record's headline 900 is therefore not crazy as a national campus figure, but it is right by coincidence: its 500 MW assumption was too small and its 30% materialization was unsourced, and the two errors partly cancel.</t>
+        </is>
+      </c>
+      <c r="J4" s="47" t="inlineStr">
+        <is>
+          <t>NO VENDOR PRICE for the specific service (filed dynamic model + disturbance-response testing + attestation package) was findable. Power-systems consulting pricing is quoted, not published; Certrec's only public pricing language is that a full NERC compliance program "costs a fraction of a full-time equivalent," with no figure. The record's $150k-$600k per campus band remains UNSOURCED — but it is not contradicted, and the adjacent regulated fee schedule sits squarely inside it.
+HARD PRICES ACTUALLY FOUND (Texas SB6 / PUCT large-load interconnection regime):
+- Interconnection study fee: $100,000 for projects 75-250 MW.
+- Interconnection study fee: $300,000 for projects over 250 MW, plus actual study costs exceeding that amount.
+- Financial security: $50,000/MW of requested load, as cash, letter of credit or investment-grade guaranty. A 1 GW data center posts $50 million.
+[Greenberg Traurig, Texas SB6 update]
+These are fees paid to the ISO/TDSP, not to a consultant — a different payee than the proposed business. What they establish is that a six-figure per-campus grid-study line item is already normal, budgeted and statutorily expected for exactly this buyer, which is the useful anchor: the buyer is not being asked to create a new budget category.
+SURROUNDING SPEND (scale context, not comparables):
+- Utility interconnection costs of $10-30M per data center depending on distance to substation and voltage. [ATK Energy]
+- Physical interconnection ranging $5M-$25M+ depending on distance from existing grid capacity.
+Against $10-30M of interconnection capex and $50M of posted security, a $150k-$600k engineering engagement is rounding error to the buyer — which supports the band's plausibility even though no vendor quote confirms it.
+DOWNWARD PRESSURE ON PRICE: ERCOT's free 24 April 2026 PSCAD AI data center load manual supplies a double-conversion UPS reference model with ride-through test cases, compressing the most billable part of the scope.</t>
+        </is>
+      </c>
+      <c r="K4" s="55" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L4" s="47" t="inlineStr">
+        <is>
+          <t>It stands as a real, billable engineering services business. It does not stand as the thing the record ranked #1, and every load-bearing pillar of the why_this_rank paragraph broke under sourcing.
+WHAT SURVIVED, and it is not nothing: the underlying demand is confirmed loudly and precisely. Four dated triggers exist to the exact day claimed — that is a striking hit rate for a record built without web access. Repeated losses of 1,000+ MW of computational load in seconds are real, the FERC 31 December 2026 standards deadline is real, NOGRR 282's 14 November 2025 grandfather cliff is real, and the ERCOT queue is larger than recorded (474 GW, not 438 GW). The buyer already carries a statutorily-expected six-figure per-campus grid-study line ($100k/$300k PUCT fees) against $10-30M of interconnection capex, so the ACV band is plausible and the buyer is price-insensitive at this scale. Mandatory standards genuinely are coming, and when CLE registration finalizes in December 2026 the obligation becomes real and penalized.
+WHAT BROKE, in descending order of damage:
+1. "Revenue exists in month one" — the beachhead froze three days ago. Abbott's audit stopped ERCOT's Batch Zero process pending a 20 August PUCT exemption request; BNEF has 20% of the US pipeline at delay risk. Selling interconnection-compliance engineering into a market that just suspended its interconnection process is the opposite of month-one revenue.
+2. "The buyer is under an enforcement clock" — false. The Level 3 Alert carries no penalties and is not a Reliability Standard. The real clock starts around 31 Dec 2026, which converts this from "revenue now" to "revenue in 6-18 months," changing the risk profile entirely and eliminating the ranking's core advantage over the nuclear and customs ideas it was ranked above.
+3. "The head start is real" — false. Keentel, PSC, EPE, Danovo and Utility Services already sell the named deliverable; GridStrong has $10M to automate it for large-load operators specifically; and ERCOT gives away the reference UPS PSCAD model that the record calls the moat.
+4. The named buyer is the wrong party. Data centers are not registered entities and are not bound; utilities and transmission planners are. The go-to-market must invert to the record's secondary buyer, which is a different sale with a different budget and a much longer cycle.
+5. RM26-4 does not reach ERCOT, so the "nationalizing" trigger and the chosen starting market are disjoint.
+6. The second product has a ~36 MW total addressable installed base in ERCOT CLR terms.
+NET: the record's own kill_risk was right and understated it. This is a consultancy, in a contested field, whose differentiating artifact is being commoditized by the ISO, whose regulatory urgency is six to eighteen months away rather than immediate, whose named buyer is not the obligated party, and whose beachhead market is under a state-ordered freeze as of this week. Real business, real demand, wrong rank, wrong buyer, wrong entry market, and the confidence of 5 should come down rather than up despite four triggers verifying perfectly.</t>
+        </is>
+      </c>
+      <c r="M4" s="46" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" ht="150" customHeight="1">
+      <c r="A5" s="52" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="53" t="inlineStr">
+        <is>
+          <t>Entry Type 13 and instrument-aware duty recovery for the post-de-minimis long tail</t>
+        </is>
+      </c>
+      <c r="C5" s="52" t="inlineStr">
+        <is>
+          <t>partly-confirmed</t>
+        </is>
+      </c>
+      <c r="D5" s="53" t="inlineStr">
+        <is>
+          <t>The regulatory spine is REAL and mostly verifies — including the two things the scout flagged as unverified and load-bearing. But two dated claims are materially misstated, and one instrument change since the record was written rewires the whole recovery half.
+CONFIRMED — Entry Type 13 exists, on the exact date claimed: CBP published a Trade Information Notice, "Implementation of Entry Type 13 Test in ACE for U.S. Mail Processing." ET13 "deploys to the ACE Certification (CERT) environment on July 24, 2026, and to Production (PROD) on September 22, 2026." It lets filers "electronically submit shipment-level data, including HTSUS tariff classification, origin, value, duty calculations, and the required customs bond information." Entry "can only be made by an owner or purchaser of the merchandise being mailed to the United States, or a licensed customs broker properly designated" — this directly supports the license-as-moat claim.
+CONTRADICTED — ET13's SCOPE. The record calls it "a fully electronic informal-entry path for shipments valued at $2,500 or less." It is not general. It is scoped to INTERNATIONAL MAIL: "a voluntary test for a new electronic informal entry process for international mail shipments valued at $2,500 or less." The record's own buildable_today (a Shopify/Woo app filing entries for merchants importing pallets and consolidated air/ocean freight) is largely OUTSIDE ET13. Note also CERT opened 24 July 2026 — already two weeks past as of today — so "the integration door opens in seven weeks" was already stale when written.
+CONFIRMED EXACTLY — the SCOTUS holding the scout could not verify. Learning Resources, Inc. v. Trump, No. 24-1287, decided 20 February 2026, 6-3, holding IEEPA does not authorize tariffs (Thomas, Kavanaugh, Alito dissenting). "All US tariffs imposed by the Trump Administration under the International Emergency Economic Powers Act terminated at 12:00 am eastern time on February 24, 2026."
+CONFIRMED EXACTLY — the CAPE figures the scout could not verify. CBP launched Phase 1 of Consolidated Administration and Processing of Entries (CAPE) in the ACE portal on 20 April 2026. "As of April 26, 2026, importers and brokers had submitted approximately 75,300 CAPE declarations covering more than 11.2 million individual entries." Both numbers land on the nose. Additional sourced context the record lacks: ~$121.75B in potential and certified refunds accepted into CAPE and ~$86.3B already sent to Treasury for disbursement — i.e. the CAPE wave is largely SPENT, not ahead of a new entrant.
+CONFIRMED — de minimis remains suspended post-ruling. SCOTUS "did not address suspension of the de minimis exemption using IEEPA." OBBBA repeal verifies: the statutory commercial-shipment exception under 19 USC 1321 is removed effective 1 July 2027, with personal gift parcels under $100 ($200 for Mexico/Canada/Caribbean) preserved.
+CORRECTED — the "24 June 2026 indefinite suspension." What actually happened: on 23 JUNE 2026 CBP published TWO PROPOSED RULES (NPRMs) "establishing a new legal basis for indefinitely suspending the de minimis duty exemption." Proposed, not final. And it is under live attack — importer Detroit Axle argued at the Court of International Trade that the SCOTUS decision confirms IEEPA cannot be used to end de minimis, and the court ruled the case can proceed. The record treats a contested NPRM as settled law.
+NEW AND MISSED — the instrument base moved. Section 122 (the 10% global baseline that replaced IEEPA on 20 Feb 2026) "expired by operation of law" at 12:01 a.m. ET on Friday 24 July 2026. USTR announced final action in Section 301 forced-labour investigations on 23 July 2026, effective 12:01 a.m. 24 July — additional duties of 10% or 12.5% on products of 60 economies "accounting for roughly 99% of US imports." Section 232 (steel/aluminum/copper/lumber 25%) continues. This cuts BOTH ways for the thesis and the record models neither direction.</t>
+        </is>
+      </c>
+      <c r="E5" s="52" t="inlineStr">
+        <is>
+          <t>crowded</t>
+        </is>
+      </c>
+      <c r="F5" s="53" t="inlineStr">
+        <is>
+          <t>Amari AI — $4.5M raised Feb 2026, co-led by First Round Capital and Pear VC; founded by ex-Google engineer Sam Basu and ex-LinkedIn engineer Arushi Vashist. Positions as 'the leading AI partner for customs brokers,' automating data entry and paperwork for brokers with real-time trade-rule monitoring. 30+ customers signed, $15B+ of goods moved. THIS IS THE BROKER-CAPACITY-MULTIPLICATION THESIS, ALREADY FUNDED — the exact thing the record says 'nobody has attacked.'
+Caspian — $5.4M seed led by Primary Venture Partners, with Blank Ventures. An approved tech company AND licensed customs broker; files claims directly with CBP or partners with enterprises and brokers; automates analysis of shipping and inventory data to identify eligible duty refunds and submits claims in days rather than months. Covers BOTH of the record's two products in one funded company.
+Zonos — ~$69M raised over 2 rounds from 8 investors; 50,000+ merchants, 70+ postal operators. ACQUIRED Evolve Trade Services (licensed US customs brokerage, Type 11 informal entry specialist for high-volume D2C parcel) on 30 April 2026 and launched Zonos Brokerage Services for low-value informal entries to merchants, postal operators, 3PLs and forwarders. Also one of CBP's 12 certified qualified parties. The record's named down-market threat, already executed.
+Zollback — $4.5M seed, founded 2024, launched 17 March 2026. First AI-powered duty drawback platform automating identification, optimization and filing of tariff refund claims; targets SMBs explicitly; claims 15-20% more recovery than traditional providers in 10-15 working days vs 9-12 months; $10M in refunds already processed, revenue tripling. CEO Elena Zhao, Stanford PhD in operations research. Markets on the identical '$15B unclaimed / 80% never file' framing the record uses as its own overlooked insight — and appears in the record's OWN evidence_urls.
+Evolve Trade Services — licensed US customs brokerage, high-volume ecommerce clearance, Type 11 informal entries; now the licensed brokerage entity behind Zonos Brokerage Services while continuing to operate separately. Also independently on CBP's certified qualified-parties list.
+Flexport — CBP-certified qualified party for duty collection on international mail; named in the record as adjacent but is in fact directly certified on the target flow.
+BoxC — CBP-certified qualified party, ecommerce parcel clearance.
+Importal Customs — CBP-certified qualified party.
+SafePackage — CBP-certified qualified party, authorized as a third-party provider BEFORE the 29 Aug 2025 de minimis ban took effect.
+International Bonded Couriers, Advance Customs Broker &amp; Logistics, R&amp;H International Brokerage, James CB TX, JFS, North American Ecommerce Solutions — remaining CBP-certified qualified parties on the international-mail duty-collection list.
+KlearNow.AI — customs clearance automation software platform, established player publishing 2026 category guidance.
+Charter Brokerage — approx. one-third of all US duty drawback refunds (record's own claim, not independently sourced by me).
+Alliance Drawback Services — contingency-based drawback, no upfront cost; named in 2026 market comparisons.
+Comstock, Tradewin — established drawback incumbents (Tradewin publishes de minimis repeal guidance for importers).
+Lightsource.ai — drawback practical-guide publisher and service provider; appears in the record's own evidence_urls.
+Camtom, TariffLens, Artemus Group, GingerControl — AI HTS classification and trade-compliance tooling vendors publishing 2026 classification guidance and operating in the classification-assistant layer.
+Gaia Dynamics — venture-tracked trade/customs AI startup.
+Passport Global (~$27M+), Portless, Avalara, iCustoms, Hurricane Commerce — cross-border ecommerce compliance layer named in the record.
+Descartes, WiseTech/CargoWise, Thomson Reuters OneSource, E2open — entrenched ABI filing and global trade management incumbents, any of whom can ship ET13 support as a release feature.
+DHL, UPS, FedEx — own the parcel flow and bundle their own de minimis replacement entry services, amortized across the network.</t>
+        </is>
+      </c>
+      <c r="G5" s="53" t="inlineStr">
+        <is>
+          <t>The record's crowding_check was written from training knowledge and got the direction right but the timing catastrophically wrong. It framed the threats as future risks. Every one of them has already happened, and all within the last six months.
+BOTH HALVES ARE OCCUPIED BY FUNDED, LAUNCHED, NAMED COMPANIES:
+Broker-capacity multiplication — the record's core "nobody has attacked this" claim. Amari AI, $4.5M from First Round Capital and Pear VC in February 2026, sells AI throughput multiplication directly TO customs brokers, with 30+ customers and $15B+ of goods moved. Two of the best seed firms in the market underwrote this exact thesis six months ago.
+Licensed broker plus automated refunds in one entity — the record's two-product plan. Caspian, $5.4M seed led by Primary Venture Partners, is simultaneously an approved tech company and a licensed customs broker, filing entries and identifying eligible duty refunds directly with CBP.
+Low-value informal entry for the long tail. Zonos closed the Evolve Trade Services acquisition on 30 April 2026 and launched Zonos Brokerage Services for low-value informal entries. It brings a licensed brokerage with documented Type 11 informal-entry expertise, ~$69M of capital, 50,000 merchants and 70 postal operators of distribution. The record predicted this as a race it might lose; the race was already run.
+SMB drawback. Zollback, $4.5M seed, launched 17 March 2026, AI-native, SMB-targeted, claiming 10-15 working days versus the 9-12 month incumbent cycle — and marketing on the identical "$15B unclaimed, 80% never file" framing the record presents as its proprietary insight. It is cited in the record's own evidence_urls, meaning the scout read a competitor's content marketing and mistook it for market evidence.
+THE REGULATOR PUBLISHED THE COMPETITOR LIST. CBP certified 12 qualified parties to collect duties on international mail under EO 14324 — Advance Customs Broker &amp; Logistics, BoxC, Evolve, Flexport, Importal, International Bonded Couriers, James CB TX, JFS, North American Ecommerce Solutions, R&amp;H International Brokerage, SafePackage, Zonos. ET13 is a MAIL process. These twelve are already licensed and certified on the exact flow ET13 governs, and two of them were authorized before the ban even took effect.
+ONE STRUCTURAL POINT IN THE RECORD'S FAVOUR: this crowd is genuinely segmented and none of it is winner-take-all. A licensed brokerage with a real book of accounts is a durable asset regardless of who else exists. But "crowded" is the honest verdict — the specific unoccupied gap the record identified does not exist, and the four most direct competitors all shipped between March and April 2026.</t>
+        </is>
+      </c>
+      <c r="H5" s="66" t="n">
+        <v>300000</v>
+      </c>
+      <c r="I5" s="53" t="inlineStr">
+        <is>
+          <t>SOURCED CEILING, not the addressable segment. CBP directly reports it "manages over 300,000 active unique importer-of-record numbers annually, accounting for 30.4 million commercial transactions, which represents approximately $2.4 trillion dollars in imports, and generates over $40 billion dollars in duties, fees, and taxes." A 2012 CBP regulatory filing independently estimated ~300,000 respondents annually filing Form 5106 (Importer ID Input Record), and CBP processed 36M+ entry summaries in FY2022 — three consistent anchors.
+DERIVATION AND WHY THE RECORD'S 150,000 IS NOT SUPPORTED: 300,000 active IORs is the total population of entities that file entries at all, enterprise and SMB combined. The record's buyer_universe of 150,000 is a flat 50% haircut of a number the scout only half-remembered ("200,000-250,000" — the real figure is higher, 300,000+, so the recall was low). No source establishes the SMB-only subset. Applying the record's own three filters — (a) SMB not enterprise, (b) not captive to a parcel carrier's own entry service, (c) reachable via Shopify app or 3PL referral — against $2.4T spread over 300,000 IORs (a mean of $8M/importer, with a power-law skew that puts most importers well below the $1-20M band's midpoint) leaves an addressable count I can bound but not source: somewhere between 50,000 and 200,000. I report the sourced 300,000 ceiling rather than dress a haircut as evidence.
+TWO OFFSETTING FORCES NOT IN THE 300,000: upward, de-minimis-era merchants who never held an IOR must now obtain one, expanding the pool (FY2024 saw 1.36B de minimis parcels). Downward, CBP has already certified 12 qualified parties to collect duties on international mail — Zonos, Flexport, BoxC, SafePackage, Evolve and others — who intermediate a large share of that flow, meaning the merchant never becomes your account.
+SUPPLY SIDE (the moat's actual size): approximately 11,000-11,400 active individual and corporate customs broker licenses in the US per CBP records, confirmed via the early-2026 triennial status reports under 19 CFR 111.30. That is a real constraint but a looser one than "12-22% pass rate" rhetoric implies — 11,400 licensees against 300,000 importers is roughly one broker per 26 importers.</t>
+        </is>
+      </c>
+      <c r="J5" s="53" t="inlineStr">
+        <is>
+          <t>ENTRY FILING (product one's market):
+- Informal entries (under $2,500 — exactly the ET13 band): $75-$150 in broker fees. Source: customsbrokerindex.com.
+- Flat fees range $40-$200 per entry, add-ons $25-$100, and "most brokers have a minimum entry fee of $125-$200 regardless of shipment value." That minimum is the real floor the record is trying to undercut.
+- Formal entry benchmark: Greenwich Mercantile publishes "$100-$250 Per Entry" as the 2026 US customs brokerage range.
+- Section 321 / de minimis-style simple entries: "$35-$65 in broker fees" — the closest true substitute for the record's target work, and notably the CHEAPEST tier in the market.
+- Government fees stack on top and are not compressible: MPF on informal entries is $2.69 / $8.06 / $12.09 per shipment depending on tier, with more recent figures of $9.06 automated / $34.69 manual.
+READ ON THE RECORD'S $15/ENTRY: the record claims incumbents charge "$50-100" and proposes "$15/entry." The incumbent band is actually higher than the record thinks for informal entries ($75-150, with $125-200 minimums), which widens the nominal discount — but $15 sits BELOW the manual MPF ($34.69) and below the cheapest existing substitute tier ($35-65). Nobody in the sourced market clears an entry for $15, which is evidence about cost-to-serve, not about incumbent laziness.
+DUTY RECOVERY (product two's market):
+- Contingency: "10-25% of the recovered duty amount"; more precisely "most traditional brokers charge a contingency (15-25% of recovered duties)."
+- Flat alternative ALREADY OFFERED: "a flat project fee ranging from $1,500 to $10,000+ depending on claim complexity and volume."
+- Alliance Drawback Services: contingency-based, percentage of amount recovered, no upfront cost.
+- Zollback (venture-backed entrant) claims recovery of 15-20% more than traditional providers in 10-15 working days versus the incumbent 9-12 months — competing on speed and yield, not on the flat-vs-contingency axis the record picked.
+- Adjacent premium anchor the record cites and I could not independently source: "$800/hour trade-attorney time" for instrument-aware planning. Treat as unsourced.</t>
+        </is>
+      </c>
+      <c r="K5" s="60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L5" s="53" t="inlineStr">
+        <is>
+          <t>The MARKET is real and the regulatory clock verifies better than the scout dared hope. The SPECIFIC OPPORTUNITY as written does not survive sourcing.
+WHAT SURVIVES, AND IT IS NOT NOTHING: the statutory spine is exactly as durable as claimed — OBBBA removes the commercial de minimis exception from 19 USC 1321 effective 1 July 2027 and no executive action reverses that. ET13 is real, dated 22 September 2026 for PROD, and restricts filing to owners, purchasers, or designated licensed brokers, which is a genuine license-gated channel. The scout's two self-flagged doubts both check out precisely: SCOTUS 6-3 on 20 February 2026, CAPE at 75,300 declarations over 11.2M entries by 26 April. And there is a tailwind the record never saw — Section 122's expiry on 24 July 2026 into Section 301 duties of 10-12.5% covering ~99% of US imports moves the entire baseline tariff wall into a drawback-ELIGIBLE instrument.
+WHY IT STILL FAILS, IN ORDER OF SEVERITY:
+1. The differentiating claim is false. "Nobody has attacked the broker-capacity bottleneck itself, which is the actual scarce asset, because investors read 'customs brokerage' as a low-margin services business." First Round Capital and Pear VC read it correctly and funded Amari AI in February 2026; Primary Venture Partners funded Caspian. The premise that sophisticated investors are mispricing this sector is empirically wrong, and it was the entire why_overlooked.
+2. ACV is roughly half, and the record cannot fix it without abandoning its own positioning. Sourced CBP data puts the population MEAN at ~101 entries per importer per year against the record's assumed 350. The record's own key_sensitivity says "If it is 100, the unit economics collapse exactly the way the kill_risk predicts." The evidence returned 101. Reaching $8,000 ACV requires pricing at ~$50/entry, which discards "well under the incumbent $50-100" — the product's whole reason to exist.
+3. Product two's wedge is aimed at a phantom. Incumbent drawback contingency is 15-25%, not 50/50, and flat project fees of $1,500-$10,000 are already sold. "Priced flat, which is the obvious wedge against 50/50 contingency incumbents" is a wedge against a price nobody charges. Zollback meanwhile competes on speed (10-15 days vs 9-12 months) and yield, axes the record never considered.
+4. ET13's scope is mail, not general low-value freight — so the day-one integration play does not serve the Shopify merchant importing a pallet, and the twelve CBP-certified parties already hold the mail flow.
+5. The moat argument is weakening as it is being made. Instrument-aware reasoning was pitched as the durable LLM-native edge, but the instrument landscape just CONSOLIDATED into one dominant Section 301 regime covering 99% of imports plus a stable Section 232 carve-out. Per-SKU-per-instrument reasoning is getting simpler, and CBP HQ Ruling H350722 pushes the valuable part of it behind a license — which favours the eleven thousand existing licensees and the funded entrants who already bought one, not a new team hiring a broker as co-founder.
+6. Timing is against a 90-day plan with 8 months to first revenue. CAPE has already sent ~$86.3B to Treasury and is narrowing eligible entry types. ET13 CERT opened 24 July 2026. The de minimis bridge to July 2027 rests on a 23 June 2026 PROPOSED rule under live challenge at the CIT.
+WHAT A HONEST REVISION WOULD LOOK LIKE: not entry-as-a-service for the SMB long tail — that is contested by Zonos with a licensed brokerage and by twelve CBP-certified parties. The residual defensible position is narrower and less venture-shaped: buy or partner with an existing licensed brokerage rather than build one, target the ~$5-50M mid-market importer where 101 entries/year and a $4,000-10,000 flat drawback engagement actually clear cost-to-serve, and price entries near the real $75-150 informal band rather than at $15. That is a good services business with software leverage. It is not the compounding regulatory moat that earned this idea rank 2, and it should not draw the $550,000 of pre-revenue capital the model calls for on the strength of a why_overlooked that live search contradicts outright.</t>
+        </is>
+      </c>
+      <c r="M5" s="52" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" ht="150" customHeight="1">
+      <c r="A6" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="47" t="inlineStr">
+        <is>
+          <t>NQA-1 qualification and commercial grade dedication as a service</t>
+        </is>
+      </c>
+      <c r="C6" s="46" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="D6" s="47" t="inlineStr">
+        <is>
+          <t>The central trigger is REAL and the record's quote is verbatim accurate — which is notable because the record's own screening said "The 23 Mar 2026 NSI report could not be verified." It is verified. The Nuclear Scaling Initiative's "Landscape of U.S. Domestic Advanced Nuclear Energy Supply Chain" exists, was published March 2026 (PDF hosted at nuclearscaling.org/wp-content/uploads/2026/03/), was prepared by consultancy Solestiss with support from the Bezos Earth Fund, and is built on interviews with 40+ industry stakeholders. ANS/Nuclear Newswire covered it on 23 March 2026 at exactly the cited URL. The NQA-1 language quoted in the record checks out: "Strict quality standards, including NQA-1, narrow the supplier base and slow expansion, and without more efficient, repeatable approval pathways, growing the domestic industrial base will remain difficult." The report also confirms the surrounding claims: "a self-reinforcing cycle of market paralysis — in which suppliers hesitate to invest without firm demand signals and buyers hesitate to commit without supply chain certainty"; bottlenecks "increasingly downstream in machining, welding, finishing, inspection, and non-destructive examination, requiring nuclear-qualified facilities"; and workforce gaps in "nuclear-qualified machinists, welders, inspectors, non-destructive examination specialists." NuclearNet (3 Feb 2026) and Neutron Bytes (20 Mar 2026) corroborate independently. IMPORTANT NUANCE ON WHAT BINDS WHOM: the trigger is a think-tank diagnosis, not a regulation with a compliance date. Nothing in it compels any shop to buy anything. The actual binding instruments are 10 CFR 50 Appendix B and 10 CFR Part 21, which are decades old and unchanged — there is no new deadline, docket, or enforcement date creating 2026 urgency. The record's framing implies a clock; the evidence shows a structural condition. Also note the report's headline RECOMMENDATION cuts against the startup's premise: it recommends "repeated deployment of Gen III+ reactor designs" and "simplifying supply chains to tap into the traditional nuclear business' existing materials and know-how" — i.e. route work to already-qualified incumbent suppliers, which shrinks rather than grows the population of shops needing a fresh Appendix B install. The naval-side trigger is real but STALE (see corrections): the BlueForge award is dated 10 September 2024, not 2025-2026.</t>
+        </is>
+      </c>
+      <c r="E6" s="46" t="inlineStr">
+        <is>
+          <t>contested</t>
+        </is>
+      </c>
+      <c r="F6" s="47" t="inlineStr">
+        <is>
+          <t>Forged Operations Inc (forgedops.com) — THE DIRECT SOFTWARE COMPETITOR THE RECORD MISSED WHILE CITING ITS WEBSITE AS EVIDENCE. Tagline: 'The Operating System for Nuclear Quality.' Product OpsAssist provides real-time compliance dashboards against ASME NQA-1 and CSA N299, manages 'the full supplier qualification lifecycle, including initial qualification, QSL maintenance, re-evaluation scheduling, surveillance tracking, and NCR linkage,' plus 'pre-award surveys, source inspection scheduling, CoC tracking, and receipt inspection records,' with AI-driven work package validation and documentation-gap flagging. Funding: ~$100K raised per Crunchbase-sourced extract; investors Forum Ventures and Right Side Capital Management; also listed by F4 Fund as an enterprise software portfolio company; has a PitchBook profile and an AI Hub (Canada) success-story writeup. STAGE: pre-seed/very early — so the record's software thesis is not dead, but the claim that the category is vendorless is false and the first mover is already shipping.
+Curtiss-Wright Nuclear / Scientech Division — explicit third-party dedicating entity offering commercial grade dedication; 30+ years supplying products, services and software to the global power industry; also sells Nuclear Regulatory Services and compliance software (ssis.scientech.us). The record named this risk; it is confirmed and it spans BOTH the services and the software layer the startup wants.
+Paragon Energy Solutions (paragones.com) — 'performs in-house testing and commercial grade dedication to the highest standards'; largest US CGD house per the record, confirmed as an active provider.
+Westinghouse Nuclear — publishes a Commercial Grade Dedication service data sheet; incumbent dedicating entity.
+Kinectrics — dedicated Commercial Grade Dedication service line under materials/nuclear component testing.
+Constellation PowerLabs — Commercial Grade Dedication Testing Services with public 'Free Quote' funnel, plus Appendix B calibrations as a nuclear-approved supplier. A utility-affiliated entrant selling dedication to third parties.
+Joseph Oat Corporation — CGD offered as a named quality-assurance service line.
+Dupill Group — Commercial Grade Dedication service provider.
+Jets Quality Consultants — Commercial Grade Dedication Workshop at $995/person (6-12 attendees); the training substitute for the record's 'guided Method 1-4 workflow.'
+NAC International — NQA-1 consulting: lead auditors 'support and train emergent Nuclear Safety-related Quality Assurance suppliers, and established suppliers expanding their offerings,' developing QA programs meeting 10 CFR 50 App B, ANSI N45.2 and NQA-1. This is the record's product one, sold today.
+Strata-G — 'develops, implements, and manages quality assurance programs' for nuclear operations.
+Global Quality Assurance (globalqualityassurance.com) — 'development and implementation of NQA-1 and 10CFR50 Appendix B nuclear quality programs, developing a timeline for program design with milestones.' Verbatim the record's readiness sprint.
+Enhance Quality Services (enhancequality.com) — NQA-1:2022 training and implementation.
+Tennessee MEP (tmep.cis.tennessee.edu) — FEDERALLY SUBSIDIZED COMPETITOR IN THE RECORD'S OWN BEACHHEAD STATE. Runs an NQA-1 program to 'build NQA-1-compliant quality programs to enter and sustain work in the nuclear supply chain,' with a 'no cost Gemba walk to start.'
+Catalyst Connection (Pittsburgh MEP) — published 'NQA-1 EXPLAINED: NUCLEAR QUALITY MANAGEMENT' whitepaper, January 2026; same subsidized model, adjacent geography.
+BlueForge Alliance — $950,744,520 sole-source NAVSEA prime contract (Sept 2024, options to ~$980M) to do supplier qualification and supply-chain diversification for the submarine industrial base. Federally funded quasi-competitor that the record also names as its channel.
+iBASEt / Solumina — manufacturing operations management platform explicitly marketed to nuclear for regulatory compliance and quality management; an incumbent MES vendor that can add supplier-qualification workflow as a feature.
+Nuclearn — nuclear AI/automation platform, $10.5M Series A in 2025, 'automates repetitive and compliance-heavy processes unique to nuclear facilities' including documentation and reporting. Adjacent, better funded, one product decision away.
+EPRI — owns the critical-characteristics methodology as a member good (ant.epri.com supply chain program); the structural reason a cross-buyer CC library may never be a startup's to own.
+NUPIC / NIAC — incumbent shared-audit utilities (NUPIC ~93 assessments/yr; NIAC 170+ members globally) that already perform the reuse function the startup proposes to sell.</t>
+        </is>
+      </c>
+      <c r="G6" s="47" t="inlineStr">
+        <is>
+          <t>Split verdict by layer, and both layers are worse than the record assumed. SERVICES LAYER: crowded, decisively. Third-party commercial grade dedication is an established service business with at least eight named providers found in a handful of searches — Curtiss-Wright/Scientech, Paragon, Westinghouse, Kinectrics, Constellation PowerLabs, Joseph Oat, Dupill Group — several with public quote funnels. NQA-1 readiness consulting is equally populated: NAC International, Strata-G, Global Quality Assurance and Enhance Quality Services all describe the record's 'product one' almost verbatim. Worse, two NIST MEP centers (Tennessee, and Catalyst Connection in Pittsburgh) deliver the same onboarding under federal cost-share with a free entry engagement, in and adjacent to the exact states the record names as its beachhead. Competing against a subsidized incumbent for a speculative six-figure purchase is the hardest possible opening position. SOFTWARE LAYER: contested, not empty — this is the finding that changes the record. The screening explicitly bet that 'the claim no vendor is wrong at the services layer but survives at the software layer: nobody has productized guided Method 1-4 dedication with a cross-buyer reusable CC library.' Forged Operations has productized the surrounding workflow and is selling it: NQA-1 and CSA N299 compliance dashboards, full supplier qualification lifecycle, QSL maintenance, pre-award surveys, source inspection scheduling, CoC and receipt-inspection records, with AI documentation-gap detection. It is very early (~$100K raised, Forum Ventures and Right Side Capital) so the category is not closed — but 'no vendor' is false, and the startup would now be second, not first, with a competitor already indexing the practitioner vocabulary well enough that this record's own scouts used its glossary as a primary source. Add two adjacent platforms that could absorb the feature — iBASEt/Solumina already sells nuclear compliance MES, and Nuclearn raised $10.5M Series A for nuclear compliance automation — plus Curtiss-Wright/Scientech, which sells regulatory compliance software AND holds the dedicating-entity audit history, and the 'incumbent ships it as a feature next quarter' risk is concrete rather than theoretical. Not yet 'crowded' at the software layer because no one has raised real money against it and the CC-library reuse problem remains genuinely unsolved; firmly 'contested' because the empty-category premise is gone.</t>
+        </is>
+      </c>
+      <c r="H6" s="65" t="n">
+        <v>350</v>
+      </c>
+      <c r="I6" s="47" t="inlineStr">
+        <is>
+          <t>DERIVATION FROM FOUND COUNTS, bounded rather than precise. Anchor 1 (qualified manufacturers): "In the 1970s and 1980s, about 500 U.S. companies held nuclear stamps, but today only about 100 do" (Power Engineering, corroborated by Sandia's N-stamp trends study). ASME N-stamp is Section III component certification, adjacent to but not identical with an Appendix B/NQA-1 QA program, so treat ~100 as the count of fully code-qualified US nuclear manufacturers. Anchor 2 (audited supplier pool): NUPIC performs ~93 joint utility assessments/year including 80 joint audits; against the roughly 3-year (record says 33-month) audit cycle that implies a standing audited pool of ~220-280 suppliers. Anchor 3 (trade-body membership): NIAC has "more than one hundred seventy (170) members globally" and Nuclear Suppliers Organization is "approximately 60 companies" — both consistent with a low-hundreds population, not thousands. Anchor 4 (CGD-side buyers): ~20 US operating-plant owner/operators plus 10-15 serious advanced-reactor developers, i.e. ~30-35 high-value accounts. SYNTHESIS: the already-qualified population that buys CGD and re-audit services is ~250-300 firms. The un-qualified aspirant population that would buy an Appendix B install is genuinely uncounted in any public source — MEP centers are recruiting it from the general precision-manufacturer base — so I bound it at 100-300 firms plausibly chasing nuclear work in a given cycle, with heavy overlap onto the audited pool. Total realistic buying universe: 300-500, midpoint ~350. NOT 1,200. The record reached 1,200 by taking 15% of the ~5,000-firm SUBMARINE supplier base (~750) and adding commercial-nuclear entrants — but naval suppliers qualify to NAVSEA/NAVSEA-prime requirements, not 10 CFR 50 App B, and their qualification is already funded through BlueForge's $951M federal contract. That ~750 is not an Appendix B buyer universe and should be struck. Marked as estimate: no public register of Appendix B program holders exists (searches confirmed the NRC publishes no such total; qualified-supplier lists are maintained privately by each licensee).</t>
+        </is>
+      </c>
+      <c r="J6" s="47" t="inlineStr">
+        <is>
+          <t>HONEST HEADLINE: this market does not publish prices, and the two real prices I could find are both far below the record's anchor. WHAT I FOUND WITH ACTUAL NUMBERS: (1) Jets Quality Consultants sells a Commercial Grade Dedication Workshop at $995.00 per person, minimum 6 and maximum 12 attendees — i.e. $5,970-$11,940 per delivered engagement for the training substitute (https://jetsquality.com/commercial-grade-dedication-workshop/). (2) Tennessee MEP prices the front of the NQA-1 funnel at ZERO — "no cost Gemba walk to start" — as part of a federally cost-shared program that "helps manufacturers build NQA-1-compliant quality programs to enter and sustain work in the nuclear supply chain" (https://tmep.cis.tennessee.edu/nqa-1). A subsidized $0 on-ramp in the record's own beachhead state is the single most important pricing fact here. (3) LABOR COST FLOOR, the only defensible way to build an ACV: NQA-1 Lead Auditor compensation is posted at $117,000-$125,000 for North Carolina roles, with the broader market at $80k-$132k (https://www.ziprecruiter.com/Jobs/Temp-Nqa-1-Lead-Auditor). Fully loaded with travel and benefits that is roughly $170-200k/yr, or ~$800-1,000/day at the record's own 60-65% billability assumption. A readiness sprint delivering a QA manual, procedure set and mock audit is realistically 8-14 auditor-weeks, i.e. $40k-$70k of delivered labor — supporting a $60-110k price only if the buyer has no subsidized alternative, which in Tennessee they do. WHAT NOBODY PUBLISHES: every CGD and NQA-1 provider found quotes per-project on request — Kinectrics, Constellation PowerLabs ("Free Quote"), Westinghouse, Dupill Group, Joseph Oat, NAC International, Strata-G, Global Quality Assurance, Enhance Quality Services. DOE's own handbook (DOE-HDBK-1230-2019) instructs that "an estimate of the cost to perform the CGD process should be completed prior to initiating it, so that cost-effectiveness of pursuing CGD versus buying from a supplier with an ASME NQA-1 program can be determined" — meaning CGD pricing is explicitly disciplined by the make-vs-buy alternative and cannot drift upward. This caps per-lot dedication fees at the delta between a commercial part and its qualified equivalent, which is exactly the ceiling the record's $8-25k/package estimate ignores. No source was found for ASME's NQA-1 certification survey fee.</t>
+        </is>
+      </c>
+      <c r="K6" s="55" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L6" s="47" t="inlineStr">
+        <is>
+          <t>STANDS AS THE CONSULTANCY THE SCREENER ALREADY SAID IT WAS; DOES NOT STAND AS THE SOFTWARE THESIS THAT EARNED IT RANK 3. What survives, and it is not nothing: the bottleneck is real and independently documented at the exact URL cited, in the exact words quoted — NQA-1 'narrows the supplier base and slows expansion' and the industry lacks 'more efficient, repeatable approval pathways.' The demand side is confirmed (400 GW by 2050 target from the May 2025 EOs; $951M obligated to BlueForge; submarine base contracted from ~17,000 to ~5,000). Qualification genuinely gates revenue, incumbents genuinely bill hourly, and a three-person firm with an ex-NUPIC lead auditor can build a profitable services business here. The record's own downside case — ~20 accounts, $1.6-1.8M revenue, a viable consultancy — is now the BASE case, not the downside. WHAT BREAKS: (1) The differentiating claim is falsified. why_overlooked's 'no vendor' and the screening's 'survives at the software layer' both fail against Forged Operations, which sells NQA-1/CSA N299 supplier-qualification software today — and which the record cited as a source four times without recognizing it as a company. A diligence process that scrapes the competitor's glossary to define the market it thinks is empty has an evidence-quality problem, not just a fact error. (2) The beachhead is subsidized. Tennessee MEP offers the readiness-sprint value proposition with a free on-ramp under federal cost-share, in the first state named in the go-to-market. (3) The universe is 3-10x smaller than modeled: ~100 US nuclear-stamped manufacturers, ~250-300 in the audited supplier pool, versus 1,200 claimed — and 750 of that 1,200 came from the naval base, which qualifies to NAVSEA rather than Appendix B and is already funded through BlueForge. Y5 of 65 accounts was framed as 5% of the universe; against ~350 it is 19%, a market-share assumption, not a penetration assumption. (4) The ACV has no external support at $95k and I can only defend ~$60k. (5) The trigger, while real, is a think-tank diagnosis with no compliance date — and its headline recommendation (deploy repeat Gen III+ designs, 'simplify supply chains to tap into the traditional nuclear business' existing materials and know-how') points work toward already-qualified incumbents, which shrinks the aspirant population that is the startup's primary customer. NET: a real business against a real constraint, with the venture case removed. Rank 3 was awarded substantially on 'no vendor at the software layer.' That premise is gone, and the record should be re-ranked accordingly.</t>
+        </is>
+      </c>
+      <c r="M6" s="46" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" ht="150" customHeight="1">
+      <c r="A7" s="52" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="53" t="inlineStr">
+        <is>
+          <t>PFAS-Compliant Biosolids Outlet Exchange for the Mid-Atlantic</t>
+        </is>
+      </c>
+      <c r="C7" s="52" t="inlineStr">
+        <is>
+          <t>partly-confirmed</t>
+        </is>
+      </c>
+      <c r="D7" s="53" t="inlineStr">
+        <is>
+          <t>The DATES are all real; the BITE is much weaker than the record claims, and the record missed the one Mid-Atlantic rule that binds earliest.
+CONFIRMED: Maryland SB 719 was signed 28 April 2026. It "prohibits land application of biosolids with a concentration of PFOA, PFOS, or a combination thereof equal to or greater than 50 ppb on or after October 1, 2028," with a 25-50 ppb restricted tier capped at "three dry metric tons per acre and subject to Class B biosolids setback requirements," plus notice to the landowner and local government. It also directs MDE to strengthen industrial pretreatment. All exactly as recorded.
+BUT THE TRIGGER LARGELY DOES NOT BIND: Maryland's law "is drawing criticism from environmental and public health advocates who say the thresholds are set high enough that most wastewater plants in the state already meet them." MDE's own August 2024 recommendation, based on "comprehensive data from in-state and out-of-state biosolids sources," was to stop land application only at 100 ppb or above — i.e. the regulator's read of the actual data was that the problem sits well above 50 ppb. MDE also reports that "most affected systems already meet the quarterly testing frequency mandated under the bill." A ban that most of the regulated population already clears displaces little tonnage, which is the entire mechanism of this business.
+EPA GUIDANCE IS VOLUNTARY AND STILL DRAFT: The 1 July 2026 memorandum "provides voluntary recommendations" and EPA states it "does not have the force and effect of law, nor does it bind the public in any way." It is in a 60-day comment period closing 4 September 2026 under Docket EPA-HQ-OW-2026-2509, with listening sessions 12 and 18 August 2026. Federal Register publication was 6 July 2026. As of today it is a request for feedback, not a push.
+PENNSYLVANIA IS LOOSER, NOT PARALLEL: DEP published draft general permits PAG-07 and PAG-08 in the Pennsylvania Bulletin on 4 July 2026, comments open until 2 September 2026. The proposed prohibition is at 100 µg/kg PFOA or PFOS — twice as permissive as Maryland's 50 ppb — with a reduced application rate and source reduction plan required at 20 µg/kg. Still draft as of August 2026.
+VIRGINIA IS THE REAL MID-ATLANTIC CLOCK AND THE RECORD OMITS IT: HB 1443 (Chapter 853), signed April 2026, requires representative sampling by any sewage treatment works that land applies, markets or distributes biosolids starting 1 January 2027, and prohibits land application where the rolling 12-month average of PFOS or PFOA reaches or exceeds 50 ppb. That binds 21 months before Maryland's October 2028 date.
+MAINE PRECEDENT CONFIRMED WITH NUMBERS: LD 1911 banned land application of biosolids and sale of sludge-derived compost. A Maine facility's Casella base rate was $82.46 per wet ton with an additional $39.75 per wet ton imposed 8 August 2022 "due to impacts of LD 1911." Companion LD 1639 cut the imported C&amp;D bulking agent at Juniper Ridge by 14 percent while sludge deliveries rose 15 percent monthly, producing the 2023 municipal "crisis" coverage. The mechanism did run once for real, as claimed.</t>
+        </is>
+      </c>
+      <c r="E7" s="52" t="inlineStr">
+        <is>
+          <t>contested</t>
+        </is>
+      </c>
+      <c r="F7" s="53" t="inlineStr">
+        <is>
+          <t>Synagro Technologies — largest US biosolids manager, Baltimore-headquartered (i.e. sited in the exact target region), Goldman Sachs infrastructure-backed. Acquired Denali's California municipal biosolids business in the August 2024 asset transfer. Under active PFAS pressure: defending litigation tied to Johnson County, Kansas, and Fort Worth terminated a 10-year contract covering 26,500 tons/yr of fertilizer over PFAS concerns.
+Denali Water Solutions — PE-backed (PitchBook-tracked); took Synagro's industrial non-biosolids organics assets in Arkansas and Missouri in the 2024 swap. Holds municipal land-application contracts including the Johnson County KS award the record cites.
+Veolia North America — 'Biosolids &amp; Residuals Management' line offering full DBOM/F contracts, Class A solutions, and marketing/sales/distribution of EQ compost, dried pellets and fertilizer, managing thousands of dry tons into agricultural land. Delivers the record's exact outcome bundled with operations.
+Agri-Sludge, Inc. — in the biosolids management business since 1977, explicitly advertising 'full-service biosolids solutions from land application to landfilling, with the equipment, expertise, and permits.' This is the record's proposition with trucks and permits attached.
+Casella Waste Systems — controls the Northeast landfill outlet (Juniper Ridge) and set the post-LD 1911 surcharge; the outlet owner, not a broker, and can price the intermediary out.
+Midwest Injection Inc. — transport and disposal of sludge, biosolids and wastewater product.
+US Submergent (USST) — comprehensive biosolids management services.
+Merrell Bros. — full-service biosolids management (named in the record, not independently re-verified this pass).
+AMCS BrokerCloud — enterprise waste brokerage platform with a digital marketplace connecting generators, haulers and processors, offering real-time spot pricing, contract management and compliance tracking. This is the record's 'exchange' shape, already built, one vertical away.
+Rubicon Technologies — digital waste marketplace connecting generators, brokers, haulers and disposal facilities with automated RFPs, real-time bidding and AI-driven matching to cost-effective disposal options.
+Wastebits — real-time connection of waste generators, haulers and disposal facilities with transparency across the chain; publishes on waste brokerage technology.
+Retrans — waste broker platform for load matching, dispatch and billing.
+WastePlace — waste hauler software/marketplace.
+Bulk Exchange — San Rafael-based online materials hauling marketplace, part of an emerging 'materials hauling marketplace' product category.
+Hazen and Sawyer — dedicated Biosolids and Residuals practice covering the full sludge value chain; incumbent on the source-control/pretreatment product.
+Brown and Caldwell, CDM Smith, EA Engineering — same consulting layer (named in the record, not re-verified this pass).
+Battelle — publishing practitioner guidance on managing PFAS in biosolids and sewage sludge, positioning into the same advisory slot.
+Maryland Environmental Service — state-affiliated biosolids management provider operating inside the target state.
+Bluefield Research — owns the analytical/market-intelligence position on biosolids spend.
+30+ active PE roll-up platforms in water/wastewater services tracked as of 2026 — consolidation capital is actively acquiring in this exact services layer, which both raises acquisition odds and shortens the window before a funded roll-up bundles this.</t>
+        </is>
+      </c>
+      <c r="G7" s="53" t="inlineStr">
+        <is>
+          <t>The record's crowding_check was right that no dedicated biosolids capacity exchange exists — I could not find one either, across three differently-worded query framings using practitioner language ('residuals management', 'sludge disposal broker', 'biosolids broker ... spot market'). But 'unbuilt' and 'uncontested' are different claims, and this is contested on three independent fronts the record either understates or misses.
+FRONT ONE — THE OUTCOME IS ALREADY SOLD. Agri-Sludge has been doing exactly this since 1977 and markets 'full-service biosolids solutions from land application to landfilling, with the equipment, expertise, and permits.' Veolia sells full DBOM/F contracts plus marketing and distribution of the end product. Synagro is the largest US biosolids manager and is headquartered in Baltimore, inside the target region. A utility director choosing between a two-person broker's compliance binder and a bonded firm with trucks and permits is not facing a hard choice.
+FRONT TWO — THE EXCHANGE SOFTWARE ALREADY EXISTS ONE VERTICAL OVER. This is the check the record never ran. AMCS BrokerCloud already provides a digital marketplace connecting generators, haulers and processors with real-time spot pricing, contract management and compliance tracking. Rubicon runs automated RFPs, real-time bidding and matching to disposal options. Wastebits, Retrans, WastePlace and Bulk Exchange occupy the same layer. None is biosolids-specific today, which is precisely the problem: adding a biosolids vertical with a PFAS-threshold field is a feature release for them, not a company. The record's defensibility concern was 'Synagro can price-match'; the sharper risk is that AMCS ships the matching layer.
+FRONT THREE — THE STICKY SECOND PRODUCT IS THE MOST CROWDED PART. Industrial source control is the incumbent consulting engineers' home turf — Hazen and Sawyer runs a dedicated Biosolids and Residuals practice spanning the full sludge value chain, and Battelle is publishing directly into 'Managing PFAS in Biosolids and Sewage Sludge.' Maryland Environmental Service serves the target state as a state-affiliated provider. Notably, EPA's July 2026 draft guidance pushing source identification will be read and operationalized by exactly these firms, who already hold the utility relationship.
+FOURTH SIGNAL: 30+ active PE roll-up platforms in water/wastewater services are tracked as of 2026. Capital is consolidating this services layer now, which compresses the window in which an unbonded regional broker can accumulate referenceable tonnage.
+Not 'crowded' — nobody sells the specific exchange. Firmly 'contested' — every component is owned by someone with more assets, more capital, or the customer relationship already.</t>
+        </is>
+      </c>
+      <c r="H7" s="66" t="n">
+        <v>220</v>
+      </c>
+      <c r="I7" s="53" t="inlineStr">
+        <is>
+          <t>Built bottom-up from two sourced state counts plus population scaling, then cross-checked top-down against the national figure.
+SOURCED COMPONENTS: (1) Virginia — the fiscal impact analysis for HB 1443 says the PFAS testing and 50 ppb prohibition "would impact about 60 wastewater treatment plants around the state." (2) Maryland — MDE reports "about 50 biosolids generators are submitting PFAS testing data," consistent with Maryland's 595,000 wet tons of biosolids produced in 2023 and ~120,000 tons land applied annually.
+ESTIMATED COMPONENTS: Pennsylvania and Delaware have no published affected-facility count I could source. Scaling Maryland's ratio (50 generators / 6.2M residents ≈ 8 per million) and Virginia's (60 / 8.8M ≈ 6.8 per million) to Pennsylvania (13.0M) gives ~90-105, and to Delaware (1.0M) gives ~7-8. Taking the midpoint: PA ~100, DE ~8.
+TOTAL: 50 (MD, sourced) + 60 (VA, sourced) + ~100 (PA, estimated) + ~8 (DE, estimated) ≈ 220 biosolids-generating entities across the four Mid-Atlantic states.
+TOP-DOWN CROSS-CHECK: EPA collects biosolids annual reports from roughly 2,500 larger plants nationally — those serving 10,000+ people, major POTWs at design flow ≥1 MGD, and Class 1 facilities. MD+PA+VA+DE is ~29M of ~335M US residents, or 8.7%, implying ~217 such facilities. The two methods agree at ~220, which is why I report that figure rather than a range.
+NARROWER SET THE RECORD ACTUALLY TARGETS: the buyer is defined as a 10-25 MGD authority. That is a minority of the 220 — most biosolids generators are far smaller. My judgment is 60-100 of the 220 are large enough to run a competitive per-wet-ton procurement with board approval, and fewer still sit in a state where a threshold currently binds. I report 220 as the outer universe and flag that the serviceable set is likely under 100.</t>
+        </is>
+      </c>
+      <c r="J7" s="53" t="inlineStr">
+        <is>
+          <t>Real, named prices found — and they broadly validate the record's recalled per-ton range while undercutting its take rate.
+BASELINE ALL-IN COST: Tipping fees run $30-80 per wet ton depending on region, with hauling adding $15-40 per wet ton depending on distance, for a total of $45-120 per wet ton (Toolgrit sludge cost guide). The record's recalled "$60-90/wet ton" sits inside this, so that input was roughly right.
+MAINE, POST-BAN, WITH NAMED COUNTERPARTY: A Maine wastewater facility's base rate to Casella was $82.46 per wet ton, with an additional $39.75 per wet ton surcharge imposed as of 8 August 2022 explicitly "due to impacts of LD 1911" — a delivered price of $122.21 per wet ton, a 48% step-up attributable to the ban. This is the single best-documented instance of the price move the business is betting on.
+CONCORD, NEW HAMPSHIRE: beginning 1 July 2020 a city of ~44,000 "began paying 3.5 times as much per wet ton — meaning a total of $600,000 more per year — for managing biosolids" after losing its beneficial reuse outlet. Implies prior annual spend ~$240k and new spend ~$840k for a small city.
+GENERAL PFAS EFFECT: NACWA/WEF/NEBRA find facilities that reverted to landfill after abandoning beneficial reuse are "burdened with management costs at least double what they used to pay."
+MARKET-LEVEL: Bluefield Research puts total US municipal biosolids management spend at $2.5 billion in 2025 rising to more than $4.8 billion annually by 2035; disposal costs have risen 3-5% annually for two decades and the trend is accelerating.
+LIVE PROCUREMENTS CONFIRM THE UNIT AND THE SCALE: City of Buckeye is seeking up to three contractors for biosolids disposal at estimated contract values of $500,000 to $2,000,000; Kennewick WA (RFB #P2609-26), Duvall WA (2026-2028), Irvine Ranch Water District and Dover Township PA all bid dewatering/hauling/land application on a per-wet-ton basis. No awarded per-ton unit price was retrievable — search returns titles only and I cannot open bid tabs.</t>
+        </is>
+      </c>
+      <c r="K7" s="60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L7" s="53" t="inlineStr">
+        <is>
+          <t>It does not stand as recorded. The sector distress is real, but all three load-bearing legs of this specific opportunity moved against it under sourcing.
+LEG ONE — THE TRIGGER LARGELY DOES NOT BIND. The record's ranking rests explicitly on Maryland SB 719 as 'the strongest-verified trigger in its batch.' The statute is real and dated exactly as claimed. But the law is being criticized because its thresholds 'are set high enough that most wastewater plants in the state already meet them,' and MDE's own data-driven recommendation was 100 ppb, double the enacted line. If most Maryland tonnage already clears 50 ppb, the October 2028 date does not displace the tons this business exists to re-route. Pennsylvania's draft sits at 100 ppb and is not final. EPA's July 2026 guidance is voluntary by its own text and still in comment until 4 September 2026. The one Mid-Atlantic rule that genuinely bites earliest — Virginia HB 1443, testing from January 2027 with a 50 ppb prohibition — is absent from the record entirely.
+LEG TWO — THE ARITHMETIC DOESN'T CLOSE. Buyer universe is ~220 rather than 900, and the serviceable 10-25 MGD subset is likely under 100. Sourced ACV is ~$120k, not $200k, because the 12-13% take rate has no comparable and the record itself concedes incumbents can price-match. Worse, the model is internally inconsistent: Y5 at 42 POTWs and ~$70M GMV would be roughly 30% of the entire ~$220M Mid-Atlantic annual biosolids spend implied by Bluefield's $2.5B national figure — for a firm with no trucks. Recomputed honestly, Y5 is maybe 20-25 authorities at ~$120k, or $2.4-3.0M revenue. That is the record's own downside_note, reached as the base case.
+LEG THREE — LIABILITY LANDS ON THE BROKER. The record treats PFAS liability as a background 'increasingly uninsurable' note. In fact Synagro is defending PFAS litigation over Johnson County, Kansas, and Fort Worth terminated a 10-year contract over PFAS. Directing tons onto farmland is now a litigated position. A two-person brokerage taking firm-price obligations to route material onto third-party fields is assuming that exposure with no balance sheet and no insurance market — a structurally worse risk position than the incumbent it is trying to undercut.
+WHAT SURVIVES. Three findings genuinely support a smaller business. Maine's price move is documented and large: $82.46 to $122.21 per wet ton, a 48% step-up explicitly attributed to LD 1911. Costs are rising structurally — 3-5% annually for two decades, accelerating, with national spend nearly doubling to $4.8B by 2035. And Virginia's January 2027 clock is real and closer than anything the record identified. That supports a regional PFAS-biosolids advisory practice — threshold interpretation, outlet contingency planning, source-control diligence, sold to the ~60 Virginia and ~50 Maryland generators facing testing regimes — as a few-million-dollar consultancy. It does not support a firm-price outlet exchange with a 900-buyer universe and a $200k retained ACV. The rank-4 placement was earned by a trigger whose bite the record could not check without live search; checked, the bite is much softer.</t>
+        </is>
+      </c>
+      <c r="M7" s="52" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" ht="150" customHeight="1">
+      <c r="A8" s="46" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="47" t="inlineStr">
+        <is>
+          <t>Reachability-grade SBOMs and kernel-CVE triage for embedded Linux</t>
+        </is>
+      </c>
+      <c r="C8" s="46" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="D8" s="47" t="inlineStr">
+        <is>
+          <t>The regulatory clock is real, dated, and un-slipped — this is the strongest part of the record.
+1) ART. 14 REPORTING, 11 SEP 2026 — CONFIRMED. European Commission: "the main obligations apply from 11 December 2027, with reporting obligations already applying as of 11 September 2026." Mechanics confirmed: "an early warning within 24 hours of becoming aware, and a full notification within 72 hours. A final report... no later than 14 days after a corrective measure is available for actively exploited vulnerabilities and within a month for severe incidents." The Single Reporting Platform "will be operational by 11 September 2026." Crowell &amp; Moring ran a "less than 100 days away" client alert in June 2026. Keysight confirms it binds "all manufacturers of products with digital elements shipped to the EU, including software, IoT devices, OT systems, medical equipment, networking gear, and embedded systems" — so it does bind the party the record names.
+2) NO DELAY FROM THE DIGITAL OMNIBUS — CHECKED EXPLICITLY. The Nov 2025 Digital Omnibus postponed AI Act high-risk deadlines (provisional political agreement 7 May 2026); it touched CRA only to consolidate multi-regulation incident reporting. No evidence of any postponement of the 11 Sep 2026 CRA reporting date. The record never flagged this risk; it turns out not to have materialised.
+3) NOTIFIED BODIES, 11 JUN 2026, ZERO DESIGNATED — CONFIRMED, with new detail the record missed: Art. 35(2) sets 11 Dec 2026 as the target for sufficient notified-body capacity, and "accreditation and designation of new bodies typically takes 12 to 18 months, which means the pool of CRA Notified Bodies will remain small well into 2027." Only 29 EUCC certs issued in year one.
+4) KERNEL CVE FLOOD — CONFIRMED BUT THE RECORD'S NUMBER IS WRONG (see corrections). The "~50/week unscored" line traces to a single blog (techveda). Observed 2026 volume is bursty and far larger: 763 kernel CVEs in the week 18-25 Jul 2026 (almost all in one batch on 25 Jul), 432 in a single day on 2026-07-19, ~440 across July per another tracker, versus only 3 in the week 11-18 Jul.
+5) BSI TR-03183-2 — REAL, v2.1.0, released 2025-08-20, still current as of Aug 2026. But BSI itself states the guideline "is not binding, cannot serve as a presumption of conformity, and will be replaced by harmonized European standards once those exist," and as of the July 2026 Commission guidance no harmonised standard has been adopted.
+6) NOT VERIFIED: the "LTS support contracted from six years to two" claim and the "vertical product standards requested for delivery by 30 October 2026" claim did not surface in searches. Treat both as unconfirmed.</t>
+        </is>
+      </c>
+      <c r="E8" s="46" t="inlineStr">
+        <is>
+          <t>crowded</t>
+        </is>
+      </c>
+      <c r="F8" s="47" t="inlineStr">
+        <is>
+          <t>Yocto Project (upstream, FREE) — improve_kernel_cve_report.py in the official security manual: filters kernel CVEs by SPDX_INCLUDE_COMPILED_SOURCES compiled-file analysis, 'reducing CVE false positives by 70%-80%', consumes and emits VEX, enriches from the Linux kernel CNA, runs outside BitBake. Upstreamed from Ericsson's 'Check compiled files to filter kernel CVEs' oe-core series (Daniel Turull, v3, Apr 2025). This IS the record's product, shipped in the build system the customer already uses.
+Exein (Rome) — €100M Dec 2025 led by Blue Cloud Ventures (HV Capital, Intrepid Growth, Geodesic Capital, J.P. Morgan); €170M total in 2025; ~€700M valuation; embedded hardware-agnostic security on 1.5B+ devices heading past 2B in Q1 2026; explicit multi-deal M&amp;A programme across Europe and the US in 2026; publishes CRA manufacturer guidance. ABSENT FROM THE RECORD.
+Lynx Software / Timesys Vigiles — SBOM lifecycle + config-aware CVE triage for edge/embedded, listed on Gartner Peer Insights as 'Lynx Vigiles'; also sells Embedded Linux LTS &amp; BSP Maintenance for 10+ year lifecycles. The record calls Timesys a boutique consultancy; it is a shipping product with a Gartner listing and a maintenance annuity business.
+Wind River — Wind River Linux: commercial Yocto-based, '10+ years support, proactive CVE monitoring, and compliance artifacts', standard support 10 years or longer; publishes an EU CRA FAQ; maintains meta-wr-sbom.
+Foundries.io (acquired by Qualcomm) — FoundriesFactory: subscription embedded Linux with continuous CVE remediation, $1/month/device falling to zero at 100k devices, free Community Edition, Professional and Production tiers.
+Cybellum (LG) — 'creates high fidelity SBOMs by merging binaries, source code and uploaded SBOM files, then auto-fixes, validates and manages the approval process across teams... manages and automates regulatory evidence creation for FDA PMA, ISO 21434, and CRA as well as custom policy frameworks.' Binary + source SBOM merge plus CRA evidence automation is the record's differentiated output, already shipping.
+ONEKEY — Product Cybersecurity &amp; Compliance Platform (OCP): automated firmware scanning, continuous firmware monitoring, plus a packaged 'Cyber Resilience Act Impact Assessment / CRA Readiness Assessment' offering.
+NetRise — binary-code software supply chain security; $24.8M raised over 3 rounds; ACQUIRED BY ACCENTURE.
+MedCrypt (Helm) — automatically generates single or multi-product compliance-ready CDX and SPDX SBOMs, VEX, VDR and vulnerability reports; also publishing on the 2026 CISA SBOM minimum-elements update.
+Black Duck — dedicated EU CRA vulnerability-reporting solution built around the 24-hour requirement; ships bd_scan_yocto_via_sbom.
+Tria Technologies — CVE Scanner, 'a vulnerability monitoring solution designed for embedded environments to support customers in meeting CRA requirements', delivered with Witekio for secure OS config, SBOM generation and long-term software maintenance. This is the record's exact wedge, already productised for embedded.
+Balena — dedicated CRA page; provides CVE data for OS images as part of vulnerability monitoring.
+RunSafe Security — publishing 'Preparing for the EU CRA: SBOMs for Embedded Software'.
+CRA Evidence (craevidence.com) — CRA Compliance Platform: SBOM, VEX and ENISA reporting, with published guidance on BSI TR-03183 SBOM quality levels and conformity-assessment routing.
+Interlynk — 'SBOM Requirements for the CRA: A Guide to BSI TR-03183' — i.e. already occupying the record's free-wedge positioning (TR-03183-2 scoring).
+Sbomify — EU CRA SBOM requirements compliance product.
+PrismorSec/product-sbom-vex (GitHub) — 'Last Mile EU CRA Compliance Tooling. Bring your own build SBOMs to generate product level SBOM and VEX based on CSAF 2.0.'
+Finite State — named as a NetRise competitor in the firmware/binary SBOM category.
+Keysight, Koan Software, Bootlin (meta-sbom-cve-check), savoirfairelinux (VulnScout) — services and OSS layers already occupying the embedded-CRA advisory niche.</t>
+        </is>
+      </c>
+      <c r="G8" s="47" t="inlineStr">
+        <is>
+          <t>The record graded this "thin on GitHub, crowded off-GitHub" and still under-called it on both axes.
+THE DIFFERENTIATOR IS FREE AND UPSTREAM. This is the finding that reorders everything. The record's why_overlooked rests on the claim that vendors "crowded into SBOM generation, storage and policy documentation and skipped both ends of the real work: the reachability decision." The Yocto Project did not skip it. improve_kernel_cve_report.py is documented in the official security manual, does compiled-file-granular kernel CVE filtering (strictly finer than the record's proposed .config/defconfig/driver-set granularity), claims 70-80% false-positive reduction, consumes and emits VEX, and pulls Linux kernel CNA metadata. It was contributed by Ericsson and merged upstream in 2025. A startup cannot charge $22k/family/year for a worse version of a script that ships with BitBake. The GitHub star-count evidence in the record (shipcheck 17, complira/yocto-sbom 3, BitVex 1) measured the wrong repositories entirely — the incumbent implementation is in oe-core, not in a standalone "yocto SBOM" repo.
+THE COMMERCIAL LANE IS ALSO FULL. At least seventeen named vendors ship overlapping product today. Two of them do the record's specific bundle: Cybellum "merges binaries, source code and uploaded SBOM files" and "automates regulatory evidence creation for... CRA" — that is binary SBOM extraction plus CRA technical-file assembly, the record's paid tier. Tria Technologies sells "CVE Scanner, a vulnerability monitoring solution designed for embedded environments to support customers in meeting CRA requirements," with Witekio attached for the BSP maintenance — that is the record's entire offering including the services wrapper. And the free wedge is taken twice over: Interlynk already publishes the BSI TR-03183 SBOM guide and CRA Evidence already publishes TR-03183 SBOM quality-level scoring.
+CAPITAL IS PRESENT, NOT ABSENT. Exein at €170M raised in 2025 and ~€700M valuation is not a fair fight for a two-person 90-day team, and it is explicitly deploying that capital on European and US acquisitions in 2026 — meaning any promising embedded-CRA startup is more likely an acquisition target than a category winner. NetRise already went to Accenture. This category is consolidating, which is the late phase, not the empty phase.
+THE RECORD'S OWN KILL_RISK WAS RIGHT AND IS NOW SOURCED. "Distribution is owned by whoever already ships the BSP" is confirmed by pricing: Wind River bundles "proactive CVE monitoring and compliance artifacts" into 10+ year Linux support; Lynx bundles triage into BSP maintenance at under half a junior engineer; Foundries/Qualcomm bundles continuous remediation and drives marginal device cost to zero. The record then modelled the base case as if bundling were a sensitivity rather than the observed status quo.
+The only genuinely thin spot found: no harmonised European standard exists yet, and zero notified bodies are designated. That is a real gap — but it is a gap in ASSESSMENT capacity, which is a services and lab business, not a SaaS one.</t>
+        </is>
+      </c>
+      <c r="H8" s="65" t="n">
+        <v>2210</v>
+      </c>
+      <c r="I8" s="47" t="inlineStr">
+        <is>
+          <t>Derivation, and it is a bound not a count. The record's unit is "makers of embedded-Linux devices with a Yocto/Buildroot/PetaLinux BSP, large enough to pay a per-device-family annual subscription." No authority publishes that. I found exactly one countable anchor: Landbase technology-adoption tracking reports 2,210 verified companies using Yocto as of 2026. I use that as the ceiling proxy for the Yocto slice and then adjust in both directions. UPWARD: it misses Buildroot- and PetaLinux-only shops entirely, misses private manufacturers whose stacks are not detectable by tech-tracking crawlers (most industrial and medical OEMs never expose a scannable surface), and misses firms shipping vendor BSPs unmodified. DOWNWARD, and harder: the 2,210 includes semiconductor vendors, BSP consultancies, tool vendors and cloud firms that are suppliers rather than buyers here; it includes firms too small to fund a subscription; and it includes every firm already inside a Wind River, Lynx, Qualcomm/Foundries or SoC-vendor bundle, which the record's own kill_risk identifies as the population that will never buy standalone. The two corrections do not cancel — the exclusions bite harder than the omissions, because the excluded groups are precisely the ones with existing coverage. Sanity check from the other side: the Yocto Project has only "30+ member companies," i.e. the population willing to pay dues to the ecosystem at all is two orders of magnitude below 2,210. I therefore report 2,210 as a sourced upper-bound proxy for the technical population and judge the PAYING universe materially lower — plausibly 700-1,500 firms globally — against the record's unsourced 6,000. No search returned a company count from the EU CRA impact assessment; that document quantifies cost (~€29bn compliance vs ~€290bn avoided incident cost), not firms, so the record's "tens of thousands of firms" recollection is also unanchored.</t>
+        </is>
+      </c>
+      <c r="J8" s="47" t="inlineStr">
+        <is>
+          <t>Four real anchors found, and they all sit below the record's ACV.
+1) LYNX / TIMESYS VIGILES — the direct incumbent. Lynx's own marketing claims Vigiles' "automation and filtering capabilities can reduce manual security tasks by 90%, with potential annual savings of up to $48,000 a year per SBOM." That is the incumbent's self-reported VALUE CEILING for the entire SBOM+CVE-triage function, and vendors do not understate their own ROI. List price is not published (subscription, tiered — SoftwareSuggest confirms tiered subscription with no public figures), but a rational buyer will not pay $55k for a product whose category leader claims $48k of annual savings.
+2) LYNX EMBEDDED LINUX LTS &amp; BSP MAINTENANCE — "less than 1/2 the cost of a junior engineer." At a $90-130k loaded junior embedded engineer, that is roughly $40-60k/yr, and it buys the whole BSP maintenance relationship including security updates for a 10+ year device lifecycle — not just the triage layer. This is the price the record's product must fit UNDER, as an add-on.
+3) FOUNDRIES.IO (QUALCOMM) FOUNDRIESFACTORY — the only publicly posted price in the category. "Device pricing starts at $1/month/device and decreases to zero with volume up to 100,000 devices," on top of a fixed monthly Professional/Production subscription including CI/CD seats and device blocks, plus a free Community Edition. A 10,000-unit fleet is ~$120k/yr but that is the entire platform — build, deploy, OTA, and continuous CVE remediation bundled. Per-device cost goes to ZERO at high volume, which is the exact opposite of the record's "annuity attached to hundreds of millions of shipped units" intuition: at scale, the bundled incumbent charges nothing marginal for this.
+4) BSP CONSULTING, ONE-TIME — Lynx: "Developing a BSP typically takes two to eight weeks, and if done as a consulting project costs between $20K to $100K." That is the services price for far more work than annual CVE triage.
+5) THE FLOOR IS $0. Yocto ships improve_kernel_cve_report.py upstream, and Foundries ships a free Community Edition. Any pricing model has to explain what the customer gets above free upstream tooling.
+Net: a standalone per-device-family triage subscription realistically clears at $10-25k, not $22k/family x 2.5 families = $55k. The record's own downside_note ($10k/account) is closer to the sourced anchors than its base case.</t>
+        </is>
+      </c>
+      <c r="K8" s="60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L8" s="47" t="inlineStr">
+        <is>
+          <t>The trigger stands; the business does not, as scoped.
+WHAT SURVIVED. Every dated regulatory claim checked out and none has slipped — 11 Sep 2026 Art. 14 reporting with 24h/72h/14d clocks, 11 Dec 2027 full application, notified-body rules live since 11 Jun 2026 with zero bodies designated and 12-18 month accreditation lead times, and the Digital Omnibus explicitly did NOT delay CRA (it delayed the AI Act). The kernel CVE flood is real and worse than described. The pain is genuine and the clock is honest. This is a well-sourced regulatory-clock record on the demand side.
+WHAT KILLED IT. Three findings compound, and they compound multiplicatively rather than additively:
+1. The moat is $0. Yocto ships upstream, free, compiled-file-granular kernel CVE filtering with VEX output and kernel-CNA enrichment, claiming 70-80% false-positive reduction. The record's entire technical differentiation — "index reachability from the kernel .config, defconfig and driver set... emit OpenVEX" — is a coarser reimplementation of something already in the customer's build system. The record's confidence rested on why_overlooked being true; it is false.
+2. The price is roughly half what was modelled. Sourced anchors put the ceiling at ~$25k, not $55k: the category leader claims only $48k of annual savings for the whole function, full BSP maintenance sells for under half a junior engineer, and the bundled platform prices marginal devices to zero at volume.
+3. The universe is roughly a third of what was assumed. 2,210 Yocto-using companies is the only live anchor against an unsourced 6,000, and the paying subset is smaller still because the excluded groups — firms already inside a Wind River, Lynx or Qualcomm/Foundries bundle — are exactly the ones the record needs to sell to.
+Run the three together: ~$25k ACV against a paying universe plausibly 700-1,500 firms, competing against free upstream tooling and a €700M-valuation acquirer, gives a Y5 that lands nearer the record's own downside_note (~$1M ARR, acquisition target) than its base case ($17.6M). The record assigned confidence 4 and named the right kill risk in kill_risk and key_sensitivity — then modelled the base case as though that risk were contingent. It is the observed present state, sourced from the incumbents' own pricing pages.
+WHAT WOULD STILL WORK, NARROWLY. Two adjacent shapes survive the sourcing. First, the assessment-capacity gap is real and un-served: zero notified bodies, 12-18 month accreditation, only 29 EUCC certs in year one, and an Art. 35(2) target of 11 Dec 2026 that will be missed. That is a lab, auditor and technical-file services business with genuine scarcity pricing — not SaaS, and not what the record proposed. Second, the legally load-bearing piece nobody sells is signed attestation and liability transfer on VEX justifications, since the record correctly notes each justification is an assertion the manufacturer signs. But that is an insurance-and-services posture requiring a balance sheet, not two engineers and 90 days. Both are different companies from the one described.</t>
+        </is>
+      </c>
+      <c r="M8" s="46" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" ht="150" customHeight="1">
+      <c r="A9" s="52" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="53" t="inlineStr">
+        <is>
+          <t>Funded-Claim Detection for Casualty Reserving</t>
+        </is>
+      </c>
+      <c r="C9" s="52" t="inlineStr">
+        <is>
+          <t>partly-confirmed</t>
+        </is>
+      </c>
+      <c r="D9" s="53" t="inlineStr">
+        <is>
+          <t>The statutory triggers are REAL and dated correctly — but the commercial premise built on top of them does not survive sourcing.
+CONFIRMED — Georgia SB 69. "Georgia's Senate Bill 69, effective Jan. 1, 2026, outlines new third-party litigation funding regulations, including registration, disclosure requirements and penalties for non-compliance." Registration runs through NMLS with the Georgia Department of Banking and Finance; the disclosure threshold is $25,000, at or above which the agreement is discoverable and the funder faces joint-and-several liability for sanctions; noncompliance penalties run to $10,000 fines and 1-5 years imprisonment. No evidence of any stay, injunction, or slipped effective date. The "5% beneficial ownership" specific was not independently confirmed in search results — what is confirmed is that SB 69 "eliminates foreign influence in civil cases by restricting foreign ownership of litigation financiers" and that the registry data does expose ownership.
+CONFIRMED — S.3826. "The Litigation Funding Transparency Act of 2026 (S. 3826) was introduced on February 11, 2026, by Mr. Grassley (for himself, Mr. Tillis, Mr. Kennedy, and Mr. Cornyn) and referred to the Committee on the Judiciary." Scope matches the record: "class actions, actions consolidated in multidistrict litigation, or those involving at least 100 individual cases." Status: "introduced on Feb. 11, 2026 and is in the first stage of the legislative process" — no committee action six months on.
+CONFIRMED — the Law.com piece, but it cuts AGAINST the record. Two articles, not one. 13 Jul 2026: "At Least 41 Companies Have Registered as Litigation Funders in Georgia. Some Ask if It Really Matters." 17 Jul 2026: "Georgia's New Litigation Funding Registry Reveals Industry's Owners, Lawyer Ties" — "Law.com received a list of the companies that have registered with the Nationwide Multistate Licensing System, as well as who owns them, via an open records request." So ALM has already assembled and published the funder-owner-and-lawyer-ties dataset that the record proposes to sell as its wedge SKU, and framed the skeptical case that the registry may not matter because major industry players are not fully captured.
+CONTRADICTED IN PART — the registry is NOT hard to get. Georgia DBF's own instruction: "To search for litigation financiers, please visit www.nmlsconsumeraccess.org." The list of registered litigation financiers is a free public lookup. The FOIA was needed only for the ownership overlay, which is now published.
+TRIGGER BINDS THE WRONG PARTY FOR THE PRODUCT'S CORE CLAIM. Georgia's registry binds funders, not cases. Nothing in SB 69 creates a case-to-funder mapping. The record's kill_risk already concedes this; sourcing confirms there is no public artifact linking a registrant to a specific open claim.</t>
+        </is>
+      </c>
+      <c r="E9" s="52" t="inlineStr">
+        <is>
+          <t>contested</t>
+        </is>
+      </c>
+      <c r="F9" s="53" t="inlineStr">
+        <is>
+          <t>Findevor (New York, founded 2024) — CLOSEST DIRECT OVERLAP AND CONFIRMED FUNDED. 'Findevor Launches AI-Powered Legal System Abuse Prevention Product for Casualty Insurers,' analyzing 'external risk signals — such as OSHA violations, judicial hotspots, and plaintiff firm activity — and cross-references them with internal portfolio trends to help insurers catch emerging litigation exposure before it impacts the book.' That is the record's product described in the record's own terms. Funding: 'In November 2025, Findevor announced that it has formally filed to raise $5 million in its Seed round,' phase one for 'tier 1 carrier partners,' phase two in 2026 to 'scale the platform across tier 2 and tier 3 carriers and large MGAs.' Also hired insurance leader Chris Kopser specifically 'to take on legal system abuse.'
+Verisk (NYSE: VRSK, ~$782.6M Q1 2026 revenue) — has the substrate, the carrier relationships, and an active TPLF content program: a dedicated Third-Party Litigation Funding campaign page, a Social Inflation emerging-issues hub, Litigation Analytics, and a published 'Claim Scoring' product line with release notes. Shipping fraud/claims platforms through 2026 (Weightmans partnership). This is the 'incumbent ships it as a feature next quarter' risk, and it is the most likely acquirer-or-killer.
+CLARA Analytics — 'the leading casualty claims intelligence platform… used at carriers, MGA/MGUs, reinsurers and self-insured organizations,' i.e. the record's exact buyer list. Raised a $24M Series C in September 2023 and has 'more than doubled its annual recurring revenue.' Already predicts attorney involvement and litigation propensity — funder inference is an adjacent feature on an existing contract, not a new purchase order.
+Milliman IntelliScript — MOST UNDER-RATED THREAT, MISSED ENTIRELY BY THE RECORD. Published 'The role of NLP and AI in third-party litigation funding: How insurers can leverage data analytics to level the playing field.' Milliman is simultaneously the actuarial firm that runs many carriers' reserve reviews — it sits inside the exact budget line and the exact meeting the record targets.
+ALM / Law.com (Daily Report) — already published the Georgia funder-ownership dataset (17 Jul 2026) with an announced ongoing series on who has and has not registered. A subscription legal publisher giving the wedge deliverable away as editorial is a pricing ceiling on the wedge SKU.
+Darrow — 'the AI Lab for Legal Risk' launched a platform in May 2026 'to Let Plaintiffs' Firms Manage Litigation Like an Investment Portfolio.' Opposite side of the market, same entity-resolution and case-graph substrate, venture-funded, moving faster.
+Westfleet Advisors — publishes the annual commercial litigation finance market report (the industry's reference count of funders). Market-level not claim-level, as the record says, but it owns the funder-universe franchise and could extend downward.
+LexisNexis Lex Machina, UniCourt, Docket Alarm, Premonition — docket substrate. Priced from $49/mo to 'tens of thousands' per year; any of them can add a funder-entity tag.
+CSC — 'the leading provider of UCC Search, Filing, and Online Portfolio Management services… the industry's largest online UCC database.' Owns the UCC-1 leg of the proposed cross-join as an existing commercial product.
+Gen Re — published 'Who's Really Behind That Lawsuit? Claims Handling Challenges From Third-Party Litigation Funding' (Aug 2025), a reinsurer-authored practitioner guide to detecting funded claims, distributed free to the exact buyer.</t>
+        </is>
+      </c>
+      <c r="G9" s="53" t="inlineStr">
+        <is>
+          <t>The record's crowding_check was directionally right that no one has productized registry-to-claim linkage, and I found no such product either. But it rated the space too kindly on three counts that live search exposes.
+First, Findevor is not merely "closest overlap" — it is the same product, funded, with an insurance-industry operator hired to sell it, and a stated 2026 plan to move from tier-1 carriers down to tier-2/3 and MGAs. A two-person startup entering in 2026 arrives after Findevor's carrier pilots.
+Second, the record missed Milliman IntelliScript entirely. Milliman publishing on NLP/AI for TPLF detection is qualitatively worse than Verisk doing so, because Milliman already sits inside the reserve review — the exact meeting where this signal would be consumed. There is no wedge to open; the door is already occupied.
+Third, the whitespace argument rested on an artifact that turns out to be a competitor. ALM did the open-records work, published the owners-and-lawyer-ties dataset in July 2026, and announced a continuing series. The record cited this as proof of absence. It is proof of presence, from a publisher with better distribution to the legal side and a subscription business that gives it away.
+Not "crowded" — nobody has shipped case-level funder attribution, and the entity-resolution work is genuinely unglamorous. But "thin" or "empty" is unsustainable when four parties (Findevor, Verisk, CLARA, Milliman) each hold both the substrate and the carrier relationship, the raw registry is a free public lookup covering 41 entities, and the flagship deliverable has already been published editorially.</t>
+        </is>
+      </c>
+      <c r="H9" s="66" t="n">
+        <v>175</v>
+      </c>
+      <c r="I9" s="53" t="inlineStr">
+        <is>
+          <t>ESTIMATE, BOUNDED — no search returned a direct count of US carriers writing commercial casualty at reserving-team scale, and I am not dressing one up. Derivation from the published enumerations that did surface: (1) NAIC's Market Share Reports for Property/Casualty enumerate the top 125 groups countrywide — this is the standard boundary of "groups large enough to be individually tracked," and the industry's own top-list convention is a Top 100 US P&amp;C list (Reinsurance News). (2) AM Best publishes "World's 50 Largest Reinsurers," and "the ten largest reinsurers account for approximately 70% of total global P&amp;C reinsurance premiums in 2025," so the reinsurer buying set is concentrated and small — call it 40-50 with any casualty appetite. (3) Upper bound therefore ~125 + ~50 = 175 signable entities. The realistic figure is LOWER, because a large share of the top-125 P&amp;C groups are personal-lines or property-dominant and have no casualty reserving problem — the record itself makes this filter. I report 175 as the defensible upper bound and would place the true casualty-relevant set at 120-175. Cross-check on the supply side, which is the more damning number: only 41 companies have registered as litigation funders in Georgia, so the entire universe the product resolves is 41 entities. Confidence: LOW on the buyer count, HIGH on the 41.</t>
+        </is>
+      </c>
+      <c r="J9" s="53" t="inlineStr">
+        <is>
+          <t>REAL PRICES FOUND (all on the legal-data substrate side, which is what this product actually resells):
+Lex Machina (LexisNexis) — the record's own named comparable. "Lex Machina pricing involves annual subscriptions that can range from several thousand to tens of thousands of dollars, depending on the size and needs of the organization." Custom by firm size. This is the single most damaging price point: the record asserted a "$50k-$300k per year" band for exactly this class of product and used it to justify $125k. The sourced ceiling is "tens of thousands."
+Docket Alarm (Fastcase/vLex) — published pricing: "$99/month per legal professional" flat-fee membership, "$39.99/month" pay-as-you-go; "Enterprise rates commonly fall in the $150-$250 per user per month range." At 20 enterprise seats that is $36k-$60k/yr.
+UniCourt Enterprise API — published tiers: "$49/month for the Personal plan, $149/month for the Professional plan, and $299/month for the Premium plan," with custom usage-based enterprise pricing above that.
+CSC — largest commercial UCC-1 search/filing database; price not published, but it is a purchasable commodity service, meaning the UCC leg is a COGS line, not differentiation.
+NO PRICE FOUND, EXPLICITLY: CLARA Analytics does not disclose pricing — "specific pricing details… such as cost per claim, subscription pricing tiers, or contract values — are not disclosed in publicly available sources… custom pricing quotes based on factors like claim volume." Same for Verisk claims-analytics modules and Findevor. So the record's implied $175k-$250k insurance-side enterprise band is UNSOURCED in both directions — I could neither confirm nor refute it, and it should not be treated as evidence.
+Anchoring judgment: the only prices I can actually stand behind put a single-signal legal-data subscription in the $10k-$60k/yr range. Insurance-carrier enterprise ACVs are plausibly higher, but no public number supports that for this category.</t>
+        </is>
+      </c>
+      <c r="K9" s="60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L9" s="53" t="inlineStr">
+        <is>
+          <t>The problem is real and the trigger is real. The BUSINESS does not survive sourcing.
+What held: Georgia SB 69 effective 1 Jan 2026 with NMLS registration, $25k discoverability threshold, and criminal penalties — exactly as described. S.3826 introduced 11 Feb 2026 by Grassley with Tillis, Kennedy, Cornyn, covering class actions, MDLs and 100+ case aggregations — exactly as described. EY's 4%-5.2% loss-ratio drag confirmed. Casualty is genuinely bleeding: other liability (occurrence) ran a 114.7 combined ratio in 2025 with an ~$11B underwriting loss. Carriers want this signal.
+What broke, in order of severity:
+1. THE MOAT IS A FREE PUBLIC LOOKUP OF 41 ROWS. Georgia DBF directs the public to nmlsconsumeraccess.org to search litigation financiers. At least 41 companies are registered. The record's why_overlooked — that a FOIA request proves no vendor had the list — inverts the actual fact pattern: the list is free, the ownership overlay took one records request, and a journalist has already published it. There is no proprietary raw material here.
+2. THE WEDGE SKU EXISTS AS FREE-ISH JOURNALISM. Law.com published "Georgia's New Litigation Funding Registry Reveals Industry's Owners, Lawyer Ties" on 17 Jul 2026 — the funders, the owners, the lawyer ties — and announced a continuing series. You cannot sell a $50k quarterly report whose contents ALM prints for subscription price, and whose own trade press headline asks whether it "Really Matters."
+3. THE INFERENCE WINDOW IS CLOSING IN 2026, NOT 2029. The record priced five years of runway before disclosure erodes the need for detection. Live: Arizona's Supreme Court now requires disclosure of funder identity, financial terms and degree of control at the outset of civil litigation; New York's registration regime took effect 17 June 2026; Ohio is enacting commercial-and-consumer funder registration with AG disclosure; West Virginia and Wisconsin have automatic disclosure; Georgia makes agreements discoverable at $25k. A court rule that hands defendants the funder's identity per case, for free, is a direct substitute for a paid inference product. The record's five-year ramp (36 customers by Y5) runs straight into it.
+4. THE ACV IS ~2.5x TOO HIGH ON SOURCED EVIDENCE. Lex Machina, the record's own comparable, sells for "several thousand to tens of thousands" per year. The record's asserted $50k-$300k band starts where the real one ends.
+5. THE UNRESOLVED TECHNICAL FACT STAYED UNRESOLVED. Nothing in fifteen searches suggests anyone — including four better-resourced incumbents — has linked funder identity to individual open claims. The record's key_sensitivity said this is "the entire difference between a $2M and a $7M business." Sourcing gives no reason to believe the $7M branch.
+Net: what survives is precisely the record's downside_note — a firm-level list at $40-60k to perhaps 15-20 subscribers, with a shrinking half-life and Verisk, CLARA, Milliman or Findevor able to absorb it as a feature. That is a good consulting product and a poor venture one. Rank 6 was too generous; on this evidence it does not belong on the list.</t>
+        </is>
+      </c>
+      <c r="M9" s="52" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" ht="150" customHeight="1">
+      <c r="A10" s="46" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="47" t="inlineStr">
+        <is>
+          <t>Forward exchange for transformer and switchgear production slots</t>
+        </is>
+      </c>
+      <c r="C10" s="46" t="inlineStr">
+        <is>
+          <t>partly-confirmed</t>
+        </is>
+      </c>
+      <c r="D10" s="47" t="inlineStr">
+        <is>
+          <t>THE REGULATORY TRIGGER IS REAL AND THE DATES CHECK OUT, BUT THE RECORD MISCITES THE DOCKET AND IGNORES THE SLIP MECHANISM.
+Confirmed: On 18 June 2026 FERC issued Federal Power Act Section 206 show cause orders to all six FERC-jurisdictional RTOs/ISOs -- PJM, MISO, SPP, CAISO, ISO-NE and NYISO -- directing each to demonstrate that its tariff adequately enables interconnection of large loads or propose reforms. Confirmed across eight independent law-firm alerts (McGuireWoods, Baker Botts, Bracewell, Day Pitney, White &amp; Case, Orrick, Ashurst/Perkins Coie, Morgan Lewis). The 50 MW / &gt;69 kV definition is confirmed: "FERC defined large loads as those with a peak load in excess of 50 MW that interconnect to transmission lines greater than 69 kV." The 17 Aug 2026 response date is confirmed: "The RTOs and ISOs must respond to FERC's orders within 60 days by August 17, 2026."
+CORRECTION 1 -- WRONG DOCKET. The record says the show cause orders were issued "in the RM26-4 proceeding" / "(Docket RM26-4)." They were not. FERC "chose to proceed through individualized show cause proceedings rather than a notice-and-comment rulemaking," and separately "is leaving the existing rulemaking docket (Docket No. RM26-4-000) open and encourages entities to file comments in that docket as necessary." RM26-4 is the parallel generic rulemaking, not the vehicle for the six orders. Anyone citing RM26-4 as the show-cause docket is citing the wrong proceeding.
+CORRECTION 2 -- THE DEADLINE IS SOFT AND MAY ALREADY HAVE SLIPPED. The record presents 17 Aug 2026 as a hard forcing date. It is not: "Within 45 days of the show cause orders by August 3, 2026, RTOs/ISOs and/or their transmission owners can request that these proceedings be held in abeyance for up to 90 days to develop and file with FERC reforms," and "RTOs/ISOs may request and receive an extension of these timelines from FERC." Today is 6 Aug 2026 -- the abeyance window closed three days ago and I could not establish from search whether any RTO invoked it. A 90-day abeyance pushes this to mid-November 2026. The record also omits the 30-day informational report that was due 20 July 2026.
+CORRECTION 3 -- THE CAUSAL CHAIN RUNS BACKWARD. The record asserts the orders "will pull even more simultaneous orders into the queue and deepen the double-booking." The orders' stated purpose is the opposite -- they "target reliability, cost allocation and delays tied to data center power demand" and push RTOs toward screening and study discipline for speculative large loads. Tightening large-load interconnection screens plausibly reduces phantom queue entries, which shrinks rather than grows the orphaned-slot pool this business needs.
+SUPPLY-SIDE CLAIMS: lead times confirmed and in fact understated by the record. "Large power transformers are averaging 128 weeks, while GSUs average 144 weeks according to Wood Mackenzie's second quarter 2025 survey. Wood Mackenzie's 2026 read puts substation units above 160 weeks (roughly three years), with the largest high-voltage units reaching up to four years." Deposit mechanic confirmed: "Most manufacturers will hold a production slot for 10-30% of equipment cost." GE Vernova confirmed: gas power backlog plus slot reservation agreements grew from 83 to 100 GW in Q1 2026, later reported at 116 GW.</t>
+        </is>
+      </c>
+      <c r="E10" s="46" t="inlineStr">
+        <is>
+          <t>contested</t>
+        </is>
+      </c>
+      <c r="F10" s="47" t="inlineStr">
+        <is>
+          <t>Anza Exchange / Anza Renewables -- THE CLOSEST AND MOST DANGEROUS. Runs exchange.anzarenewables.com, an operating B2B marketplace to buy and sell NEW power transformers, HV breakers and solar modules, and separately launched a Transformer Procurement Service 'designed to streamline how developers, IPPs, EPCs, utilities, and data center developers procure medium- and high-voltage transformers.' Spun out of Borrego as a standalone company in 2023; supported procurement of over 2 GW of solar modules in 2025, exceeding all of 2024 in eight months. Has the buyers, the equipment class, the voltage range and the transaction rails already. Listing undelivered order positions is a feature release, not a pivot.
+Build.inc -- publishes 'Data Center Transformer Procurement in 2026: Why Electrical Equipment Is Now a Development Constraint,' and is the source of the slot-deposit mechanics (10-30% to hold a slot, 8-16 extra weeks without one) this record cites as proprietary insight. Sitting in the advisory seat next to the same buyer.
+GE Vernova -- not a startup competitor but the structural incumbent that makes the market unnecessary. Runs the slot book itself: gas power backlog plus slot reservation agreements went 83 GW to 100 GW in Q1 2026, then to 116 GW, with a raised target of 110 GW+ by year end. When an order is released the OEM reallocates it to the next buyer in line. GEV already IS the clearinghouse, holds the waitlist, and captures the reallocation spread.
+CTG Power Systems International -- surplus electrical power equipment with inventory spanning 1 MVA distribution units to 350 MVA utility-grade power transformers including GSU, step-down and substation class. This is the substitute a buyer reaches for instead of a forward slot.
+Maddox Transformer -- markets directly at 'Transformers for Data Centers | Fastest Lead Times.' Inventory-based speed-to-power, targeting the identical urgency.
+Transformer Exchange Inc -- buy and sell used transformers, takes a negotiated commission on successful sale to end user. Established brokerage muscle in the adjacent physical market.
+Electrical Trader -- online marketplace for electrical components and power distribution equipment with category filters and direct buyer-seller messaging; also publishes 10-year transformer pricing trend research and shortage/pricing analysis. Note it competes on BOTH legs of this thesis: the marketplace and the price-transparency data product.
+Surplus Record -- runs a dedicated Used Data Center Equipment category for electrical power gear.
+Circuit Breaker Buyer USA -- data center electrical surplus removal and resale, explicitly working the datacenter decommissioning channel.
+surplustransformer.com -- used and substation transformer marketplace.
+VAWN -- publishes the Electrical Equipment Lead Time Index. This is the forward-curve data product the record positions as its year-3 moat, already shipping.
+Terrapin Consulting Group -- publishes switchgear, transformer and generator lead times with 'real numbers for data center, industrial' plus a broader commercial construction lead time index. Same data layer.
+Heron Power -- $140M Series B closed February 2026, founded by former Tesla energy executive Drew Baglino. Solid-state transformers. Not a marketplace, but this is where the capital chasing this pain is actually going -- supply-side, not intermediation.
+DG Matrix -- solid-state transformers focused on data center applications, differentiating on balancing multiple AC and DC sources. Same supply-side answer to the same shortage.
+GridCARE -- $64M Series A May 2026 (after $13.5M seed in late May 2025), uses AI to unlock the grid's underutilized capacity. A direct substitute for 'speed to power': if you can find existing grid headroom you do not need a 2029 transformer slot.
+Critical Loop -- $26M Series A April 2026, Long Beach microgrid startup explicitly framed as solving grid scarcity and getting stalled infrastructure projects back on track. Another substitute path around the equipment queue.
+Giga Energy -- sells transformers to AI datacenter builds and publishes public transformer price ranges 'to budget your AI factory build,' commoditizing the price transparency this record intends to monetize.
+Gridcog -- $8.3M Series A July 2026 led by ABB Electrification Ventures with Axpo, DNV and Verbund Ventures. Energy modelling SaaS; notable because ABB, an equipment OEM, is now funding the software layer around its own hardware.</t>
+        </is>
+      </c>
+      <c r="G10" s="47" t="inlineStr">
+        <is>
+          <t>The record's own crowding check was right about the narrow question and wrong about what it means.
+NARROW QUESTION -- IS ANYONE TRADING FORWARD SLOTS? No. Two differently-worded searches using practitioner language ("production slot" / "order slot" resale, assignment, secondary market; broker / factory slot / reservation transfer) returned zero venues. The only "slot marketplace" hit was Slotcycle, which trades casino gaming machines. The record's claim that this specific venue does not exist survives sourcing.
+BUT THAT ABSENCE IS NOT AN OPENING, AND HERE IS WHY THE VERDICT IS CONTESTED RATHER THAN EMPTY:
+1. The function is already performed, by the OEM, for free. "When real orders do fall away, the slot is reallocated to the next buyer in line rather than vanishing." A market does not exist because the incumbent already clears it internally and has no reason to share the spread. Empty markets that stay empty for a structural reason are not opportunities.
+2. Every adjacent layer is occupied and several are funded. New-equipment exchange: Anza. Surplus inventory: CTG (1-350 MVA), Maddox, Transformer Exchange, Surplus Record, surplustransformer.com, Circuit Breaker Buyer USA. Procurement advisory into the exact ICP: Anza Transformer Procurement Service, Build.inc. Lead-time and price data -- the record's stated year-3 moat: VAWN's Electrical Equipment Lead Time Index, Terrapin's lead-time report, Electrical Trader's pricing series, Giga Energy's published price ranges. The forward curve the record wants to own as proprietary is being given away today by four separate parties.
+3. Capital is flowing to substitutes, not intermediation. Heron Power took $140M Series B in Feb 2026 and DG Matrix is building solid-state transformers for datacenters -- both attack the shortage by making more iron. GridCARE took $64M in May 2026 to find existing grid headroom so you never need the slot. Critical Loop took $26M in Apr 2026 for microgrids. One analysis notes substation equipment has the highest capital-share-to-deal-share ratio in the grid dataset at 2.29. Investors have looked at this pain and repeatedly chosen supply-side and grid-side answers over a trading venue.
+4. Anza specifically is not "one product decision away" as the record says -- it is closer than that. It already operates a marketplace listing new power transformers and HV breakers AND a procurement desk naming data center developers, IPPs, EPCs and utilities for MV/HV transformers. It has the listings infrastructure, the buyer relationships and the OEM relationships. If forward slots ever become tradeable, Anza ships it as a tab.</t>
+        </is>
+      </c>
+      <c r="H10" s="65" t="n">
+        <v>500</v>
+      </c>
+      <c r="I10" s="47" t="inlineStr">
+        <is>
+          <t>ESTIMATE, BOUNDED BY SOURCED DENOMINATORS -- no source gives a count of "entities that procure MV/HV production slots," so I built one from four sourced counts and state the derivation.
+Utility side (sourced): 2,896 electric utility companies operate in the US, broken into 168 investor-owned utilities, 1,958 publicly owned utilities averaging only 12,100 customers each, and 812 cooperatives averaging 24,500 customers each (EIA). Only entities with transmission-connected substations buy power-class transformers and GSUs. The 168 IOUs all qualify. Of the 1,958 POUs and 812 co-ops, the overwhelming majority are small distribution-only municipals; I take the largest ~10% of that combined 2,770 as power-class buyers, giving ~275. Utility subtotal: ~440. But utilities are structurally the wrong seller -- they defer, they do not liquidate.
+Data center side (sourced facility counts, no operator count found): 4,011 US data centers as of March 2026 (estimates range 3,698 to 5,400 depending on classification); 135 US hyperscale facilities, with Amazon, Microsoft and Google alone accounting for 59% of hyperscale capacity. Facilities are not buyers -- operators are, and no source published an operator count. Ownership is heavily concentrated, so a few hundred distinct US developers, colocation operators and hyperscaler build arms is the defensible band. I use 150-250.
+IPP and BESS developers: no count sourced. Not included as a separate block to avoid double-counting the IPPs already inside the utility-side figure.
+GROSS UNIVERSE: roughly 400-800 US entities that procure medium- or high-voltage iron at slot scale; point estimate 500. This is close enough to the record's 600 that I do not treat the headline number as an error.
+THE REAL PROBLEM IS THAT THE GROSS UNIVERSE IS NOT THE ADDRESSABLE ONE. The addressable universe is entities that could actually SELL an orphaned slot, and evidence collapses it hard. SemiAnalysis: cancelled projects that never placed orders never occupied a slot, and released real orders are "reallocated to the next buyer in line." DC Byte Q1 2026: 80.5% of US data center pipeline projects sit in pre-construction, up from 59.8% in Q1 2023 -- pre-construction projects are exactly the ones that have not placed equipment orders. GE Vernova's slot reservation agreements are non-firm and deferrable, so a holder with a dead site defers instead of selling. Netting these, the population of entities in any given year holding a firm, placed, transferable order they are motivated to assign is plausibly under 100 nationwide, and I could not source it at all. That, not the 600, is the number that kills the model.</t>
+        </is>
+      </c>
+      <c r="J10" s="47" t="inlineStr">
+        <is>
+          <t>REAL PRICES FOUND, AND THEY UNDERCUT THE RECORD'S $6M AVERAGE PACKAGE.
+Transformer unit economics (sourced):
+- Recent 50-100 MVA transformer awards in Europe have cleared at $30,000-$35,000 per MVA. That puts a single 100 MVA unit at roughly $3.0-3.5M -- not $6M (Electrical Trader, 10-year pricing overview).
+- Transformers in the 10-100 MVA band cost $300,000 to $2 million, described as the most common utility and industrial grid units (Taishan Transformer cost-range guide).
+- Price escalation is confirmed and steep: unit prices up 77% for power transformers and 45% for GSUs since 2019, some distribution classes up 95%; power transformers up roughly 75% since 2019. 2026 forecast escalation is only 3-5% as new capacity comes online, i.e. the price spike has flattened -- which also flattens the spread a slot broker would be arbitraging.
+- Giga Energy publishes transformer price ranges explicitly framed for AI datacenter budgeting, and Build.inc publishes datacenter transformer procurement guidance -- both give away the price transparency this record proposes to sell.
+Slot deposit economics (sourced):
+- "Most manufacturers will hold a production slot for 10-30% of equipment cost," and without a slot reservation nominal lead time extends another 8-16 weeks (Build.inc). This confirms the record's deposit range.
+- Turbines are an order of magnitude larger: GE Vernova requires around 20% of contract price to designate a slot reservation agreement -- on a $300M two-unit CCGT package that is roughly $60M on deposit. If turbine slots ever became assignable, a single trade would dwarf every transformer trade combined. But SRAs are non-firm and deferrable, so the holder has no reason to sell.
+Fee and take-rate comparables (sourced):
+- Industrial equipment broker fee is "typically calculated as 10% of the net value of goods sold as a direct result of an introduction"; a worked example cites 8% on a $50,000 sale; auction platforms charge seller commissions of 5-12% (iDRY Wood broker terms; Maas Companies).
+- Transformer Exchange runs a negotiated commission paid on successful sale to the end user -- rate not published, which is itself evidence that headline take rates in this niche are set deal by deal, not by a posted 3%.
+Substitute pricing pressure: CTG Power Systems carries surplus inventory from 1 MVA to 350 MVA and Maddox markets transformers to datacenters on "fastest lead times." A buyer facing a 160-week OEM queue can buy physical surplus today. That surplus channel is the real price ceiling on any forward slot, and the record does not model it.</t>
+        </is>
+      </c>
+      <c r="K10" s="60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L10" s="47" t="inlineStr">
+        <is>
+          <t>NO, NOT AS WRITTEN -- and the reason is not the OEM-consent objection the record spent its ranking argument rebutting. It is the seller side, which nobody checked.
+The record staked everything on one sentence: "The monetizable fact is that half the announced projects will never break ground." Live sourcing breaks that in two independent places.
+First, the inventory does not exist. SemiAnalysis established on 18 June 2026 that "projects getting canceled that never placed equipment orders don't remove orders from manufacturers' books, and when real orders do fall away, the slot is reallocated to the next buyer in line rather than vanishing." Cancellation and orphaned slots are different events, and the record conflated them. DC Byte confirms 80.5% of the US pipeline sits in pre-construction -- precisely the stage before an equipment order is placed. The announced-versus-built gap the record monetizes is a gap between press releases and orders, not between orders and deliveries.
+Second, the seller has no reason to sell. GE Vernova's slot reservation agreements are "non-firm arrangements where a reservation can be deferred or cancelled if power demand forecasts soften or financing tightens." A developer whose 2028 site dies defers to 2030 and keeps the option. There is no forfeited-deposit distress, so there is no motivated counterparty, so there is no two-sided market. The record's model explicitly identifies the distressed seller as the party that makes the trade possible; the evidence removes them.
+Third, the record's own why_now number is refuted by the same document it cites in kill_risk. It uses "12-16 GW announced with only about 5 GW under construction" as proof of collapse. SemiAnalysis's satellite verification puts the two largest hyperscalers' self-build alone above 5 GW, and its own capacity projections moved ~1% and under 5% over six months. Building the thesis on a statistic you have already flagged as rebutted, and then ranking it #7 anyway, is the load-bearing error in this record.
+WHAT DOES SURVIVE. The scarcity is completely real and if anything worse than stated: Wood Mackenzie's 2026 read puts substation transformers above 160 weeks and the largest HV units at four years, MV switchgear is effectively sold out through 2028, and prices are up 77% for power transformers and 45% for GSUs since 2019. The FERC trigger is real, dated, and binds all six RTOs. Deposits of 10-30% to hold a slot are confirmed. The buyer's pain is not in question.
+But the pain is being addressed by four better-positioned business models -- surplus inventory (CTG, Maddox), procurement services into the exact ICP (Anza, Build.inc), more supply (Heron $140M, DG Matrix), and grid-side workarounds (GridCARE $64M) -- and the record's proposed data moat, a forward curve on lead times and prices, is already published free by VAWN, Terrapin, Electrical Trader and Giga Energy.
+VERDICT: the trigger stands, the scarcity stands, the market does not. The record's own downside_note describes a "25-30 trade-per-year niche brokerage doing $4-5M at Y5 with no data moat." Sourcing says even that is optimistic, because it assumes an orphan pool that the OEMs demonstrably reabsorb. The honest residual is a procurement and expediting desk competing head-on with a funded Anza -- a real business, but a different one, and not what was ranked.</t>
+        </is>
+      </c>
+      <c r="M10" s="46" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" ht="150" customHeight="1">
+      <c r="A11" s="52" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="53" t="inlineStr">
+        <is>
+          <t>Key-state custody for LMS/XMSS firmware signing under CNSA 2.0</t>
+        </is>
+      </c>
+      <c r="C11" s="52" t="inlineStr">
+        <is>
+          <t>partly-confirmed</t>
+        </is>
+      </c>
+      <c r="D11" s="53" t="inlineStr">
+        <is>
+          <t>THE MANDATE IS REAL BUT THE PRODUCT'S CORE MECHANISM IS PROHIBITED UNDER IT.
+Confirmed: CNSA 2.0 does specify the stateful hash-based schemes LMS and XMSS (not ML-DSA) for software and firmware signing. Timeline confirmed across multiple sources: "support and preference for CNSA 2.0 by 2025 where available, and exclusive use by 2030"; "from January 1, 2027, new National Security Systems acquisitions are expected to be CNSA 2.0-compliant by default"; most transitions targeted for 2033 ahead of the NSM-10 2035 goal (safelogic.com/compliance/cnsa-2, postquantum.com/cnsa-2-0/complete-guide). So the record's "1 Jan 2027 procurement gate" is NOT merely a vendor-blog invention — it recurs in independent secondary coverage. It is, however, phrased as "expected to be compliant by default," which is softer than the record's "must support."
+FATAL, from the CNSA 2.0 FAQ coverage: "HSS (the multi-tree variant of LMS) and XMSS^MT are not approved for NSS. Only single-tree LMS and XMSS are allowed for software and firmware signing." wolfSSL states it independently: "The multi-tree algorithms HSS and XMSSMT are not allowed... The hyper-tree (colloquially known as 'tree of trees') components specified in NIST SP 800-208 are not approved." The product's stated differentiator — "reserves disjoint HSS/XMSS-MT subtrees per builder so parallel CI can never collide" — is built on the exact two variants the named buyer is forbidden from using.
+KILL RISK HAS ALREADY PARTLY LANDED, it is not a future event: the updated CNSA 2.0 FAQ states "validated ML-DSA is approved for all signing use cases and when it is available it may be the most appropriate choice for some software/firmware signing use cases," and "ML-DSA-87 can be used for software/firmware signing." LMS/XMSS remain NSA's near-term *preference* on availability grounds, not an exclusive requirement. The record's model treats this as a 2027-2028 binary; it is already in the published guidance as of the current FAQ revision.
+Civilian side confirmed: OMB M-26-15 "Execution of the Migration to Post-Quantum Cryptography" published 24 June 2026, signed by OMB Director Russell T. Vought, five-phase schedule 2026-2035. The EO number contradiction the record flagged is REAL AND STILL UNRESOLVED in live sources: most coverage says EO 14412 (signed two days before M-26-15); Wiz and Gopher Security both publish under EO 14409 (22 June 2026), titled "Securing the Nation Against Advanced Cryptographic Attacks." I could not resolve this without fetching the Federal Register (fetching is blocked). Treat any citation of the EO number as unverified.</t>
+        </is>
+      </c>
+      <c r="E11" s="52" t="inlineStr">
+        <is>
+          <t>crowded</t>
+        </is>
+      </c>
+      <c r="F11" s="53" t="inlineStr">
+        <is>
+          <t>Thales TCT (Trusted Cyber Technologies) — SHIPPING. LMS and its multi-tree variant HSS available in all Luna T-Series HSMs from v7.15.0, marketed explicitly as 'CNSA Compliant Code Signing.' Publicly traded parent (Thales). Note: the record's own evidence_urls cite Thales's quantum-resistant code signing whitepaper as proof the market is empty.
+Utimaco — SHIPPING WITH NAMED USE CASES. Stateful HBS tested and running on SecurityServer; 'several customers have successfully completed PQC migration projects using Utimaco's proper state handling architecture, from securing satellite communications to reliable firmware over-the-air updates.' Private, PE-backed (SGT Capital). This is the exact buyer and exact workload the record claims is unserved.
+Keyfactor — SHIPPING. SignServer supports LMS, SLH-DSA and ML-DSA from v7.1 via Bouncy Castle; SignServer 7.5.0 extends PQC support to Entrust nShield 5c. Signum is signing-as-a-service for 'code, containers, software, and firmware.' Late-stage private, Insight Partners-backed. Adding index-state orchestration is a release note for them, not a company.
+Cryptomathic + PQShield — STRATEGIC ALLIANCE announced specifically for PQC code signing 'in compliance with latest NIST and CNSA recommendations,' with 'full support of standardized PQC algorithms including stateful hash-based signature schemes like LMS and XMSS in hardware and software, with streamlined key management and automation workflows.' PQShield is VC-backed (Addition, Oxford Science Enterprises); funding figure not established by these searches.
+Crypto4A Technologies — co-author of the IETF state-management draft (Jim Goodman, Bruno Couillard). Canadian HSM vendor; funding not established by these searches.
+ISARA Corporation — Radiate Security Solution Suite 1.4 added XMSS 'to complete its offering of stateful hash-based signatures for quantum-safe roots of trust.' Quantum Valley Investments-backed; current stage not established by these searches.
+DigiCert Software Trust Manager — enterprise code signing with HSM-backed keys and CI/CD integration, subscription-tiered. Clearlake/Crosspoint-owned. PQC/LMS support not confirmed by these searches.
+Cloud HSM providers as substitutes — AWS CloudHSM (FIPS 140-3 L3, Marvell LiquidSecurity 2), Azure Dedicated HSM (Thales Luna 7), Google Cloud HSM (Marvell). Whether they expose LMS is not established by search; if they do, the wedge narrows further.
+IETF PQUIP working group, draft-ietf-pquip-hbs-state-03 — not a company but a competitor to the business model. Publication Requested as of rev 2025-12-16; authors from PQShield, BSI (x2), Google, Crypto4A. Commoditises the guidance the startup would sell as expertise.
+PATENT HOLDERS (unnamed assignees, not resolved) — US 11438172 and US 11750403 'Robust state synchronization for stateful hash-based signatures'; US 11722313 'State synchronization for post-quantum signing facilities.' The granted claims describe synchronizing one-time-signature state across multiple HSM signers to prevent counter reuse, which is the product.</t>
+        </is>
+      </c>
+      <c r="G11" s="53" t="inlineStr">
+        <is>
+          <t>The record's central claim — "nobody ships state management" — is contradicted on every axis I could search. The problem is simultaneously (a) shipping in commercial HSM firmware, (b) shipping in a signing-as-a-service platform, (c) covered by granted US patents, and (d) one revision from an IETF RFC written by the incumbents.
+Specifically: Thales Luna T-Series has shipped LMS and HSS since v7.15.0 under the banner "CNSA Compliant Code Signing." Utimaco not only implements state handling but cites production customers doing firmware-over-the-air signing and satellite comms — the record's exact ICP. Keyfactor SignServer has signed with LMS since 7.1 and sells Signum explicitly for firmware. Cryptomathic and PQShield formed an alliance whose announced scope is LMS/XMSS code signing with "streamlined key management and automation workflows" — a description that maps almost word-for-word onto the proposed product. ISARA completed its stateful HBS suite with XMSS.
+The strongest single disqualifier is the patent estate. US 11722313 "State synchronization for post-quantum signing facilities" and US 11438172 / 11750403 "Robust state synchronization for stateful hash-based signatures" claim multi-HSM state synchronization to prevent one-time-key counter reuse. That is not adjacent to the product; it IS the product, described in the patent abstract in the same terms the record uses in its one_line.
+The GitHub scarcity that drove this to rank 8 was measuring public repositories in a domain where all serious implementation lives inside FIPS-validated HSM firmware and patent filings. It was a false negative, and it was the only evidence supporting the overlooked score.
+What remains genuinely unowned is narrow: a vendor-portable orchestration layer that works identically across Luna, nShield, Utimaco and CloudHSM. That is a real integration gap. It is also a feature, sized in engineer-months, that any of the five named vendors or Keyfactor can close in a release — and Keyfactor's own release notes show them adding HSM-by-HSM PQC support on exactly that cadence.</t>
+        </is>
+      </c>
+      <c r="H11" s="66" t="n">
+        <v>400</v>
+      </c>
+      <c r="I11" s="53" t="inlineStr">
+        <is>
+          <t>NOT SOURCED — this is a bounded estimate and I am labelling it as such. Three searches failed to produce a count of the actual buying unit (organisations that generate firmware/bootloader signing keys for National Security Systems). What searches DID establish are only outer bounds, all far too broad: the US Defense Industrial Base is "over 60,000 companies and 1.17 million employees" (congress.gov CRS), and the DIB partnership counts "more than 100,000 DIB companies and their subcontractors" (cisa.gov). Those are 100x the relevant unit — the overwhelming majority of DIB firms manufacture no firmware and hold no signing key. I attempted to bound from the tighter side using the NSA CSfC Components List and the NIAP Product Compliant List — the correct proxy, since those enumerate vendors whose crypto-bearing products are actually accepted into NSS — but neither publishes a count in search-visible text and page fetching is blocked, so I could not retrieve it. Recommend that count be pulled directly from home.niap-ccevs.org/Product/PCL.cfm and nsa.gov CSfC Components List as the first diligence step; my expectation is low hundreds of vendors, which would put the record's 600 in the right order of magnitude but at the top of the plausible range. Two live findings should shrink it further: (a) only single-tree LMS/XMSS is permitted for NSS, so any buyer whose driver was multi-tree parallel CI is not a buyer; (b) ML-DSA is already approved for firmware signing, so every architect who chooses stateless leaves the universe permanently. I carry 400 as a midpoint of a 150-800 band, ESTIMATED.</t>
+        </is>
+      </c>
+      <c r="J11" s="53" t="inlineStr">
+        <is>
+          <t>Real prices found, ranked by relevance:
+1. KEYFACTOR (closest functional comparable — Signum signing-as-a-service, SignServer, Command PKI; already ships LMS signing): "Keyfactor cost bundles typically range from $2,000 to $10,000+/month, based on industry benchmarks for enterprise-grade IT Management and PKI solutions, with actual costs varying depending on infrastructure complexity, the number of endpoints, and selected modules." That is $24,000-$120,000+/year for a FULL PKI + signing platform. Source: https://softwarefinder.com/it-management-software/keyfactor
+2. DIGICERT SOFTWARE TRUST MANAGER: subscription model, "tiers that scale based on the number of code signing certificates and usage requirements" — specific annual pricing not publicly disclosed. Listed on CDW (SKU DIGI-SOFT-TRST-MGR-CDE-SIG) but no price in search-visible text. Sources: https://www.digicert.com/software-trust-manager , https://www.cdw.com/product/digicert-software-trust-manager/8102333
+3. DIGICERT RETAIL CODE SIGNING CERTIFICATES (the floor of the market): OV $399.99-$549/yr, EV from $581/yr; reseller floors as low as $178-$215.99/yr. Note the market-wide change: from 15 February 2026 code signing certificate lifespans are capped at one year, so everything is now an annual renewal. Sources: https://www.ssl2buy.com/digicert-ov-code-signing-certificate.php , https://signmycode.com/digicert-code-signing , https://codesigncert.com/digicert-code-signing-certificate
+4. SIGNPATH: Code Signing Starter and Basic priced per active user account; enterprise pricing not disclosed. Source: https://about.signpath.io/product/editions-explained
+5. COGS ANCHOR (this is the load-bearing price finding): AWS CloudHSM $1.45 per HSM-hour = ~$12,700/HSM-year; Azure Dedicated HSM ~$4.85/hour = ~$42,500/HSM-year, Thales Luna Network HSM 7 hardware, FIPS 140-2 Level 3 with 140-3 L3 migration tracked through 2026; Google Cloud HSM billed per key-version and per operation. AWS CloudHSM is FIPS 140-3 Level 3 on Marvell LiquidSecurity 2. Source: https://evertrust.io/blog/hsm-as-a-service-vs-on-prem/ and https://www.qcecuring.com/education/hsm/cloud-hsm-and-managed-services
+No public price exists for anything sold specifically as LMS/XMSS state custody — that part of the record remains unpriceable from public sources.</t>
+        </is>
+      </c>
+      <c r="K11" s="60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L11" s="53" t="inlineStr">
+        <is>
+          <t>No. Four independent findings each land near-fatally, and they are not correlated — fixing one does not rescue the others.
+1. THE MECHANISM IS PROHIBITED FOR THE NAMED BUYER. The differentiator is disjoint HSS/XMSS-MT subtrees per CI builder. CNSA 2.0 approves only single-tree LMS and XMSS for NSS; HSS and XMSS^MT are explicitly disallowed. The product's parallelism story and its buyer are mutually exclusive. This is not a pivot away from an assumption — it is the one_line being unsellable to the ICP.
+2. THE KILL RISK ALREADY FIRED. Both record and screener framed stateless ML-DSA as a future regulatory event to be feared. The current CNSA 2.0 FAQ already approves validated ML-DSA for all signing use cases including firmware, and says it "may be the most appropriate choice for some software/firmware signing use cases." The record's own key_sensitivity says "nothing else in the model matters as much." It has happened. Every architect choosing today can choose the algorithm with no state to custody and remain compliant.
+3. THE VOID DOES NOT EXIST. Thales, Utimaco, Keyfactor, ISARA, Cryptomathic+PQShield all ship stateful HBS handling, with Utimaco citing production firmware-OTA customers. The IETF PQUIP working group is at Publication Requested on the state-and-backup-management guidance, authored by PQShield, BSI, Google and Crypto4A. And the multi-HSM state-synchronization mechanism is covered by at least three granted US patents. The measured "tooling void" was an artefact of searching GitHub for work that lives in HSM firmware and patent filings.
+4. THE UNIT ECONOMICS INVERT. SP 800-208 forbids key export, so tenants cannot share HSM capacity. Replicated cloud HSMs cost ~$76k/year per customer at AWS's $1.45/HSM-hour, against a sourced ACV band whose midpoint is $60k. The 72% gross margin is unreachable; at the record's own $110k it is roughly 31%.
+The insight that started this — CNSA 2.0 picking stateful hash-based schemes turns code signing into a crash-consistent distributed-state problem — is genuinely sharp and remains true as a technical observation. It is simply not a company: the people who own the state own the HSM, they already ship it, they patented it, and they are writing the RFC. The only honest residue is an open-source vendor-portable state manager and fork detector, which is worth building for reputation and has no path to the hosted-control-plane revenue the model requires. If anything survives diligence it is a services/tooling business at a fraction of the modelled ACV, not the $110k-ACV, 600-account SaaS described.</t>
+        </is>
+      </c>
+      <c r="M11" s="52" t="n">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:L1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D79"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="5" customWidth="1" min="3" max="3"/>
+    <col width="150" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="67" t="inlineStr">
+        <is>
+          <t>76 factual corrections that live sourcing made to the original research. The original study ran with no live search for these checks, so this is where it was wrong. Read this before acting on anything in the earlier sheets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="34" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>Opportunity</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>Correction</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="78" customHeight="1">
+      <c r="A4" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="47" t="inlineStr">
+        <is>
+          <t>Ride-through models and curtailment proof for NERC-registered data centers</t>
+        </is>
+      </c>
+      <c r="C4" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="47" t="inlineStr">
+        <is>
+          <t>FATAL TO THE RANKING RATIONALE: The record says 'the buyer is under an enforcement clock' and calls the 3 Aug 2026 Level 3 Alert deadline the reason 'revenue exists in month one.' The Alert is not enforceable. Davis Wright Tremaine: 'The Essential Actions are not the same as Reliability Standards and are not mandatory obligations. Registered entities are not subject to penalties for failing to implement the Essential Actions.' There is no penalty behind the date. Source: https://www.dwt.com/blogs/energy--environmental-law-blog/2026/05/nerc-level-3-alert-large-loads-data-centers</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="78" customHeight="1">
+      <c r="A5" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="53" t="inlineStr">
+        <is>
+          <t>Ride-through models and curtailment proof for NERC-registered data centers</t>
+        </is>
+      </c>
+      <c r="C5" s="52" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="53" t="inlineStr">
+        <is>
+          <t>BUYER INVERSION: The record's first_pass_model names the primary buyer as 'the VP of Energy / interconnection lead at a large-load data centre developer' and demotes the utility to secondary. Backwards. The Level 3 Alert is directed at transmission owners, transmission planners, transmission operators, planning coordinators, reliability coordinators and balancing authorities. Data centers 'are currently not required to be registered with NERC and are not directly bound.' The obligated party today is the utility/TP the record lists second. Sources: https://www.utilitydive.com/news/nerc-issues-rare-level-3-alert-over-data-center-load-losses/819295/ and https://www.nerc.com/globalassets/who-we-are/rules-of-procedure/proposed/computational-load-entity-summary-of-changes-april-2026-posting.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="78" customHeight="1">
+      <c r="A6" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="47" t="inlineStr">
+        <is>
+          <t>Ride-through models and curtailment proof for NERC-registered data centers</t>
+        </is>
+      </c>
+      <c r="C6" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" s="47" t="inlineStr">
+        <is>
+          <t>THE BEACHHEAD IS NOT COVERED BY THE TRIGGER: The record says FERC issued Section 206 orders 'to every RTO' on 18 June 2026 and then proposes 'starting in ERCOT.' The six RM26-4 show-cause orders went to PJM, CAISO, MISO, NYISO, ISO-NE and SPP. ERCOT is not FERC-jurisdictional and received no order. RM26-4 creates zero obligation in the market the plan starts in. Source: https://www.mcguirewoods.com/client-resources/alerts/2026/6/ferc-issues-section-208-show-cause-orders (see https://www.velaw.com/insights/ferc-institutes-six-simultaneous-section-206-proceedings-targeting-large-load-interconnection-across-all-rto-iso-markets/)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="78" customHeight="1">
+      <c r="A7" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="53" t="inlineStr">
+        <is>
+          <t>Ride-through models and curtailment proof for NERC-registered data centers</t>
+        </is>
+      </c>
+      <c r="C7" s="52" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" s="53" t="inlineStr">
+        <is>
+          <t>THE BEACHHEAD JUST FROZE — EVENT POSTDATES THE RECORD ENTIRELY: On ~3 August 2026 Gov. Abbott ordered an audit of all data centers in the ERCOT queue; ERCOT issued a market notice DELAYING the Batch Zero process and will ask the PUCT for a good-cause timeline exemption on 20 August 2026. Queue restated at ~474 GW. BNEF estimates 20% of the US data center pipeline is at risk of delay. The record's 'revenue exists in month one' claim collides directly with a freeze on the exact ERCOT process it planned to sell into. Sources: https://www.utilitydive.com/news/texas-hits-pause-data-center-interconnections/827046/ and https://www.texastribune.org/2026/08/03/texas-data-center-project-audit-greg-abbott/</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="78" customHeight="1">
+      <c r="A8" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="B8" s="47" t="inlineStr">
+        <is>
+          <t>Ride-through models and curtailment proof for NERC-registered data centers</t>
+        </is>
+      </c>
+      <c r="C8" s="46" t="n">
+        <v>5</v>
+      </c>
+      <c r="D8" s="47" t="inlineStr">
+        <is>
+          <t>NERC REGISTRATION IS NOT YET LAW: The record treats data centers as already 'becoming NERC-registered reliability entities.' The Computational Load Entity registry criteria are a draft — posted for comment 1 April 2026, revised draft due August 2026, Board approval targeted 5 December 2026, FERC filing by 31 December 2026. No data center is a registered entity today. Source: https://www.nerc.com/globalassets/who-we-are/rules-of-procedure/proposed/computational-load-entity-summary-of-changes-april-2026-posting.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="78" customHeight="1">
+      <c r="A9" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="B9" s="53" t="inlineStr">
+        <is>
+          <t>Ride-through models and curtailment proof for NERC-registered data centers</t>
+        </is>
+      </c>
+      <c r="C9" s="52" t="n">
+        <v>6</v>
+      </c>
+      <c r="D9" s="53" t="inlineStr">
+        <is>
+          <t>'TINY CONSULTANCIES' IS WRONG: The record dismisses the incumbent field as 'a handful of tiny consultancies (EPE Consulting, Keentel Engineering).' Keentel Engineering has 27 years of operation, offices in Tampa, Austin, Sacramento and Baltimore, former NERC audit team leads on staff, project history across ERCOT, PJM, MISO, WECC and SERC, and an explicit productized line in 'Level 3 Alert response engineering, large-load system impact and contingency studies, disturbance monitoring and instrumentation design, protection coordination at large-load POIs.' It also dominates organic search for nearly every practitioner query in this space. EPE Consulting has already published 'Turning NERC's Level 3 Essential Actions into a Defensible Response.' Sources: https://keentelengineering.com/nerc-large-load-compliance and https://epeconsulting.com/epe-intelligence/news/turning-nerc-s-level-3-essential-actions-into-a-defensible-response</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="78" customHeight="1">
+      <c r="A10" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" s="47" t="inlineStr">
+        <is>
+          <t>Ride-through models and curtailment proof for NERC-registered data centers</t>
+        </is>
+      </c>
+      <c r="C10" s="46" t="n">
+        <v>7</v>
+      </c>
+      <c r="D10" s="47" t="inlineStr">
+        <is>
+          <t>THE SCARCE MODELING INPUT IS BEING GIVEN AWAY FREE BY THE ISO: The record's moat is 'the person who can translate IEC 62040-3 UPS transfer behavior into an ISO-acceptable load model.' On 24 April 2026 ERCOT published 'Dynamic Modeling of AI Data Center Load in PSCAD' — a public manual whose Section 6 presents a double-conversion UPS-based AI data center model with test cases for voltage ride-through performance, operating mode transitions and computing load fluctuations. The reference model is a free download from the ISO. Source: https://www.ercot.com/files/docs/2026/04/24/Dynamic-Modeling-of-AI-Data-Center-Load-in-PSCAD-Manual.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="78" customHeight="1">
+      <c r="A11" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="B11" s="53" t="inlineStr">
+        <is>
+          <t>Ride-through models and curtailment proof for NERC-registered data centers</t>
+        </is>
+      </c>
+      <c r="C11" s="52" t="n">
+        <v>8</v>
+      </c>
+      <c r="D11" s="53" t="inlineStr">
+        <is>
+          <t>THE SECOND PRODUCT HAS ALMOST NO MARKET TODAY: The record bolts on ERCOT PCLR registration and curtailment proof as 'a second product on the same relationship.' Total current Controllable Load Resource capacity in ERCOT is about 36 MW. That is the entire installed base the curtailment-record product would sell against today. Source: https://www.ercot.com/services/programs/load/laar</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="78" customHeight="1">
+      <c r="A12" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="B12" s="47" t="inlineStr">
+        <is>
+          <t>Ride-through models and curtailment proof for NERC-registered data centers</t>
+        </is>
+      </c>
+      <c r="C12" s="46" t="n">
+        <v>9</v>
+      </c>
+      <c r="D12" s="47" t="inlineStr">
+        <is>
+          <t>QUEUE FIGURE IS STALE: The record cites 438 GW. As of the August 2026 pause the figure is ~474 GW. Minor, and directionally in the record's favor. Source: https://www.utilitydive.com/news/texas-hits-pause-data-center-interconnections/827046/</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="78" customHeight="1">
+      <c r="A13" s="52" t="n">
+        <v>2</v>
+      </c>
+      <c r="B13" s="53" t="inlineStr">
+        <is>
+          <t>Entry Type 13 and instrument-aware duty recovery for the post-de-minimis long tail</t>
+        </is>
+      </c>
+      <c r="C13" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="53" t="inlineStr">
+        <is>
+          <t>ET13 SCOPE IS MAIL-ONLY, NOT GENERAL LOW-VALUE. Record: 'a fully electronic informal-entry path for shipments valued at $2,500 or less.' CBP's actual Trade Information Notice is titled 'Implementation of Entry Type 13 Test in ACE for U.S. Mail Processing' and scopes it to 'international mail shipments valued at $2,500 or less.' The record's day-one product (a Shopify/WooCommerce app filing entries for merchants importing consolidated air/ocean freight and pallets) is largely outside ET13's scope. The single most load-bearing 'integration door' in the thesis opens onto a narrower room than described. Source: https://www.cbp.gov/document/guidance/trade-information-notice-implementation-entry-type-13-test-ace-us-mail-processing and https://www.ghy.com/trade-compliance/cbp-entry-type-13-test-ace-us-mail-processing/</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="78" customHeight="1">
+      <c r="A14" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="B14" s="47" t="inlineStr">
+        <is>
+          <t>Entry Type 13 and instrument-aware duty recovery for the post-de-minimis long tail</t>
+        </is>
+      </c>
+      <c r="C14" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" s="47" t="inlineStr">
+        <is>
+          <t>THE DOOR IS ALREADY OPEN AND THE RECORD SAYS SEVEN WEEKS. ET13 hit the ACE CERT environment on 24 July 2026 — two weeks before today's date — with PROD on 22 September 2026. 'The integration door opens in seven weeks' was stale on arrival; certification-environment participants are already integrating. Source: https://www.ghy.com/trade-compliance/cbp-entry-type-13-test-ace-us-mail-processing/</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="78" customHeight="1">
+      <c r="A15" s="52" t="n">
+        <v>2</v>
+      </c>
+      <c r="B15" s="53" t="inlineStr">
+        <is>
+          <t>Entry Type 13 and instrument-aware duty recovery for the post-de-minimis long tail</t>
+        </is>
+      </c>
+      <c r="C15" s="52" t="n">
+        <v>3</v>
+      </c>
+      <c r="D15" s="53" t="inlineStr">
+        <is>
+          <t>'NOBODY HAS ATTACKED THE BROKER-CAPACITY BOTTLENECK ITSELF' IS FLATLY FALSE. Amari AI — founded by an ex-Google engineer (Sam Basu) and ex-LinkedIn engineer (Arushi Vashist) — raised $4.5M co-led by First Round Capital and Pear VC in February 2026, explicitly to 'modernize customs brokerage' and automate data entry and paperwork FOR CUSTOMS BROKERS. It markets itself as 'the leading AI partner for customs brokers,' has signed 30+ customers and moved $15B+ of goods. That is precisely the broker-throughput-multiplication wedge the record claims is unoccupied, funded by two top-tier seed firms six months ago. Sources: https://app.dealroom.co/news/feed/ex-google-and-linkedin-engineers-raise-4-5m-for-ai-customs-broker-startup-amid-trump-tariffs and https://amari.ai/</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="78" customHeight="1">
+      <c r="A16" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="B16" s="47" t="inlineStr">
+        <is>
+          <t>Entry Type 13 and instrument-aware duty recovery for the post-de-minimis long tail</t>
+        </is>
+      </c>
+      <c r="C16" s="46" t="n">
+        <v>4</v>
+      </c>
+      <c r="D16" s="47" t="inlineStr">
+        <is>
+          <t>BOTH HALVES OF THE THESIS ARE ALREADY IN ONE FUNDED COMPANY. Caspian raised $5.4M seed led by Primary Venture Partners (with Blank Ventures). It is 'an approved tech company and licensed customs broker that can file claims directly with U.S. Customs or partner with large enterprises and customs brokers,' and it 'automates analyzing international shipping and inventory data to identify eligible duty refunds, submitting claims within days instead of months.' Licensed broker + entry automation + instrument-aware refund identification is the record's entire two-product plan, already capitalized. Sources: https://pulse2.com/caspian-5-4-million-seed-funding-raised-for-ai-based-customs-compliance/ and https://www.startup-weekly.com/Caspian-launches-AI-powered-global-trade-advisory-platform-with-5-4m-seed-funding/</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="78" customHeight="1">
+      <c r="A17" s="52" t="n">
+        <v>2</v>
+      </c>
+      <c r="B17" s="53" t="inlineStr">
+        <is>
+          <t>Entry Type 13 and instrument-aware duty recovery for the post-de-minimis long tail</t>
+        </is>
+      </c>
+      <c r="C17" s="52" t="n">
+        <v>5</v>
+      </c>
+      <c r="D17" s="53" t="inlineStr">
+        <is>
+          <t>ZONOS DID NOT 'MOVE DOWN-MARKET FASTER THAN YOU' AS A FUTURE RISK — IT ALREADY DID IT, ON 30 APRIL 2026. Zonos acquired Evolve Trade Services, a licensed U.S. customs brokerage specializing in high-volume ecommerce clearance with 'deep ecommerce customs expertise, including Type 11 informal entries,' and used it to launch Zonos Brokerage Services, 'a new offering focused on low-value informal entries into the U.S. for merchants, postal operators, logistics providers and freight forwarders.' Zonos serves 50,000+ merchants and 70+ postal operators. The record's kill_risk describes this as a threat that could materialize; it materialized three months before the record was written. Source: https://www.prweb.com/releases/zonos-acquires-evolve-trade-services-to-build-customs-brokerage-directly-into-its-cross-border-operating-system-302758951.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="78" customHeight="1">
+      <c r="A18" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="B18" s="47" t="inlineStr">
+        <is>
+          <t>Entry Type 13 and instrument-aware duty recovery for the post-de-minimis long tail</t>
+        </is>
+      </c>
+      <c r="C18" s="46" t="n">
+        <v>6</v>
+      </c>
+      <c r="D18" s="47" t="inlineStr">
+        <is>
+          <t>THE DRAWBACK PRICING WEDGE IS ATTACKING A PRICE THAT ISN'T THE MARKET PRICE. Record: incumbents run '50/50 contingency splits' and 'priced flat, which is the obvious wedge against 50/50 contingency incumbents.' Actual market: brokers 'typically charge either a contingency fee of 10-25% of the recovered duty amount or a flat project fee ranging from $1,500 to $10,000+.' Another source: 'most traditional brokers charge a contingency (15-25% of recovered duties).' The incumbent take is roughly one-third of what the record claims, AND flat-fee pricing already exists in the market. The central commercial wedge of product two largely evaporates. Sources: https://customsbrokerindex.com/blog/7-best-customs-brokers-for-duty/ and https://www.ajot.com/news/best-duty-drawback-companies-in-2026-compared-by-speed-cost-recovery</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="78" customHeight="1">
+      <c r="A19" s="52" t="n">
+        <v>2</v>
+      </c>
+      <c r="B19" s="53" t="inlineStr">
+        <is>
+          <t>Entry Type 13 and instrument-aware duty recovery for the post-de-minimis long tail</t>
+        </is>
+      </c>
+      <c r="C19" s="52" t="n">
+        <v>7</v>
+      </c>
+      <c r="D19" s="53" t="inlineStr">
+        <is>
+          <t>ENTRIES PER ACCOUNT — THE RECORD'S OWN NAMED KEY SENSITIVITY — RESOLVES AGAINST IT. The record assumes ~350 entries/account/year with 'no anchor at all,' and states plainly: 'If it is 100, the unit economics collapse.' CBP data: 'over 300,000 active unique importer-of-record numbers annually, accounting for 30.4 million commercial transactions.' That is a MEAN of ~101 entries per importer per year, and because the distribution is power-law (a handful of enterprise importers file the bulk of the 30.4M), the SMB median sits materially BELOW 101. The record's assumption is roughly 3.5x the population mean and likely 5-10x the target-segment median. Source: https://cbpauthority.com/cbp-statistics-and-data/</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="78" customHeight="1">
+      <c r="A20" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="B20" s="47" t="inlineStr">
+        <is>
+          <t>Entry Type 13 and instrument-aware duty recovery for the post-de-minimis long tail</t>
+        </is>
+      </c>
+      <c r="C20" s="46" t="n">
+        <v>8</v>
+      </c>
+      <c r="D20" s="47" t="inlineStr">
+        <is>
+          <t>A CBP RULING THE RECORD NEVER MENTIONS CONSTRAINS PRODUCT ONE DIRECTLY. In January 2026 CBP issued Headquarters Ruling H350722, its first ruling addressing an AI-powered classification tool, 'drawing a clear line between what software may do and what only a licensed person may do.' Per the ruling's logic: if an AI tool provides classifications beyond six digits for merchandise that will be entered with CBP, and the tool's output directs or influences the classification on the entry, THE TOOL IS CONDUCTING CUSTOMS BUSINESS. The record's 'HTS classification assistant ... delivered as a Shopify/WooCommerce/marketplace app that classifies a merchant's SKU catalog' is squarely in scope. This cuts both ways — it hardens the license moat, but it also means every one of the 10-digit classifications must carry licensed-broker involvement, which raises the per-entry labour cost the 62% gross margin already struggles to absorb. Sources: https://gingercontrol.com/blog/ai-hts-classification-tools-legal-requirements and https://artemusgroupusa.com/ai-in-custom-entries/</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="78" customHeight="1">
+      <c r="A21" s="52" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="53" t="inlineStr">
+        <is>
+          <t>Entry Type 13 and instrument-aware duty recovery for the post-de-minimis long tail</t>
+        </is>
+      </c>
+      <c r="C21" s="52" t="n">
+        <v>9</v>
+      </c>
+      <c r="D21" s="53" t="inlineStr">
+        <is>
+          <t>THE 'INDEFINITE SUSPENSION' IS A PROPOSED RULE UNDER ACTIVE LITIGATION, NOT SETTLED LAW. Record: 'on 24 June 2026 CBP published an indefinite suspension of the administrative exemption.' Actual: on 23 JUNE 2026 CBP published TWO PROPOSED RULES 'establishing a new legal basis for indefinitely suspending the de minimis duty exemption for low-value imports.' NPRMs, not final rules. Separately, importer Detroit Axle is arguing at the Court of International Trade that Learning Resources confirms IEEPA cannot be used to end de minimis, and the CIT ruled that case may proceed. The 1 July 2027 OBBBA statutory repeal is durable; the 2025-2027 bridge the entire 90-day plan depends on is not. Sources: https://www.rvia.org/news-insights/customs-publishes-proposed-rules-permanently-suspend-de-minimis-exemption-program and https://www.supplychaindive.com/news/de-minimis-exemption-lawsuit-case-status/814329/</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="78" customHeight="1">
+      <c r="A22" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="47" t="inlineStr">
+        <is>
+          <t>Entry Type 13 and instrument-aware duty recovery for the post-de-minimis long tail</t>
+        </is>
+      </c>
+      <c r="C22" s="46" t="n">
+        <v>10</v>
+      </c>
+      <c r="D22" s="47" t="inlineStr">
+        <is>
+          <t>THE FLOW IS ALREADY LICENSED AND ENUMERATED — CBP PUBLISHED THE COMPETITOR LIST. Under EO 14324, CBP certified 12 qualified parties to collect and pay duties on international mail: Advance Customs Broker &amp; Logistics; BoxC; Evolve Trade Services; Flexport; Importal Customs; International Bonded Couriers; James CB TX; JFS; North American Ecommerce Solutions; R&amp;H International Brokerage; SafePackage; and Zonos. These are the incumbents on precisely the ET13 mail flow, named by the regulator, with SafePackage and Zonos authorized before the 29 Aug 2025 ban even took effect. Sources: https://wwd.com/sourcing-journal/logistics/cbp-customs-de-minimis-provision-12-companies-international-mail-shipments-postal-collect-duties-1238856408/ and https://content.govdelivery.com/accounts/USDHSCBP/bulletins/3eeee57</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="78" customHeight="1">
+      <c r="A23" s="52" t="n">
+        <v>2</v>
+      </c>
+      <c r="B23" s="53" t="inlineStr">
+        <is>
+          <t>Entry Type 13 and instrument-aware duty recovery for the post-de-minimis long tail</t>
+        </is>
+      </c>
+      <c r="C23" s="52" t="n">
+        <v>11</v>
+      </c>
+      <c r="D23" s="53" t="inlineStr">
+        <is>
+          <t>THE CAPE REFUND WAVE IS LARGELY OVER, NOT AHEAD. The record frames CAPE as an opening opportunity. Sourced: ~$121.75B in potential and certified refunds already accepted into CAPE and ~$86.3B in duties and interest already sent to Treasury for disbursement; CBP is now REMOVING entry types (warehouse Entry Types 21 and 22 no longer accepted on a CAPE Declaration effective 7 July 2026). A team starting a 90-day build today, needing 8 months to first revenue per the model, arrives after the disbursement peak. Source: https://www.ghy.com/trade-compliance/cbp-cape-ieepa-refund-progress/</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="78" customHeight="1">
+      <c r="A24" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="B24" s="47" t="inlineStr">
+        <is>
+          <t>Entry Type 13 and instrument-aware duty recovery for the post-de-minimis long tail</t>
+        </is>
+      </c>
+      <c r="C24" s="46" t="n">
+        <v>12</v>
+      </c>
+      <c r="D24" s="47" t="inlineStr">
+        <is>
+          <t>IN THE RECORD'S FAVOUR — THE SCOUT'S SELF-DOUBT WAS UNWARRANTED. Every figure flagged 'VERIFY BEFORE ACTING' checks out exactly: SCOTUS 6-3 on 20 Feb 2026 (Learning Resources v. Trump, No. 24-1287), CAPE launched 20 April 2026, and ~75,300 declarations covering 11.2M+ entries as of 26 April 2026. The scout was more accurate than it believed. Sources: https://www.supremecourt.gov/opinions/25pdf/24-1287_4gcj.pdf and https://www.cbp.gov/sites/default/files/2026-04/trade_information_notice_cape_508c.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="78" customHeight="1">
+      <c r="A25" s="52" t="n">
+        <v>2</v>
+      </c>
+      <c r="B25" s="53" t="inlineStr">
+        <is>
+          <t>Entry Type 13 and instrument-aware duty recovery for the post-de-minimis long tail</t>
+        </is>
+      </c>
+      <c r="C25" s="52" t="n">
+        <v>13</v>
+      </c>
+      <c r="D25" s="53" t="inlineStr">
+        <is>
+          <t>IN THE RECORD'S FAVOUR — A TAILWIND IT MISSED, WHICH ALSO WEAKENS ITS MOAT CLAIM. Section 122's 10% global baseline expired 24 July 2026 and was replaced the same minute by Section 301 duties of 10% or 12.5% on 60 economies covering ~99% of US imports (USTR final action announced 23 July 2026). Section 301 duties are generally drawback-eligible; IEEPA duties were not. So the entire post-IEEPA baseline tariff wall is now RECOVERABLE — a materially larger drawback surface than the record models. But the same fact undercuts the 'instrument-aware reasoning is the moat' argument: with one dominant instrument covering 99% of imports plus a stable Section 232 carve-out, per-SKU-per-instrument reasoning gets SIMPLER, not harder. The legal-grade-reasoning premium shrinks as the instrument landscape consolidates. Sources: https://www.tarifftax.org/analysis/section-122-what-comes-next and https://sterlinxglobal.com/usa-update-section-122-tariff-expired-july-24-2026-changes-to-section-301-tariffs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="78" customHeight="1">
+      <c r="A26" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="B26" s="47" t="inlineStr">
+        <is>
+          <t>NQA-1 qualification and commercial grade dedication as a service</t>
+        </is>
+      </c>
+      <c r="C26" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="47" t="inlineStr">
+        <is>
+          <t>FATAL TO THE CORE CLAIM — the record's 'no vendor' assertion is refuted by a URL in its own evidence list. why_overlooked states: 'Searches for nuclear supplier qualification software return NRC pages, EPRI reports and consortium PDFs — no vendor,' and the screening says the software-layer claim 'survives' because 'nobody has productized guided Method 1-4 dedication with a cross-buyer reusable CC library.' But evidence_urls[3] is forgedops.com/glossary/procurement-supplier-qa. forgedops.com is Forged Operations Inc, whose homepage tagline is literally 'The Operating System for Nuclear Quality.' Its product OpsAssist 'gives QA leaders a real-time view of compliance against frameworks like CSA N299 and ASME NQA-1' and 'manages the full supplier qualification lifecycle, including initial qualification, QSL maintenance, re-evaluation scheduling, surveillance tracking, and NCR linkage,' plus 'pre-award surveys, source inspection scheduling, CoC tracking, and receipt inspection records, with AI flagging documentation gaps at receipt.' That is the record's own product description. The scouts scraped this company's SEO glossary for definitions of NQA-1, CGD and supplier qualification and never noticed it was the competitor. Sources: https://forgedops.com/ , https://www.forgedops.com/opsassist , https://www.forgedops.com/about-us , https://pitchbook.com/profiles/company/847304-65 , https://www.crunchbase.com/organization/opsassist</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="78" customHeight="1">
+      <c r="A27" s="52" t="n">
+        <v>3</v>
+      </c>
+      <c r="B27" s="53" t="inlineStr">
+        <is>
+          <t>NQA-1 qualification and commercial grade dedication as a service</t>
+        </is>
+      </c>
+      <c r="C27" s="52" t="n">
+        <v>2</v>
+      </c>
+      <c r="D27" s="53" t="inlineStr">
+        <is>
+          <t>WEDGE GEOGRAPHY IS ALREADY SERVED BY A FEDERALLY SUBSIDIZED COMPETITOR OFFERING A FREE ON-RAMP. buildable_today proposes selling '$75-150k per shop' Appendix B readiness sprints to 'five non-nuclear precision shops in Tennessee, Ohio and the Carolinas that already hold AS9100 or ISO 9001.' Tennessee MEP (the NIST Manufacturing Extension Partnership center at Univ. of Tennessee) runs a dedicated NQA-1 program that 'helps manufacturers build NQA-1-compliant quality programs to enter and sustain work in the nuclear supply chain' and offers a 'no cost Gemba walk to start.' Catalyst Connection (the Pittsburgh MEP) published an 'NQA-1 EXPLAINED: NUCLEAR QUALITY MANAGEMENT' whitepaper dated January 2026. MEP services are cost-shared with federal funds and priced far below commercial consulting. The record's beachhead is a subsidized market. Sources: https://tmep.cis.tennessee.edu/nqa-1 , https://www.catalystconnection.org/wp-content/uploads/2026/01/NQA-1-Whitepaper-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="78" customHeight="1">
+      <c r="A28" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="B28" s="47" t="inlineStr">
+        <is>
+          <t>NQA-1 qualification and commercial grade dedication as a service</t>
+        </is>
+      </c>
+      <c r="C28" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="D28" s="47" t="inlineStr">
+        <is>
+          <t>BUYER UNIVERSE OVERSTATED BY ROUGHLY 3-10x. first_pass_model claims 1,200 with the author admitting it is 'a chain of my own inferences.' Hard counterevidence: 'In the 1970s and 1980s, about 500 U.S. companies held nuclear stamps, but today only about 100 do, although the total is beginning to creep back up.' The entire currently-qualified US nuclear manufacturing base is ~100 firms, not 1,200. Corroborating small numbers: Nuclear Suppliers Organization is 'approximately 60 companies'; NIAC has '170 members globally'; NUPIC performs only ~93 joint utility assessments per year including 80 joint audits. Sources: https://www.power-eng.com/nuclear/stamp-of-approval/ , https://www.sandia.gov/research/publications/details/global-trends-of-asme-n-stamp-certifications-for-nuclear-component-vendors-2021-08-17/ , https://nuclearsuppliers.org/ , https://niac-usa.org/executive-summary/ , https://www.nrc.gov/docs/ML0834/ML083400286.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="78" customHeight="1">
+      <c r="A29" s="52" t="n">
+        <v>3</v>
+      </c>
+      <c r="B29" s="53" t="inlineStr">
+        <is>
+          <t>NQA-1 qualification and commercial grade dedication as a service</t>
+        </is>
+      </c>
+      <c r="C29" s="52" t="n">
+        <v>4</v>
+      </c>
+      <c r="D29" s="53" t="inlineStr">
+        <is>
+          <t>why_now MISSTATES THE FEDERAL TARGET: it says 'a federal 300 GW-by-2050 target.' The actual target from the four executive orders signed 23 May 2025 is 400 GW by 2050 — quadrupling from ~100 GW. The record's own screening flagged this error but the why_now text was never corrected, so the error is still live in the record. Source: https://www.utilitydive.com/news/trump-aims-for-400-gw-of-nuclear-by-2050-10-large-reactors-under-construct/749107/ , https://www.energy.gov/ne/articles/9-key-takeaways-president-trumps-executive-orders-nuclear-energy</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="78" customHeight="1">
+      <c r="A30" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="B30" s="47" t="inlineStr">
+        <is>
+          <t>NQA-1 qualification and commercial grade dedication as a service</t>
+        </is>
+      </c>
+      <c r="C30" s="46" t="n">
+        <v>5</v>
+      </c>
+      <c r="D30" s="47" t="inlineStr">
+        <is>
+          <t>BLUEFORGE MONEY IS ~23 MONTHS OLD, NOT A 2026 TRIGGER. why_now frames it as current momentum ('the money is already obligated'). The award was made 10 September 2024: $950,744,520 cost-plus-fixed-fee, with $503M of FY2024 money obligated and options to ~$980M, sole-sourced under 10 U.S.C. 3204(a)(1). Amount and existence confirmed; recency is not. Sources: https://news.usni.org/2024/09/10/navy-awards-blueforge-alliance-951m-contract-for-uplifting-u-s-submarine-base , https://breakingdefense.com/2024/09/navy-awards-blueforge-alliance-new-950m-contract-to-boost-sub-industrial-base/</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="78" customHeight="1">
+      <c r="A31" s="52" t="n">
+        <v>3</v>
+      </c>
+      <c r="B31" s="53" t="inlineStr">
+        <is>
+          <t>NQA-1 qualification and commercial grade dedication as a service</t>
+        </is>
+      </c>
+      <c r="C31" s="52" t="n">
+        <v>6</v>
+      </c>
+      <c r="D31" s="53" t="inlineStr">
+        <is>
+          <t>SUBMARINE SUPPLIER CONTRACTION CONFIRMED BUT WITH A CONFLICTING DATA POINT. '17,000 to about 5,000' is corroborated ('roughly 5,000 domestic suppliers today compared to nearly 17,000 at the end of the Cold War'). However another source states that by 2017 there were only ~3,000 active suppliers in the submarine industrial base, implying the 5,000 figure may count re-recruited/inactive firms. Either way, this population is gated by NAVSEA requirements, not Appendix B/NQA-1 — the record silently blends two different qualification regimes into one buyer universe. Sources: https://www.businessfacilities.com/u-s-navys-maritime-industrial-base-program-releases-1st-annual-report/ , https://americanaffairsjournal.org/2024/05/sunk-at-the-pier-crisis-in-the-american-submarine-industrial-base/ , https://warontherocks.com/the-sinking-submarine-industrial-base/</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="78" customHeight="1">
+      <c r="A32" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="B32" s="47" t="inlineStr">
+        <is>
+          <t>NQA-1 qualification and commercial grade dedication as a service</t>
+        </is>
+      </c>
+      <c r="C32" s="46" t="n">
+        <v>7</v>
+      </c>
+      <c r="D32" s="47" t="inlineStr">
+        <is>
+          <t>POSITIVE CORRECTION — the record was too pessimistic about its own trigger. screening states 'The 23 Mar 2026 NSI report could not be verified.' It is fully verified, at the exact URL, with the NQA-1 quote intact. Source: https://www.ans.org/news/2026-03-23/article-7870/nsi-report-addresses-supply-chain-bottlenecks/</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="78" customHeight="1">
+      <c r="A33" s="52" t="n">
+        <v>3</v>
+      </c>
+      <c r="B33" s="53" t="inlineStr">
+        <is>
+          <t>NQA-1 qualification and commercial grade dedication as a service</t>
+        </is>
+      </c>
+      <c r="C33" s="52" t="n">
+        <v>8</v>
+      </c>
+      <c r="D33" s="53" t="inlineStr">
+        <is>
+          <t>NO PUBLISHED PRICE ANYWHERE SUPPORTS THE $75-150k ANCHOR. The '$75-150k per shop' figure originates in the record itself and searches found zero corroboration. Every CGD and NQA-1 provider found (Kinectrics, Constellation PowerLabs, Westinghouse, Dupill, Joseph Oat, NAC International, Strata-G, GQA) quotes per-project on request with no published rates; DOE's own CGD handbook advises estimating CGD cost case-by-case against simply buying from an NQA-1 supplier. The only hard prices found in the entire adjacent market are a $995/person CGD workshop and a $0 MEP on-ramp. acv_usd of $95,000 is therefore an unsourced assumption inherited from the record, not a market price. Sources: https://jetsquality.com/commercial-grade-dedication-workshop/ , https://tmep.cis.tennessee.edu/nqa-1 , https://www.standards.doe.gov/standards-documents/1200/1230-bhdbk-2019/@@images/file</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="78" customHeight="1">
+      <c r="A34" s="46" t="n">
+        <v>4</v>
+      </c>
+      <c r="B34" s="47" t="inlineStr">
+        <is>
+          <t>PFAS-Compliant Biosolids Outlet Exchange for the Mid-Atlantic</t>
+        </is>
+      </c>
+      <c r="C34" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" s="47" t="inlineStr">
+        <is>
+          <t>THE CENTRAL PREMISE IS UNDERCUT: The record calls Maryland SB 719 'the strongest-verified trigger in this batch.' It is verified as to text and date, but Maryland's 50 ppb threshold is being criticized precisely because 'the thresholds are set high enough that most wastewater plants in the state already meet them,' and MDE's own August 2024 data-based recommendation was a 100 ppb cutoff. A ban most plants already clear does not convert a free disposal route into a paid one at scale. Source: https://www.medicaldaily.com/maryland-pfas-biosolids-law-sb719-farmland-criticism-476824 and https://www.bdlaw.com/publications/evolving-state-regulation-of-biosolids-recycling-in-the-pfas-era/</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="78" customHeight="1">
+      <c r="A35" s="52" t="n">
+        <v>4</v>
+      </c>
+      <c r="B35" s="53" t="inlineStr">
+        <is>
+          <t>PFAS-Compliant Biosolids Outlet Exchange for the Mid-Atlantic</t>
+        </is>
+      </c>
+      <c r="C35" s="52" t="n">
+        <v>2</v>
+      </c>
+      <c r="D35" s="53" t="inlineStr">
+        <is>
+          <t>EPA'S 1 JULY 2026 GUIDANCE IS VOLUNTARY, DRAFT, AND STILL IN COMMENT. EPA's own language: it 'provides voluntary recommendations' and 'does not have the force and effect of law, nor does it bind the public in any way.' Comment period closes 4 September 2026 (Docket EPA-HQ-OW-2026-2509). The record's why_now treats it as 'pushing systems toward industrial source identification' — it requests feedback on doing so. Source: https://www.epa.gov/biosolids/draft-guidance-reducing-risk-perfluorooctanoic-acid-pfoa-and-perfluorooctane-sulfonic</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="78" customHeight="1">
+      <c r="A36" s="46" t="n">
+        <v>4</v>
+      </c>
+      <c r="B36" s="47" t="inlineStr">
+        <is>
+          <t>PFAS-Compliant Biosolids Outlet Exchange for the Mid-Atlantic</t>
+        </is>
+      </c>
+      <c r="C36" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="D36" s="47" t="inlineStr">
+        <is>
+          <t>PENNSYLVANIA'S PROPOSED THRESHOLD IS 100 ppb, NOT COMPARABLE TO MARYLAND'S 50 ppb. The record's 90-day plan targets 'where Maryland's October 2028 clock and Pennsylvania's pending rule overlap.' PA's draft PAG-07/PAG-08 permits (published 4 July 2026, comments to 2 September 2026) prohibit at 100 µg/kg — twice as permissive — with only a reduced-rate/source-reduction trigger at 20 µg/kg. The overlap the wedge depends on is half as tight as assumed, and PA's rule is not final. Source: https://www.wastedive.com/news/pennsylvania-regulators-propose-pfas-in-biosolids-limits/825770/</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="78" customHeight="1">
+      <c r="A37" s="52" t="n">
+        <v>4</v>
+      </c>
+      <c r="B37" s="53" t="inlineStr">
+        <is>
+          <t>PFAS-Compliant Biosolids Outlet Exchange for the Mid-Atlantic</t>
+        </is>
+      </c>
+      <c r="C37" s="52" t="n">
+        <v>4</v>
+      </c>
+      <c r="D37" s="53" t="inlineStr">
+        <is>
+          <t>THE RECORD MISSES VIRGINIA ENTIRELY AS A TRIGGER. Virginia HB 1443 (Chapter 853), signed April 2026, mandates sampling from 1 January 2027 and prohibits land application at a 12-month rolling average of 50 ppb PFOS or PFOA. That binds 21 months BEFORE Maryland's 1 October 2028 date. The record lists Virginia only as a target geography and names Washington, Rhode Island, Oregon and Wisconsin instead. The earliest Mid-Atlantic clock was not in the record. Source: https://www.wastedive.com/news/virginia-biosolids-land-application-ban-limits-PFAS/815044/</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="78" customHeight="1">
+      <c r="A38" s="46" t="n">
+        <v>4</v>
+      </c>
+      <c r="B38" s="47" t="inlineStr">
+        <is>
+          <t>PFAS-Compliant Biosolids Outlet Exchange for the Mid-Atlantic</t>
+        </is>
+      </c>
+      <c r="C38" s="46" t="n">
+        <v>5</v>
+      </c>
+      <c r="D38" s="47" t="inlineStr">
+        <is>
+          <t>BUYER UNIVERSE OVERSTATED ROUGHLY 4x. Record says 900. Sourced counts: Virginia's fiscal impact analysis puts the affected population at 'about 60 wastewater treatment plants around the state'; Maryland has 'about 50 biosolids generators submitting PFAS testing data.' Scaling those to PA and DE gives ~220 biosolids-generating entities across MD/PA/VA/DE, cross-checked against roughly 2,500 major POTWs filing EPA biosolids annual reports nationwide. Sources: https://www.wastedive.com/news/virginia-biosolids-land-application-ban-limits-PFAS/815044/ , https://conduitstreet.mdcounties.org/2026/03/02/tackling-pfas-while-addressing-ratepayer-impacts-and-implementation-feasibility/ , https://echo.epa.gov/help/facility-search/biosolids-annual-report-search-results-help</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="78" customHeight="1">
+      <c r="A39" s="52" t="n">
+        <v>4</v>
+      </c>
+      <c r="B39" s="53" t="inlineStr">
+        <is>
+          <t>PFAS-Compliant Biosolids Outlet Exchange for the Mid-Atlantic</t>
+        </is>
+      </c>
+      <c r="C39" s="52" t="n">
+        <v>6</v>
+      </c>
+      <c r="D39" s="53" t="inlineStr">
+        <is>
+          <t>THE MODEL IS INTERNALLY INCONSISTENT AGAINST REAL MARKET SIZE. Bluefield Research puts total US municipal biosolids management spend at $2.5 billion in 2025, rising to more than $4.8 billion annually by 2035. The four Mid-Atlantic states are ~8.7% of US population, implying roughly $220M of annual regional spend today. The record's Y5 of 42 POTWs and 'roughly $70M of GMV under management' would be about 30% of the entire Mid-Atlantic biosolids spend, routed by a firm the record itself describes as a two-person broker with no trucks. Source: https://smartwatermagazine.com/news/bluefield-research/us-utilities-face-48-billion-biosolids-challenge-amid-rising-costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="78" customHeight="1">
+      <c r="A40" s="46" t="n">
+        <v>4</v>
+      </c>
+      <c r="B40" s="47" t="inlineStr">
+        <is>
+          <t>PFAS-Compliant Biosolids Outlet Exchange for the Mid-Atlantic</t>
+        </is>
+      </c>
+      <c r="C40" s="46" t="n">
+        <v>7</v>
+      </c>
+      <c r="D40" s="47" t="inlineStr">
+        <is>
+          <t>THE 'CROSS-STATE ARBITRAGE' IS AN EXISTING, ALREADY-RUNNING TRADE ROUTE, NOT A GAP. 'About one-fourth of the 115,000 dry tons of biosolids spread on farmland in Virginia in 2024 came from Maryland, according to the Virginia Department of Environmental Quality.' Maryland-to-Virginia interstate movement is established practice served by incumbent haulers — Synagro is headquartered in Baltimore. Source: https://www.bayjournal.com/news/pollution/forever-chemicals-in-sludge-fertilizer-resisted-in-virginia-maryland/article_68cc43c2-f99d-4cb4-99cd-2b984453af71.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="78" customHeight="1">
+      <c r="A41" s="52" t="n">
+        <v>4</v>
+      </c>
+      <c r="B41" s="53" t="inlineStr">
+        <is>
+          <t>PFAS-Compliant Biosolids Outlet Exchange for the Mid-Atlantic</t>
+        </is>
+      </c>
+      <c r="C41" s="52" t="n">
+        <v>8</v>
+      </c>
+      <c r="D41" s="53" t="inlineStr">
+        <is>
+          <t>THE SYNAGRO/DENALI 'SWAP' RAN ONE DIRECTION ON MUNICIPAL BIOSOLIDS. The record says 'the two swapped asset portfolios in Aug 2024,' implying symmetry. In fact Synagro acquired Denali's municipal biosolids services business in California in exchange for Synagro's industrial non-biosolids organics assets in Arkansas and Missouri — municipal biosolids concentrated further into Synagro. Source: https://www.synagro.com/2024/08/22/synagro-and-denali-close-mutually-beneficial-asset-transfer-agreement/</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="78" customHeight="1">
+      <c r="A42" s="46" t="n">
+        <v>4</v>
+      </c>
+      <c r="B42" s="47" t="inlineStr">
+        <is>
+          <t>PFAS-Compliant Biosolids Outlet Exchange for the Mid-Atlantic</t>
+        </is>
+      </c>
+      <c r="C42" s="46" t="n">
+        <v>9</v>
+      </c>
+      <c r="D42" s="47" t="inlineStr">
+        <is>
+          <t>PFAS LIABILITY ON THE ROUTING PARTY IS ALREADY MATERIALIZING, WHICH THE RECORD FLAGS ONLY AS 'increasingly uninsurable.' Concretely: Synagro is defending a PFAS lawsuit tied to Johnson County, Kansas, and Fort Worth terminated a 10-year Synagro biosolids contract producing 26,500 tons of fertilizer annually over PFAS concerns. A broker that directs tons to farmland inherits that exposure with no balance sheet behind it. Sources: https://www.wastedive.com/news/synagro-johnson-county-pfas-lawsuit-study/742927/ , https://www.mgmlaw.com/news-insights/biosolids-on-trial-the-pfas-lawsuit-against-synagro</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="78" customHeight="1">
+      <c r="A43" s="52" t="n">
+        <v>5</v>
+      </c>
+      <c r="B43" s="53" t="inlineStr">
+        <is>
+          <t>Reachability-grade SBOMs and kernel-CVE triage for embedded Linux</t>
+        </is>
+      </c>
+      <c r="C43" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" s="53" t="inlineStr">
+        <is>
+          <t>FATAL — THE CORE DIFFERENTIATOR IS ALREADY UPSTREAM IN YOCTO, FOR FREE. The record's product is 'index reachability from the kernel .config, defconfig and driver set... emit OpenVEX with justification strings.' The Yocto Project's own security manual ships improve_kernel_cve_report.py, which 'leverages CVE kernel metadata and the SPDX_INCLUDE_COMPILED_SOURCES variable to update CVE reports, reducing CVE false positives by 70%-80% and providing detailed responses for all kernel-related CVEs by analyzing the files used to build the kernel.' It consumes VEX as input, enriches it with Linux kernel CNA data, and 'is decoupled from the build and can be run outside of the BitBake environment.' It came from an Ericsson patch series titled literally 'Check compiled files to filter kernel CVEs' (Daniel Turull, oe-core patchwork v3, 29 Apr 2025). The record's why_overlooked asserts the market 'skipped... the reachability decision.' It did not — the base build system the customer already runs does it, at $0, and it is compiled-file-granular rather than merely .config-granular. Sources: https://docs.yoctoproject.org/security-manual/vulnerabilities.html and https://patchwork.yoctoproject.org/project/oe-core/cover/20250429143904.634082-1-daniel.turull@ericsson.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="78" customHeight="1">
+      <c r="A44" s="46" t="n">
+        <v>5</v>
+      </c>
+      <c r="B44" s="47" t="inlineStr">
+        <is>
+          <t>Reachability-grade SBOMs and kernel-CVE triage for embedded Linux</t>
+        </is>
+      </c>
+      <c r="C44" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="D44" s="47" t="inlineStr">
+        <is>
+          <t>MAJOR — THE BEST-FUNDED COMPETITOR IS ABSENT FROM THE RECORD. Exein (Rome) raised €100M in Dec 2025 led by Blue Cloud Ventures with HV Capital, Intrepid Growth Partners, Geodesic Capital and J.P. Morgan, taking 2025 total to €170M at roughly €700M valuation. Its embedded, hardware-agnostic security platform 'already protects more than 1.5 billion devices' across energy, healthcare, defence, automotive, aerospace, industrial automation and semiconductors, expected to pass two billion in Q1 2026, and the money funds 'a multi-deal M&amp;A programme in 2026 in Europe and the US.' Exein publishes CRA manufacturer guidance directly. The record's crowding_check names Timesys/Lynx, Wind River, Foundries/Qualcomm and Black Duck and misses an EU-native, €700M-valuation incumbent that is actively acquiring in this exact space. Sources: https://www.securityweek.com/iot-security-firm-exein-raises-e100-million/ , https://resiliencemedia.co/exein-the-embedded-security-startup-nabs-e100m-at-e700m-valuation/ , https://www.exein.io/blog/cyber-resilience-act-what-manufacturers-need-to-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="78" customHeight="1">
+      <c r="A45" s="52" t="n">
+        <v>5</v>
+      </c>
+      <c r="B45" s="53" t="inlineStr">
+        <is>
+          <t>Reachability-grade SBOMs and kernel-CVE triage for embedded Linux</t>
+        </is>
+      </c>
+      <c r="C45" s="52" t="n">
+        <v>3</v>
+      </c>
+      <c r="D45" s="53" t="inlineStr">
+        <is>
+          <t>MAJOR — ACV $55,000 IS ABOVE WHAT THE INCUMBENTS' OWN PRICE ANCHORS SUPPORT. Lynx markets Vigiles as delivering 'potential annual savings of up to $48,000 a year per SBOM' — i.e. the incumbent's own claimed VALUE ceiling for the whole triage function is $48k, and the record wants $55k of PRICE for a subset of it. Lynx separately prices its Linux OS/BSP Maintenance service at 'less than 1/2 the cost of a junior engineer' — call it $40-60k/yr for a bundle that includes the BSP itself, not just CVE triage. The record's acv_basis instead reasons from displacing 0.25-0.4 FTE of a SENIOR engineer at $60-100k loaded. Wrong reference class: the market clears against junior-engineer economics, with a $0 upstream floor. Sources: https://www.lynx.com/press-releases/lynx-sees-growing-demand-for-timesys-vigiles , https://www.lynx.com/solutions/linux-lts-bsp-maintenance</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="78" customHeight="1">
+      <c r="A46" s="46" t="n">
+        <v>5</v>
+      </c>
+      <c r="B46" s="47" t="inlineStr">
+        <is>
+          <t>Reachability-grade SBOMs and kernel-CVE triage for embedded Linux</t>
+        </is>
+      </c>
+      <c r="C46" s="46" t="n">
+        <v>4</v>
+      </c>
+      <c r="D46" s="47" t="inlineStr">
+        <is>
+          <t>THE '~50 KERNEL CVEs/WEEK' FIGURE IS A BAD AVERAGE AND MISDESCRIBES THE WORKLOAD. Observed 2026 data: 763 kernel CVEs in the week 18-25 Jul 2026, nearly all in one batch on 25 Jul; 432 published in a single day on 2026-07-19; but only 3 in the week 11-18 Jul. The load is bursty batches in the hundreds, not a steady ~50. This cuts BOTH ways — it makes manual triage even less viable (good for the thesis) but it means a 24-hour Art. 14 clock has to absorb 700-CVE dumps, which is a much harder SLA than the record scoped. Sources: https://www.techveda.live/2026/07/25/linux-kernel-cves-25-jul-2026/ , https://www.techveda.live/2026/07/18/linux-kernel-cves-18-jul-2026/ , https://itstorage.net/index.php/hem/newsm/899-massive-linux-security-update-432-kernel-cves-published-in-single-day-2026-07-19-disclosure-surge</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="78" customHeight="1">
+      <c r="A47" s="52" t="n">
+        <v>5</v>
+      </c>
+      <c r="B47" s="53" t="inlineStr">
+        <is>
+          <t>Reachability-grade SBOMs and kernel-CVE triage for embedded Linux</t>
+        </is>
+      </c>
+      <c r="C47" s="52" t="n">
+        <v>5</v>
+      </c>
+      <c r="D47" s="53" t="inlineStr">
+        <is>
+          <t>BSI TR-03183-2 IS NOT A COMPLIANCE BAR — IT IS A NON-BINDING GERMAN GUIDELINE SCHEDULED FOR REPLACEMENT. The record's screening states 'BSI TR-03183-2 is real and is the de facto EU quality bar' and the product's free wedge is 'a free BSI TR-03183-2 scoring report.' BSI's own position: the guideline 'is not binding, cannot serve as a presumption of conformity, and will be replaced by harmonized European standards once those exist.' De facto reference today, yes; but the wedge is anchored to a document with a known expiry and no legal force, and a manufacturer's actual presumption of conformity will come from harmonised standards that do not yet exist. Sources: https://craevidence.com/cra-compliance/sbom/bsi-tr-03183 , https://www.bsi.bund.de/EN/Themen/Unternehmen-und-Organisationen/Standards-und-Zertifizierung/Technische-Richtlinien/TR-nach-Thema-sortiert/tr03183/tr-03183.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="78" customHeight="1">
+      <c r="A48" s="46" t="n">
+        <v>5</v>
+      </c>
+      <c r="B48" s="47" t="inlineStr">
+        <is>
+          <t>Reachability-grade SBOMs and kernel-CVE triage for embedded Linux</t>
+        </is>
+      </c>
+      <c r="C48" s="46" t="n">
+        <v>6</v>
+      </c>
+      <c r="D48" s="47" t="inlineStr">
+        <is>
+          <t>BUYER_UNIVERSE 6,000 HAS NO SOURCE AND THE ONE LIVE ANCHOR IS ~2,210. The record's own buyer_universe_basis admits 'MY REASONING/RECALL, not researched.' The only countable proxy I could source is 2,210 verified companies using Yocto as of 2026 (Landbase technology-adoption data); the Yocto Project itself has only '30+ member companies.' No EU impact-assessment company count exists in public search results — the impact assessment quantifies euros (~€29bn compliance cost vs ~€290bn incident savings), not firms. 6,000 is roughly 2.7x the only observable anchor. Source: https://data.landbase.com/technology/yocto/</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="78" customHeight="1">
+      <c r="A49" s="52" t="n">
+        <v>5</v>
+      </c>
+      <c r="B49" s="53" t="inlineStr">
+        <is>
+          <t>Reachability-grade SBOMs and kernel-CVE triage for embedded Linux</t>
+        </is>
+      </c>
+      <c r="C49" s="52" t="n">
+        <v>7</v>
+      </c>
+      <c r="D49" s="53" t="inlineStr">
+        <is>
+          <t>NETRISE — THE BINARY-SBOM ADJACENT — HAS BEEN ACQUIRED BY ACCENTURE (total raised $24.8M over 3 rounds). The record treats binary firmware analysis as an open niche; it is consolidating into a global services firm that sells to exactly the industrial and medical manufacturers named as first customers. Source: https://tracxn.com/d/companies/netrise/__RqUz9fXFppaOuqosh8zeXUzr2U52M2lHYDoZUPSMZGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="78" customHeight="1">
+      <c r="A50" s="46" t="n">
+        <v>5</v>
+      </c>
+      <c r="B50" s="47" t="inlineStr">
+        <is>
+          <t>Reachability-grade SBOMs and kernel-CVE triage for embedded Linux</t>
+        </is>
+      </c>
+      <c r="C50" s="46" t="n">
+        <v>8</v>
+      </c>
+      <c r="D50" s="47" t="inlineStr">
+        <is>
+          <t>INTERNAL INCONSISTENCY IN THE RECORD ITSELF: why_overlooked says "'yocto SBOM' returns eleven repositories"; the screening block says "'yocto SBOM' returns 17 repos... All exactly as claimed." Both cannot be right, and the screening block claims to have verified the first. Minor, but it means the GitHub scarcity evidence was not actually re-checked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="78" customHeight="1">
+      <c r="A51" s="52" t="n">
+        <v>6</v>
+      </c>
+      <c r="B51" s="53" t="inlineStr">
+        <is>
+          <t>Funded-Claim Detection for Casualty Reserving</t>
+        </is>
+      </c>
+      <c r="C51" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" s="53" t="inlineStr">
+        <is>
+          <t>THE REGISTRY IS FREE AND PUBLIC. The record's central why_overlooked claim — 'a journalist doing FOIA to build the list means no commercial data provider had it' — is materially wrong. Georgia DBF instructs the public: 'To search for litigation financiers, please visit www.nmlsconsumeraccess.org.' The registrant list is a no-cost public lookup on NMLS Consumer Access. Source: https://dbf.georgia.gov/litigation-financiers/how-do-i-apply-litigation-financier-registration</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="78" customHeight="1">
+      <c r="A52" s="46" t="n">
+        <v>6</v>
+      </c>
+      <c r="B52" s="47" t="inlineStr">
+        <is>
+          <t>Funded-Claim Detection for Casualty Reserving</t>
+        </is>
+      </c>
+      <c r="C52" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="D52" s="47" t="inlineStr">
+        <is>
+          <t>THE WEDGE PRODUCT HAS ALREADY SHIPPED — AS JOURNALISM. The record proposes selling 'the list of funders, their owners, their affiliated firms' as a paid quarterly report. ALM published exactly that on 17 Jul 2026: 'Georgia's New Litigation Funding Registry Reveals Industry's Owners, Lawyer Ties,' built from the open-records return, with an explicit ongoing series on 'companies that have — and haven't — registered.' The record cites this article as PROOF OF WHITESPACE; it is in fact a competitor shipping the deliverable. Source: https://www.law.com/dailyreportonline/2026/07/17/dataset-who-owns-georgias-litigation-funders/</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="78" customHeight="1">
+      <c r="A53" s="52" t="n">
+        <v>6</v>
+      </c>
+      <c r="B53" s="53" t="inlineStr">
+        <is>
+          <t>Funded-Claim Detection for Casualty Reserving</t>
+        </is>
+      </c>
+      <c r="C53" s="52" t="n">
+        <v>3</v>
+      </c>
+      <c r="D53" s="53" t="inlineStr">
+        <is>
+          <t>THE DATASET IS 41 ROWS. 'At Least 41 Companies Have Registered as Litigation Funders in Georgia' (Law.com, 13 Jul 2026). The record never states the size of the raw material it calls the moat. Forty-one entities is a spreadsheet, not a data utility, and the same article carries the industry's own verdict in its headline: 'Some Ask if It Really Matters,' noting major industry players may not be captured. Source: https://www.law.com/dailyreportonline/2026/07/13/at-least-41-companies-have-registered-as-litigation-funders-in-ga-some-ask-if-it-really-matters/</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="78" customHeight="1">
+      <c r="A54" s="46" t="n">
+        <v>6</v>
+      </c>
+      <c r="B54" s="47" t="inlineStr">
+        <is>
+          <t>Funded-Claim Detection for Casualty Reserving</t>
+        </is>
+      </c>
+      <c r="C54" s="46" t="n">
+        <v>4</v>
+      </c>
+      <c r="D54" s="47" t="inlineStr">
+        <is>
+          <t>THE EY FIGURE IS OVERSTATED ~2x AS APPLIED TO INSURERS. Record: 'EY projects TPLF could add as much as $50B in costs to US insurers over five years.' Sourced: 'the top end of a range of estimates of direct costs that will be paid to funders by casualty insurers estimated at $25 billion over a five-year period (2024-2028), while the full $50 billion figure includes indirect costs.' The 4%-5.2% loss-ratio drag IS confirmed. Sources: https://www.insurancejournal.com/magazines/mag-features/2025/10/06/842440.htm and https://www.insurancebusinessmag.com/us/news/breaking-news/insurers-warned-tplf-could-add-50b-to-industry-costs-552353.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="78" customHeight="1">
+      <c r="A55" s="52" t="n">
+        <v>6</v>
+      </c>
+      <c r="B55" s="53" t="inlineStr">
+        <is>
+          <t>Funded-Claim Detection for Casualty Reserving</t>
+        </is>
+      </c>
+      <c r="C55" s="52" t="n">
+        <v>5</v>
+      </c>
+      <c r="D55" s="53" t="inlineStr">
+        <is>
+          <t>THE SELF-CANNIBALIZATION IS HAPPENING NOW, NOT IN 2028-29. The record's downside_note models free disclosure arriving 'by 2029.' Live evidence puts it in 2026: the Arizona Supreme Court 'has amended rules of civil procedure in the state, requiring parties in civil cases to disclose the identity, financial terms, and degree of strategic control of any third-party litigation funders at the outset of litigation'; New York's Consumer Litigation Funding Act 'takes effect June 17, 2026, requiring every consumer litigation funding company doing business in the state to register, post a surety bond, and submit to character-and-fitness review'; Ohio 'requires both commercial and consumer funders to register with the state and disclose funding agreements to the attorney general'; West Virginia and Wisconsin have automatic disclosure. Court-rule disclosure at the outset of litigation delivers funder identity per case, for free — which is the exact output the product infers. Sources: https://global.lockton.com/us/en/news-insights/third-party-litigation-funding-reforms-gain-momentum-but-liability-market-pressures-persist , https://www.harrisbeachmurtha.com/insights/ny-consumer-litigation-funding-act-litigation-implications-for-defendants/ , https://news.bloomberglaw.com/business-and-practice/ohio-to-join-growing-list-of-states-regulating-litigation-funding</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="78" customHeight="1">
+      <c r="A56" s="46" t="n">
+        <v>6</v>
+      </c>
+      <c r="B56" s="47" t="inlineStr">
+        <is>
+          <t>Funded-Claim Detection for Casualty Reserving</t>
+        </is>
+      </c>
+      <c r="C56" s="46" t="n">
+        <v>6</v>
+      </c>
+      <c r="D56" s="47" t="inlineStr">
+        <is>
+          <t>THE $125,000 ACV HAS NO SOURCED SUPPORT AND THE ONLY REAL PRICES I COULD FIND ARE AN ORDER OF MAGNITUDE LOWER. Lex Machina — the closest named comparable in the record's own acv_basis — sells at 'annual subscriptions that can range from several thousand to tens of thousands of dollars.' Docket Alarm is $99/user/month list, $150-250/user/month enterprise. UniCourt Enterprise API tops out at $299/month on published tiers. Sources: https://www.selecthub.com/p/legal-software/lex-machina/ , https://www.docketalarm.com/pricing , https://unicourt.com/pricing</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="78" customHeight="1">
+      <c r="A57" s="52" t="n">
+        <v>6</v>
+      </c>
+      <c r="B57" s="53" t="inlineStr">
+        <is>
+          <t>Funded-Claim Detection for Casualty Reserving</t>
+        </is>
+      </c>
+      <c r="C57" s="52" t="n">
+        <v>7</v>
+      </c>
+      <c r="D57" s="53" t="inlineStr">
+        <is>
+          <t>THE UCC-1 LEG IS A COMMODITY PURCHASE, NOT A MOAT. CSC is 'the leading provider of UCC Search, Filing, and Online Portfolio Management services, providing the industry's largest online UCC database.' Anyone can buy the same substrate. Source: https://www.cscglobal.com/service/business-administration/ucc-services/</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="78" customHeight="1">
+      <c r="A58" s="46" t="n">
+        <v>6</v>
+      </c>
+      <c r="B58" s="47" t="inlineStr">
+        <is>
+          <t>Funded-Claim Detection for Casualty Reserving</t>
+        </is>
+      </c>
+      <c r="C58" s="46" t="n">
+        <v>8</v>
+      </c>
+      <c r="D58" s="47" t="inlineStr">
+        <is>
+          <t>THE RECORD'S first_pass_model BUYER UNIVERSE OF 250 IS LIKELY 30-50% TOO HIGH. Public sizing artifacts stop well short of 250 casualty-relevant groups: NAIC's market share reports cover the top 125 P&amp;C groups countrywide, AM Best publishes a World's 50 Largest Reinsurers list, and the standard US ranking is a Top 100. Sources: https://content.naic.org/sites/default/files/publication-msr-pb-property-casualty.pdf , https://web.ambest.com/docs/default-source/events/best's-market-segment-report---worlds-top-50-largest-reinsurers.pdf , https://www.reinsurancene.ws/top-100-u-s-property-casualty-insurance-companies/</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="78" customHeight="1">
+      <c r="A59" s="52" t="n">
+        <v>7</v>
+      </c>
+      <c r="B59" s="53" t="inlineStr">
+        <is>
+          <t>Forward exchange for transformer and switchgear production slots</t>
+        </is>
+      </c>
+      <c r="C59" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="D59" s="53" t="inlineStr">
+        <is>
+          <t>CORE PREMISE CONTRADICTED -- THE OEM IS ALREADY THE CLEARINGHOUSE. The record's monetizable fact is that dead projects strand paid-for slots with 'no way to resell.' SemiAnalysis (18 June 2026) states the opposite mechanism directly: 'Projects getting canceled that never placed equipment orders don't remove orders from manufacturers' books, and when real orders do fall away, the slot is reallocated to the next buyer in line rather than vanishing.' Two things follow. (a) The vast majority of cancelled announcements never placed an order, so no slot exists to orphan. (b) When a real order is released, the OEM -- who holds the waitlist -- reallocates it instantly and captures the value. There is no accumulating pool of orphaned slots for a third-party desk to clear. Source: https://newsletter.semianalysis.com/p/stop-saying-half-of-2026-us-datacenter</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="78" customHeight="1">
+      <c r="A60" s="46" t="n">
+        <v>7</v>
+      </c>
+      <c r="B60" s="47" t="inlineStr">
+        <is>
+          <t>Forward exchange for transformer and switchgear production slots</t>
+        </is>
+      </c>
+      <c r="C60" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="D60" s="47" t="inlineStr">
+        <is>
+          <t>SLOTS ARE NOT DISTRESSED ASSETS -- THEY ARE DEFERRABLE OPTIONS THE HOLDER KEEPS. The record models the slot as a de facto option that becomes worthless to a seller with a dead site, creating a motivated counterparty. GE Vernova's slot reservation agreements are described as 'non-firm arrangements where a reservation can be deferred or cancelled if power demand forecasts soften or financing tightens, distinguishing them from firm equipment orders.' A developer whose site dies defers the slot rather than forfeiting it. That removes the motivated seller the entire two-sided market depends on. Source: https://electroneconomics.substack.com/p/slotting-in-the-future-gas-turbine</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="78" customHeight="1">
+      <c r="A61" s="52" t="n">
+        <v>7</v>
+      </c>
+      <c r="B61" s="53" t="inlineStr">
+        <is>
+          <t>Forward exchange for transformer and switchgear production slots</t>
+        </is>
+      </c>
+      <c r="C61" s="52" t="n">
+        <v>3</v>
+      </c>
+      <c r="D61" s="53" t="inlineStr">
+        <is>
+          <t>THE PHANTOM-DEMAND STATISTIC THE THESIS RESTS ON WAS PUBLICLY REBUTTED, AND ON THE SAME DAY AS THE FERC TRIGGER. SemiAnalysis published 'Stop Saying Half of 2026 US Datacenter Capacity Is Canceled' on 18 June 2026, arguing the narrative came from AI tools scraping unverified press releases with 'severe statistical denominator bias.' Its counter-evidence: it revised its own 2026 US self-build capacity projection by only ~1% and hosted capacity by under 5% over six months, and satellite verification put the two largest US hyperscalers alone above 5 GW of self-build under construction. The record's why_now cites '12-16 GW announced with only about 5 GW under construction' as evidence of collapse -- that 5 GW figure is exceeded by two companies' self-build alone. The record acknowledges the rebuttal exists in kill_risk but still builds the thesis on the refuted number. Source: https://newsletter.semianalysis.com/p/stop-saying-half-of-2026-us-datacenter</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="78" customHeight="1">
+      <c r="A62" s="46" t="n">
+        <v>7</v>
+      </c>
+      <c r="B62" s="47" t="inlineStr">
+        <is>
+          <t>Forward exchange for transformer and switchgear production slots</t>
+        </is>
+      </c>
+      <c r="C62" s="46" t="n">
+        <v>4</v>
+      </c>
+      <c r="D62" s="47" t="inlineStr">
+        <is>
+          <t>LEAD-TIME FIGURES ARE MISATTRIBUTED AND INTERNALLY INCONSISTENT. The record gives two different sets: why_now says '75-110 weeks substation, 100-150+ weeks GSU'; screening says '128 weeks LPT, 144 weeks GSU' attributed to 'pv-magazine USA, 11 May 2026.' The 128/144 pair is Wood Mackenzie's Q2 2025 survey, not a May 2026 original. Wood Mackenzie's 2026 read is higher still: substation units above 160 weeks, largest HV units up to four years. The record simultaneously understates the constraint and miscites its own source. Sources: https://www.powermag.com/transformers-in-2026-shortage-scramble-or-self-inflicted-crisis/ and https://www.industrialsage.com/power-transformer-lead-times-us-grid-shortage/</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="78" customHeight="1">
+      <c r="A63" s="52" t="n">
+        <v>7</v>
+      </c>
+      <c r="B63" s="53" t="inlineStr">
+        <is>
+          <t>Forward exchange for transformer and switchgear production slots</t>
+        </is>
+      </c>
+      <c r="C63" s="52" t="n">
+        <v>5</v>
+      </c>
+      <c r="D63" s="53" t="inlineStr">
+        <is>
+          <t>GE VERNOVA SLOT TIGHTNESS IS MOSTLY NOT A DATA CENTER STORY. The record leans on GEV slot scarcity as proof of the datacenter-driven squeeze. In fact 'roughly 80% of the 100 gigawatts under contract is with traditional utility, independent power producer and industrial customers, while the remaining 20% is explicitly tied to data center load.' The tradeable-slot population in the buyer segment the record targets is one fifth the size implied. Source: https://www.power-eng.com/gas/turbines/data-centers-drive-record-surge-in-ge-vernova-power-equipment-orders-as-turbine-slots-tighten-through-2030/</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="78" customHeight="1">
+      <c r="A64" s="46" t="n">
+        <v>7</v>
+      </c>
+      <c r="B64" s="47" t="inlineStr">
+        <is>
+          <t>Forward exchange for transformer and switchgear production slots</t>
+        </is>
+      </c>
+      <c r="C64" s="46" t="n">
+        <v>6</v>
+      </c>
+      <c r="D64" s="47" t="inlineStr">
+        <is>
+          <t>SHOW CAUSE ORDERS WERE NOT ISSUED IN DOCKET RM26-4. The record cites '(Docket RM26-4)' twice. FERC proceeded via individualized Section 206 show cause proceedings against each RTO and left RM26-4 open as a separate generic rulemaking. Source: https://www.ferc.gov/rm26-4</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="78" customHeight="1">
+      <c r="A65" s="52" t="n">
+        <v>7</v>
+      </c>
+      <c r="B65" s="53" t="inlineStr">
+        <is>
+          <t>Forward exchange for transformer and switchgear production slots</t>
+        </is>
+      </c>
+      <c r="C65" s="52" t="n">
+        <v>7</v>
+      </c>
+      <c r="D65" s="53" t="inlineStr">
+        <is>
+          <t>THE 17 AUG 2026 DEADLINE IS EXTENDABLE AND MAY ALREADY BE IN ABEYANCE. RTOs could request abeyance of up to 90 days by 3 Aug 2026, and may request further extensions. The record presents 17 Aug as a fixed forcing function. Source: https://www.bracewell.com/resources/ferc-show-cause-orders-data-center-interconnection/</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="78" customHeight="1">
+      <c r="A66" s="46" t="n">
+        <v>7</v>
+      </c>
+      <c r="B66" s="47" t="inlineStr">
+        <is>
+          <t>Forward exchange for transformer and switchgear production slots</t>
+        </is>
+      </c>
+      <c r="C66" s="46" t="n">
+        <v>8</v>
+      </c>
+      <c r="D66" s="47" t="inlineStr">
+        <is>
+          <t>THE 2-4% TAKE RATE IS BELOW REAL MARKET COMPARABLES, NOT above them. Industrial equipment brokerage runs materially higher: a broker fee is 'typically calculated as 10% of the net value of goods sold as a direct result of an introduction,' and auction platforms charge seller commissions of 5-12%. This is the one correction that favors the record's economics -- but it applies to a transaction count the evidence says will be far smaller. Sources: https://idrywood.com/used-equipment-broker-terms and https://maascompanies.com/blog/article/used-equipment-resale-maximize-asset-recovery-in-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="78" customHeight="1">
+      <c r="A67" s="52" t="n">
+        <v>7</v>
+      </c>
+      <c r="B67" s="53" t="inlineStr">
+        <is>
+          <t>Forward exchange for transformer and switchgear production slots</t>
+        </is>
+      </c>
+      <c r="C67" s="52" t="n">
+        <v>9</v>
+      </c>
+      <c r="D67" s="53" t="inlineStr">
+        <is>
+          <t>ANZA IS FURTHER INTO THE BUYER'S WORKFLOW THAN THE RECORD CREDITS. The record describes Anza as a new-equipment exchange that is 'one product decision away.' Anza has already shipped a Transformer Procurement Service 'designed to streamline how developers, IPPs, EPCs, utilities, and data center developers procure medium- and high-voltage transformers' -- naming the exact buyer persona, the exact equipment class, and the exact voltage range in this record's ICP, on top of the exchange that already lists new power transformers and HV breakers. Sources: https://www.anzarenewables.com/press-release/anza-launches-novel-transformer-procurement-service-to-bring-transparency-and-efficiency-to-substation-equipment-sourcing/ and https://exchange.anzarenewables.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="78" customHeight="1">
+      <c r="A68" s="46" t="n">
+        <v>7</v>
+      </c>
+      <c r="B68" s="47" t="inlineStr">
+        <is>
+          <t>Forward exchange for transformer and switchgear production slots</t>
+        </is>
+      </c>
+      <c r="C68" s="46" t="n">
+        <v>10</v>
+      </c>
+      <c r="D68" s="47" t="inlineStr">
+        <is>
+          <t>THE 'ROUGHLY 200 DEVELOPERS WITH CANCELLED OR DELAYED PROJECTS' SELL-SIDE COUNT IS UNSOURCED AND I COULD NOT CORROBORATE IT. It appears only inside the record's own buildable_today text and is then reused as the basis for the 600-entity buyer universe. No search returned any count of distressed slot-holding developers. Both numbers should be treated as unsupported.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="78" customHeight="1">
+      <c r="A69" s="52" t="n">
+        <v>7</v>
+      </c>
+      <c r="B69" s="53" t="inlineStr">
+        <is>
+          <t>Forward exchange for transformer and switchgear production slots</t>
+        </is>
+      </c>
+      <c r="C69" s="52" t="n">
+        <v>11</v>
+      </c>
+      <c r="D69" s="53" t="inlineStr">
+        <is>
+          <t>CONSENT IS A VALUE-CAPTURE MOMENT FOR THE OEM, WHICH SHARPENS THE KILL RISK RATHER THAN SOFTENING IT. Novation 'cannot occur without the consent of all parties' and 'requires the counterparty's affirmative agreement to discharge the assignor,' and in practice 'suppliers use consent moments to ask for updated pricing, new minimums, shorter payment terms, or a reset of exclusivity.' The record's rebuttal to the skeptics -- that consent is routine when the OEM's slot stays filled at no cost -- ignores that the consent moment is precisely where the OEM reprices to market. Sources: https://www.upcounsel.com/assignment-vs-novation and https://olenderfeldman.com/anti-assignment-clauses-in-commercial-contracts-and-their-impact-on-sale-transactions/</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="78" customHeight="1">
+      <c r="A70" s="46" t="n">
+        <v>8</v>
+      </c>
+      <c r="B70" s="47" t="inlineStr">
+        <is>
+          <t>Key-state custody for LMS/XMSS firmware signing under CNSA 2.0</t>
+        </is>
+      </c>
+      <c r="C70" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="D70" s="47" t="inlineStr">
+        <is>
+          <t>CORE MECHANISM IS BANNED FOR THE TARGET BUYER. The one_line, thesis and buildable_today all rest on 'reserves disjoint HSS/XMSS-MT subtrees per builder so parallel CI can never collide.' CNSA 2.0 permits ONLY single-tree LMS and XMSS for NSS software/firmware signing; HSS and XMSS^MT are explicitly not approved. Source: https://www.wolfssl.com/cnsa-2-0-update-part-3-lms-and-xmss-2/ ('The multi-tree algorithms HSS and XMSSMT are not allowed... The hyper-tree components specified in NIST SP 800-208 are not approved') and https://postquantum.com/security-pqc/nsa-cnsa-2-0-faq-v2-1-update/. The product cannot ship its stated parallelism story to the buyer it names. It must instead serialize a single tree — which is the strictly harder distributed-state problem, and the one the HSM vendors already solve in-module.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="78" customHeight="1">
+      <c r="A71" s="52" t="n">
+        <v>8</v>
+      </c>
+      <c r="B71" s="53" t="inlineStr">
+        <is>
+          <t>Key-state custody for LMS/XMSS firmware signing under CNSA 2.0</t>
+        </is>
+      </c>
+      <c r="C71" s="52" t="n">
+        <v>2</v>
+      </c>
+      <c r="D71" s="53" t="inlineStr">
+        <is>
+          <t>THE KILL RISK IS NOT PENDING, IT IS PUBLISHED. Record and screener both say 'NSA has signaled it ANTICIPATES permitting stateless ML-DSA in FUTURE guidance.' The current FAQ already approves it: 'validated ML-DSA is approved for all signing use cases and when it is available it may be the most appropriate choice for some software/firmware signing use cases'; 'ML-DSA-87 can be used for software/firmware signing.' Source: https://postquantum.com/security-pqc/nsa-cnsa-2-0-faq-v2-1-update/ and https://www.encryptionconsulting.com/future-of-code-signing-with-cnsa-2/. key_sensitivity is therefore mis-dated by several years: an architect choosing today can already choose stateless and be compliant. LMS/XMSS survive as NSA's near-term preference on availability grounds only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="78" customHeight="1">
+      <c r="A72" s="46" t="n">
+        <v>8</v>
+      </c>
+      <c r="B72" s="47" t="inlineStr">
+        <is>
+          <t>Key-state custody for LMS/XMSS firmware signing under CNSA 2.0</t>
+        </is>
+      </c>
+      <c r="C72" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="D72" s="47" t="inlineStr">
+        <is>
+          <t>'NOBODY SHIPS STATE MANAGEMENT' IS FALSE — MULTIPLE VENDORS SHIP IT IN PRODUCTION. Thales TCT released LMS and its multi-tree variant HSS in all Luna T-Series HSMs from version 7.15.0 (https://www.thalestct.com/cnsa-compliant-code-signing/). Utimaco: 'several customers have successfully completed PQC migration projects using Utimaco's proper state handling architecture, from securing satellite communications to reliable firmware over-the-air updates' — i.e. shipped, referenced, firmware-signing customers (https://utimaco.com/news/blog-posts/stateful-hash-based-signature-schemes-hidden-champions-pqc). Keyfactor SignServer has supported LMS signing since 7.1 (https://docs.keyfactor.com/signserver/latest/post-quantum-code-signing-how-to). ISARA Radiate added XMSS to complete its stateful HBS offering (https://www.isara.com/blog-posts/isararadiate-xmss-stateful-hash-based-signatures.html).</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="78" customHeight="1">
+      <c r="A73" s="52" t="n">
+        <v>8</v>
+      </c>
+      <c r="B73" s="53" t="inlineStr">
+        <is>
+          <t>Key-state custody for LMS/XMSS firmware signing under CNSA 2.0</t>
+        </is>
+      </c>
+      <c r="C73" s="52" t="n">
+        <v>4</v>
+      </c>
+      <c r="D73" s="53" t="inlineStr">
+        <is>
+          <t>THE GITHUB-REPO-COUNT EVIDENCE IS A BROKEN PROXY AND THE SCREENER TREATED IT AS THE DECIDING FACT. 'Exactly three repositories worldwide' was the single reason this idea ranked 8 and the only claim said to have 'survived live verification.' Stateful HBS state management is implemented inside HSM firmware, in commercial products, and in PATENTS — none of which appear on GitHub. Public repo scarcity here measures the wrong thing entirely.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="78" customHeight="1">
+      <c r="A74" s="46" t="n">
+        <v>8</v>
+      </c>
+      <c r="B74" s="47" t="inlineStr">
+        <is>
+          <t>Key-state custody for LMS/XMSS firmware signing under CNSA 2.0</t>
+        </is>
+      </c>
+      <c r="C74" s="46" t="n">
+        <v>5</v>
+      </c>
+      <c r="D74" s="47" t="inlineStr">
+        <is>
+          <t>THE MECHANISM IS PATENTED. Granted US patents cover the specific architecture proposed: US 11438172 and US 11750403 'Robust state synchronization for stateful hash-based signatures'; US 11722313 'State synchronization for post-quantum signing facilities' — the latter explicitly covering the multi-HSM availability case: 'Multiple HSMs are used to improve availability of signing systems, and these facilities need to offer a mechanism to securely synchronize the state across all HSM signers available in the facility to prevent reusing the same counter.' That is verbatim the company's product. Sources: https://image-ppubs.uspto.gov/dirsearch-public/print/downloadPdf/11438172 , https://image-ppubs.uspto.gov/dirsearch-public/print/downloadPdf/11750403 , https://image-ppubs.uspto.gov/dirsearch-public/print/downloadPdf/11722313 . The record contains zero freedom-to-operate analysis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="78" customHeight="1">
+      <c r="A75" s="52" t="n">
+        <v>8</v>
+      </c>
+      <c r="B75" s="53" t="inlineStr">
+        <is>
+          <t>Key-state custody for LMS/XMSS firmware signing under CNSA 2.0</t>
+        </is>
+      </c>
+      <c r="C75" s="52" t="n">
+        <v>6</v>
+      </c>
+      <c r="D75" s="53" t="inlineStr">
+        <is>
+          <t>THE GUIDANCE GAP IS BEING CLOSED BY AN IETF WORKING GROUP, AUTHORED BY THE INCUMBENTS. draft-ietf-pquip-hbs-state-03 'Hash-based Signatures: State and Backup Management' is a PQUIP working-group document at 'Publication Requested' status, latest revision 2025-12-16. Authors: T. Wiggers (PQShield), K. Bashiri (BSI), S. Kolbl (Google), J. Goodman (Crypto4A), S. Kousidis (BSI). https://datatracker.ietf.org/doc/draft-ietf-pquip-hbs-state/ . The record's why_overlooked claims 'there is no portable answer' — a standards-track portable answer is one step from RFC publication, written by an HSM vendor, a chip-security vendor, the German BSI and Google.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="78" customHeight="1">
+      <c r="A76" s="46" t="n">
+        <v>8</v>
+      </c>
+      <c r="B76" s="47" t="inlineStr">
+        <is>
+          <t>Key-state custody for LMS/XMSS firmware signing under CNSA 2.0</t>
+        </is>
+      </c>
+      <c r="C76" s="46" t="n">
+        <v>7</v>
+      </c>
+      <c r="D76" s="47" t="inlineStr">
+        <is>
+          <t>THE SCREENER'S OWN 'CORRECTION' OF THE FIPS CLAIM IS ITSELF WRONG. The screener wrote: "The 'FIPS 140 Level 3' claim overstates SP 800-208, which requires a validated hardware module." Sources say the record was right: SP 800-208 requires key generation and signing inside modules 'validated to provide FIPS 140-2 or FIPS 140-3 Level 3 or higher physical security,' with no export of secret keying material. Sources: https://www.thalestct.com/wp-content/uploads/2024/01/quantum-resistant-code-signing-wp-1-18-24.pdf , https://www.wolfssl.com/special-rules-for-lms-and-xmss/ , https://nvlpubs.nist.gov/nistpubs/SpecialPublications/NIST.SP.800-208.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="78" customHeight="1">
+      <c r="A77" s="52" t="n">
+        <v>8</v>
+      </c>
+      <c r="B77" s="53" t="inlineStr">
+        <is>
+          <t>Key-state custody for LMS/XMSS firmware signing under CNSA 2.0</t>
+        </is>
+      </c>
+      <c r="C77" s="52" t="n">
+        <v>8</v>
+      </c>
+      <c r="D77" s="53" t="inlineStr">
+        <is>
+          <t>GROSS MARGIN OF 72% IS NOT ACHIEVABLE IN THE DESCRIBED ARCHITECTURE. AWS CloudHSM is $1.45 per HSM-hour (~$12,700/HSM-year); Azure Dedicated HSM is ~$4.85/hour (~$42,500/HSM-year). Source: https://evertrust.io/blog/hsm-as-a-service-vs-on-prem/ . SP 800-208 forbids key export, so keys cannot be pooled across tenants in software. A 2-HSM HA cluster replicated across 3 regions is 6 HSMs = ~$76,000/year of COGS per customer on the cheapest option — 69% of the record's own $110k ACV before any engineering or audit labour. The record's gross_margin_basis names this cost driver and then still books 72%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="78" customHeight="1">
+      <c r="A78" s="46" t="n">
+        <v>8</v>
+      </c>
+      <c r="B78" s="47" t="inlineStr">
+        <is>
+          <t>Key-state custody for LMS/XMSS firmware signing under CNSA 2.0</t>
+        </is>
+      </c>
+      <c r="C78" s="46" t="n">
+        <v>9</v>
+      </c>
+      <c r="D78" s="47" t="inlineStr">
+        <is>
+          <t>COMPLIANT PQC HSMs MAY NOT EVEN EXIST YET AT THE REQUIRED VALIDATION. 'As of late 2025, several vendors have obtained CAVP certification for the PQC algorithms, and several hold FIPS 140-3 Level 3 CMVP validation for their HSMs — but none have yet obtained FIPS 140-3 Level 3 with PQC support combined, with the CMVP validation process taking more than two years on average and final approvals expected in 2026 or 2027.' Source: https://www.qnulabs.com/blog/pqc-hsm . This cuts both ways: it delays everyone, but it also means the binding constraint on customers is HSM validation, not orchestration software — and it is the HSM vendors, not a startup, who relieve it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="78" customHeight="1">
+      <c r="A79" s="52" t="n">
+        <v>8</v>
+      </c>
+      <c r="B79" s="53" t="inlineStr">
+        <is>
+          <t>Key-state custody for LMS/XMSS firmware signing under CNSA 2.0</t>
+        </is>
+      </c>
+      <c r="C79" s="52" t="n">
+        <v>10</v>
+      </c>
+      <c r="D79" s="53" t="inlineStr">
+        <is>
+          <t>EO NUMBER STILL CONTRADICTORY IN LIVE SOURCES. Majority coverage says EO 14412 (signed 22 June 2026, M-26-15 following 24 June); Wiz and Gopher Security both publish under EO 14409. Unresolved. Do not cite either number as fact.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:D79"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="90" customWidth="1" min="4" max="4"/>
+    <col width="85" customWidth="1" min="5" max="5"/>
+    <col width="110" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="68" t="inlineStr">
+        <is>
+          <t>The cheapest experiment that would falsify each thesis inside 30 days. This is the most actionable sheet in the workbook - it tells you what to do on Monday instead of what to believe.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="34" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>Opportunity</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Base case defensible?</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>Fatal flaw</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>Weakest number</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>The 30-day falsification test</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>Bear Y5</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="150" customHeight="1">
+      <c r="A4" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="47" t="inlineStr">
+        <is>
+          <t>Ride-through models and curtailment proof for NERC-registered data centers</t>
+        </is>
+      </c>
+      <c r="C4" s="60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D4" s="47" t="inlineStr">
+        <is>
+          <t>The firm owns nothing that survives the standard being published. Its stated differentiation is "depth on the load-side artifact plus speed of publication against the filed standard text" — a two-person head start measured in weeks, against Keentel (27 years, four offices, ex-NERC audit team leads, already selling "Level 3 Alert response engineering"), Certrec (130+ managed registered sites, RSAW machinery the CLE category flows straight into), and every EPC grid practice that will read the same filed text on the same morning. The modeled pivot then makes the utility the primary buyer — correct on the regulation, fatal on the go-to-market. Utilities buy engineering through master service agreements, approved-vendor lists and qualified-supplier registers that take 18-24 months to enter and that the incumbents already occupy. The enforcement clock (FERC action on NERC's 31 Dec 2026 filing, realistically effective 2028) therefore arrives at roughly the moment the incumbents finish locking the MSAs. The firm correctly identified the demand, has no mechanism to hold the contracts, and its one scarce input — the senior EMT modeler — is bid for by firms with better benches and deeper pockets. The plan's own M36 note concedes the real acquirable asset is "approved vendor on &gt;=4 utility MSAs," which is an admission that the moat is a queue position, not an engineering capability.</t>
+        </is>
+      </c>
+      <c r="E4" s="47" t="inlineStr">
+        <is>
+          <t>avg_loaded_salary_usd = $180,000, read against headcount_y5 = 34. Market data puts senior PSCAD/EMT power-systems roles at $136,850-$185,150 in BASE salary as of 2026 (https://www.ziprecruiter.com/Jobs/Power-System-Studies-Pscad, https://www.ziprecruiter.com/Jobs/Power-Systems-Pscad); loaded at a normal 1.3-1.4x that is $178k-$260k for one senior modeler. The model uses $180k as the blended LOADED average across all 34 heads — approximately the base salary of the single hire the business depends on. This work cannot be pyramided: an ISO will not accept a dynamic load model, a UPS ride-through study or a POI protection scheme signed by a three-year engineer, and the plan's own risk register calls one senior modeler leaving a $700k-$900k revenue event. So the mix must stay senior and a defensible blended loaded average is $215k-$235k. At $220k the added cost is $1.36M against a modeled Y5 EBITDA of $1.19M — the entire profit is erased by correcting one input the record chose rather than sourced, and it is erased in every year, not just Y5. Second, smaller but real: $160k of working capital is budgeted against roughly $690k of receivables outstanding at Y2 revenue on the net-60/net-90 utility terms the model itself names, so the $650k "no second raise" claim fails on cash timing before it fails on P&amp;L.</t>
+        </is>
+      </c>
+      <c r="F4" s="47" t="inlineStr">
+        <is>
+          <t>Sell the inverted buyer something priced, and require a purchase order — not a meeting. Pull the service lists for the six RM26-4 dockets from FERC eLibrary (public, free) and assemble 40 NAMED transmission-planning, planning-coordinator and compliance managers at load-serving utilities and TOs in PJM, MISO and SPP. Email each a fixed-fee $18,500, two-week "Level 3 Alert Essential Actions gap review" that delivers a written scope, schedule and cost envelope for their implementation program. Not a free assessment — free assessments measure curiosity. Pre-registered threshold: 3 signed POs or purchase requisitions inside 30 days. Cost: founder time and roughly $0. The single untested assumption in the entire revised plan is that a utility will spend money with an unqualified vendor outside an existing MSA; if 0-2 close, that assumption is false, entry requires 18-24 months of vendor qualification, $650k cannot fund the wait, and the correct move is to subcontract to an incumbent EPC rather than to found a firm. Run one parallel leg for $500: post a single "Senior EMT/PSCAD Large-Load Modeling Engineer — $200k base" advertisement and count applicants with ISO-accepted dynamic model filing experience. Fewer than 5 qualified applicants in 21 days and the 4-to-34 hiring curve is fiction regardless of how real the demand is — that leg tests supply, the PO leg tests demand, and the business needs both to be true.</t>
+        </is>
+      </c>
+      <c r="G4" s="50" t="n">
+        <v>2800000</v>
+      </c>
+    </row>
+    <row r="5" ht="150" customHeight="1">
+      <c r="A5" s="52" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="53" t="inlineStr">
+        <is>
+          <t>Entry Type 13 and instrument-aware duty recovery for the post-de-minimis long tail</t>
+        </is>
+      </c>
+      <c r="C5" s="60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D5" s="53" t="inlineStr">
+        <is>
+          <t>Every differentiator was traded away to survive sourcing, and what is left is an ordinary licensed customs brokerage at market price, funded on venture terms. The price wedge is gone ($15/entry became $85, inside the incumbent $75-150 band). The segment moved up-market directly into decades-old broker relationships. ET13 turned out to be mail-scoped with twelve CBP-certified incumbents already on the flow. The only surviving claim is throughput leverage — 30-40 entries per licensed broker per day against a manual 10-15 — and CBP HQ Ruling H350722 (Jan 2026) places a licensed person inside every 10-digit classification that directs or influences an entry, which is precisely where the leverage was supposed to come from. If the real supervised ceiling is 20 rather than 35 there is no company, only a brokerage with a better UI carrying $4.2M of equity it cannot return, against Zonos ($69M raised, 50,000 merchants, 70+ postal operators, a licensed brokerage acquired outright in April 2026), Caspian, Amari AI, Zollback, and carriers who price entry at near-zero incremental cost across their own networks. The plan's own exit thesis concedes the downside is "returning less than capital" — for a business whose entire premise ("nobody has attacked the broker-capacity bottleneck") was disproven by two top-tier seed firms funding exactly that six months ago.</t>
+        </is>
+      </c>
+      <c r="E5" s="53" t="inlineStr">
+        <is>
+          <t>White-label filing units_y5 = 60,000, which combined with 46,800 direct entries puts 106,800 entries through the firm in Year 5 — about 427 per business day. The confidence note allocates Y5 headcount as roughly 24 entry writers, 6 engineers and 4 licensed brokers. That is 107 entries per licensed broker per day. The model's own M36 milestone defines success as "entries per licensed broker per day sustained above 30." Four brokers at 30/day over 250 business days is 30,000 entries — 28% of the modeled volume. Filing 106,800 entries at the throughput the model itself nominates as proof of leverage requires roughly 14 licensed brokers, not 4. Ten additional at $155k loaded is $1.55M of cost against a modeled Y5 EBITDA of +$330k, so Year 5 is a ~$1.2M loss and the model never crosses over. This is not an outside challenge; the model contradicts itself, and it does so on the one ratio that distinguishes it from a normal brokerage. Compounding it: 19 CFR 111.28 sets no numeric ratio but requires "a sufficient number of licensed brokers relative to the job complexity" under CBP's discretionary factors (https://www.ecfr.gov/current/title-19/chapter-I/part-111/subpart-C/section-111.28), so a 4-broker/106,800-entry structure is also a live responsible-supervision exposure — and a broker whose license is at risk leaves, which under the plan's own key-person risk stops all filing immediately.</t>
+        </is>
+      </c>
+      <c r="F5" s="53" t="inlineStr">
+        <is>
+          <t>Buy data, not meetings, and kill it on arithmetic before contacting anyone. A 30-day ImportGenius or Panjiva subscription costs a few hundred dollars. Pull trailing-12-month bill-of-lading records for 200 US importers filtered to $5-50M import value with both inbound and outbound/destruction flows — the only population where drawback actually pays — and count arrivals per importer as the direct proxy for annual entries. Pre-register the threshold before pulling: if the MEDIAN is under 60 shipments per year rather than the modeled 120, ACV falls from ~$16,000 to ~$8,000, an $8,500 CAC never pays back, and the model is dead without a single conversation. The honest prior says it will fail — CBP's own population figure is 30.4M commercial transactions across 300,000+ active IORs, a mean of ~101, on a power-law distribution that puts the mid-market median well below the mean. Cost under $1,000, elapsed time five days. Only if the median clears 60 do you spend the remaining three weeks emailing the top 40 names from that same pull a PRICED $2,500 Section 301 drawback scoping engagement, threshold 4 signed POs. Both legs run inside 30 days for under $2,000 — versus the $180,000 and 90 days the plan budgets for its own kill-check — and the data leg alone falsifies the thesis, because entries-per-account was named the key sensitivity by the original record and has still never been measured on the actual target segment rather than inferred from a national mean.</t>
+        </is>
+      </c>
+      <c r="G5" s="54" t="n">
+        <v>2100000</v>
+      </c>
+    </row>
+    <row r="6" ht="150" customHeight="1">
+      <c r="A6" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="47" t="inlineStr">
+        <is>
+          <t>NQA-1 qualification and commercial grade dedication as a service</t>
+        </is>
+      </c>
+      <c r="C6" s="60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D6" s="47" t="inlineStr">
+        <is>
+          <t>The line that carries the model is gated behind an asset that cannot be bought, accelerated, or built with capital. Commercial grade dedication is 37% of Y5 revenue ($2.59M) and effectively all of the durable differentiation, but dedication packages are only saleable to a licensee that has already audited you and placed you on its approved supplier list — and NUPIC performs roughly 93 assessments a year across a standing pool of ~250-300 suppliers, so the audit queue is itself the barrier. Curtiss-Wright/Scientech, Paragon and Westinghouse already hold that standing and already sit inside the licensees' vendor systems; no utility has a reason to spend a scarce audit slot qualifying a three-person startup for work it can already buy. The moat this business needs is the identical moat protecting the firms it intends to displace. The other two legs are each independently undercut: the readiness sprint competes against a $0 federally cost-shared NIST MEP substitute in and adjacent to the named beachhead, and the March 2026 NSI report that is the entire trigger recommends "simplifying supply chains to tap into the traditional nuclear business' existing materials and know-how" — i.e. routing work back to the ~100 already-qualified incumbents, which directly shrinks the aspirant population that buys sprints. The trigger argues against the customer.</t>
+        </is>
+      </c>
+      <c r="E6" s="47" t="inlineStr">
+        <is>
+          <t>CGD package units_y1 = 10, and the 10 → 38 → 85 → 135 → 185 ramp it anchors. Ten billable dedications in the entity's first twelve months is not achievable in sequence. A dedication package is only saleable once a licensee has qualified you as a supplier, which requires your own Appendix B/NQA-1 program to be written, implemented, operating with accumulated audit evidence, then externally audited with findings closed — and the plan's own M3 milestone is "on the audit calendar of 3 licensees," meaning that at month three the audits have not yet been scheduled, let alone executed and closed. Realistic shape: 0 lots in Y1, low single digits in Y2 once a first approval closes, with the whole curve shifting right roughly two years and Y5 landing at 40-50 lots rather than 185. That removes ~$1.9M from Y5 revenue and the majority of EBITDA on its own. Price is the second problem on the same line: $14,000/lot has zero external support (fifteen searches found no published rate anywhere in this market), and DOE-HDBK-1230-2019 explicitly instructs buyers to cost CGD against simply purchasing from an NQA-1 supplier, which caps the fee at the qualified-versus-commercial price delta and forecloses value-based pricing. The plan has, in effect, pre-written a kill trigger ("if zero CGD purchase orders land by M3") around an outcome that is close to certain on its own timeline.</t>
+        </is>
+      </c>
+      <c r="F6" s="47" t="inlineStr">
+        <is>
+          <t>Fifteen phone calls, one pre-registered question, zero dollars, two weeks. Call supplier quality and procurement engineering at 10 named operating-plant licensees (NUPIC member utilities are public) and 5 advanced-reactor developers and ask exactly this: "What is your process and typical elapsed time to add a NEW third-party dedicating entity to your approved supplier list, and how many new dedicating entities have you added since 2023?" Pre-registered threshold: if the median elapsed time exceeds 12 months, OR fewer than 2 of 15 have added any new dedicating entity in three years, the CGD line cannot be built on the modeled schedule — 37% of Y5 revenue and the entire margin story go to zero, this becomes a ~$1.5M sprint-and-training shop, and it should not raise $750k. Note this is not "talk to customers": the answer is a matter of record inside each procurement organization, the question is closed-form, and the threshold is set before the first call. Second leg, same 30 days, ~$300: pull 25 AS9100 holders in south-central Ohio and upstate South Carolina from the public IAQG OASIS registry and offer a fixed, PAID $6,500 Appendix B gap assessment, threshold 4 signed POs. If fewer than 4 shops will pay $6,500 for a scoped deliverable, none will pay $70,000 for a sprint, and the line dies against the free MEP alternative. Deliberately run neither leg in Tennessee — a $0 federally subsidized substitute there makes any result uninterpretable, and the plan's original beachhead choice is itself the first thing this test invalidates.</t>
+        </is>
+      </c>
+      <c r="G6" s="50" t="n">
+        <v>1700000</v>
+      </c>
+    </row>
+    <row r="7" ht="150" customHeight="1">
+      <c r="A7" s="52" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="53" t="inlineStr">
+        <is>
+          <t>PFAS-Compliant Biosolids Outlet Exchange for the Mid-Atlantic</t>
+        </is>
+      </c>
+      <c r="C7" s="60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D7" s="53" t="inlineStr">
+        <is>
+          <t>The trigger creates a TESTING obligation, not a DISPOSAL crisis — and testing is a lab purchase, not a consulting purchase. Virginia HB 1443 requires monthly PFAS sampling (reducible to quarterly with DEQ approval after 2027). EPA Method 1633 solids analysis is priced at $304.55/sample internal, $383.73/sample external for all 40 analytes (Michigan State Center for PFAS Research fee schedule, https://www.canr.msu.edu/pfas-research/uploads/CPR_Fee%20Schedule_v1.pdf). Twelve samples a year plus duplicates, shipping and QC puts a mid-size POTW's ENTIRE statutory annual compliance cost at roughly $4,000-$10,000. This model asks that same plant for $45,000 up front plus $18,000/year — six to fifteen times the cost of the obligation it helps discharge. Worse, the commercial labs (Eurofins, Pace, ALS, Alpha, SGS) give sampling-program design, PFAS-free kits, chain-of-custody and QA protocol away free as a sales motion, because they monetize the samples, not the advice. And the buyer is not a panic buyer: the Virginia Association of Counties formally OPPOSED HB 1443 on the grounds that testing and lab costs would burden localities (https://www.vaco.org/capitol-contact/vaco-opposes-restrictive-pfas-testing-bill/). This is a cost-fighting municipal buyer being sold a premium advisory wrapper around a $6k lab bill. The displacement that would create real budget probably never fires — MDE's own data-based recommendation was 100 ppb against an enacted 50 ppb, and most Maryland plants already clear it.</t>
+        </is>
+      </c>
+      <c r="E7" s="53" t="inlineStr">
+        <is>
+          <t>price_usd: 45000 on the PFAS Threshold Readiness Engagement (units_y1 9 → units_y5 14; $630k of Y5 and the land motion every other line expands from). The modeler admits this price is their own construction with no comparable. It does not hold because the sourced total annual cost of the underlying mandate is ~$4-10k of lab work that labs will scope for free, and because the deliverable — 'sampling program design, lab selection, rolling-12-month tracking, threshold forecast' — is 3-4 weeks of a senior engineer's time against public statute text. Second-worst, and nearly as bad: price_usd 18000 × units_y5 40 on the intelligence subscription ($720k, 26% of Y5) prices a quarterly regulatory-tracker PDF at 9-90x what WEF, NACWA, NEBRA, VWEA and MD-DE-DC WEA charge in total annual dues for the same material, and assumes 18% of the entire 220-entity universe buys it. Third: headcount_y2 of 5 delivering $1.47M is $294k revenue per head in year two, against ~$150-200k typical for environmental consulting — the model is ~50% over on productivity in every year.</t>
+        </is>
+      </c>
+      <c r="F7" s="53" t="inlineStr">
+        <is>
+          <t>Two moves, both ~$0, both inside 30 days, and BOTH must pass. (1) Days 1-5 — kill the price anchor with a competitor's own quote. Send an identical RFQ to Eurofins Environment Testing, Pace Analytical and Alpha Analytical: full HB 1443-compliant program for a 15 MGD Virginia POTW, monthly Method 1633 biosolids sampling from 1 Jan 2027, including sampling-program design, PFAS-free kits, chain of custody, QA/QC protocol and rolling-12-month reporting. KILL THRESHOLD: if the all-in annual quote lands under $15,000 with program design bundled at no charge, the $45,000 engagement has no room to exist and Line 1 is dead on day 5. (2) Days 5-25 — test price, not interest. VA DEQ publishes the permitted sewage-treatment-works list; email all ~60 named plant superintendents and directors of utilities a one-page FIXED-PRICE $45,000 HB 1443 readiness offer anchored to the 1 Jan 2027 sampling date, asking for a signed LOI or a named budget line — not a call. KILL THRESHOLDS: fewer than 8 of 60 reply, or fewer than 2 will name a budget line above $20,000. Sending a price and demanding a budget line is the whole point; asking 60 utility directors whether PFAS is a concern will return 60 yeses and teach you nothing.</t>
+        </is>
+      </c>
+      <c r="G7" s="54" t="n">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="8" ht="150" customHeight="1">
+      <c r="A8" s="46" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="47" t="inlineStr">
+        <is>
+          <t>Reachability-grade SBOMs and kernel-CVE triage for embedded Linux</t>
+        </is>
+      </c>
+      <c r="C8" s="60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D8" s="47" t="inlineStr">
+        <is>
+          <t>The only two lines that make this anything other than a generic compliance body shop — signed attestation ($1.104M) and notified-body subcontract ($900k), together 27% of Y5 — each require an independent third party to volunteer to absorb or share risk it has every reason to refuse, and neither has a precedent. Attestation: under EU New Legislative Framework product law the manufacturer's conformity obligation is non-delegable, so a consultant's countersignature has no standing with a market surveillance authority. The customer is therefore buying comfort, not liability transfer, while the firm sells unlimited regulatory tail exposure on a theory with zero case law and no harmonised standard (the Commission's July 2026 guidance confirms none adopted; BSI states TR-03183-2 is non-binding and confers no presumption of conformity). No underwriter prices that at $12,000/family with 65% gross margin. Notified bodies: a body that is capacity-short does not subcontract the technical evaluation it is accredited to perform — it hires, because subcontracting is itself an ISO/IEC 17065 accreditation problem. Strip both and what remains is a €135k/head consulting firm selling technical files into a market where default-category products self-assess with no notified body at all (https://digital-strategy.ec.europa.eu/en/policies/cra-conformity-assessment), and where TÜV SÜD, TÜV Rheinland, DEKRA and the Big Four already own the CE-marking relationship — while the technical differentiator is free upstream in the customer's own build system.</t>
+        </is>
+      </c>
+      <c r="E8" s="47" t="inlineStr">
+        <is>
+          <t>units_y5: 135 on the Managed vulnerability handling retainer — $3.24M, 43% of Y5 and the largest single number in the model. It fails on three independent grounds. (a) Population: 135 accounts is 9-19% penetration of a universe the sourcing agent itself called a bound rather than a count (700-1,500 paying firms, extrapolated from one 2,210 tech-adoption datapoint; the Yocto Project has only '30+ member companies'). (b) Price versus substitutes: $24,000/yr is roughly half of Lynx's ENTIRE Linux LTS/BSP maintenance price ('less than 1/2 the cost of a junior engineer', ~$40-60k) which includes the BSP itself; Wind River bundles proactive CVE monitoring into 10+ year support; Foundries.io/Qualcomm drives marginal device cost to zero at 100k units and ships a free Community tier. The two largest slices of that universe — BSP-bundled customers and self-supporting Yocto shops running the free upstream improve_kernel_cve_report.py — each already have the capability at zero marginal cost. (c) The SLA that justifies the price is the part that cannot be sold: Art. 14's 24h early-warning obligation sits on the manufacturer with administrative-penalty exposure. Manufacturers outsource the paperwork; they do not outsource the notification decision.</t>
+        </is>
+      </c>
+      <c r="F8" s="47" t="inlineStr">
+        <is>
+          <t>Primary, ~$0 and ~15 engineer-days total. Do NOT pitch — deliver the finished answer using the free tool, and see if anyone still pays. Assemble 25 named EU embedded OEMs whose firmware images or BSP manifests are publicly downloadable (Embedded World 2026 exhibitor list filtered to industrial control, networking and building automation, cross-referenced against vendors publishing GPL source releases). For each, run the FREE upstream Yocto improve_kernel_cve_report.py with SPDX_INCLUDE_COMPILED_SOURCES against their published image, and send a one-page finished artifact: 'of the 763 kernel CVEs published in the week of 18-25 Jul 2026, N reach your shipped image, M need a backport' — attached to a fixed $18,000 quote for the readiness audit with a named delivery date. KILL THRESHOLDS: fewer than 6 of 25 book a call → the pain is not budget-bearing; fewer than 2 will discuss spend above €15k → the $18k/$55k/$24k ladder is wrong; and count the replies saying 'our BSP vendor already covers this' — 5 or more confirms bundling is the status quo, not a sensitivity. RIDER, same 30 days, 10 emails, $0, and it collapses the differentiator on its own: submit a completed proposal form to three specialist tech-liability underwriters (Beazley, CFC, Markel, via a London or Munich broker) describing the attestation product exactly — third-party countersigned attestation on OpenVEX justifications and declared support periods for CE-marked products under Reg. (EU) 2024/2847, €2M per claim. If none will quote in 30 days, or all attach a regulatory-conformity-attestation exclusion, delete $1.104M of Y5 on day 30 instead of at M6.</t>
+        </is>
+      </c>
+      <c r="G8" s="50" t="n">
+        <v>1950000</v>
+      </c>
+    </row>
+    <row r="9" ht="150" customHeight="1">
+      <c r="A9" s="52" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="53" t="inlineStr">
+        <is>
+          <t>Funded-Claim Detection for Casualty Reserving</t>
+        </is>
+      </c>
+      <c r="C9" s="60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D9" s="53" t="inlineStr">
+        <is>
+          <t>There is no decision the output changes. Booked casualty reserves are set from development triangles and case reserves with actuarial support; 'this plaintiff firm has a portfolio funding relationship' is not a variable an appointed actuary can put into a booked estimate or sign an opinion behind, and no state regulator or auditor will accept a third-party vendor's ownership inference as reserving support. The only buyer who COULD act on the signal — the claims adjuster or litigation manager setting a settlement posture — needs per-claim funder identity, which the model concedes is unsolved and which Arizona's amended civil-procedure rule, New York's CLFA (effective 17 Jun 2026), Ohio, West Virginia and Wisconsin now hand to defendants for free through mandatory disclosure. The product is therefore non-actionable exactly where it works (firm-level, to reserving) and unnecessary exactly where it would be actionable (claim-level, to claims). This is the reason four better-resourced parties holding both the substrate AND the carrier contract — Verisk, CLARA, Milliman IntelliScript, Findevor — have not shipped it. The record read that absence as whitespace. It is a market that has been priced and declined.</t>
+        </is>
+      </c>
+      <c r="E9" s="53" t="inlineStr">
+        <is>
+          <t>units_y5: 48 on the Defense-Side Funder Tracing and Expert Engagement line at $24,000 — $1.152M, 32% of Y5 and the single largest line. Three failures. (a) It is entirely unsourced; the modeler states the price is their own reasoning. (b) It assumes roughly one expert engagement per week sustained from a 10-person firm, i.e. the tracing line alone consumes more analyst-weeks than the headcount supports alongside 15 diagnostics and 20 subscription renewals. (c) It is internally contradicted by the model's own thesis: units grow 6 → 22 → 36 → 44 → 48 across precisely the years in which mandatory-disclosure regimes proliferate, and every state that mandates disclosure removes the reason to trace. Defense counsel in a disclosure fight serves an interrogatory or files a motion — billable to the carrier at counsel's own rate — rather than inserting a $24,000 third-party vendor line into a matter budget that the carrier's litigation-management guidelines cap and must pre-approve. Runner-up, and the number that should end the conversation on its own: cac_usd 62000 against a $45,000 ACV is a CAC:first-year-revenue ratio above 1.0 on the only recurring line, for a product whose raw input is a free 41-row NMLS lookup and whose flagship deliverable ALM already published editorially on 17 Jul 2026.</t>
+        </is>
+      </c>
+      <c r="F9" s="53" t="inlineStr">
+        <is>
+          <t>Price it below the procurement threshold and demand a purchase order — that removes the 'long regulated sales cycle' excuse, which is the only defense this thesis has left. Days 1-4, build the artifact from free inputs: the 41 Georgia litigation-financier registrants (no-cost lookup at nmlsconsumeraccess.org), the ALM-published ownership and lawyer-ties overlay, and UCC-1 searches naming those entities against the top 15 Georgia plaintiff casualty firms. Days 5-30, email 20 NAMED Heads of Casualty Reserving and Chief Claims Officers at US commercial casualty and E&amp;S writers (rosters are public via CLM and PLRB member directories and carrier leadership pages), attach the finished Georgia sample, and make one offer: a $10,000 fixed-fee pilot diagnostic — one state, one accident year, funded-share estimate, delivered in three weeks, decision required in 14 days. $10,000 is deliberately one-sixth the modeled diagnostic price and sits below essentially every carrier's small-dollar procurement threshold, so it clears on a department budget with no RFP, no InfoSec review and no vendor onboarding. KILL THRESHOLD: zero of 20 issue a PO or PO-equivalent inside 30 days → the $65,000 diagnostic and $45,000 subscription are fantasy and there is no company. SECOND, SHARPER READ, aimed straight at the fatal flaw: of everyone who replies, count how many name a SPECIFIC booked number, reserve segment or case-strategy decision the output would change. Fewer than 3 of 20 means the signal is non-actionable at any price, and no amount of entity resolution or per-claim linkage fixes that.</t>
+        </is>
+      </c>
+      <c r="G9" s="54" t="n">
+        <v>725000</v>
+      </c>
+    </row>
+    <row r="10" ht="150" customHeight="1">
+      <c r="A10" s="46" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="47" t="inlineStr">
+        <is>
+          <t>Forward exchange for transformer and switchgear production slots</t>
+        </is>
+      </c>
+      <c r="C10" s="60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D10" s="47" t="inlineStr">
+        <is>
+          <t>THE CLIENT HIRES THE PERSON INSTEAD. The deliverable is a senior procurement/expediting human plus OEM order-desk relationships. A data center developer with a 2029 energization date can hire a full-time equipment procurement manager for ~$180-220k loaded and get all four service lines forever, versus $125k for ONE engagement plus $120k/yr for the retainer. Every account insources at roughly two engagements per year of volume — i.e. exactly when it becomes worth serving. The model's own confidence_note calls this 'softest of all' and then builds 48 engagements and 42 retainers on top of it. Second blade: Anza already productized the engagement deliverable in Dec 2025 — 45+ MV/HV supplier network, RFP vendor list built in 30 minutes instead of weeks, pre-negotiated supplier purchase agreements (https://www.anzarenewables.com/transformer-service/ , https://transformers-magazine.com/tm-news/anza-targets-transformer-supply-bottleneck/). I could not establish that Anza charges buyers anything; if that service is supplier-funded, the $125k engagement is priced against free. Third: this is plan B for a thesis nobody underwrote — the slot exchange is already dead on the seller side, so the capital is being asked to fund a different company than the one that ranked #7.</t>
+        </is>
+      </c>
+      <c r="E10" s="47" t="inlineStr">
+        <is>
+          <t>FIELD: revenue_lines[1] (expediting retainer) gross_margin_pct = 0.88 — and the 0.82 / 0.85 alongside it. At $120k/yr and 88% GM, delivery cost is $14,400/yr = 0.078 FTE at the model's own $185k loaded salary = about 1.5 hours per WEEK to run milestone tracking, FAT scheduling and witness, change-order defense, escalation and rigging/logistics coordination across a client's entire active order book. That is an email, not a service. Same failure on engagements: 82% GM means $22,500 of labour, ~6 person-weeks, for spec standardization plus multi-OEM RFQ plus bid levelling plus deposit and contract negotiation. Labour-inclusive GM for this work is 40-55% — note the companion record in this same pair books 47% and says explicitly that delivery payroll sits in COGS. THE P&amp;L ALSO DOES NOT RECONCILE: 44 heads x $185k = $8.14M payroll, plus non-payroll opex of ~$1.37M (520k compounded at 38%), = $9.51M against $15.74M revenue = $6.23M — yet stated Y5 EBITDA is $3.05M, which forces ~$3.18M of COGS ABOVE a line that already contains the entire delivery organization. Delivery is double-counted. Fix the margins and Y5 EBITDA is roughly $0.6-1.5M, not $3.05M, and the exit collapses from $20-35M to $8-15M at the same 8-10x. Bonus contradiction the record carries unresolved: it uses Electrical Trader's $30-35k/MVA (a 100 MVA unit at $3.0-3.5M) to build a $4.0M package and a $160k assignment fee, while its own pricing_comparables also cite Taishan at $300k-$2M for 10-100 MVA units. It picked the high anchor.</t>
+        </is>
+      </c>
+      <c r="F10" s="47" t="inlineStr">
+        <is>
+          <t>TEST THE RETAINER, NOT THE ENGAGEMENT — it is 32% of Y5 revenue and 100% of the exit thesis, and it is the only line where the buyer must choose RENT over HIRE. Build a list of 40 named US data center / colo / IPP / BESS projects with disclosed 2028-2030 energization dates straight out of the public RTO large-load and generator interconnection queues (free — no DC Byte or datacenterHawk licence needed for this test). Name the procurement or project-development lead on each. Send a two-paragraph email offering (a) three verified $/MVA prints for 60-100 MVA units from the last 90 days, free, and (b) a $10k/month expediting retainer on their EXISTING order book, starting in 30 days, 30-day cancellation, first month free. Ask for a signature, not a discovery call. Two hard reads at day 30: (i) fewer than 5 replies out of 40 means the pain is not felt at the procurement seat and the whole ICP is wrong; (ii) fewer than 2 signed retainer LOIs — or more than 60% of repliers answering 'we already have someone in-house who does this' — means the function is insourced, the retainer book never forms, and both the $5.04M Y5 line and the exit thesis are gone. Cost: one person, 30 days, roughly zero dollars. FREE RIDER, same 30 days, kills the remaining slot-assignment line: phone 8 OEM order desks (Prolec GE, Virginia Transformer, WEG, Hitachi Energy, Siemens Energy, Hyundai Electric, Pennsylvania Transformer, ERMCO) and ask two questions — 'what happens to a production slot when a customer releases a placed order?' and 'would you consent to novating an order to a third party, and would you reprice at consent?' If 6 or more say 'we reallocate to the next buyer in line' and 'yes we would reprice,' delete revenue_line 3 in week 2 rather than at M6.</t>
+        </is>
+      </c>
+      <c r="G10" s="50" t="n">
+        <v>4300000</v>
+      </c>
+    </row>
+    <row r="11" ht="150" customHeight="1">
+      <c r="A11" s="52" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="53" t="inlineStr">
+        <is>
+          <t>Key-state custody for LMS/XMSS firmware signing under CNSA 2.0</t>
+        </is>
+      </c>
+      <c r="C11" s="60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D11" s="53" t="inlineStr">
+        <is>
+          <t>NSA'S OWN FAQ TELLS THIS EXACT CUSTOMER NOT TO BUY THIS PRODUCT. Per CNSA 2.0 FAQ coverage: 'For organizations whose signing workflows require more signatures than a single LMS or XMSS key tree can support, OR THAT OPERATE DISTRIBUTED SIGNING ENVIRONMENTS, ML-DSA is the appropriate choice' (https://postquantum.com/cnsa-2-0/complete-guide/ , https://media.defense.gov/2022/Sep/07/2003071836/-1/-1/0/CSI_CNSA_2.0_FAQ_.PDF). A high-volume distributed signing environment is the ONLY condition under which distributed state custody has any value — and the guidance routes precisely that buyer to the stateless algorithm that has no state to custody. Stack that on the HSS / XMSS^MT prohibition for NSS (which already killed the multi-tree parallelism story) and the residual is single-site, low-volume, already-fielded-silicon signing — exactly the case an in-module counter already handles, shipping today in Thales Luna T-Series 7.15.0, Utimaco SecurityServer and Keyfactor SignServer 7.1+. There is no customer who simultaneously needs distributed state synchronization and is permitted to use the algorithm that creates the need. NEW FACT FROM SEARCH: US 11722313 'State synchronization for post-quantum signing facilities' is assigned to INTEL CORPORATION (inventors Misoczki, Reinders, Ghosh, Sastry — https://patents.google.com/patent/US11722313). That is not an unresolved assignee; it is a litigation-capable holder whose Labs group wrote the LMS/XMSS state-synchronization literature, and US 11438172 / 11750403 almost certainly share the lineage. The FTO opinion is a month-1 blocker, not a month-3 gate.</t>
+        </is>
+      </c>
+      <c r="E11" s="53" t="inlineStr">
+        <is>
+          <t>FIELD: revenue_lines[1] (signing-state assurance subscription) units_y5 = 30. The FAQ language splits the universe such that this number cannot be filled from either half: a buyer who operates a distributed signing environment is steered to ML-DSA and needs no state ledger; a buyer who is not distributed is served by the counter inside the one HSM they already own. The 30 must therefore come from a residual the model's own confidence_note sizes at ~60 serviceable accounts — 50% share, against Thales, Utimaco, Entrust and Keyfactor who ship the capability inside a product the customer already paid for, in a universe that shrinks with every silicon respin. Two supporting fields fail with it. units_y5 = 3 on the OEM component licence is a negative-value purchase for the named buyer: HSM vendors monetize module lock-in, and a shim that makes a customer's signing state portable to a competitor's HSM is the last thing Thales or Entrust will pay $150k/yr for — that line should be zero, not $450k. And annual_churn_pct = 0.12 is incoherent with a TAM that only decreases: churn here is set by the customer's product-generation cadence, so as fielded lines respin to ML-DSA-87 the real rate is 20-33%/yr, not 12%. The model's own M24 gate ('if under 25% of new NSS firmware programs chose stateful, stop') concedes the Y5 subscription number is conditioned on a coin flip it never discounts.</t>
+        </is>
+      </c>
+      <c r="F11" s="53" t="inlineStr">
+        <is>
+          <t>DO NOT SURVEY — COUNT, then confirm with a one-question email. Both inside 30 days, both effectively free, and both are available NOW rather than at the M24 gate where the model parks them. (1) COUNT: the NSA CSfC Components List (https://www.nsa.gov/Resources/Commercial-Solutions-for-Classified-Program/Components-List/) and the NIAP Product Compliant List (https://home.niap-ccevs.org/Product/PCL.cfm) are public and enumerate the vendors whose crypto-bearing products are actually accepted into NSS. Pull every entry from the last 18 months and extract the firmware/software signing algorithm claim from each Security Target and validation report — all public PDFs. Tally LMS/XMSS versus ML-DSA-87 versus classical. (2) ASK: email the secure-boot or product-security architect at 20 named DIB embedded OEMs, silicon vendors and ODMs pulled from that same list a single question with two checkboxes — 'For your next-generation secure boot, are you signing firmware with LMS/XMSS or with ML-DSA-87?' KILL CRITERIA at day 30: fewer than 6 of 20 answering LMS/XMSS, OR under 25% of recent firmware-signing entries on the PCL/CSfC claiming stateful, means the wave this company is built on is not forming and the correct action is to never start — not to spend $1.75M and re-ask the question in 2028. One analyst, three weeks, $0. RUN CONCURRENTLY AS A VETO: commission the $75k FTO opinion on the Intel-assigned US 11722313 plus US 11438172 / 11750403 BEFORE any state-synchronization code is written; adverse and lines 2 and 4 vanish, which is 51% of Y5 revenue. FREE RIDER that tests the pain rather than the algorithm: ship the fork detector in week 1 and run it free against those 20 OEMs' existing signing logs. Zero index reuses, zero ambiguous-state-after-restore events and zero unsafe DR failovers across 30 days of real ingests means the incident the entire assurance subscription is sold against does not happen in practice, and there is no story left to sell.</t>
+        </is>
+      </c>
+      <c r="G11" s="54" t="n">
+        <v>780000</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
